--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>3309</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>19692</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.79499995708466</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>23807</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.88999998569489</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.82500004768372</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.87999999523163</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>85329</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.89499998092651</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>600</v>
+        <v>3800</v>
       </c>
       <c r="C2715" t="n">
-        <v>1.8400000333786</v>
+        <v>1.87000000476837</v>
       </c>
       <c r="D2715" t="n">
         <v>1.83500003814697</v>
       </c>
       <c r="E2715" t="n">
-        <v>1.8400000333786</v>
+        <v>1.83500003814697</v>
       </c>
       <c r="F2715" t="n">
-        <v>1.83500003814697</v>
+        <v>1.87000000476837</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>4251</v>
+        <v>600</v>
       </c>
       <c r="C2716" t="n">
-        <v>1.87000000476837</v>
+        <v>1.8400000333786</v>
       </c>
       <c r="D2716" t="n">
-        <v>1.83000004291534</v>
+        <v>1.83500003814697</v>
       </c>
       <c r="E2716" t="n">
+        <v>1.8400000333786</v>
+      </c>
+      <c r="F2716" t="n">
         <v>1.83500003814697</v>
-      </c>
-      <c r="F2716" t="n">
-        <v>1.87000000476837</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>6405</v>
+        <v>4251</v>
       </c>
       <c r="C2717" t="n">
-        <v>1.85000002384186</v>
+        <v>1.87000000476837</v>
       </c>
       <c r="D2717" t="n">
-        <v>1.82000005245209</v>
+        <v>1.83000004291534</v>
       </c>
       <c r="E2717" t="n">
         <v>1.83500003814697</v>
       </c>
       <c r="F2717" t="n">
-        <v>1.85000002384186</v>
+        <v>1.87000000476837</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,19 +62865,19 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>15560</v>
+        <v>6405</v>
       </c>
       <c r="C2718" t="n">
-        <v>1.86500000953674</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="D2718" t="n">
         <v>1.82000005245209</v>
       </c>
       <c r="E2718" t="n">
-        <v>1.85500001907349</v>
+        <v>1.83500003814697</v>
       </c>
       <c r="F2718" t="n">
         <v>1.85000002384186</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>3309</v>
+        <v>15560</v>
       </c>
       <c r="C2719" t="n">
-        <v>1.87000000476837</v>
+        <v>1.86500000953674</v>
       </c>
       <c r="D2719" t="n">
-        <v>1.80999994277954</v>
+        <v>1.82000005245209</v>
       </c>
       <c r="E2719" t="n">
-        <v>1.87000000476837</v>
+        <v>1.85500001907349</v>
       </c>
       <c r="F2719" t="n">
-        <v>1.80999994277954</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>19692</v>
+        <v>3309</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.82000005245209</v>
+        <v>1.87000000476837</v>
       </c>
       <c r="D2720" t="n">
-        <v>1.77999997138977</v>
+        <v>1.80999994277954</v>
       </c>
       <c r="E2720" t="n">
-        <v>1.82000005245209</v>
+        <v>1.87000000476837</v>
       </c>
       <c r="F2720" t="n">
-        <v>1.79499995708466</v>
+        <v>1.80999994277954</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>23807</v>
+        <v>19692</v>
       </c>
       <c r="C2721" t="n">
-        <v>1.88999998569489</v>
+        <v>1.82000005245209</v>
       </c>
       <c r="D2721" t="n">
-        <v>1.82500004768372</v>
+        <v>1.77999997138977</v>
       </c>
       <c r="E2721" t="n">
-        <v>1.87999999523163</v>
+        <v>1.82000005245209</v>
       </c>
       <c r="F2721" t="n">
-        <v>1.83000004291534</v>
+        <v>1.79499995708466</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>85329</v>
+        <v>23807</v>
       </c>
       <c r="C2722" t="n">
-        <v>1.89499998092651</v>
+        <v>1.88999998569489</v>
       </c>
       <c r="D2722" t="n">
-        <v>1.70000004768372</v>
+        <v>1.82500004768372</v>
       </c>
       <c r="E2722" t="n">
-        <v>1.86000001430511</v>
+        <v>1.87999999523163</v>
       </c>
       <c r="F2722" t="n">
         <v>1.83000004291534</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>187914</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.99500000476837</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>1.81500005722046</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -837,7 +837,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G20" t="n">
-        <v>2.20440411567688</v>
+        <v>2.2044038772583</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08540391921997</v>
+        <v>2.08540415763855</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G44" t="n">
-        <v>2.20440411567688</v>
+        <v>2.2044038772583</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G47" t="n">
-        <v>2.16086745262146</v>
+        <v>2.16086721420288</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G51" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G52" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G54" t="n">
-        <v>2.24794054031372</v>
+        <v>2.24794030189514</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G55" t="n">
-        <v>2.24794054031372</v>
+        <v>2.24794030189514</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G56" t="n">
-        <v>2.24794054031372</v>
+        <v>2.24794030189514</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G57" t="n">
-        <v>2.24794054031372</v>
+        <v>2.24794030189514</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G66" t="n">
-        <v>2.24503803253174</v>
+        <v>2.24503827095032</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G67" t="n">
-        <v>2.24503803253174</v>
+        <v>2.24503827095032</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G69" t="n">
-        <v>2.23052573204041</v>
+        <v>2.23052597045898</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>1.71824514865875</v>
+        <v>1.71824502944946</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G74" t="n">
-        <v>1.76758670806885</v>
+        <v>1.76758658885956</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G75" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G76" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G89" t="n">
-        <v>1.7327573299408</v>
+        <v>1.73275721073151</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G102" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G103" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G105" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>1.60359871387482</v>
+        <v>1.60359859466553</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>1.60359871387482</v>
+        <v>1.60359859466553</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.25</v>
       </c>
       <c r="G122" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G126" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G127" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G128" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G129" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G131" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G147" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317178726196</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G148" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317178726196</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G159" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317178726196</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G160" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G161" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G165" t="n">
-        <v>1.27925097942352</v>
+        <v>1.27925086021423</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.32061064243317</v>
+        <v>1.32061076164246</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G193" t="n">
-        <v>1.24224483966827</v>
+        <v>1.24224472045898</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G194" t="n">
-        <v>1.24224483966827</v>
+        <v>1.24224472045898</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G223" t="n">
-        <v>1.30247044563293</v>
+        <v>1.30247032642365</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G224" t="n">
-        <v>1.30247044563293</v>
+        <v>1.30247032642365</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G235" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G236" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18854963779449</v>
+        <v>1.18854951858521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18854963779449</v>
+        <v>1.18854951858521</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G274" t="n">
-        <v>1.27707397937775</v>
+        <v>1.27707409858704</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G278" t="n">
-        <v>1.46718394756317</v>
+        <v>1.46718406677246</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G290" t="n">
-        <v>1.21176910400391</v>
+        <v>1.21176898479462</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G291" t="n">
-        <v>1.21176910400391</v>
+        <v>1.21176898479462</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G292" t="n">
-        <v>1.21176910400391</v>
+        <v>1.21176898479462</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.21176910400391</v>
+        <v>1.21176898479462</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G301" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G303" t="n">
-        <v>1.24877524375916</v>
+        <v>1.24877536296844</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G304" t="n">
-        <v>1.24950087070465</v>
+        <v>1.24950075149536</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G306" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G322" t="n">
-        <v>1.67035484313965</v>
+        <v>1.67035472393036</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>1.5600620508194</v>
+        <v>1.56006217002869</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G339" t="n">
-        <v>1.42872667312622</v>
+        <v>1.42872655391693</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G340" t="n">
-        <v>1.41493999958038</v>
+        <v>1.41494011878967</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G345" t="n">
-        <v>1.41493999958038</v>
+        <v>1.41494011878967</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G355" t="n">
-        <v>1.47008645534515</v>
+        <v>1.47008633613586</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G356" t="n">
-        <v>1.43453145027161</v>
+        <v>1.4345315694809</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G360" t="n">
-        <v>1.47879385948181</v>
+        <v>1.47879374027252</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G366" t="n">
-        <v>1.52668404579163</v>
+        <v>1.52668392658234</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>1.5600620508194</v>
+        <v>1.56006217002869</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713537693024</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.77919626235962</v>
+        <v>1.77919638156891</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>1.95914781093597</v>
+        <v>1.9591475725174</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G385" t="n">
-        <v>2.16522097587585</v>
+        <v>2.16522073745728</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>2.0999162197113</v>
+        <v>2.09991598129272</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.03315997123718</v>
+        <v>2.03316020965576</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G388" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318437576294</v>
+        <v>1.94318413734436</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G395" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G403" t="n">
-        <v>1.78645241260529</v>
+        <v>1.786452293396</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563519477844</v>
+        <v>1.82563543319702</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G407" t="n">
-        <v>1.75742793083191</v>
+        <v>1.7574280500412</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G412" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G418" t="n">
-        <v>1.65874493122101</v>
+        <v>1.6587450504303</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73856198787689</v>
+        <v>1.73856210708618</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>1.80676960945129</v>
+        <v>1.80676937103271</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G424" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837940216064</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G426" t="n">
-        <v>1.80676960945129</v>
+        <v>1.80676937103271</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G429" t="n">
-        <v>1.94898915290833</v>
+        <v>1.9489893913269</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561102867126</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>1.85175752639771</v>
+        <v>1.85175728797913</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>1.85756206512451</v>
+        <v>1.85756230354309</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G438" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>1.83724522590637</v>
+        <v>1.83724510669708</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93302595615387</v>
+        <v>1.93302571773529</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G449" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G451" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207460403442</v>
+        <v>1.87207436561584</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>1.85756206512451</v>
+        <v>1.85756230354309</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561102867126</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G471" t="n">
-        <v>1.90400123596191</v>
+        <v>1.90400147438049</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>1.89094042778015</v>
+        <v>1.89094018936157</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G475" t="n">
-        <v>1.9098060131073</v>
+        <v>1.90980625152588</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>1.72114741802216</v>
+        <v>1.72114753723145</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G484" t="n">
-        <v>1.80096459388733</v>
+        <v>1.80096483230591</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G487" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837940216064</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G492" t="n">
-        <v>1.85175752639771</v>
+        <v>1.85175728797913</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G509" t="n">
-        <v>1.80096459388733</v>
+        <v>1.80096483230591</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G510" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G511" t="n">
-        <v>1.82998931407928</v>
+        <v>1.82998907566071</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G518" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>1.80676960945129</v>
+        <v>1.80676937103271</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>1.85756206512451</v>
+        <v>1.85756230354309</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G540" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G546" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G547" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G549" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G554" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G559" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G561" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G562" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G564" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G568" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G573" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G579" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G593" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.25</v>
       </c>
       <c r="G596" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.25</v>
       </c>
       <c r="G597" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.25</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.25</v>
       </c>
       <c r="G600" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G605" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G611" t="n">
-        <v>1.60359871387482</v>
+        <v>1.60359859466553</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>1.48750102519989</v>
+        <v>1.4875009059906</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G620" t="n">
-        <v>1.5382936000824</v>
+        <v>1.53829371929169</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G621" t="n">
-        <v>1.5382936000824</v>
+        <v>1.53829371929169</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>1.5382936000824</v>
+        <v>1.53829371929169</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G634" t="n">
-        <v>1.5600620508194</v>
+        <v>1.56006217002869</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G635" t="n">
-        <v>1.5600620508194</v>
+        <v>1.56006217002869</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>1.60359871387482</v>
+        <v>1.60359859466553</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G653" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.25</v>
       </c>
       <c r="G671" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.25</v>
       </c>
       <c r="G672" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.25</v>
       </c>
       <c r="G673" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713537693024</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.25</v>
       </c>
       <c r="G693" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G696" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G700" t="n">
-        <v>1.80676960945129</v>
+        <v>1.80676937103271</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G706" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G707" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713537693024</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G708" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G710" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80676960945129</v>
+        <v>1.80676937103271</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G753" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G754" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G755" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G765" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G766" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579409122467</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>1.85756206512451</v>
+        <v>1.85756230354309</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G780" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G781" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561102867126</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365975379944</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G798" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365975379944</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G812" t="n">
-        <v>2.1550624370575</v>
+        <v>2.15506267547607</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>2.24939179420471</v>
+        <v>2.24939155578613</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>2.271160364151</v>
+        <v>2.27116012573242</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>2.24939179420471</v>
+        <v>2.24939155578613</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G824" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292821884155</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G826" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292821884155</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G828" t="n">
-        <v>2.27841639518738</v>
+        <v>2.2784161567688</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G829" t="n">
-        <v>2.30744051933289</v>
+        <v>2.30744075775146</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>2.38725757598877</v>
+        <v>2.38725781440735</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G846" t="n">
-        <v>2.30744051933289</v>
+        <v>2.30744075775146</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292821884155</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>2.32195281982422</v>
+        <v>2.3219530582428</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G855" t="n">
-        <v>2.271160364151</v>
+        <v>2.27116012573242</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G856" t="n">
-        <v>2.24939179420471</v>
+        <v>2.24939155578613</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G858" t="n">
-        <v>2.27841639518738</v>
+        <v>2.2784161567688</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G859" t="n">
-        <v>2.27841639518738</v>
+        <v>2.2784161567688</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>2.36548924446106</v>
+        <v>2.36548948287964</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>2.38725757598877</v>
+        <v>2.38725781440735</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>2.43805050849915</v>
+        <v>2.43805027008057</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.38725757598877</v>
+        <v>2.38725781440735</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>2.53237962722778</v>
+        <v>2.53237986564636</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G883" t="n">
-        <v>2.75731897354126</v>
+        <v>2.75731873512268</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G889" t="n">
-        <v>2.78634333610535</v>
+        <v>2.78634357452393</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G893" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G896" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G898" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G909" t="n">
-        <v>2.75731897354126</v>
+        <v>2.75731873512268</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G910" t="n">
-        <v>2.77183127403259</v>
+        <v>2.77183103561401</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G912" t="n">
-        <v>2.78634333610535</v>
+        <v>2.78634357452393</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>2.75731897354126</v>
+        <v>2.75731873512268</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G936" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G943" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>2.82987999916077</v>
+        <v>2.82988023757935</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G951" t="n">
-        <v>2.97500205039978</v>
+        <v>2.9750018119812</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>2.97500205039978</v>
+        <v>2.9750018119812</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G963" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G964" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G969" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G977" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G980" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.5</v>
       </c>
       <c r="G985" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G992" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G994" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506368637085</v>
+        <v>3.34506320953369</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506368637085</v>
+        <v>3.34506320953369</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859963417053</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859963417053</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.75731897354126</v>
+        <v>2.75731873512268</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427075386047</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>4.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859963417053</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158818244934</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731950759888</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731950759888</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71512413024902</v>
+        <v>3.71512460708618</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829514503479</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829514503479</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829514503479</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731950759888</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829514503479</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829514503479</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829514503479</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158818244934</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829514503479</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731950759888</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731950759888</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731950759888</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731950759888</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158818244934</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.04030704498291</v>
+        <v>3.04030680656433</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.5</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>4.5</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>4.5</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.45390510559082</v>
+        <v>3.45390486717224</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>4.75</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859963417053</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427075386047</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427075386047</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.04030704498291</v>
+        <v>3.04030680656433</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.04030704498291</v>
+        <v>3.04030680656433</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427075386047</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.5</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.5</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427075386047</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427075386047</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158818244934</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.71512413024902</v>
+        <v>3.71512460708618</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158818244934</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158818244934</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.5</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.75</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>4.75</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.45390510559082</v>
+        <v>3.45390486717224</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.71512413024902</v>
+        <v>3.71512460708618</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158818244934</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.71512413024902</v>
+        <v>3.71512460708618</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158818244934</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158818244934</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859963417053</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>4.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.45390510559082</v>
+        <v>3.45390486717224</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353874206543</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.57000231742859</v>
+        <v>3.57000255584717</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.57000231742859</v>
+        <v>3.57000255584717</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1713" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>4.5</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896528244019</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.20719742774963</v>
+        <v>3.20719718933105</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1737" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.82987999916077</v>
+        <v>2.82988023757935</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.04030704498291</v>
+        <v>3.04030680656433</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1774" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.12012410163879</v>
+        <v>3.12012434005737</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.07658720016479</v>
+        <v>3.07658743858337</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.97634410858154</v>
+        <v>3.97634434700012</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.25207614898682</v>
+        <v>4.25207567214966</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.31012487411499</v>
+        <v>4.31012535095215</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.31012487411499</v>
+        <v>4.31012535095215</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1893" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.45524740219116</v>
+        <v>4.455246925354</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.55683279037476</v>
+        <v>4.5568323135376</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1900" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1909" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585643768311</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.542320728302</v>
+        <v>4.54232025146484</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.31012487411499</v>
+        <v>4.31012535095215</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1920" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585643768311</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1932" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1933" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1934" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1935" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1940" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1947" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1951" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1956" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1960" t="n">
-        <v>4.83256435394287</v>
+        <v>4.83256387710571</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1964" t="n">
-        <v>4.83256435394287</v>
+        <v>4.83256387710571</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1980" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1986" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1993" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.542320728302</v>
+        <v>4.54232025146484</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.31012487411499</v>
+        <v>4.31012535095215</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.97634410858154</v>
+        <v>3.97634434700012</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829514503479</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2058" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2059" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2063" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2064" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2065" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2066" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122205734253</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2070" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2071" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2072" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2073" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2074" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2076" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2091" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G2095" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2097" t="n">
-        <v>4.45524740219116</v>
+        <v>4.455246925354</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2098" t="n">
-        <v>4.45524740219116</v>
+        <v>4.455246925354</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2101" t="n">
-        <v>4.55683279037476</v>
+        <v>4.5568323135376</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2102" t="n">
-        <v>4.55683279037476</v>
+        <v>4.5568323135376</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2103" t="n">
-        <v>4.55683279037476</v>
+        <v>4.5568323135376</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585643768311</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2107" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2108" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2110" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2115" t="n">
-        <v>5.23890590667725</v>
+        <v>5.2389063835144</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2123" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2125" t="n">
-        <v>5.74200296401978</v>
+        <v>5.74200248718262</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2131" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2143" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2144" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2146" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2148" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2154" t="n">
-        <v>5.50006437301636</v>
+        <v>5.50006484985352</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2158" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2165" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2168" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2169" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2171" t="n">
-        <v>5.67748546600342</v>
+        <v>5.67748594284058</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2174" t="n">
-        <v>5.7903904914856</v>
+        <v>5.79039001464844</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2175" t="n">
-        <v>5.7903904914856</v>
+        <v>5.79039001464844</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -57491,7 +57491,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2197" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2197" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2199" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2201" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2203" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57673,7 +57673,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2204" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2204" t="s">
         <v>8</v>
@@ -57699,7 +57699,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2205" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2205" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>2.19000005722046</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>195184</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>2.08999991416931</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>2.19000005722046</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>2.10999989509583</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -837,7 +837,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1042697429657</v>
+        <v>2.10426998138428</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2044038772583</v>
+        <v>2.20440411567688</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14345264434814</v>
+        <v>2.14345288276672</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14345264434814</v>
+        <v>2.14345288276672</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14345264434814</v>
+        <v>2.14345288276672</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14345264434814</v>
+        <v>2.14345288276672</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08540415763855</v>
+        <v>2.08540391921997</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G44" t="n">
-        <v>2.2044038772583</v>
+        <v>2.20440411567688</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G47" t="n">
-        <v>2.16086721420288</v>
+        <v>2.16086745262146</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G51" t="n">
-        <v>2.22617220878601</v>
+        <v>2.22617244720459</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G52" t="n">
-        <v>2.22617220878601</v>
+        <v>2.22617244720459</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G54" t="n">
-        <v>2.24794030189514</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G55" t="n">
-        <v>2.24794030189514</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G56" t="n">
-        <v>2.24794030189514</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G57" t="n">
-        <v>2.24794030189514</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G66" t="n">
-        <v>2.24503827095032</v>
+        <v>2.24503803253174</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G67" t="n">
-        <v>2.24503827095032</v>
+        <v>2.24503803253174</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G69" t="n">
-        <v>2.23052597045898</v>
+        <v>2.23052573204041</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>1.71824502944946</v>
+        <v>1.71824514865875</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G74" t="n">
-        <v>1.76758658885956</v>
+        <v>1.76758670806885</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G75" t="n">
-        <v>1.76468408107758</v>
+        <v>1.76468420028687</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G76" t="n">
-        <v>1.76468408107758</v>
+        <v>1.76468420028687</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G89" t="n">
-        <v>1.73275721073151</v>
+        <v>1.7327573299408</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G102" t="n">
-        <v>1.64568388462067</v>
+        <v>1.64568400382996</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G103" t="n">
-        <v>1.64568388462067</v>
+        <v>1.64568400382996</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63117170333862</v>
+        <v>1.63117182254791</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G105" t="n">
-        <v>1.63117170333862</v>
+        <v>1.63117182254791</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G111" t="n">
-        <v>1.60359859466553</v>
+        <v>1.60359871387482</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>1.60359859466553</v>
+        <v>1.60359871387482</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.25</v>
       </c>
       <c r="G122" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G126" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G127" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G128" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G129" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G131" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G147" t="n">
-        <v>1.39317178726196</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G148" t="n">
-        <v>1.39317178726196</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G159" t="n">
-        <v>1.39317178726196</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G160" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G161" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G165" t="n">
-        <v>1.27925086021423</v>
+        <v>1.27925097942352</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.32061076164246</v>
+        <v>1.32061064243317</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G193" t="n">
-        <v>1.24224472045898</v>
+        <v>1.24224483966827</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G194" t="n">
-        <v>1.24224472045898</v>
+        <v>1.24224483966827</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G223" t="n">
-        <v>1.30247032642365</v>
+        <v>1.30247044563293</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G224" t="n">
-        <v>1.30247032642365</v>
+        <v>1.30247044563293</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G235" t="n">
-        <v>1.21902513504028</v>
+        <v>1.21902525424957</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G236" t="n">
-        <v>1.21902513504028</v>
+        <v>1.21902525424957</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>1.17403745651245</v>
+        <v>1.17403733730316</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>1.17403745651245</v>
+        <v>1.17403733730316</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18854951858521</v>
+        <v>1.18854963779449</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18854951858521</v>
+        <v>1.18854963779449</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G274" t="n">
-        <v>1.27707409858704</v>
+        <v>1.27707397937775</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G278" t="n">
-        <v>1.46718406677246</v>
+        <v>1.46718394756317</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G290" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G291" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G292" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G301" t="n">
-        <v>1.21902513504028</v>
+        <v>1.21902525424957</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G303" t="n">
-        <v>1.24877536296844</v>
+        <v>1.24877524375916</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G304" t="n">
-        <v>1.24950075149536</v>
+        <v>1.24950087070465</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G306" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G322" t="n">
-        <v>1.67035472393036</v>
+        <v>1.67035484313965</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>1.56006217002869</v>
+        <v>1.5600620508194</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G339" t="n">
-        <v>1.42872655391693</v>
+        <v>1.42872667312622</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G340" t="n">
-        <v>1.41494011878967</v>
+        <v>1.41493999958038</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G345" t="n">
-        <v>1.41494011878967</v>
+        <v>1.41493999958038</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G355" t="n">
-        <v>1.47008633613586</v>
+        <v>1.47008645534515</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G356" t="n">
-        <v>1.4345315694809</v>
+        <v>1.43453145027161</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G360" t="n">
-        <v>1.47879374027252</v>
+        <v>1.47879385948181</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G366" t="n">
-        <v>1.52668392658234</v>
+        <v>1.52668404579163</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>1.56006217002869</v>
+        <v>1.5600620508194</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64713537693024</v>
+        <v>1.64713525772095</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.77919638156891</v>
+        <v>1.77919626235962</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>1.9591475725174</v>
+        <v>1.95914781093597</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G385" t="n">
-        <v>2.16522073745728</v>
+        <v>2.16522097587585</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>2.09991598129272</v>
+        <v>2.0999162197113</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.03316020965576</v>
+        <v>2.03315997123718</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G388" t="n">
-        <v>1.98817217350006</v>
+        <v>1.98817205429077</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318413734436</v>
+        <v>1.94318437576294</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G395" t="n">
-        <v>1.86917197704315</v>
+        <v>1.86917221546173</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98817217350006</v>
+        <v>1.98817205429077</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G403" t="n">
-        <v>1.786452293396</v>
+        <v>1.78645241260529</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563543319702</v>
+        <v>1.82563519477844</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G407" t="n">
-        <v>1.7574280500412</v>
+        <v>1.75742793083191</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>1.78935480117798</v>
+        <v>1.78935492038727</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G412" t="n">
-        <v>1.78935480117798</v>
+        <v>1.78935492038727</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G418" t="n">
-        <v>1.6587450504303</v>
+        <v>1.65874493122101</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73856210708618</v>
+        <v>1.73856198787689</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>1.80676937103271</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G424" t="n">
-        <v>1.81837940216064</v>
+        <v>1.81837928295135</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G426" t="n">
-        <v>1.80676937103271</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G429" t="n">
-        <v>1.9489893913269</v>
+        <v>1.94898915290833</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.91561102867126</v>
+        <v>1.91561126708984</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>1.85175728797913</v>
+        <v>1.85175752639771</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>1.85756230354309</v>
+        <v>1.85756206512451</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G438" t="n">
-        <v>1.76468408107758</v>
+        <v>1.76468420028687</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>1.83724510669708</v>
+        <v>1.83724522590637</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93302571773529</v>
+        <v>1.93302595615387</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G449" t="n">
-        <v>1.86917197704315</v>
+        <v>1.86917221546173</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G451" t="n">
-        <v>1.86917197704315</v>
+        <v>1.86917221546173</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207436561584</v>
+        <v>1.87207460403442</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>1.85756230354309</v>
+        <v>1.85756206512451</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>1.93737924098969</v>
+        <v>1.93737947940826</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>1.91561102867126</v>
+        <v>1.91561126708984</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G471" t="n">
-        <v>1.90400147438049</v>
+        <v>1.90400123596191</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>1.89094018936157</v>
+        <v>1.89094042778015</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G475" t="n">
-        <v>1.90980625152588</v>
+        <v>1.9098060131073</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>1.72114753723145</v>
+        <v>1.72114741802216</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G484" t="n">
-        <v>1.80096483230591</v>
+        <v>1.80096459388733</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G487" t="n">
-        <v>1.81837940216064</v>
+        <v>1.81837928295135</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G492" t="n">
-        <v>1.85175728797913</v>
+        <v>1.85175752639771</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G509" t="n">
-        <v>1.80096483230591</v>
+        <v>1.80096459388733</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G510" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G511" t="n">
-        <v>1.82998907566071</v>
+        <v>1.82998931407928</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G518" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>1.80676937103271</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>1.85756230354309</v>
+        <v>1.85756206512451</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.93737924098969</v>
+        <v>1.93737947940826</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>1.89384257793427</v>
+        <v>1.89384281635284</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G540" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G546" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G547" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G549" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G554" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G559" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G561" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G562" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G564" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G568" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G573" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G579" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G593" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.25</v>
       </c>
       <c r="G596" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.25</v>
       </c>
       <c r="G597" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.25</v>
       </c>
       <c r="G598" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.25</v>
       </c>
       <c r="G600" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G605" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G611" t="n">
-        <v>1.60359859466553</v>
+        <v>1.60359871387482</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>1.4875009059906</v>
+        <v>1.48750102519989</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G620" t="n">
-        <v>1.53829371929169</v>
+        <v>1.5382936000824</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G621" t="n">
-        <v>1.53829371929169</v>
+        <v>1.5382936000824</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>1.53829371929169</v>
+        <v>1.5382936000824</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G634" t="n">
-        <v>1.56006217002869</v>
+        <v>1.5600620508194</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G635" t="n">
-        <v>1.56006217002869</v>
+        <v>1.5600620508194</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>1.60359859466553</v>
+        <v>1.60359871387482</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G653" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.25</v>
       </c>
       <c r="G671" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.25</v>
       </c>
       <c r="G672" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.25</v>
       </c>
       <c r="G673" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64713537693024</v>
+        <v>1.64713525772095</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.25</v>
       </c>
       <c r="G693" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G696" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G700" t="n">
-        <v>1.80676937103271</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G706" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G707" t="n">
-        <v>1.64713537693024</v>
+        <v>1.64713525772095</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G708" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80676937103271</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G753" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G754" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G755" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G765" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G766" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.83579409122467</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>1.85756230354309</v>
+        <v>1.85756206512451</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G780" t="n">
-        <v>1.89384257793427</v>
+        <v>1.89384281635284</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G781" t="n">
-        <v>1.91561102867126</v>
+        <v>1.91561126708984</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>1.93737924098969</v>
+        <v>1.93737947940826</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>2.00994038581848</v>
+        <v>2.0099401473999</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.97365975379944</v>
+        <v>1.97365999221802</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>2.00994038581848</v>
+        <v>2.0099401473999</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G798" t="n">
-        <v>1.97365975379944</v>
+        <v>1.97365999221802</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>2.00994038581848</v>
+        <v>2.0099401473999</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>2.1042697429657</v>
+        <v>2.10426998138428</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G812" t="n">
-        <v>2.15506267547607</v>
+        <v>2.1550624370575</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>2.27116012573242</v>
+        <v>2.271160364151</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G824" t="n">
-        <v>2.29292821884155</v>
+        <v>2.29292845726013</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G826" t="n">
-        <v>2.29292821884155</v>
+        <v>2.29292845726013</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G828" t="n">
-        <v>2.2784161567688</v>
+        <v>2.27841639518738</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G829" t="n">
-        <v>2.30744075775146</v>
+        <v>2.30744051933289</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>2.38725781440735</v>
+        <v>2.38725757598877</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G846" t="n">
-        <v>2.30744075775146</v>
+        <v>2.30744051933289</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.29292821884155</v>
+        <v>2.29292845726013</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>2.3219530582428</v>
+        <v>2.32195281982422</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G855" t="n">
-        <v>2.27116012573242</v>
+        <v>2.271160364151</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G856" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G858" t="n">
-        <v>2.2784161567688</v>
+        <v>2.27841639518738</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G859" t="n">
-        <v>2.2784161567688</v>
+        <v>2.27841639518738</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>2.36548948287964</v>
+        <v>2.36548924446106</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>2.38725781440735</v>
+        <v>2.38725757598877</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>2.43805027008057</v>
+        <v>2.43805050849915</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.38725781440735</v>
+        <v>2.38725757598877</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>2.53237986564636</v>
+        <v>2.53237962722778</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G883" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G889" t="n">
-        <v>2.78634357452393</v>
+        <v>2.78634333610535</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G893" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G896" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G898" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G909" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G910" t="n">
-        <v>2.77183103561401</v>
+        <v>2.77183127403259</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G912" t="n">
-        <v>2.78634357452393</v>
+        <v>2.78634333610535</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G936" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G943" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>2.82988023757935</v>
+        <v>2.82987999916077</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9750018119812</v>
+        <v>2.97500205039978</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>2.9750018119812</v>
+        <v>2.97500205039978</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G963" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G964" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G969" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939208984375</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G977" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G980" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.5</v>
       </c>
       <c r="G985" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G988" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G992" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G994" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506320953369</v>
+        <v>3.34506368637085</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506320953369</v>
+        <v>3.34506368637085</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.2870147228241</v>
+        <v>3.28701448440552</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939208984375</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.38859963417053</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.38859963417053</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.2870147228241</v>
+        <v>3.28701448440552</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.29427075386047</v>
+        <v>3.29427051544189</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>4.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939208984375</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.38859963417053</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67158818244934</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.94731950759888</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.94731950759888</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71512460708618</v>
+        <v>3.71512413024902</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.91829514503479</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.91829514503479</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.91829514503479</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94731950759888</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.91829514503479</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.91829514503479</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.91829514503479</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.67158818244934</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91829514503479</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.94731950759888</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.94731950759888</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.94731950759888</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.94731950759888</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.67158818244934</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.04030680656433</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.5</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>4.5</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.2870147228241</v>
+        <v>3.28701448440552</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>4.5</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.45390486717224</v>
+        <v>3.45390510559082</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.2870147228241</v>
+        <v>3.28701448440552</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>4.75</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.38859963417053</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.21445322036743</v>
+        <v>3.21445345878601</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.29427075386047</v>
+        <v>3.29427051544189</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.29427075386047</v>
+        <v>3.29427051544189</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1345" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1346" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1347" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.04030680656433</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.04030680656433</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.29427075386047</v>
+        <v>3.29427051544189</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.5</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.2870147228241</v>
+        <v>3.28701448440552</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.5</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.2870147228241</v>
+        <v>3.28701448440552</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1449" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.29427075386047</v>
+        <v>3.29427051544189</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.29427075386047</v>
+        <v>3.29427051544189</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939208984375</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.67158818244934</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.71512460708618</v>
+        <v>3.71512413024902</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.67158818244934</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.67158818244934</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.5</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.75</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>4.75</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.45390486717224</v>
+        <v>3.45390510559082</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.71512460708618</v>
+        <v>3.71512413024902</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.67158818244934</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.71512460708618</v>
+        <v>3.71512413024902</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.67158818244934</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.67158818244934</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38859963417053</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>4.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1640" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1641" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.45390486717224</v>
+        <v>3.45390510559082</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.61353874206543</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.57000255584717</v>
+        <v>3.57000231742859</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.57000255584717</v>
+        <v>3.57000231742859</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1713" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.2434778213501</v>
+        <v>3.24347758293152</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>4.5</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1729" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.22896528244019</v>
+        <v>3.22896552085876</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1732" t="n">
-        <v>3.20719718933105</v>
+        <v>3.20719742774963</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1737" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.82988023757935</v>
+        <v>2.82987999916077</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.04030680656433</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1774" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.12012434005737</v>
+        <v>3.12012410163879</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.07658743858337</v>
+        <v>3.07658720016479</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.97634434700012</v>
+        <v>3.97634410858154</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.25207567214966</v>
+        <v>4.25207614898682</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.2085394859314</v>
+        <v>4.20853996276855</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.2085394859314</v>
+        <v>4.20853996276855</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.2085394859314</v>
+        <v>4.20853996276855</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.39719820022583</v>
+        <v>4.39719772338867</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.39719820022583</v>
+        <v>4.39719772338867</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.2085394859314</v>
+        <v>4.20853996276855</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1893" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.455246925354</v>
+        <v>4.45524740219116</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.5568323135376</v>
+        <v>4.55683279037476</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1900" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1909" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>4.58585643768311</v>
+        <v>4.58585691452026</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.54232025146484</v>
+        <v>4.542320728302</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.39719820022583</v>
+        <v>4.39719772338867</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1920" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.58585643768311</v>
+        <v>4.58585691452026</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1932" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1933" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1934" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1935" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1940" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1947" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1951" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1956" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1960" t="n">
-        <v>4.83256387710571</v>
+        <v>4.83256435394287</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1964" t="n">
-        <v>4.83256387710571</v>
+        <v>4.83256435394287</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1980" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1986" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1993" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.54232025146484</v>
+        <v>4.542320728302</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.97634434700012</v>
+        <v>3.97634410858154</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.87475848197937</v>
+        <v>3.87475895881653</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.87475848197937</v>
+        <v>3.87475895881653</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.87475848197937</v>
+        <v>3.87475895881653</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.91829514503479</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.87475848197937</v>
+        <v>3.87475895881653</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2058" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2059" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2063" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2064" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2065" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2066" t="n">
-        <v>3.83122205734253</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2070" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2071" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2072" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2073" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2074" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2076" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2091" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G2095" t="n">
-        <v>4.39719820022583</v>
+        <v>4.39719772338867</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2097" t="n">
-        <v>4.455246925354</v>
+        <v>4.45524740219116</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2098" t="n">
-        <v>4.455246925354</v>
+        <v>4.45524740219116</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -54995,7 +54995,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2101" t="n">
-        <v>4.5568323135376</v>
+        <v>4.55683279037476</v>
       </c>
       <c r="H2101" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2102" t="n">
-        <v>4.5568323135376</v>
+        <v>4.55683279037476</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2103" t="n">
-        <v>4.5568323135376</v>
+        <v>4.55683279037476</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.58585643768311</v>
+        <v>4.58585691452026</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2107" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2108" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2110" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2115" t="n">
-        <v>5.2389063835144</v>
+        <v>5.23890590667725</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2123" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2125" t="n">
-        <v>5.74200248718262</v>
+        <v>5.74200296401978</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2131" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2143" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2144" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2146" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2148" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2154" t="n">
-        <v>5.50006484985352</v>
+        <v>5.50006437301636</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2158" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2165" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2168" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2169" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2171" t="n">
-        <v>5.67748594284058</v>
+        <v>5.67748546600342</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2174" t="n">
-        <v>5.79039001464844</v>
+        <v>5.7903904914856</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2175" t="n">
-        <v>5.79039001464844</v>
+        <v>5.7903904914856</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -57491,7 +57491,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2197" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2197" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2199" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2201" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2203" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57673,7 +57673,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2204" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2204" t="s">
         <v>8</v>
@@ -57699,7 +57699,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2205" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2205" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>2.10999989509583</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>109205</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>2.11999988555908</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>1.97500002384186</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18408679962158</v>
+        <v>2.18408703804016</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18408679962158</v>
+        <v>2.18408703804016</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18408679962158</v>
+        <v>2.18408703804016</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G5" t="n">
-        <v>2.18408679962158</v>
+        <v>2.18408703804016</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14055013656616</v>
+        <v>2.14055037498474</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G31" t="n">
-        <v>2.1347451210022</v>
+        <v>2.13474535942078</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G46" t="n">
-        <v>2.24648952484131</v>
+        <v>2.24648928642273</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G47" t="n">
-        <v>2.16086745262146</v>
+        <v>2.16086721420288</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G54" t="n">
-        <v>2.24794054031372</v>
+        <v>2.2479407787323</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G55" t="n">
-        <v>2.24794054031372</v>
+        <v>2.2479407787323</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G56" t="n">
-        <v>2.24794054031372</v>
+        <v>2.2479407787323</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G57" t="n">
-        <v>2.24794054031372</v>
+        <v>2.2479407787323</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G60" t="n">
-        <v>2.18408679962158</v>
+        <v>2.18408703804016</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G61" t="n">
-        <v>2.22907471656799</v>
+        <v>2.22907495498657</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>1.71824514865875</v>
+        <v>1.71824502944946</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G91" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G92" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G93" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G96" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G98" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.25</v>
       </c>
       <c r="G122" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G124" t="n">
-        <v>1.67180585861206</v>
+        <v>1.67180597782135</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G132" t="n">
-        <v>1.54409873485565</v>
+        <v>1.54409861564636</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G133" t="n">
-        <v>1.54409873485565</v>
+        <v>1.54409861564636</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G147" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317154884338</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G148" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317154884338</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G149" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G150" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G152" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G155" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G156" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G157" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G158" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G159" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317154884338</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>1.25095212459564</v>
+        <v>1.25095200538635</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G172" t="n">
-        <v>1.33875095844269</v>
+        <v>1.3387508392334</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G175" t="n">
-        <v>1.3626960515976</v>
+        <v>1.36269617080688</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G176" t="n">
-        <v>1.3626960515976</v>
+        <v>1.36269617080688</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>1.35543990135193</v>
+        <v>1.35544002056122</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22628140449524</v>
+        <v>1.22628128528595</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G223" t="n">
-        <v>1.30247044563293</v>
+        <v>1.30247032642365</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G224" t="n">
-        <v>1.30247044563293</v>
+        <v>1.30247032642365</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>1.25530576705933</v>
+        <v>1.25530564785004</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G235" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G236" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18854963779449</v>
+        <v>1.18854951858521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18854963779449</v>
+        <v>1.18854951858521</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G274" t="n">
-        <v>1.27707397937775</v>
+        <v>1.27707409858704</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G276" t="n">
-        <v>1.5832816362381</v>
+        <v>1.58328151702881</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>1.20741546154022</v>
+        <v>1.20741558074951</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.17186057567596</v>
+        <v>1.17186045646667</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G301" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>1.42219614982605</v>
+        <v>1.42219603061676</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G329" t="n">
-        <v>1.51072061061859</v>
+        <v>1.5107204914093</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G336" t="n">
-        <v>1.40260457992554</v>
+        <v>1.40260446071625</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>1.37430584430695</v>
+        <v>1.37430596351624</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G339" t="n">
-        <v>1.42872667312622</v>
+        <v>1.42872655391693</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G340" t="n">
-        <v>1.41493999958038</v>
+        <v>1.41493988037109</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G343" t="n">
-        <v>1.44178760051727</v>
+        <v>1.44178748130798</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G345" t="n">
-        <v>1.41493999958038</v>
+        <v>1.41493988037109</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>1.43235468864441</v>
+        <v>1.43235456943512</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G356" t="n">
-        <v>1.43453145027161</v>
+        <v>1.43453133106232</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G360" t="n">
-        <v>1.47879385948181</v>
+        <v>1.47879374027252</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G376" t="n">
-        <v>1.59344017505646</v>
+        <v>1.59344029426575</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.77919626235962</v>
+        <v>1.77919614315033</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G382" t="n">
-        <v>1.82708668708801</v>
+        <v>1.82708656787872</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>1.95914781093597</v>
+        <v>1.95914769172668</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G385" t="n">
-        <v>2.16522097587585</v>
+        <v>2.16522121429443</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.03315997123718</v>
+        <v>2.0331597328186</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G388" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G391" t="n">
-        <v>1.93447685241699</v>
+        <v>1.93447697162628</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G392" t="n">
-        <v>1.95044028759003</v>
+        <v>1.95044016838074</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318437576294</v>
+        <v>1.94318425655365</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G394" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G395" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917209625244</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G396" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G398" t="n">
-        <v>2.01574540138245</v>
+        <v>2.01574516296387</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G401" t="n">
-        <v>1.89239156246185</v>
+        <v>1.89239168167114</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.86191594600677</v>
+        <v>1.86191582679749</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G403" t="n">
-        <v>1.78645241260529</v>
+        <v>1.78645253181458</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563519477844</v>
+        <v>1.82563543319702</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935503959656</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G412" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935503959656</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73856198787689</v>
+        <v>1.73856210708618</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G426" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>1.79951333999634</v>
+        <v>1.79951345920563</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88658654689789</v>
+        <v>1.8865864276886</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G429" t="n">
-        <v>1.94898915290833</v>
+        <v>1.94898927211761</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561114788055</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.88658654689789</v>
+        <v>1.8865864276886</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>1.88658654689789</v>
+        <v>1.8865864276886</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88658654689789</v>
+        <v>1.8865864276886</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>1.85175752639771</v>
+        <v>1.85175740718842</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G437" t="n">
-        <v>1.81112325191498</v>
+        <v>1.81112337112427</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>1.85030615329742</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>1.83724522590637</v>
+        <v>1.83724510669708</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G441" t="n">
-        <v>1.84595227241516</v>
+        <v>1.84595239162445</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G447" t="n">
-        <v>1.9780136346817</v>
+        <v>1.97801375389099</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93302595615387</v>
+        <v>1.93302583694458</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G449" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917209625244</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>1.89964759349823</v>
+        <v>1.89964771270752</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G451" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917209625244</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>1.85030615329742</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G453" t="n">
-        <v>1.84014773368835</v>
+        <v>1.84014761447906</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207460403442</v>
+        <v>1.87207436561584</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561114788055</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G459" t="n">
-        <v>1.88513541221619</v>
+        <v>1.88513553142548</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>1.92141580581665</v>
+        <v>1.92141592502594</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G463" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G464" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G465" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G466" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G471" t="n">
-        <v>1.90400123596191</v>
+        <v>1.9040013551712</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>1.89094042778015</v>
+        <v>1.89094030857086</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>1.8807817697525</v>
+        <v>1.88078165054321</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G475" t="n">
-        <v>1.9098060131073</v>
+        <v>1.90980613231659</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G476" t="n">
-        <v>1.87497699260712</v>
+        <v>1.87497711181641</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G477" t="n">
-        <v>1.82273304462433</v>
+        <v>1.82273292541504</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G478" t="n">
-        <v>1.82273304462433</v>
+        <v>1.82273292541504</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>1.82273304462433</v>
+        <v>1.82273292541504</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G484" t="n">
-        <v>1.80096459388733</v>
+        <v>1.80096471309662</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G492" t="n">
-        <v>1.85175752639771</v>
+        <v>1.85175740718842</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G493" t="n">
-        <v>1.84159886837006</v>
+        <v>1.84159874916077</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G494" t="n">
-        <v>1.8807817697525</v>
+        <v>1.88078165054321</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G502" t="n">
-        <v>1.87062335014343</v>
+        <v>1.87062323093414</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G509" t="n">
-        <v>1.80096459388733</v>
+        <v>1.80096471309662</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G510" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G511" t="n">
-        <v>1.82998931407928</v>
+        <v>1.82998919487</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G512" t="n">
-        <v>1.77629387378693</v>
+        <v>1.77629375457764</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>1.79951333999634</v>
+        <v>1.79951345920563</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>1.85030615329742</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G518" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G525" t="n">
-        <v>1.88658654689789</v>
+        <v>1.8865864276886</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G526" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G533" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G538" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G545" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G547" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G558" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G571" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G574" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G575" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G580" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G591" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.25</v>
       </c>
       <c r="G596" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.25</v>
       </c>
       <c r="G597" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.25</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.25</v>
       </c>
       <c r="G600" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G609" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>1.57457435131073</v>
+        <v>1.57457423210144</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>1.57457435131073</v>
+        <v>1.57457423210144</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G658" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G660" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G662" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.25</v>
       </c>
       <c r="G671" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.25</v>
       </c>
       <c r="G672" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.25</v>
       </c>
       <c r="G673" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G677" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615950107574</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G682" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G684" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.25</v>
       </c>
       <c r="G693" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G694" t="n">
-        <v>1.62536692619324</v>
+        <v>1.62536704540253</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G700" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G712" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G716" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G720" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G726" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.79951333999634</v>
+        <v>1.79951345920563</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G743" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G756" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G758" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G766" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G767" t="n">
-        <v>1.71244013309479</v>
+        <v>1.7124400138855</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G768" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G775" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G778" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G781" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561114788055</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>2.01719641685486</v>
+        <v>2.01719665527344</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G790" t="n">
-        <v>2.01719641685486</v>
+        <v>2.01719665527344</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365987300873</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G798" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365987300873</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G800" t="n">
-        <v>2.01719641685486</v>
+        <v>2.01719665527344</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.0534770488739</v>
+        <v>2.05347681045532</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G804" t="n">
-        <v>2.11152601242065</v>
+        <v>2.11152577400208</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G807" t="n">
-        <v>2.11152601242065</v>
+        <v>2.11152577400208</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>2.04622101783752</v>
+        <v>2.04622077941895</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G811" t="n">
-        <v>2.09701371192932</v>
+        <v>2.09701347351074</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G813" t="n">
-        <v>2.18408679962158</v>
+        <v>2.18408703804016</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>2.22036743164062</v>
+        <v>2.22036719322205</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>2.22036743164062</v>
+        <v>2.22036719322205</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>2.24939179420471</v>
+        <v>2.24939155578613</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>2.271160364151</v>
+        <v>2.27116012573242</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>2.24939179420471</v>
+        <v>2.24939155578613</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G824" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G825" t="n">
-        <v>2.28567242622375</v>
+        <v>2.28567218780518</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G826" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G833" t="n">
-        <v>2.35097718238831</v>
+        <v>2.35097742080688</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G834" t="n">
-        <v>2.34372115135193</v>
+        <v>2.34372091293335</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G835" t="n">
-        <v>2.35097718238831</v>
+        <v>2.35097742080688</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G844" t="n">
-        <v>2.34372115135193</v>
+        <v>2.34372091293335</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G855" t="n">
-        <v>2.271160364151</v>
+        <v>2.27116012573242</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G856" t="n">
-        <v>2.24939179420471</v>
+        <v>2.24939155578613</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>2.35097718238831</v>
+        <v>2.35097742080688</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G867" t="n">
-        <v>2.35097718238831</v>
+        <v>2.35097742080688</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G869" t="n">
-        <v>2.35097718238831</v>
+        <v>2.35097742080688</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>2.36548924446106</v>
+        <v>2.36548948287964</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>2.43805050849915</v>
+        <v>2.43805027008057</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>2.53237962722778</v>
+        <v>2.53237986564636</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G889" t="n">
-        <v>2.78634333610535</v>
+        <v>2.78634309768677</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>2.91695308685303</v>
+        <v>2.91695332527161</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G899" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G902" t="n">
-        <v>3.01128268241882</v>
+        <v>3.01128244400024</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G905" t="n">
-        <v>2.91695308685303</v>
+        <v>2.91695332527161</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G910" t="n">
-        <v>2.77183127403259</v>
+        <v>2.77183103561401</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G912" t="n">
-        <v>2.78634333610535</v>
+        <v>2.78634309768677</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.75</v>
       </c>
       <c r="G915" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G916" t="n">
-        <v>2.67750191688538</v>
+        <v>2.6775016784668</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.75</v>
       </c>
       <c r="G921" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>2.7935996055603</v>
+        <v>2.79359936714172</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G924" t="n">
-        <v>2.95323395729065</v>
+        <v>2.95323371887207</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.25</v>
       </c>
       <c r="G927" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G928" t="n">
-        <v>3.02579474449158</v>
+        <v>3.02579498291016</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G936" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G941" t="n">
-        <v>3.01128268241882</v>
+        <v>3.01128244400024</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G943" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G945" t="n">
-        <v>3.01128268241882</v>
+        <v>3.01128244400024</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>3.01128268241882</v>
+        <v>3.01128244400024</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>2.82987999916077</v>
+        <v>2.82987976074219</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>3.02579474449158</v>
+        <v>3.02579498291016</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.25</v>
       </c>
       <c r="G965" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G973" t="n">
-        <v>3.42488026618958</v>
+        <v>3.424880027771</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G978" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G984" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.5</v>
       </c>
       <c r="G985" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G987" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G990" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G996" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G999" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506368637085</v>
+        <v>3.34506344795227</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506368637085</v>
+        <v>3.34506344795227</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213677406311</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213677406311</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.42488026618958</v>
+        <v>3.424880027771</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231900215149</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.42488026618958</v>
+        <v>3.424880027771</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.42488026618958</v>
+        <v>3.424880027771</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.42488026618958</v>
+        <v>3.424880027771</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213677406311</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.49744176864624</v>
+        <v>3.49744153022766</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.46116089820862</v>
+        <v>3.46116065979004</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.7500627040863</v>
+        <v>2.75006294250488</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.25</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.25</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.42488026618958</v>
+        <v>3.424880027771</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213677406311</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.03439283370972</v>
+        <v>4.03439331054688</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.03439283370972</v>
+        <v>4.03439331054688</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.03439283370972</v>
+        <v>4.03439331054688</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.77317309379578</v>
+        <v>3.7731728553772</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.49744176864624</v>
+        <v>3.49744153022766</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.59902667999268</v>
+        <v>3.59902691841125</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.04030704498291</v>
+        <v>3.04030728340149</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.5</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213677406311</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>4.5</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>4.5</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.25073385238647</v>
+        <v>3.25073409080505</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231900215149</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231900215149</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.42488026618958</v>
+        <v>3.424880027771</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231900215149</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231900215149</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.25073385238647</v>
+        <v>3.25073409080505</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.25073385238647</v>
+        <v>3.25073409080505</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.25</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.25</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.01128268241882</v>
+        <v>3.01128244400024</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.01128268241882</v>
+        <v>3.01128244400024</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.01128268241882</v>
+        <v>3.01128244400024</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.01128268241882</v>
+        <v>3.01128244400024</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.91695308685303</v>
+        <v>2.91695332527161</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.01128268241882</v>
+        <v>3.01128244400024</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.04030704498291</v>
+        <v>3.04030728340149</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.04030704498291</v>
+        <v>3.04030728340149</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.5</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.25073385238647</v>
+        <v>3.25073409080505</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.25073385238647</v>
+        <v>3.25073409080505</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.25073385238647</v>
+        <v>3.25073409080505</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.25073385238647</v>
+        <v>3.25073409080505</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.5</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.35957551002502</v>
+        <v>3.3595757484436</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231900215149</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.62079501152039</v>
+        <v>3.62079477310181</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.53372192382812</v>
+        <v>3.53372168540955</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.77317309379578</v>
+        <v>3.7731728553772</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.77317309379578</v>
+        <v>3.7731728553772</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.59902667999268</v>
+        <v>3.59902691841125</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.62079501152039</v>
+        <v>3.62079477310181</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.5</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.77317309379578</v>
+        <v>3.7731728553772</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.77317309379578</v>
+        <v>3.7731728553772</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.62079501152039</v>
+        <v>3.62079477310181</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.46116089820862</v>
+        <v>3.46116065979004</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213677406311</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>4.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>4.25</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>4.25</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.59902667999268</v>
+        <v>3.59902691841125</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.59902667999268</v>
+        <v>3.59902691841125</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1697" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1698" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1699" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1701" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>4.5</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1726" t="n">
-        <v>3.25073385238647</v>
+        <v>3.25073409080505</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>4.25</v>
       </c>
       <c r="G1728" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>4.25</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>4.25</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.82987999916077</v>
+        <v>2.82987976074219</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>3.75</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.02579474449158</v>
+        <v>3.02579498291016</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.04030704498291</v>
+        <v>3.04030728340149</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>4.25</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>4.25</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>4.25</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.08384346961975</v>
+        <v>3.08384370803833</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.99677038192749</v>
+        <v>2.99677014350891</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.77317309379578</v>
+        <v>3.7731728553772</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.03439283370972</v>
+        <v>4.03439331054688</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.97634410858154</v>
+        <v>3.97634434700012</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.25207614898682</v>
+        <v>4.25207662582397</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.23756408691406</v>
+        <v>4.2375636100769</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.23756408691406</v>
+        <v>4.2375636100769</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1853" t="n">
-        <v>4.57134485244751</v>
+        <v>4.57134437561035</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1856" t="n">
-        <v>4.36817359924316</v>
+        <v>4.36817407608032</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>4.44073486328125</v>
+        <v>4.44073438644409</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1861" t="n">
-        <v>4.28110027313232</v>
+        <v>4.28110074996948</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1874" t="n">
-        <v>4.03439283370972</v>
+        <v>4.03439331054688</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1876" t="n">
-        <v>4.03439283370972</v>
+        <v>4.03439331054688</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.03439283370972</v>
+        <v>4.03439331054688</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.03439283370972</v>
+        <v>4.03439331054688</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1890" t="n">
-        <v>4.03439283370972</v>
+        <v>4.03439331054688</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1893" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1894" t="n">
-        <v>4.28110027313232</v>
+        <v>4.28110074996948</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1897" t="n">
-        <v>4.44073486328125</v>
+        <v>4.44073438644409</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.45524740219116</v>
+        <v>4.455246925354</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.57134485244751</v>
+        <v>4.57134437561035</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.542320728302</v>
+        <v>4.54232025146484</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1918" t="n">
-        <v>4.36817359924316</v>
+        <v>4.36817407608032</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1941" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1942" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1943" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1944" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1945" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1946" t="n">
-        <v>4.70195436477661</v>
+        <v>4.70195484161377</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1947" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1951" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1970" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1972" t="n">
-        <v>4.70195436477661</v>
+        <v>4.70195484161377</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1973" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1977" t="n">
-        <v>4.70195436477661</v>
+        <v>4.70195484161377</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1993" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.70195436477661</v>
+        <v>4.70195484161377</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.70195436477661</v>
+        <v>4.70195484161377</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.70195436477661</v>
+        <v>4.70195484161377</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.70195436477661</v>
+        <v>4.70195484161377</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.70195436477661</v>
+        <v>4.70195484161377</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.542320728302</v>
+        <v>4.54232025146484</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.36817359924316</v>
+        <v>4.36817407608032</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.22305202484131</v>
+        <v>4.22305154800415</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.22305202484131</v>
+        <v>4.22305154800415</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.97634410858154</v>
+        <v>3.97634434700012</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2051" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2052" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2058" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2059" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2060" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2063" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2064" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2065" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2066" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2068" t="n">
-        <v>3.77317309379578</v>
+        <v>3.7731728553772</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2076" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2078" t="n">
-        <v>3.77317309379578</v>
+        <v>3.7731728553772</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2080" t="n">
-        <v>3.77317309379578</v>
+        <v>3.7731728553772</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.1069540977478</v>
+        <v>4.10695362091064</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2091" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2092" t="n">
-        <v>4.1069540977478</v>
+        <v>4.10695362091064</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2093" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G2095" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2097" t="n">
-        <v>4.45524740219116</v>
+        <v>4.455246925354</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2098" t="n">
-        <v>4.45524740219116</v>
+        <v>4.455246925354</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2114" t="n">
-        <v>5.0212230682373</v>
+        <v>5.02122259140015</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2115" t="n">
-        <v>5.23890590667725</v>
+        <v>5.23890542984009</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2117" t="n">
-        <v>5.32597970962524</v>
+        <v>5.32597923278809</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2118" t="n">
-        <v>5.36951589584351</v>
+        <v>5.36951637268066</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2120" t="n">
-        <v>5.32597970962524</v>
+        <v>5.32597923278809</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2121" t="n">
-        <v>5.36951589584351</v>
+        <v>5.36951637268066</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>2.00999999046326</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>124091</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.81500005722046</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G5" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G10" t="n">
-        <v>2.13909888267517</v>
+        <v>2.13909912109375</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G11" t="n">
-        <v>2.13184285163879</v>
+        <v>2.13184309005737</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G12" t="n">
-        <v>2.13184285163879</v>
+        <v>2.13184309005737</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08540391921997</v>
+        <v>2.08540368080139</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G28" t="n">
-        <v>2.09120869636536</v>
+        <v>2.09120845794678</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G46" t="n">
-        <v>2.24648928642273</v>
+        <v>2.24648904800415</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G51" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G52" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G53" t="n">
-        <v>2.2551965713501</v>
+        <v>2.25519680976868</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G54" t="n">
-        <v>2.2479407787323</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G55" t="n">
-        <v>2.2479407787323</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G56" t="n">
-        <v>2.2479407787323</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G57" t="n">
-        <v>2.2479407787323</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G60" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G61" t="n">
-        <v>2.22907495498657</v>
+        <v>2.22907471656799</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>1.71824502944946</v>
+        <v>1.71824514865875</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G73" t="n">
-        <v>1.76903784275055</v>
+        <v>1.76903772354126</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G74" t="n">
-        <v>1.76758670806885</v>
+        <v>1.76758658885956</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G75" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G76" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G77" t="n">
-        <v>1.72259867191315</v>
+        <v>1.72259879112244</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G78" t="n">
-        <v>1.72259867191315</v>
+        <v>1.72259879112244</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.5</v>
       </c>
       <c r="G85" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G91" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G92" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G93" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69937920570374</v>
+        <v>1.69937932491302</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G96" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G98" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G102" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G103" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G105" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G109" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G126" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G127" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G128" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G129" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G131" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>1.34600698947906</v>
+        <v>1.34600710868835</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G147" t="n">
-        <v>1.39317154884338</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G148" t="n">
-        <v>1.39317154884338</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G159" t="n">
-        <v>1.39317154884338</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G165" t="n">
-        <v>1.27925097942352</v>
+        <v>1.27925086021423</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G175" t="n">
-        <v>1.36269617080688</v>
+        <v>1.3626960515976</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G176" t="n">
-        <v>1.36269617080688</v>
+        <v>1.3626960515976</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G178" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G180" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G182" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G183" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G185" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G186" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G187" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G188" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22628128528595</v>
+        <v>1.22628140449524</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.75</v>
       </c>
       <c r="G203" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G207" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G210" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G211" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G231" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G232" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G239" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G240" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G249" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.75</v>
       </c>
       <c r="G250" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.75</v>
       </c>
       <c r="G251" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.75</v>
       </c>
       <c r="G252" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.75</v>
       </c>
       <c r="G254" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.75</v>
       </c>
       <c r="G255" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.75</v>
       </c>
       <c r="G257" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.75</v>
       </c>
       <c r="G258" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.75</v>
       </c>
       <c r="G259" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.75</v>
       </c>
       <c r="G262" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.75</v>
       </c>
       <c r="G263" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.75</v>
       </c>
       <c r="G264" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.75</v>
       </c>
       <c r="G265" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.75</v>
       </c>
       <c r="G266" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.75</v>
       </c>
       <c r="G267" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G284" t="n">
-        <v>1.25748252868652</v>
+        <v>1.25748264789581</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G294" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G295" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G296" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G303" t="n">
-        <v>1.24877524375916</v>
+        <v>1.24877512454987</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G308" t="n">
-        <v>1.34890937805176</v>
+        <v>1.34890949726105</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G309" t="n">
-        <v>1.34890937805176</v>
+        <v>1.34890949726105</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G313" t="n">
-        <v>1.48895227909088</v>
+        <v>1.48895215988159</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G315" t="n">
-        <v>1.42074477672577</v>
+        <v>1.42074489593506</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G316" t="n">
-        <v>1.42074477672577</v>
+        <v>1.42074489593506</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>1.42219603061676</v>
+        <v>1.42219614982605</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G320" t="n">
-        <v>1.70083045959473</v>
+        <v>1.70083057880402</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G338" t="n">
-        <v>1.42945218086243</v>
+        <v>1.42945230007172</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40405583381653</v>
+        <v>1.40405571460724</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>1.42945218086243</v>
+        <v>1.42945230007172</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G343" t="n">
-        <v>1.44178748130798</v>
+        <v>1.44178760051727</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>1.43235456943512</v>
+        <v>1.43235468864441</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G356" t="n">
-        <v>1.43453133106232</v>
+        <v>1.43453145027161</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>1.49330592155457</v>
+        <v>1.49330604076385</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.49475705623627</v>
+        <v>1.49475717544556</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G376" t="n">
-        <v>1.59344029426575</v>
+        <v>1.59344017505646</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G378" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G385" t="n">
-        <v>2.16522121429443</v>
+        <v>2.16522097587585</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>2.0999162197113</v>
+        <v>2.09991598129272</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.0331597328186</v>
+        <v>2.03315997123718</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G391" t="n">
-        <v>1.93447697162628</v>
+        <v>1.93447685241699</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318425655365</v>
+        <v>1.94318401813507</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G395" t="n">
-        <v>1.86917209625244</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G397" t="n">
-        <v>2.07234287261963</v>
+        <v>2.07234263420105</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G398" t="n">
-        <v>2.01574516296387</v>
+        <v>2.01574540138245</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.86191582679749</v>
+        <v>1.86191606521606</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G403" t="n">
-        <v>1.78645253181458</v>
+        <v>1.786452293396</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>1.78935503959656</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G412" t="n">
-        <v>1.78935503959656</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G419" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G424" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837952136993</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G428" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G429" t="n">
-        <v>1.94898927211761</v>
+        <v>1.94898903369904</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G437" t="n">
-        <v>1.81112337112427</v>
+        <v>1.81112313270569</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G438" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>1.83724510669708</v>
+        <v>1.83724534511566</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93302583694458</v>
+        <v>1.93302571773529</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G449" t="n">
-        <v>1.86917209625244</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>1.89964771270752</v>
+        <v>1.89964759349823</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G451" t="n">
-        <v>1.86917209625244</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>1.88078165054321</v>
+        <v>1.88078188896179</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G476" t="n">
-        <v>1.87497711181641</v>
+        <v>1.87497687339783</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G477" t="n">
-        <v>1.82273292541504</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G478" t="n">
-        <v>1.82273292541504</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>1.82273292541504</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>1.72114741802216</v>
+        <v>1.72114753723145</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G482" t="n">
-        <v>1.80822086334229</v>
+        <v>1.80822062492371</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G487" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837952136993</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.5</v>
       </c>
       <c r="G488" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.5</v>
       </c>
       <c r="G489" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.5</v>
       </c>
       <c r="G490" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G493" t="n">
-        <v>1.84159874916077</v>
+        <v>1.84159898757935</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G494" t="n">
-        <v>1.88078165054321</v>
+        <v>1.88078188896179</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.5</v>
       </c>
       <c r="G497" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.5</v>
       </c>
       <c r="G508" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.5</v>
       </c>
       <c r="G519" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G525" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G545" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G549" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G556" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G558" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G562" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G564" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G571" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G573" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G574" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G575" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G579" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G580" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G591" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G601" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G609" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G653" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G655" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G658" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G660" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G662" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G677" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G682" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G684" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G694" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G706" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G707" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G708" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G713" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G729" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.5</v>
       </c>
       <c r="G737" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G741" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.5</v>
       </c>
       <c r="G747" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.5</v>
       </c>
       <c r="G748" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.5</v>
       </c>
       <c r="G749" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G767" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G780" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>1.96640372276306</v>
+        <v>1.96640396118164</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>2.01719665527344</v>
+        <v>2.01719641685486</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G789" t="n">
-        <v>2.06073307991028</v>
+        <v>2.0607328414917</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G790" t="n">
-        <v>2.01719665527344</v>
+        <v>2.01719641685486</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G800" t="n">
-        <v>2.01719665527344</v>
+        <v>2.01719641685486</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.05347681045532</v>
+        <v>2.0534770488739</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G804" t="n">
-        <v>2.11152577400208</v>
+        <v>2.11152601242065</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G807" t="n">
-        <v>2.11152577400208</v>
+        <v>2.11152601242065</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G813" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G825" t="n">
-        <v>2.28567218780518</v>
+        <v>2.28567242622375</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G830" t="n">
-        <v>2.25664782524109</v>
+        <v>2.25664806365967</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G833" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G835" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G854" t="n">
-        <v>2.25664782524109</v>
+        <v>2.25664806365967</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G856" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G867" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G869" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G886" t="n">
-        <v>2.62670922279358</v>
+        <v>2.626708984375</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G889" t="n">
-        <v>2.78634309768677</v>
+        <v>2.78634333610535</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>2.91695332527161</v>
+        <v>2.91695308685303</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G898" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G902" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G905" t="n">
-        <v>2.91695332527161</v>
+        <v>2.91695308685303</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.69201397895813</v>
+        <v>2.69201421737671</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G911" t="n">
-        <v>2.74280667304993</v>
+        <v>2.74280691146851</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G912" t="n">
-        <v>2.78634309768677</v>
+        <v>2.78634333610535</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>2.69201397895813</v>
+        <v>2.69201421737671</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G919" t="n">
-        <v>2.69927000999451</v>
+        <v>2.69927024841309</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G920" t="n">
-        <v>2.670245885849</v>
+        <v>2.67024564743042</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.25</v>
       </c>
       <c r="G927" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G941" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G945" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.25</v>
       </c>
       <c r="G965" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G973" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G977" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G987" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G990" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G994" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G996" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.75006294250488</v>
+        <v>2.7500627040863</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.25</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.25</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.38134360313416</v>
+        <v>3.38134384155273</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>5</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>5</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>5</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>5</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.04030728340149</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.25</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.25</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.91695332527161</v>
+        <v>2.91695308685303</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.04030728340149</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.04030728340149</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.62079477310181</v>
+        <v>3.62079524993896</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>5</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.53372168540955</v>
+        <v>3.53372192382812</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>5</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>5</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>5</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.62079477310181</v>
+        <v>3.62079524993896</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.50469732284546</v>
+        <v>3.50469756126404</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>5</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>5</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.62079477310181</v>
+        <v>3.62079524993896</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>5</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>5</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.38134360313416</v>
+        <v>3.38134384155273</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>4.25</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>4.25</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.49018526077271</v>
+        <v>3.49018549919128</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1664" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>5</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>5</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1713" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1726" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>4.25</v>
       </c>
       <c r="G1728" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>4.25</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>4.25</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.80811166763306</v>
+        <v>2.80811142921448</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.80811166763306</v>
+        <v>2.80811142921448</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.80811166763306</v>
+        <v>2.80811142921448</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.04030728340149</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>4.25</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>4.25</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>4.25</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.99677014350891</v>
+        <v>2.99677038192749</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1818" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1822" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1824" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.2375636100769</v>
+        <v>4.23756408691406</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.2375636100769</v>
+        <v>4.23756408691406</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.51329565048218</v>
+        <v>4.51329612731934</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1853" t="n">
-        <v>4.57134437561035</v>
+        <v>4.57134485244751</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1856" t="n">
-        <v>4.36817407608032</v>
+        <v>4.36817359924316</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1874" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1876" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1890" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.455246925354</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.57134437561035</v>
+        <v>4.57134485244751</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1918" t="n">
-        <v>4.36817407608032</v>
+        <v>4.36817359924316</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1946" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1962" t="n">
-        <v>4.81805181503296</v>
+        <v>4.81805229187012</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1963" t="n">
-        <v>4.81805181503296</v>
+        <v>4.81805229187012</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1972" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1977" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1998" t="n">
-        <v>4.81805181503296</v>
+        <v>4.81805229187012</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.51329565048218</v>
+        <v>4.51329612731934</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.36817407608032</v>
+        <v>4.36817359924316</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.22305154800415</v>
+        <v>4.22305202484131</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.22305154800415</v>
+        <v>4.22305202484131</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2051" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2052" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2068" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2070" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2071" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2072" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2073" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2074" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2078" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2080" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.10695362091064</v>
+        <v>4.1069540977478</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2092" t="n">
-        <v>4.10695362091064</v>
+        <v>4.1069540977478</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2097" t="n">
-        <v>4.455246925354</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2098" t="n">
-        <v>4.455246925354</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2100" t="n">
-        <v>4.51329565048218</v>
+        <v>4.51329612731934</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2115" t="n">
-        <v>5.23890542984009</v>
+        <v>5.23890590667725</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2118" t="n">
-        <v>5.36951637268066</v>
+        <v>5.36951589584351</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2119" t="n">
-        <v>5.340491771698</v>
+        <v>5.34049129486084</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2121" t="n">
-        <v>5.36951637268066</v>
+        <v>5.36951589584351</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2122" t="n">
-        <v>5.71780872344971</v>
+        <v>5.71780920028687</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>1.83000004291534</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>63356</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.73500001430511</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1.8400000333786</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -525,7 +525,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17537927627563</v>
+        <v>2.17537951469421</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G7" t="n">
-        <v>2.17537927627563</v>
+        <v>2.17537951469421</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G8" t="n">
-        <v>2.17537927627563</v>
+        <v>2.17537951469421</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G10" t="n">
-        <v>2.13909888267517</v>
+        <v>2.13909912109375</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G11" t="n">
-        <v>2.13184285163879</v>
+        <v>2.13184309005737</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G12" t="n">
-        <v>2.13184285163879</v>
+        <v>2.13184309005737</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2044038772583</v>
+        <v>2.20440411567688</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14345240592957</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14345240592957</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14345240592957</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14345240592957</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08540391921997</v>
+        <v>2.08540368080139</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G28" t="n">
-        <v>2.09120869636536</v>
+        <v>2.09120845794678</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16231846809387</v>
+        <v>2.16231870651245</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G37" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G38" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G44" t="n">
-        <v>2.2044038772583</v>
+        <v>2.20440411567688</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G46" t="n">
-        <v>2.24648928642273</v>
+        <v>2.24648904800415</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>2.17247724533081</v>
+        <v>2.17247700691223</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G66" t="n">
-        <v>2.24503827095032</v>
+        <v>2.24503803253174</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G67" t="n">
-        <v>2.24503827095032</v>
+        <v>2.24503803253174</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G68" t="n">
-        <v>2.17973327636719</v>
+        <v>2.17973303794861</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G69" t="n">
-        <v>2.23052597045898</v>
+        <v>2.23052573204041</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>1.71824491024017</v>
+        <v>1.71824514865875</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G73" t="n">
-        <v>1.76903784275055</v>
+        <v>1.76903772354126</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G77" t="n">
-        <v>1.72259867191315</v>
+        <v>1.72259879112244</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G78" t="n">
-        <v>1.72259867191315</v>
+        <v>1.72259879112244</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.5</v>
       </c>
       <c r="G85" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G86" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G89" t="n">
-        <v>1.73275721073151</v>
+        <v>1.7327573299408</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69937920570374</v>
+        <v>1.69937932491302</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G96" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G98" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G102" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G103" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G113" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>1.40768384933472</v>
+        <v>1.40768396854401</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G160" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G161" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>1.25095212459564</v>
+        <v>1.25095200538635</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G172" t="n">
-        <v>1.33875095844269</v>
+        <v>1.3387508392334</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G173" t="n">
-        <v>1.33947658538818</v>
+        <v>1.33947646617889</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G175" t="n">
-        <v>1.36269593238831</v>
+        <v>1.3626960515976</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G176" t="n">
-        <v>1.36269593238831</v>
+        <v>1.3626960515976</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G178" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G180" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G182" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G183" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G185" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G186" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G187" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G188" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.32061076164246</v>
+        <v>1.32061064243317</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G193" t="n">
-        <v>1.24224472045898</v>
+        <v>1.24224483966827</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G194" t="n">
-        <v>1.24224472045898</v>
+        <v>1.24224483966827</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22628128528595</v>
+        <v>1.22628140449524</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.75</v>
       </c>
       <c r="G203" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G212" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>1.25530576705933</v>
+        <v>1.25530564785004</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G231" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G232" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G249" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.75</v>
       </c>
       <c r="G250" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.75</v>
       </c>
       <c r="G251" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.75</v>
       </c>
       <c r="G252" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.75</v>
       </c>
       <c r="G254" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.75</v>
       </c>
       <c r="G255" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.75</v>
       </c>
       <c r="G257" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.75</v>
       </c>
       <c r="G258" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.75</v>
       </c>
       <c r="G259" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G260" t="n">
-        <v>1.25240337848663</v>
+        <v>1.25240325927734</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.75</v>
       </c>
       <c r="G262" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.75</v>
       </c>
       <c r="G263" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.75</v>
       </c>
       <c r="G264" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.75</v>
       </c>
       <c r="G265" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.75</v>
       </c>
       <c r="G266" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.75</v>
       </c>
       <c r="G267" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G273" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G277" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G278" t="n">
-        <v>1.46718406677246</v>
+        <v>1.46718394756317</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>1.40768384933472</v>
+        <v>1.40768396854401</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G281" t="n">
-        <v>1.42727530002594</v>
+        <v>1.42727541923523</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32133615016937</v>
+        <v>1.32133626937866</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G284" t="n">
-        <v>1.25748252868652</v>
+        <v>1.25748264789581</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>1.20741546154022</v>
+        <v>1.20741558074951</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G290" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G291" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G292" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.17186057567596</v>
+        <v>1.17186045646667</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G303" t="n">
-        <v>1.24877524375916</v>
+        <v>1.24877512454987</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G304" t="n">
-        <v>1.24950075149536</v>
+        <v>1.24950087070465</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G306" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G313" t="n">
-        <v>1.48895227909088</v>
+        <v>1.48895215988159</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G315" t="n">
-        <v>1.42074477672577</v>
+        <v>1.42074489593506</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G316" t="n">
-        <v>1.42074477672577</v>
+        <v>1.42074489593506</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>1.4845986366272</v>
+        <v>1.48459851741791</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G320" t="n">
-        <v>1.70083045959473</v>
+        <v>1.70083057880402</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G322" t="n">
-        <v>1.67035472393036</v>
+        <v>1.67035484313965</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G329" t="n">
-        <v>1.51072061061859</v>
+        <v>1.5107204914093</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G330" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G332" t="n">
-        <v>1.40478134155273</v>
+        <v>1.40478146076202</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G335" t="n">
-        <v>1.43815946578979</v>
+        <v>1.43815958499908</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G336" t="n">
-        <v>1.40260457992554</v>
+        <v>1.40260446071625</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>1.37430584430695</v>
+        <v>1.37430596351624</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G340" t="n">
-        <v>1.41494011878967</v>
+        <v>1.41493988037109</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40405583381653</v>
+        <v>1.40405571460724</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>1.40768384933472</v>
+        <v>1.40768396854401</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G345" t="n">
-        <v>1.41494011878967</v>
+        <v>1.41493988037109</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G347" t="n">
-        <v>1.47298872470856</v>
+        <v>1.47298884391785</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5586109161377</v>
+        <v>1.55861079692841</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G351" t="n">
-        <v>1.41566550731659</v>
+        <v>1.41566562652588</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G355" t="n">
-        <v>1.47008633613586</v>
+        <v>1.47008645534515</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.49475705623627</v>
+        <v>1.49475717544556</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G367" t="n">
-        <v>1.54554998874664</v>
+        <v>1.54554986953735</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.58473289012909</v>
+        <v>1.5847327709198</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G378" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.77919626235962</v>
+        <v>1.77919614315033</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G384" t="n">
-        <v>2.10281872749329</v>
+        <v>2.10281848907471</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G388" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G389" t="n">
-        <v>2.00558686256409</v>
+        <v>2.00558662414551</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318413734436</v>
+        <v>1.94318401813507</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G394" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G396" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G397" t="n">
-        <v>2.07234287261963</v>
+        <v>2.07234263420105</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G398" t="n">
-        <v>2.01574516296387</v>
+        <v>2.01574540138245</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G401" t="n">
-        <v>1.89239156246185</v>
+        <v>1.89239168167114</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.86191594600677</v>
+        <v>1.86191606521606</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563555240631</v>
+        <v>1.82563543319702</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G407" t="n">
-        <v>1.7574280500412</v>
+        <v>1.75742793083191</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G409" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G412" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G418" t="n">
-        <v>1.6587450504303</v>
+        <v>1.65874493122101</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G419" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G429" t="n">
-        <v>1.94898915290833</v>
+        <v>1.94898903369904</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>1.85175728797913</v>
+        <v>1.85175740718842</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>1.85756230354309</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G437" t="n">
-        <v>1.81112325191498</v>
+        <v>1.81112313270569</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>1.85030603408813</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>1.83724522590637</v>
+        <v>1.83724534511566</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G441" t="n">
-        <v>1.84595227241516</v>
+        <v>1.84595239162445</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G443" t="n">
-        <v>1.87352561950684</v>
+        <v>1.87352573871613</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G446" t="n">
-        <v>2.01139187812805</v>
+        <v>2.01139163970947</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G447" t="n">
-        <v>1.9780136346817</v>
+        <v>1.97801375389099</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>1.85030603408813</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207424640656</v>
+        <v>1.87207436561584</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>1.85756230354309</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G459" t="n">
-        <v>1.8851352930069</v>
+        <v>1.88513553142548</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G461" t="n">
-        <v>1.87787926197052</v>
+        <v>1.87787938117981</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>1.92141604423523</v>
+        <v>1.92141592502594</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G463" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G464" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G465" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G466" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>1.90835511684418</v>
+        <v>1.90835499763489</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>1.92286717891693</v>
+        <v>1.92286729812622</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G470" t="n">
-        <v>1.90255010128021</v>
+        <v>1.90254998207092</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G471" t="n">
-        <v>1.90400123596191</v>
+        <v>1.9040013551712</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>1.89094018936157</v>
+        <v>1.89094030857086</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G473" t="n">
-        <v>1.90255010128021</v>
+        <v>1.90254998207092</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>1.88078165054321</v>
+        <v>1.88078188896179</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G475" t="n">
-        <v>1.90980637073517</v>
+        <v>1.90980613231659</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G476" t="n">
-        <v>1.87497711181641</v>
+        <v>1.87497687339783</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G482" t="n">
-        <v>1.808220744133</v>
+        <v>1.80822062492371</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G484" t="n">
-        <v>1.80096483230591</v>
+        <v>1.80096471309662</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.5</v>
       </c>
       <c r="G488" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.5</v>
       </c>
       <c r="G489" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.5</v>
       </c>
       <c r="G490" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G491" t="n">
-        <v>1.83869636058807</v>
+        <v>1.83869624137878</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G492" t="n">
-        <v>1.85175728797913</v>
+        <v>1.85175740718842</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G493" t="n">
-        <v>1.84159886837006</v>
+        <v>1.84159898757935</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G494" t="n">
-        <v>1.88078165054321</v>
+        <v>1.88078188896179</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>1.82853770256042</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.5</v>
       </c>
       <c r="G497" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G501" t="n">
-        <v>1.88368427753448</v>
+        <v>1.8836841583252</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G502" t="n">
-        <v>1.87062346935272</v>
+        <v>1.87062323093414</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.5</v>
       </c>
       <c r="G508" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G509" t="n">
-        <v>1.80096483230591</v>
+        <v>1.80096471309662</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>1.82853770256042</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>1.85030603408813</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.5</v>
       </c>
       <c r="G519" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G520" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G523" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G525" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G526" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>1.85756230354309</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>1.92286717891693</v>
+        <v>1.92286729812622</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.75</v>
       </c>
       <c r="G529" t="n">
-        <v>1.99542808532715</v>
+        <v>1.99542820453644</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G533" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G537" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G538" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G540" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G546" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G549" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G552" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G554" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G556" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G559" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G561" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G562" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G564" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G568" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G573" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G593" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G601" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G605" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>1.57457435131073</v>
+        <v>1.57457423210144</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>1.57457435131073</v>
+        <v>1.57457423210144</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G614" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>1.4875009059906</v>
+        <v>1.48750102519989</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>1.54554998874664</v>
+        <v>1.54554986953735</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G618" t="n">
-        <v>1.54554998874664</v>
+        <v>1.54554986953735</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G623" t="n">
-        <v>1.55280590057373</v>
+        <v>1.55280601978302</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G624" t="n">
-        <v>1.55280590057373</v>
+        <v>1.55280601978302</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G629" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G630" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G631" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G653" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G655" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G658" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G660" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G668" t="n">
-        <v>1.54554998874664</v>
+        <v>1.54554986953735</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G677" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G679" t="n">
-        <v>1.61085486412048</v>
+        <v>1.61085474491119</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G680" t="n">
-        <v>1.61085486412048</v>
+        <v>1.61085474491119</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G696" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G706" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G707" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G712" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G713" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G716" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G719" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G720" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G721" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G722" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G723" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G726" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G729" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G735" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G736" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.5</v>
       </c>
       <c r="G737" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G739" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G740" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G741" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G743" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>1.82853770256042</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.5</v>
       </c>
       <c r="G747" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.5</v>
       </c>
       <c r="G748" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.5</v>
       </c>
       <c r="G749" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G753" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G754" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G755" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G756" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G758" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G765" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G768" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>1.82853770256042</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G775" t="n">
-        <v>1.82853770256042</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>1.85756230354309</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G778" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90835511684418</v>
+        <v>1.90835499763489</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.75</v>
       </c>
       <c r="G793" t="n">
-        <v>1.99542808532715</v>
+        <v>1.99542820453644</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365987300873</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.75</v>
       </c>
       <c r="G796" t="n">
-        <v>1.99542808532715</v>
+        <v>1.99542820453644</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G798" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365987300873</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.05347681045532</v>
+        <v>2.0534770488739</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G805" t="n">
-        <v>2.13329434394836</v>
+        <v>2.13329410552979</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>2.13329434394836</v>
+        <v>2.13329410552979</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G811" t="n">
-        <v>2.09701371192932</v>
+        <v>2.09701347351074</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G812" t="n">
-        <v>2.15506267547607</v>
+        <v>2.1550624370575</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G814" t="n">
-        <v>2.16957449913025</v>
+        <v>2.16957473754883</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G815" t="n">
-        <v>2.16957449913025</v>
+        <v>2.16957473754883</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G824" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G826" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G829" t="n">
-        <v>2.30744075775146</v>
+        <v>2.30744051933289</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G830" t="n">
-        <v>2.25664782524109</v>
+        <v>2.25664806365967</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G834" t="n">
-        <v>2.34372115135193</v>
+        <v>2.34372091293335</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>2.38725781440735</v>
+        <v>2.38725757598877</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G844" t="n">
-        <v>2.34372115135193</v>
+        <v>2.34372091293335</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G846" t="n">
-        <v>2.30744075775146</v>
+        <v>2.30744051933289</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>2.3219530582428</v>
+        <v>2.32195281982422</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G854" t="n">
-        <v>2.25664782524109</v>
+        <v>2.25664806365967</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G856" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.40176963806152</v>
+        <v>2.4017698764801</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>2.38725781440735</v>
+        <v>2.38725757598877</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.38725781440735</v>
+        <v>2.38725757598877</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G883" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>2.86616063117981</v>
+        <v>2.86616039276123</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G890" t="n">
-        <v>2.85164856910706</v>
+        <v>2.85164833068848</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>2.91695332527161</v>
+        <v>2.91695308685303</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G896" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G898" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G899" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G905" t="n">
-        <v>2.91695332527161</v>
+        <v>2.91695308685303</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G909" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G911" t="n">
-        <v>2.74280667304993</v>
+        <v>2.74280691146851</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G913" t="n">
-        <v>2.85164856910706</v>
+        <v>2.85164833068848</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.75</v>
       </c>
       <c r="G915" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G916" t="n">
-        <v>2.67750191688538</v>
+        <v>2.6775016784668</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G919" t="n">
-        <v>2.69927000999451</v>
+        <v>2.69927024841309</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G920" t="n">
-        <v>2.670245885849</v>
+        <v>2.67024564743042</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.75</v>
       </c>
       <c r="G921" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.25</v>
       </c>
       <c r="G927" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G930" t="n">
-        <v>2.94597744941711</v>
+        <v>2.94597768783569</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G935" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G939" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>2.82988023757935</v>
+        <v>2.82987976074219</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G949" t="n">
-        <v>2.92420959472656</v>
+        <v>2.92420935630798</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G950" t="n">
-        <v>2.92420959472656</v>
+        <v>2.92420935630798</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9750018119812</v>
+        <v>2.97500205039978</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G959" t="n">
-        <v>2.94597744941711</v>
+        <v>2.94597768783569</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>2.9750018119812</v>
+        <v>2.97500205039978</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G962" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.25</v>
       </c>
       <c r="G965" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.09109997749329</v>
+        <v>3.09109973907471</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G977" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G978" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G980" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G983" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G984" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G987" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G990" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G993" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G994" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G996" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G997" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G998" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G999" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506320953369</v>
+        <v>3.34506344795227</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506320953369</v>
+        <v>3.34506344795227</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.49744176864624</v>
+        <v>3.49744153022766</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.46116089820862</v>
+        <v>3.46116065979004</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.75006294250488</v>
+        <v>2.7500627040863</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.81536769866943</v>
+        <v>2.81536793708801</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>4.25</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.25</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>4.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>5</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>5.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71512460708618</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>5.5</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>5.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>5.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.49744176864624</v>
+        <v>3.49744153022766</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.54823398590088</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>5</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>5</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>5</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.56274652481079</v>
+        <v>3.56274628639221</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.45390486717224</v>
+        <v>3.45390510559082</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>4.75</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.25</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.25</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.91695332527161</v>
+        <v>2.91695308685303</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.62079501152039</v>
+        <v>3.62079524993896</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>5</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>5</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>5</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.71512460708618</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>5</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.62079501152039</v>
+        <v>3.62079524993896</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.50469732284546</v>
+        <v>3.50469756126404</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.75</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1572" t="n">
-        <v>3.09109997749329</v>
+        <v>3.09109973907471</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>4.75</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.45390486717224</v>
+        <v>3.45390510559082</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.71512460708618</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>5</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.71512460708618</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>5</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.62079501152039</v>
+        <v>3.62079524993896</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.46116089820862</v>
+        <v>3.46116065979004</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.52646565437317</v>
+        <v>3.52646589279175</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.54823398590088</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>5</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>5</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.54823398590088</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.52646565437317</v>
+        <v>3.52646589279175</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>4.25</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>4.25</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.45390486717224</v>
+        <v>3.45390510559082</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.49018526077271</v>
+        <v>3.49018549919128</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1664" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1668" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.56274652481079</v>
+        <v>3.56274628639221</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>5</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>5</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.54823398590088</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1683" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.57000255584717</v>
+        <v>3.57000231742859</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.57000255584717</v>
+        <v>3.57000231742859</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1713" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>4.25</v>
       </c>
       <c r="G1728" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>4.25</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>4.25</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.81536769866943</v>
+        <v>2.81536793708801</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.80811166763306</v>
+        <v>2.80811142921448</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.82988023757935</v>
+        <v>2.82987976074219</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.80811166763306</v>
+        <v>2.80811142921448</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.80811166763306</v>
+        <v>2.80811142921448</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.77908706665039</v>
+        <v>2.77908730506897</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>3.75</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>4.25</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1775" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>4.25</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>4.25</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>5.5</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>5.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1819" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.97634410858154</v>
+        <v>3.97634434700012</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.25207614898682</v>
+        <v>4.25207662582397</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.26658868789673</v>
+        <v>4.26658821105957</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.26658868789673</v>
+        <v>4.26658821105957</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.51329565048218</v>
+        <v>4.51329612731934</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.26658868789673</v>
+        <v>4.26658821105957</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>5.5</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1893" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1896" t="n">
-        <v>4.32463693618774</v>
+        <v>4.3246374130249</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1900" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1909" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1912" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1920" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1926" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1928" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1929" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1930" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1931" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1932" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1933" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1934" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1935" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1940" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1941" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1942" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1943" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1944" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1945" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1956" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1959" t="n">
-        <v>4.80353927612305</v>
+        <v>4.80353975296021</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1960" t="n">
-        <v>4.83256387710571</v>
+        <v>4.83256435394287</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1961" t="n">
-        <v>4.80353927612305</v>
+        <v>4.80353975296021</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1962" t="n">
-        <v>4.81805181503296</v>
+        <v>4.81805229187012</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1963" t="n">
-        <v>4.81805181503296</v>
+        <v>4.81805229187012</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1964" t="n">
-        <v>4.83256387710571</v>
+        <v>4.83256435394287</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1970" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1973" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1980" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1986" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1990" t="n">
-        <v>4.80353927612305</v>
+        <v>4.80353975296021</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1998" t="n">
-        <v>4.81805181503296</v>
+        <v>4.81805229187012</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.51329565048218</v>
+        <v>4.51329612731934</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.26658868789673</v>
+        <v>4.26658821105957</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>5.5</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.97634410858154</v>
+        <v>3.97634434700012</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2051" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2052" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2053" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2054" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2055" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2056" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2057" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2060" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2061" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2067" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2068" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2076" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2078" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2080" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.10695362091064</v>
+        <v>4.1069540977478</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2092" t="n">
-        <v>4.10695362091064</v>
+        <v>4.1069540977478</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2093" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2100" t="n">
-        <v>4.51329565048218</v>
+        <v>4.51329612731934</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2107" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2108" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2110" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2114" t="n">
-        <v>5.0212230682373</v>
+        <v>5.02122259140015</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2117" t="n">
-        <v>5.32597970962524</v>
+        <v>5.32597923278809</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2118" t="n">
-        <v>5.36951637268066</v>
+        <v>5.36951589584351</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2119" t="n">
-        <v>5.340491771698</v>
+        <v>5.34049129486084</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2120" t="n">
-        <v>5.32597970962524</v>
+        <v>5.32597923278809</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2121" t="n">
-        <v>5.36951637268066</v>
+        <v>5.36951589584351</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2123" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2125" t="n">
-        <v>5.74200248718262</v>
+        <v>5.74200296401978</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2131" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2143" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2144" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2146" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2148" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2154" t="n">
-        <v>5.50006484985352</v>
+        <v>5.50006437301636</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2158" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2165" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2168" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2169" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2171" t="n">
-        <v>5.67748594284058</v>
+        <v>5.67748546600342</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2174" t="n">
-        <v>5.79039001464844</v>
+        <v>5.7903904914856</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2175" t="n">
-        <v>5.79039001464844</v>
+        <v>5.7903904914856</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -57491,7 +57491,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2197" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2197" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2199" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2201" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2203" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57673,7 +57673,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2204" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2204" t="s">
         <v>8</v>
@@ -57699,7 +57699,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2205" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2205" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>1.81500005722046</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>34389</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>1.85500001907349</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>1.85500001907349</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>1.74000000953674</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.74000000953674</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>7200</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.75499999523163</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -63288,13 +63288,36 @@
         <v>1.75499999523163</v>
       </c>
       <c r="D2736" t="n">
-        <v>1.73000001907349</v>
+        <v>1.72500002384186</v>
       </c>
       <c r="E2736" t="n">
         <v>1.74000000953674</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.72500002384186</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>41037</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.72500002384186</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1.72500002384186</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.7150000333786</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>10381</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.72500002384186</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.70000004768372</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.72500002384186</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>44183</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.88999998569489</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -629,7 +629,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G10" t="n">
-        <v>2.13909888267517</v>
+        <v>2.13909912109375</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G11" t="n">
-        <v>2.13184285163879</v>
+        <v>2.13184309005737</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G12" t="n">
-        <v>2.13184285163879</v>
+        <v>2.13184309005737</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08540391921997</v>
+        <v>2.08540368080139</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G28" t="n">
-        <v>2.09120869636536</v>
+        <v>2.09120845794678</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14055013656616</v>
+        <v>2.14055037498474</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G31" t="n">
-        <v>2.1347451210022</v>
+        <v>2.13474535942078</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G46" t="n">
-        <v>2.24648952484131</v>
+        <v>2.24648904800415</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G47" t="n">
-        <v>2.16086745262146</v>
+        <v>2.16086721420288</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G51" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G52" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G53" t="n">
-        <v>2.2551965713501</v>
+        <v>2.25519680976868</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G73" t="n">
-        <v>1.76903784275055</v>
+        <v>1.76903772354126</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G74" t="n">
-        <v>1.76758670806885</v>
+        <v>1.76758658885956</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G75" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G76" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G77" t="n">
-        <v>1.72259867191315</v>
+        <v>1.72259879112244</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G78" t="n">
-        <v>1.72259867191315</v>
+        <v>1.72259879112244</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.5</v>
       </c>
       <c r="G85" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69937920570374</v>
+        <v>1.69937932491302</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G96" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G98" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G102" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G103" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G105" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G109" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.25</v>
       </c>
       <c r="G122" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G124" t="n">
-        <v>1.67180585861206</v>
+        <v>1.67180597782135</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G126" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G127" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G128" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G129" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G131" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G132" t="n">
-        <v>1.54409873485565</v>
+        <v>1.54409861564636</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G133" t="n">
-        <v>1.54409873485565</v>
+        <v>1.54409861564636</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>1.34600698947906</v>
+        <v>1.34600710868835</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G149" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G150" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G152" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G155" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G156" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G157" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G158" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>1.25095212459564</v>
+        <v>1.25095200538635</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G165" t="n">
-        <v>1.27925097942352</v>
+        <v>1.27925086021423</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G172" t="n">
-        <v>1.33875095844269</v>
+        <v>1.3387508392334</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>1.35543990135193</v>
+        <v>1.35544002056122</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G178" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G180" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G182" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G183" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G185" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G186" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G187" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G188" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.75</v>
       </c>
       <c r="G203" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G207" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G210" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G211" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G223" t="n">
-        <v>1.30247044563293</v>
+        <v>1.30247032642365</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G224" t="n">
-        <v>1.30247044563293</v>
+        <v>1.30247032642365</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>1.25530576705933</v>
+        <v>1.25530564785004</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G231" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G232" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G235" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G236" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G239" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G240" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18854963779449</v>
+        <v>1.18854951858521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18854963779449</v>
+        <v>1.18854951858521</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G249" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.75</v>
       </c>
       <c r="G250" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.75</v>
       </c>
       <c r="G251" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.75</v>
       </c>
       <c r="G252" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.75</v>
       </c>
       <c r="G254" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.75</v>
       </c>
       <c r="G255" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.75</v>
       </c>
       <c r="G257" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.75</v>
       </c>
       <c r="G258" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.75</v>
       </c>
       <c r="G259" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.75</v>
       </c>
       <c r="G262" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.75</v>
       </c>
       <c r="G263" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.75</v>
       </c>
       <c r="G264" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.75</v>
       </c>
       <c r="G265" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.75</v>
       </c>
       <c r="G266" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.75</v>
       </c>
       <c r="G267" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G274" t="n">
-        <v>1.27707397937775</v>
+        <v>1.27707409858704</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G276" t="n">
-        <v>1.5832816362381</v>
+        <v>1.58328151702881</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G284" t="n">
-        <v>1.25748252868652</v>
+        <v>1.25748264789581</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>1.20741546154022</v>
+        <v>1.20741558074951</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G294" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G295" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G296" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.17186057567596</v>
+        <v>1.17186045646667</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G301" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G303" t="n">
-        <v>1.24877524375916</v>
+        <v>1.24877512454987</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G308" t="n">
-        <v>1.34890937805176</v>
+        <v>1.34890949726105</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G309" t="n">
-        <v>1.34890937805176</v>
+        <v>1.34890949726105</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G313" t="n">
-        <v>1.48895227909088</v>
+        <v>1.48895215988159</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G315" t="n">
-        <v>1.42074477672577</v>
+        <v>1.42074489593506</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G316" t="n">
-        <v>1.42074477672577</v>
+        <v>1.42074489593506</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G320" t="n">
-        <v>1.70083045959473</v>
+        <v>1.70083057880402</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G329" t="n">
-        <v>1.51072061061859</v>
+        <v>1.5107204914093</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G336" t="n">
-        <v>1.40260457992554</v>
+        <v>1.40260446071625</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>1.37430584430695</v>
+        <v>1.37430596351624</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G338" t="n">
-        <v>1.42945218086243</v>
+        <v>1.42945230007172</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G339" t="n">
-        <v>1.42872667312622</v>
+        <v>1.42872655391693</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G340" t="n">
-        <v>1.41493999958038</v>
+        <v>1.41493988037109</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40405583381653</v>
+        <v>1.40405571460724</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>1.42945218086243</v>
+        <v>1.42945230007172</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G345" t="n">
-        <v>1.41493999958038</v>
+        <v>1.41493988037109</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>1.49330592155457</v>
+        <v>1.49330604076385</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G360" t="n">
-        <v>1.47879385948181</v>
+        <v>1.47879374027252</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.49475705623627</v>
+        <v>1.49475717544556</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G378" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.77919626235962</v>
+        <v>1.77919614315033</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G382" t="n">
-        <v>1.82708668708801</v>
+        <v>1.82708656787872</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>1.95914781093597</v>
+        <v>1.95914769172668</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>2.0999162197113</v>
+        <v>2.09991598129272</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G388" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G392" t="n">
-        <v>1.95044028759003</v>
+        <v>1.95044016838074</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318437576294</v>
+        <v>1.94318401813507</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G394" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G395" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G396" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G397" t="n">
-        <v>2.07234287261963</v>
+        <v>2.07234263420105</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G401" t="n">
-        <v>1.89239156246185</v>
+        <v>1.89239168167114</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.86191594600677</v>
+        <v>1.86191606521606</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G403" t="n">
-        <v>1.78645241260529</v>
+        <v>1.786452293396</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563519477844</v>
+        <v>1.82563543319702</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G412" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G419" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73856198787689</v>
+        <v>1.73856210708618</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G424" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837952136993</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G426" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>1.79951333999634</v>
+        <v>1.79951345920563</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G429" t="n">
-        <v>1.94898915290833</v>
+        <v>1.94898903369904</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561114788055</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>1.85175752639771</v>
+        <v>1.85175740718842</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G437" t="n">
-        <v>1.81112325191498</v>
+        <v>1.81112313270569</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G438" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>1.85030615329742</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>1.83724522590637</v>
+        <v>1.83724534511566</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G441" t="n">
-        <v>1.84595227241516</v>
+        <v>1.84595239162445</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G447" t="n">
-        <v>1.9780136346817</v>
+        <v>1.97801375389099</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93302595615387</v>
+        <v>1.93302571773529</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G449" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G451" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>1.85030615329742</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G453" t="n">
-        <v>1.84014773368835</v>
+        <v>1.84014761447906</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207460403442</v>
+        <v>1.87207436561584</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561114788055</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G459" t="n">
-        <v>1.88513541221619</v>
+        <v>1.88513553142548</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>1.92141580581665</v>
+        <v>1.92141592502594</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G463" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G464" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G465" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G466" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G471" t="n">
-        <v>1.90400123596191</v>
+        <v>1.9040013551712</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>1.89094042778015</v>
+        <v>1.89094030857086</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>1.8807817697525</v>
+        <v>1.88078188896179</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G475" t="n">
-        <v>1.9098060131073</v>
+        <v>1.90980613231659</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G476" t="n">
-        <v>1.87497699260712</v>
+        <v>1.87497687339783</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G477" t="n">
-        <v>1.82273304462433</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G478" t="n">
-        <v>1.82273304462433</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>1.82273304462433</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>1.72114741802216</v>
+        <v>1.72114753723145</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G482" t="n">
-        <v>1.80822086334229</v>
+        <v>1.80822062492371</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G484" t="n">
-        <v>1.80096459388733</v>
+        <v>1.80096471309662</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G487" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837952136993</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.5</v>
       </c>
       <c r="G488" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.5</v>
       </c>
       <c r="G489" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.5</v>
       </c>
       <c r="G490" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G492" t="n">
-        <v>1.85175752639771</v>
+        <v>1.85175740718842</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G493" t="n">
-        <v>1.84159886837006</v>
+        <v>1.84159898757935</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G494" t="n">
-        <v>1.8807817697525</v>
+        <v>1.88078188896179</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.5</v>
       </c>
       <c r="G497" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G502" t="n">
-        <v>1.87062335014343</v>
+        <v>1.87062323093414</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.5</v>
       </c>
       <c r="G508" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G509" t="n">
-        <v>1.80096459388733</v>
+        <v>1.80096471309662</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G510" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G511" t="n">
-        <v>1.82998931407928</v>
+        <v>1.82998919487</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G512" t="n">
-        <v>1.77629387378693</v>
+        <v>1.77629375457764</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>1.79951333999634</v>
+        <v>1.79951345920563</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>1.85030615329742</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G518" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.5</v>
       </c>
       <c r="G519" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G525" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G526" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G533" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G538" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G547" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G549" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G556" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G562" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G564" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G573" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G579" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.25</v>
       </c>
       <c r="G596" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.25</v>
       </c>
       <c r="G597" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.25</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.25</v>
       </c>
       <c r="G600" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G601" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>1.57457435131073</v>
+        <v>1.57457423210144</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>1.57457435131073</v>
+        <v>1.57457423210144</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G653" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G655" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G658" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G660" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.25</v>
       </c>
       <c r="G671" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.25</v>
       </c>
       <c r="G672" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.25</v>
       </c>
       <c r="G673" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G677" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.25</v>
       </c>
       <c r="G693" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G700" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G706" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G707" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G708" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G712" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G713" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G716" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G720" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G726" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G729" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.79951333999634</v>
+        <v>1.79951345920563</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.5</v>
       </c>
       <c r="G737" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G741" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G743" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.5</v>
       </c>
       <c r="G747" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.5</v>
       </c>
       <c r="G748" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.5</v>
       </c>
       <c r="G749" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G756" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G758" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G766" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G768" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G775" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G778" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G780" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G781" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561114788055</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>1.96640372276306</v>
+        <v>1.96640396118164</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G789" t="n">
-        <v>2.06073307991028</v>
+        <v>2.0607328414917</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365987300873</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G798" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365987300873</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>2.04622101783752</v>
+        <v>2.04622077941895</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G811" t="n">
-        <v>2.09701371192932</v>
+        <v>2.09701347351074</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>2.22036743164062</v>
+        <v>2.22036719322205</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>2.22036743164062</v>
+        <v>2.22036719322205</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>2.271160364151</v>
+        <v>2.27116012573242</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G824" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G826" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G830" t="n">
-        <v>2.25664782524109</v>
+        <v>2.25664806365967</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G834" t="n">
-        <v>2.34372115135193</v>
+        <v>2.34372091293335</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G844" t="n">
-        <v>2.34372115135193</v>
+        <v>2.34372091293335</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G854" t="n">
-        <v>2.25664782524109</v>
+        <v>2.25664806365967</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G855" t="n">
-        <v>2.271160364151</v>
+        <v>2.27116012573242</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>2.36548924446106</v>
+        <v>2.36548948287964</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>2.43805050849915</v>
+        <v>2.43805027008057</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>2.53237962722778</v>
+        <v>2.53237986564636</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G886" t="n">
-        <v>2.62670922279358</v>
+        <v>2.626708984375</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G898" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G899" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.69201397895813</v>
+        <v>2.69201421737671</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G910" t="n">
-        <v>2.77183127403259</v>
+        <v>2.77183103561401</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G911" t="n">
-        <v>2.74280667304993</v>
+        <v>2.74280691146851</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>2.69201397895813</v>
+        <v>2.69201421737671</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>3.75</v>
       </c>
       <c r="G915" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G916" t="n">
-        <v>2.67750191688538</v>
+        <v>2.6775016784668</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G919" t="n">
-        <v>2.69927000999451</v>
+        <v>2.69927024841309</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G920" t="n">
-        <v>2.670245885849</v>
+        <v>2.67024564743042</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.75</v>
       </c>
       <c r="G921" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>2.7935996055603</v>
+        <v>2.79359936714172</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G924" t="n">
-        <v>2.95323395729065</v>
+        <v>2.95323371887207</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G928" t="n">
-        <v>3.02579474449158</v>
+        <v>3.02579498291016</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G936" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G943" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>2.82987999916077</v>
+        <v>2.82987976074219</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>3.02579474449158</v>
+        <v>3.02579498291016</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G977" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G978" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G984" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.5</v>
       </c>
       <c r="G985" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G994" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G999" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506368637085</v>
+        <v>3.34506344795227</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506368637085</v>
+        <v>3.34506344795227</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.49744176864624</v>
+        <v>3.49744153022766</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.46116089820862</v>
+        <v>3.46116065979004</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.38134360313416</v>
+        <v>3.38134384155273</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>5</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.49744176864624</v>
+        <v>3.49744153022766</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>5</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.59902667999268</v>
+        <v>3.59902691841125</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>5</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>5</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>4.5</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>4.5</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>4.5</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>4.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.5</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.5</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>4.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.62079501152039</v>
+        <v>3.62079524993896</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>5</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>5</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.59902667999268</v>
+        <v>3.59902691841125</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>5</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>5</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.62079501152039</v>
+        <v>3.62079524993896</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.50469732284546</v>
+        <v>3.50469756126404</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.5</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>5</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610024452209</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061254501343</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>5</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.62079501152039</v>
+        <v>3.62079524993896</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.46116089820862</v>
+        <v>3.46116065979004</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>5</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>5</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.38134360313416</v>
+        <v>3.38134384155273</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>4.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.49018526077271</v>
+        <v>3.49018549919128</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1664" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256358146667</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>5</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>5</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.59902667999268</v>
+        <v>3.59902691841125</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.59902667999268</v>
+        <v>3.59902691841125</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1697" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1698" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1699" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1701" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1713" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>4.5</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.80811166763306</v>
+        <v>2.80811142921448</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.82987999916077</v>
+        <v>2.82987976074219</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.80811166763306</v>
+        <v>2.80811142921448</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.80811166763306</v>
+        <v>2.80811142921448</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>3.75</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.02579474449158</v>
+        <v>3.02579498291016</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1818" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.97634410858154</v>
+        <v>3.97634434700012</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1822" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1824" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.25207614898682</v>
+        <v>4.25207662582397</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.51329565048218</v>
+        <v>4.51329612731934</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>4.44073486328125</v>
+        <v>4.44073438644409</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1861" t="n">
-        <v>4.28110027313232</v>
+        <v>4.28110074996948</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1893" t="n">
-        <v>4.16500282287598</v>
+        <v>4.16500234603882</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1894" t="n">
-        <v>4.28110027313232</v>
+        <v>4.28110074996948</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1897" t="n">
-        <v>4.44073486328125</v>
+        <v>4.44073438644409</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.45524740219116</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.542320728302</v>
+        <v>4.54232025146484</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1941" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1942" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1943" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1944" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1945" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1947" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1951" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1962" t="n">
-        <v>4.81805181503296</v>
+        <v>4.81805229187012</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1963" t="n">
-        <v>4.81805181503296</v>
+        <v>4.81805229187012</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1970" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1973" t="n">
-        <v>4.68744230270386</v>
+        <v>4.6874418258667</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1993" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1998" t="n">
-        <v>4.81805181503296</v>
+        <v>4.81805229187012</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.73097848892212</v>
+        <v>4.73097896575928</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.51329565048218</v>
+        <v>4.51329612731934</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.542320728302</v>
+        <v>4.54232025146484</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.97634410858154</v>
+        <v>3.97634434700012</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2058" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2059" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2060" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2063" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2064" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2065" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2066" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2068" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54189,7 +54189,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2070" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2070" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2071" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2072" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2073" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2074" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2076" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414873123169</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2078" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2080" t="n">
-        <v>3.77317309379578</v>
+        <v>3.77317333221436</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2091" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2093" t="n">
-        <v>4.19402742385864</v>
+        <v>4.19402694702148</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G2095" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2097" t="n">
-        <v>4.45524740219116</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2098" t="n">
-        <v>4.45524740219116</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2100" t="n">
-        <v>4.51329565048218</v>
+        <v>4.51329612731934</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2114" t="n">
-        <v>5.0212230682373</v>
+        <v>5.02122259140015</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2117" t="n">
-        <v>5.32597970962524</v>
+        <v>5.32597923278809</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2119" t="n">
-        <v>5.340491771698</v>
+        <v>5.34049129486084</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2120" t="n">
-        <v>5.32597970962524</v>
+        <v>5.32597923278809</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2122" t="n">
-        <v>5.71780872344971</v>
+        <v>5.71780920028687</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>1.86000001430511</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>18552</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>1.88999998569489</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>1.7849999666214</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>1.85500001907349</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -655,7 +655,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G11" t="n">
-        <v>2.13184309005737</v>
+        <v>2.13184285163879</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G12" t="n">
-        <v>2.13184309005737</v>
+        <v>2.13184285163879</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G20" t="n">
-        <v>2.20440411567688</v>
+        <v>2.2044038772583</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G21" t="n">
-        <v>2.15215992927551</v>
+        <v>2.15216016769409</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G22" t="n">
-        <v>2.15215992927551</v>
+        <v>2.15216016769409</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08540368080139</v>
+        <v>2.08540391921997</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G37" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G38" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G44" t="n">
-        <v>2.20440411567688</v>
+        <v>2.2044038772583</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G46" t="n">
-        <v>2.24648904800415</v>
+        <v>2.24648928642273</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>2.17247700691223</v>
+        <v>2.17247724533081</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23487949371338</v>
+        <v>2.2348792552948</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>2.23487949371338</v>
+        <v>2.2348792552948</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G68" t="n">
-        <v>2.17973303794861</v>
+        <v>2.17973327636719</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G70" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.5</v>
       </c>
       <c r="G85" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G89" t="n">
-        <v>1.7327573299408</v>
+        <v>1.73275721073151</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69937932491302</v>
+        <v>1.69937920570374</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G96" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G98" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G113" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G124" t="n">
-        <v>1.67180597782135</v>
+        <v>1.67180609703064</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G134" t="n">
-        <v>1.48314726352692</v>
+        <v>1.48314738273621</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>1.40768396854401</v>
+        <v>1.40768384933472</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G147" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317154884338</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G148" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317154884338</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G159" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317154884338</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G172" t="n">
-        <v>1.3387508392334</v>
+        <v>1.33875095844269</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G178" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G180" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G182" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G183" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G185" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G186" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G187" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G188" t="n">
-        <v>1.33584833145142</v>
+        <v>1.33584845066071</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.32061064243317</v>
+        <v>1.32061076164246</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G193" t="n">
-        <v>1.24224483966827</v>
+        <v>1.24224472045898</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G194" t="n">
-        <v>1.24224483966827</v>
+        <v>1.24224472045898</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G195" t="n">
-        <v>1.26473867893219</v>
+        <v>1.2647385597229</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26473867893219</v>
+        <v>1.2647385597229</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G197" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G199" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G200" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22628140449524</v>
+        <v>1.22628128528595</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.75</v>
       </c>
       <c r="G203" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G212" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>1.25530564785004</v>
+        <v>1.25530576705933</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G231" t="n">
-        <v>1.20451307296753</v>
+        <v>1.20451295375824</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G232" t="n">
-        <v>1.20451307296753</v>
+        <v>1.20451295375824</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>1.17403745651245</v>
+        <v>1.17403733730316</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>1.17403745651245</v>
+        <v>1.17403733730316</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G249" t="n">
-        <v>1.20451307296753</v>
+        <v>1.20451295375824</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.75</v>
       </c>
       <c r="G250" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.75</v>
       </c>
       <c r="G251" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.75</v>
       </c>
       <c r="G252" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.75</v>
       </c>
       <c r="G254" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.75</v>
       </c>
       <c r="G255" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.75</v>
       </c>
       <c r="G257" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.75</v>
       </c>
       <c r="G258" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.75</v>
       </c>
       <c r="G259" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.75</v>
       </c>
       <c r="G262" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.75</v>
       </c>
       <c r="G263" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>1.75</v>
       </c>
       <c r="G264" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.75</v>
       </c>
       <c r="G265" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.75</v>
       </c>
       <c r="G266" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.75</v>
       </c>
       <c r="G267" t="n">
-        <v>1.26981806755066</v>
+        <v>1.26981794834137</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G273" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G277" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>1.40768396854401</v>
+        <v>1.40768384933472</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32133626937866</v>
+        <v>1.32133615016937</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G284" t="n">
-        <v>1.25748264789581</v>
+        <v>1.25748252868652</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G285" t="n">
-        <v>1.23353743553162</v>
+        <v>1.23353755474091</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G288" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>1.20741558074951</v>
+        <v>1.20741546154022</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.17186045646667</v>
+        <v>1.17186057567596</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>1.23353743553162</v>
+        <v>1.23353755474091</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G303" t="n">
-        <v>1.24877512454987</v>
+        <v>1.24877524375916</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G304" t="n">
-        <v>1.24950087070465</v>
+        <v>1.24950075149536</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G313" t="n">
-        <v>1.48895215988159</v>
+        <v>1.48895227909088</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>1.42219614982605</v>
+        <v>1.42219626903534</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G322" t="n">
-        <v>1.67035484313965</v>
+        <v>1.67035472393036</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G329" t="n">
-        <v>1.5107204914093</v>
+        <v>1.51072061061859</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>1.48024487495422</v>
+        <v>1.48024475574493</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G332" t="n">
-        <v>1.40478146076202</v>
+        <v>1.40478134155273</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>1.48024487495422</v>
+        <v>1.48024475574493</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>1.48024487495422</v>
+        <v>1.48024475574493</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G335" t="n">
-        <v>1.43815958499908</v>
+        <v>1.43815946578979</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G336" t="n">
-        <v>1.40260446071625</v>
+        <v>1.40260457992554</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>1.37430596351624</v>
+        <v>1.37430584430695</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G340" t="n">
-        <v>1.41493988037109</v>
+        <v>1.41493999958038</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40405571460724</v>
+        <v>1.40405583381653</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>1.40768396854401</v>
+        <v>1.40768384933472</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G345" t="n">
-        <v>1.41493988037109</v>
+        <v>1.41493999958038</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G347" t="n">
-        <v>1.47298884391785</v>
+        <v>1.47298872470856</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G349" t="n">
-        <v>1.52087903022766</v>
+        <v>1.52087914943695</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G350" t="n">
-        <v>1.43380582332611</v>
+        <v>1.4338059425354</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G355" t="n">
-        <v>1.47008645534515</v>
+        <v>1.47008633613586</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.49475717544556</v>
+        <v>1.49475705623627</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.5847327709198</v>
+        <v>1.58473289012909</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>1.66890370845795</v>
+        <v>1.66890358924866</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G388" t="n">
-        <v>1.98817217350006</v>
+        <v>1.98817229270935</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G389" t="n">
-        <v>2.00558662414551</v>
+        <v>2.00558686256409</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318401813507</v>
+        <v>1.94318413734436</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G394" t="n">
-        <v>1.90109872817993</v>
+        <v>1.90109884738922</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G396" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G397" t="n">
-        <v>2.07234263420105</v>
+        <v>2.07234287261963</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98817217350006</v>
+        <v>1.98817229270935</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G401" t="n">
-        <v>1.89239168167114</v>
+        <v>1.89239156246185</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.86191606521606</v>
+        <v>1.86191594600677</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563543319702</v>
+        <v>1.82563555240631</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>1.78935480117798</v>
+        <v>1.78935492038727</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G412" t="n">
-        <v>1.78935480117798</v>
+        <v>1.78935492038727</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G419" t="n">
-        <v>1.66890370845795</v>
+        <v>1.66890358924866</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G425" t="n">
-        <v>1.79515981674194</v>
+        <v>1.79515969753265</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>1.79951345920563</v>
+        <v>1.79951333999634</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88658666610718</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G429" t="n">
-        <v>1.94898903369904</v>
+        <v>1.94898915290833</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.88658666610718</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>1.88658666610718</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88658666610718</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>1.85175740718842</v>
+        <v>1.85175752639771</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G437" t="n">
-        <v>1.81112313270569</v>
+        <v>1.81112325191498</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>1.85030627250671</v>
+        <v>1.85030603408813</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>1.83724534511566</v>
+        <v>1.83724522590637</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G441" t="n">
-        <v>1.84595239162445</v>
+        <v>1.84595251083374</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G443" t="n">
-        <v>1.87352573871613</v>
+        <v>1.87352561950684</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G447" t="n">
-        <v>1.97801375389099</v>
+        <v>1.9780136346817</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>1.85030627250671</v>
+        <v>1.85030603408813</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207436561584</v>
+        <v>1.87207448482513</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>1.90109872817993</v>
+        <v>1.90109884738922</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G461" t="n">
-        <v>1.87787938117981</v>
+        <v>1.8778795003891</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>1.92141592502594</v>
+        <v>1.92141604423523</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G463" t="n">
-        <v>1.94463539123535</v>
+        <v>1.94463551044464</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G464" t="n">
-        <v>1.94463539123535</v>
+        <v>1.94463551044464</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G465" t="n">
-        <v>1.94463539123535</v>
+        <v>1.94463551044464</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G466" t="n">
-        <v>1.94463539123535</v>
+        <v>1.94463551044464</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>1.90835499763489</v>
+        <v>1.90835511684418</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>1.90109872817993</v>
+        <v>1.90109884738922</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>1.92286729812622</v>
+        <v>1.92286717891693</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G470" t="n">
-        <v>1.90254998207092</v>
+        <v>1.90255010128021</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G471" t="n">
-        <v>1.9040013551712</v>
+        <v>1.90400123596191</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>1.89094030857086</v>
+        <v>1.89094042778015</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G473" t="n">
-        <v>1.90254998207092</v>
+        <v>1.90255010128021</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>1.88078188896179</v>
+        <v>1.88078165054321</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G476" t="n">
-        <v>1.87497687339783</v>
+        <v>1.87497711181641</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G482" t="n">
-        <v>1.80822062492371</v>
+        <v>1.808220744133</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G484" t="n">
-        <v>1.80096471309662</v>
+        <v>1.80096459388733</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.5</v>
       </c>
       <c r="G488" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.5</v>
       </c>
       <c r="G489" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.5</v>
       </c>
       <c r="G490" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G491" t="n">
-        <v>1.83869624137878</v>
+        <v>1.83869636058807</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G492" t="n">
-        <v>1.85175740718842</v>
+        <v>1.85175752639771</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G494" t="n">
-        <v>1.88078188896179</v>
+        <v>1.88078165054321</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.5</v>
       </c>
       <c r="G497" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.5</v>
       </c>
       <c r="G508" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G509" t="n">
-        <v>1.80096471309662</v>
+        <v>1.80096459388733</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>1.79951345920563</v>
+        <v>1.79951333999634</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>1.85030627250671</v>
+        <v>1.85030603408813</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.5</v>
       </c>
       <c r="G519" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G525" t="n">
-        <v>1.88658666610718</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G526" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>1.92286729812622</v>
+        <v>1.92286717891693</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.75</v>
       </c>
       <c r="G529" t="n">
-        <v>1.99542820453644</v>
+        <v>1.99542832374573</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G533" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G547" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G556" t="n">
-        <v>1.66890370845795</v>
+        <v>1.66890358924866</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>1.66890370845795</v>
+        <v>1.66890358924866</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G572" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.66890370845795</v>
+        <v>1.66890358924866</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66890370845795</v>
+        <v>1.66890358924866</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G601" t="n">
-        <v>1.66890370845795</v>
+        <v>1.66890358924866</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>1.57457423210144</v>
+        <v>1.57457435131073</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>1.57457423210144</v>
+        <v>1.57457435131073</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G614" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>1.48024487495422</v>
+        <v>1.48024475574493</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G629" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G655" t="n">
-        <v>1.66890370845795</v>
+        <v>1.66890358924866</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G658" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G660" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.66890370845795</v>
+        <v>1.66890358924866</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G677" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>1.67615973949432</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.79951345920563</v>
+        <v>1.79951333999634</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.5</v>
       </c>
       <c r="G737" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.5</v>
       </c>
       <c r="G747" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.5</v>
       </c>
       <c r="G748" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.5</v>
       </c>
       <c r="G749" t="n">
-        <v>1.81402540206909</v>
+        <v>1.81402564048767</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G751" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G766" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84305012226105</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G778" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>1.90109872817993</v>
+        <v>1.90109884738922</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90835499763489</v>
+        <v>1.90835511684418</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.75</v>
       </c>
       <c r="G793" t="n">
-        <v>1.99542820453644</v>
+        <v>1.99542832374573</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.97365987300873</v>
+        <v>1.97365999221802</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.75</v>
       </c>
       <c r="G796" t="n">
-        <v>1.99542820453644</v>
+        <v>1.99542832374573</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G798" t="n">
-        <v>1.97365987300873</v>
+        <v>1.97365999221802</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.0534770488739</v>
+        <v>2.05347681045532</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G802" t="n">
-        <v>2.06798911094666</v>
+        <v>2.06798887252808</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>2.06798911094666</v>
+        <v>2.06798887252808</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G805" t="n">
-        <v>2.13329410552979</v>
+        <v>2.13329434394836</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>2.13329410552979</v>
+        <v>2.13329434394836</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G810" t="n">
-        <v>2.06798911094666</v>
+        <v>2.06798887252808</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G811" t="n">
-        <v>2.09701347351074</v>
+        <v>2.09701371192932</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G829" t="n">
-        <v>2.30744051933289</v>
+        <v>2.30744075775146</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G830" t="n">
-        <v>2.25664806365967</v>
+        <v>2.25664782524109</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G834" t="n">
-        <v>2.34372091293335</v>
+        <v>2.34372115135193</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G844" t="n">
-        <v>2.34372091293335</v>
+        <v>2.34372115135193</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G846" t="n">
-        <v>2.30744051933289</v>
+        <v>2.30744075775146</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G854" t="n">
-        <v>2.25664806365967</v>
+        <v>2.25664782524109</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>2.36548948287964</v>
+        <v>2.36548924446106</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G877" t="n">
-        <v>2.46707487106323</v>
+        <v>2.46707510948181</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G878" t="n">
-        <v>2.4960994720459</v>
+        <v>2.49609923362732</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>2.53237986564636</v>
+        <v>2.53237962722778</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>2.86616039276123</v>
+        <v>2.86616063117981</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>2.71378231048584</v>
+        <v>2.71378254890442</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G888" t="n">
-        <v>2.71378231048584</v>
+        <v>2.71378254890442</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G889" t="n">
-        <v>2.78634333610535</v>
+        <v>2.78634309768677</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G890" t="n">
-        <v>2.85164833068848</v>
+        <v>2.85164856910706</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>2.96048974990845</v>
+        <v>2.96048951148987</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G899" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G911" t="n">
-        <v>2.74280691146851</v>
+        <v>2.74280667304993</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G912" t="n">
-        <v>2.78634333610535</v>
+        <v>2.78634309768677</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G913" t="n">
-        <v>2.85164833068848</v>
+        <v>2.85164856910706</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G916" t="n">
-        <v>2.6775016784668</v>
+        <v>2.67750191688538</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G920" t="n">
-        <v>2.67024564743042</v>
+        <v>2.670245885849</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>2.79359936714172</v>
+        <v>2.79359912872314</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G930" t="n">
-        <v>2.94597768783569</v>
+        <v>2.94597744941711</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G931" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G935" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G939" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G943" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>2.82987976074219</v>
+        <v>2.82987999916077</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G952" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G956" t="n">
-        <v>2.9677460193634</v>
+        <v>2.96774578094482</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>2.96048974990845</v>
+        <v>2.96048951148987</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G959" t="n">
-        <v>2.94597768783569</v>
+        <v>2.94597744941711</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939256668091</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G978" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G983" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G984" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G987" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G990" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G996" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G997" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G998" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G999" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506344795227</v>
+        <v>3.34506320953369</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506344795227</v>
+        <v>3.34506320953369</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939256668091</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.35231947898865</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.40311193466187</v>
+        <v>3.40311217308044</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.3160388469696</v>
+        <v>3.31603908538818</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.3160388469696</v>
+        <v>3.31603908538818</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.13463664054871</v>
+        <v>3.13463640213013</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.9677460193634</v>
+        <v>2.96774578094482</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.81536793708801</v>
+        <v>2.81536769866943</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.96048974990845</v>
+        <v>2.96048951148987</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.3160388469696</v>
+        <v>3.31603908538818</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.3160388469696</v>
+        <v>3.31603908538818</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939256668091</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>5</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>5.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>5.5</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>5.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>5.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.77317333221436</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>5</v>
       </c>
       <c r="G1210" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.59902691841125</v>
+        <v>3.59902667999268</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>5</v>
       </c>
       <c r="G1216" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>5</v>
       </c>
       <c r="G1217" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1229" t="n">
-        <v>3.13463664054871</v>
+        <v>3.13463640213013</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1238" t="n">
-        <v>3.40311193466187</v>
+        <v>3.40311217308044</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.40311193466187</v>
+        <v>3.40311217308044</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.35231947898865</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.35231947898865</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1294" t="n">
-        <v>3.40311193466187</v>
+        <v>3.40311217308044</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.40311193466187</v>
+        <v>3.40311217308044</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.35231947898865</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.35231947898865</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.13463664054871</v>
+        <v>3.13463640213013</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1353" t="n">
-        <v>2.9677460193634</v>
+        <v>2.96774578094482</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.96048974990845</v>
+        <v>2.96048951148987</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.13463664054871</v>
+        <v>3.13463640213013</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.13463664054871</v>
+        <v>3.13463640213013</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.35231947898865</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939256668091</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.62079524993896</v>
+        <v>3.62079501152039</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>5</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>5</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.77317333221436</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.77317333221436</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.59902691841125</v>
+        <v>3.59902667999268</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>5</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>5</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.62079524993896</v>
+        <v>3.62079501152039</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1578" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>5</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.68610024452209</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.77317333221436</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.77317333221436</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>5</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.62079524993896</v>
+        <v>3.62079501152039</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>5</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>5</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>3.40311193466187</v>
+        <v>3.40311217308044</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1636" t="n">
-        <v>3.33780741691589</v>
+        <v>3.33780717849731</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.64256358146667</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>5</v>
       </c>
       <c r="G1680" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>5</v>
       </c>
       <c r="G1681" t="n">
-        <v>3.62805080413818</v>
+        <v>3.62805128097534</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.59902691841125</v>
+        <v>3.59902667999268</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.59902691841125</v>
+        <v>3.59902667999268</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.57000231742859</v>
+        <v>3.57000255584717</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.57000231742859</v>
+        <v>3.57000255584717</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1738" t="n">
-        <v>3.13463664054871</v>
+        <v>3.13463640213013</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.9677460193634</v>
+        <v>2.96774578094482</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.81536793708801</v>
+        <v>2.81536769866943</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.80811142921448</v>
+        <v>2.80811166763306</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.82987976074219</v>
+        <v>2.82987999916077</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.80811142921448</v>
+        <v>2.80811166763306</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.80811142921448</v>
+        <v>2.80811166763306</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.77908730506897</v>
+        <v>2.77908706665039</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.77317333221436</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>5.5</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>5.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.13597822189331</v>
+        <v>4.13597774505615</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1819" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.97634434700012</v>
+        <v>3.9763445854187</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.23756408691406</v>
+        <v>4.23756456375122</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.23756408691406</v>
+        <v>4.23756456375122</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.19402694702148</v>
+        <v>4.19402742385864</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.13597822189331</v>
+        <v>4.13597774505615</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.13597822189331</v>
+        <v>4.13597774505615</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.51329612731934</v>
+        <v>4.51329565048218</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1864" t="n">
-        <v>4.17951536178589</v>
+        <v>4.17951488494873</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>5.5</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1893" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1912" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1920" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1926" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1928" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1929" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1930" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1931" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1940" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1941" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1942" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1943" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1944" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1945" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1947" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1951" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1962" t="n">
-        <v>4.81805229187012</v>
+        <v>4.81805181503296</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1963" t="n">
-        <v>4.81805229187012</v>
+        <v>4.81805181503296</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1970" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1973" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1993" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1998" t="n">
-        <v>4.81805229187012</v>
+        <v>4.81805181503296</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.51329612731934</v>
+        <v>4.51329565048218</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.19402694702148</v>
+        <v>4.19402742385864</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.19402694702148</v>
+        <v>4.19402742385864</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>5.5</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.97634434700012</v>
+        <v>3.9763445854187</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2051" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2052" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2053" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2054" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2055" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2056" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2057" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2060" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2061" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2067" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2068" t="n">
-        <v>3.77317333221436</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2076" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2078" t="n">
-        <v>3.77317333221436</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2080" t="n">
-        <v>3.77317333221436</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.1069540977478</v>
+        <v>4.10695362091064</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54579,7 +54579,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.13597822189331</v>
+        <v>4.13597774505615</v>
       </c>
       <c r="H2085" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2092" t="n">
-        <v>4.1069540977478</v>
+        <v>4.10695362091064</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2093" t="n">
-        <v>4.19402694702148</v>
+        <v>4.19402742385864</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2100" t="n">
-        <v>4.51329612731934</v>
+        <v>4.51329565048218</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55333,7 +55333,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2114" t="n">
-        <v>5.02122259140015</v>
+        <v>5.0212230682373</v>
       </c>
       <c r="H2114" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2115" t="n">
-        <v>5.23890590667725</v>
+        <v>5.23890542984009</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2119" t="n">
-        <v>5.34049129486084</v>
+        <v>5.340491771698</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2123" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2125" t="n">
-        <v>5.74200296401978</v>
+        <v>5.74200248718262</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2131" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2143" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56113,7 +56113,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2144" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2144" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2146" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2148" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2154" t="n">
-        <v>5.50006437301636</v>
+        <v>5.50006484985352</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2158" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56659,7 +56659,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2165" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2165" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2168" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2169" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2171" t="n">
-        <v>5.67748546600342</v>
+        <v>5.67748594284058</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2174" t="n">
-        <v>5.7903904914856</v>
+        <v>5.79039001464844</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2175" t="n">
-        <v>5.7903904914856</v>
+        <v>5.79039001464844</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -57491,7 +57491,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2197" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2197" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2199" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2201" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57647,7 +57647,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2203" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2203" t="s">
         <v>8</v>
@@ -57673,7 +57673,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2204" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2204" t="s">
         <v>8</v>
@@ -57699,7 +57699,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2205" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2205" t="s">
         <v>8</v>
@@ -71678,7 +71678,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="D2743" t="n">
-        <v>1.7849999666214</v>
+        <v>1.76999998092651</v>
       </c>
       <c r="E2743" t="n">
         <v>1.85500001907349</v>
@@ -71690,6 +71690,32 @@
         <v>1.79999995231628</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>7186</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.83500003814697</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.83500003814697</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -485,7 +485,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G5" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17537951469421</v>
+        <v>2.17537927627563</v>
       </c>
       <c r="H6" t="n">
         <v>1800</v>
@@ -572,7 +572,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G7" t="n">
-        <v>2.17537951469421</v>
+        <v>2.17537927627563</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G8" t="n">
-        <v>2.17537951469421</v>
+        <v>2.17537927627563</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H18" t="n">
         <v>3000</v>
@@ -949,7 +949,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G20" t="n">
-        <v>2.20440411567688</v>
+        <v>2.2044038772583</v>
       </c>
       <c r="H20" t="n">
         <v>600</v>
@@ -1036,7 +1036,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14345264434814</v>
+        <v>2.14345240592957</v>
       </c>
       <c r="H23" t="n">
         <v>1800</v>
@@ -1065,7 +1065,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14345264434814</v>
+        <v>2.14345240592957</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14345264434814</v>
+        <v>2.14345240592957</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14345264434814</v>
+        <v>2.14345240592957</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16231870651245</v>
+        <v>2.16231846809387</v>
       </c>
       <c r="H30" t="n">
         <v>1200</v>
@@ -1297,7 +1297,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H32" t="n">
         <v>3000</v>
@@ -1326,7 +1326,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G37" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G38" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G44" t="n">
-        <v>2.20440411567688</v>
+        <v>2.2044038772583</v>
       </c>
       <c r="H44" t="n">
         <v>4800</v>
@@ -1819,7 +1819,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>2.17247700691223</v>
+        <v>2.17247724533081</v>
       </c>
       <c r="H50" t="n">
         <v>600</v>
@@ -1848,7 +1848,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G51" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H51" t="n">
         <v>2400</v>
@@ -1877,7 +1877,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G52" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G53" t="n">
-        <v>2.2551965713501</v>
+        <v>2.25519680976868</v>
       </c>
       <c r="H53" t="n">
         <v>3000</v>
@@ -1935,7 +1935,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G54" t="n">
-        <v>2.2479407787323</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H54" t="n">
         <v>1200</v>
@@ -1964,7 +1964,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G55" t="n">
-        <v>2.2479407787323</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G56" t="n">
-        <v>2.2479407787323</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G57" t="n">
-        <v>2.2479407787323</v>
+        <v>2.24794054031372</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G60" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H60" t="n">
         <v>3600</v>
@@ -2138,7 +2138,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G61" t="n">
-        <v>2.22907495498657</v>
+        <v>2.22907471656799</v>
       </c>
       <c r="H61" t="n">
         <v>1200</v>
@@ -2283,7 +2283,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G66" t="n">
-        <v>2.24503803253174</v>
+        <v>2.24503827095032</v>
       </c>
       <c r="H66" t="n">
         <v>1200</v>
@@ -2312,7 +2312,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G67" t="n">
-        <v>2.24503803253174</v>
+        <v>2.24503827095032</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G68" t="n">
-        <v>2.17973303794861</v>
+        <v>2.17973327636719</v>
       </c>
       <c r="H68" t="n">
         <v>5400</v>
@@ -2370,7 +2370,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G69" t="n">
-        <v>2.23052573204041</v>
+        <v>2.23052597045898</v>
       </c>
       <c r="H69" t="n">
         <v>7200</v>
@@ -2428,7 +2428,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H71" t="n">
         <v>1560</v>
@@ -2457,7 +2457,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>1.71824502944946</v>
+        <v>1.71824491024017</v>
       </c>
       <c r="H72" t="n">
         <v>780</v>
@@ -2515,7 +2515,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G74" t="n">
-        <v>1.76758670806885</v>
+        <v>1.76758658885956</v>
       </c>
       <c r="H74" t="n">
         <v>1560</v>
@@ -2544,7 +2544,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G75" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H75" t="n">
         <v>780</v>
@@ -2573,7 +2573,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G76" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>1.74872076511383</v>
+        <v>1.74872088432312</v>
       </c>
       <c r="H82" t="n">
         <v>1560</v>
@@ -2863,7 +2863,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G86" t="n">
-        <v>1.76323294639587</v>
+        <v>1.76323282718658</v>
       </c>
       <c r="H86" t="n">
         <v>5460</v>
@@ -2950,7 +2950,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G89" t="n">
-        <v>1.7327573299408</v>
+        <v>1.73275721073151</v>
       </c>
       <c r="H89" t="n">
         <v>1560</v>
@@ -2979,7 +2979,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H90" t="n">
         <v>3900</v>
@@ -3008,7 +3008,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G91" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G92" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G93" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H95" t="n">
         <v>3120</v>
@@ -3153,7 +3153,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G96" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G98" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H104" t="n">
         <v>1560</v>
@@ -3414,7 +3414,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G105" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H106" t="n">
         <v>3120</v>
@@ -3472,7 +3472,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G109" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G113" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H113" t="n">
         <v>780</v>
@@ -4023,7 +4023,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G126" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H126" t="n">
         <v>3120</v>
@@ -4052,7 +4052,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G127" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G128" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G129" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G131" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H140" t="n">
         <v>3900</v>
@@ -4458,7 +4458,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H141" t="n">
         <v>19500</v>
@@ -4487,7 +4487,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H142" t="n">
         <v>3900</v>
@@ -4516,7 +4516,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>1.40768396854401</v>
+        <v>1.40768384933472</v>
       </c>
       <c r="H144" t="n">
         <v>4680</v>
@@ -4574,7 +4574,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H145" t="n">
         <v>3900</v>
@@ -4603,7 +4603,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>1.34600698947906</v>
+        <v>1.34600710868835</v>
       </c>
       <c r="H146" t="n">
         <v>1560</v>
@@ -4632,7 +4632,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G147" t="n">
-        <v>1.39317154884338</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H147" t="n">
         <v>4680</v>
@@ -4661,7 +4661,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G148" t="n">
-        <v>1.39317154884338</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G159" t="n">
-        <v>1.39317154884338</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H159" t="n">
         <v>13260</v>
@@ -5009,7 +5009,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G160" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H160" t="n">
         <v>5460</v>
@@ -5038,7 +5038,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G161" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>1.25095200538635</v>
+        <v>1.25095212459564</v>
       </c>
       <c r="H164" t="n">
         <v>780</v>
@@ -5154,7 +5154,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G165" t="n">
-        <v>1.27925097942352</v>
+        <v>1.27925086021423</v>
       </c>
       <c r="H165" t="n">
         <v>780</v>
@@ -5357,7 +5357,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G172" t="n">
-        <v>1.3387508392334</v>
+        <v>1.33875095844269</v>
       </c>
       <c r="H172" t="n">
         <v>1560</v>
@@ -5386,7 +5386,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G173" t="n">
-        <v>1.33947646617889</v>
+        <v>1.33947658538818</v>
       </c>
       <c r="H173" t="n">
         <v>780</v>
@@ -5415,7 +5415,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H174" t="n">
         <v>780</v>
@@ -5444,7 +5444,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G175" t="n">
-        <v>1.36269617080688</v>
+        <v>1.36269593238831</v>
       </c>
       <c r="H175" t="n">
         <v>780</v>
@@ -5473,7 +5473,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G176" t="n">
-        <v>1.36269617080688</v>
+        <v>1.36269593238831</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.32061064243317</v>
+        <v>1.32061076164246</v>
       </c>
       <c r="H190" t="n">
         <v>2340</v>
@@ -5966,7 +5966,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G193" t="n">
-        <v>1.24224483966827</v>
+        <v>1.24224472045898</v>
       </c>
       <c r="H193" t="n">
         <v>1560</v>
@@ -5995,7 +5995,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G194" t="n">
-        <v>1.24224483966827</v>
+        <v>1.24224472045898</v>
       </c>
       <c r="H194" t="n">
         <v>780</v>
@@ -6285,7 +6285,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H204" t="n">
         <v>1560</v>
@@ -6314,7 +6314,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G207" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G210" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G211" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G212" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H212" t="n">
         <v>780</v>
@@ -6546,7 +6546,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H213" t="n">
         <v>1560</v>
@@ -6575,7 +6575,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H218" t="n">
         <v>780</v>
@@ -6720,7 +6720,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>1.25530564785004</v>
+        <v>1.25530576705933</v>
       </c>
       <c r="H230" t="n">
         <v>7020</v>
@@ -7126,7 +7126,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H233" t="n">
         <v>6240</v>
@@ -7155,7 +7155,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G239" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H239" t="n">
         <v>3120</v>
@@ -7329,7 +7329,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G240" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H240" t="n">
         <v>1560</v>
@@ -7387,7 +7387,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H242" t="n">
         <v>1560</v>
@@ -7416,7 +7416,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H243" t="n">
         <v>16380</v>
@@ -7909,7 +7909,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G260" t="n">
-        <v>1.25240325927734</v>
+        <v>1.25240337848663</v>
       </c>
       <c r="H260" t="n">
         <v>3120</v>
@@ -8286,7 +8286,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G273" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H273" t="n">
         <v>3900</v>
@@ -8402,7 +8402,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G277" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H277" t="n">
         <v>13260</v>
@@ -8431,7 +8431,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G278" t="n">
-        <v>1.46718394756317</v>
+        <v>1.46718406677246</v>
       </c>
       <c r="H278" t="n">
         <v>15600</v>
@@ -8460,7 +8460,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>1.40768396854401</v>
+        <v>1.40768384933472</v>
       </c>
       <c r="H279" t="n">
         <v>7020</v>
@@ -8518,7 +8518,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G281" t="n">
-        <v>1.42727541923523</v>
+        <v>1.42727530002594</v>
       </c>
       <c r="H281" t="n">
         <v>7800</v>
@@ -8576,7 +8576,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32133626937866</v>
+        <v>1.32133615016937</v>
       </c>
       <c r="H283" t="n">
         <v>3900</v>
@@ -8750,7 +8750,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>1.20741558074951</v>
+        <v>1.20741546154022</v>
       </c>
       <c r="H289" t="n">
         <v>24180</v>
@@ -8779,7 +8779,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G290" t="n">
-        <v>1.21176910400391</v>
+        <v>1.21176898479462</v>
       </c>
       <c r="H290" t="n">
         <v>1560</v>
@@ -8808,7 +8808,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G291" t="n">
-        <v>1.21176910400391</v>
+        <v>1.21176898479462</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G292" t="n">
-        <v>1.21176910400391</v>
+        <v>1.21176898479462</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.21176910400391</v>
+        <v>1.21176898479462</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G294" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H294" t="n">
         <v>3900</v>
@@ -8924,7 +8924,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G295" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H295" t="n">
         <v>3120</v>
@@ -8953,7 +8953,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G296" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.17186045646667</v>
+        <v>1.17186057567596</v>
       </c>
       <c r="H297" t="n">
         <v>3120</v>
@@ -9185,7 +9185,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G304" t="n">
-        <v>1.24950087070465</v>
+        <v>1.24950075149536</v>
       </c>
       <c r="H304" t="n">
         <v>780</v>
@@ -9243,7 +9243,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G306" t="n">
-        <v>1.37865948677063</v>
+        <v>1.37865936756134</v>
       </c>
       <c r="H306" t="n">
         <v>7800</v>
@@ -9301,7 +9301,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G308" t="n">
-        <v>1.34890937805176</v>
+        <v>1.34890949726105</v>
       </c>
       <c r="H308" t="n">
         <v>1560</v>
@@ -9330,7 +9330,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G309" t="n">
-        <v>1.34890937805176</v>
+        <v>1.34890949726105</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>1.42219603061676</v>
+        <v>1.42219614982605</v>
       </c>
       <c r="H317" t="n">
         <v>3120</v>
@@ -9591,7 +9591,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>1.48459851741791</v>
+        <v>1.4845986366272</v>
       </c>
       <c r="H318" t="n">
         <v>7800</v>
@@ -9620,7 +9620,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52378141880035</v>
+        <v>1.52378153800964</v>
       </c>
       <c r="H319" t="n">
         <v>30420</v>
@@ -9678,7 +9678,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H321" t="n">
         <v>83460</v>
@@ -9707,7 +9707,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G322" t="n">
-        <v>1.67035484313965</v>
+        <v>1.67035472393036</v>
       </c>
       <c r="H322" t="n">
         <v>65520</v>
@@ -9736,7 +9736,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H323" t="n">
         <v>76440</v>
@@ -9823,7 +9823,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H326" t="n">
         <v>30420</v>
@@ -9910,7 +9910,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G329" t="n">
-        <v>1.5107204914093</v>
+        <v>1.51072061061859</v>
       </c>
       <c r="H329" t="n">
         <v>9360</v>
@@ -9939,7 +9939,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G330" t="n">
-        <v>1.52378141880035</v>
+        <v>1.52378153800964</v>
       </c>
       <c r="H330" t="n">
         <v>10140</v>
@@ -9997,7 +9997,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G332" t="n">
-        <v>1.40478146076202</v>
+        <v>1.40478134155273</v>
       </c>
       <c r="H332" t="n">
         <v>53040</v>
@@ -10084,7 +10084,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G335" t="n">
-        <v>1.43815958499908</v>
+        <v>1.43815946578979</v>
       </c>
       <c r="H335" t="n">
         <v>56160</v>
@@ -10113,7 +10113,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G336" t="n">
-        <v>1.40260446071625</v>
+        <v>1.40260457992554</v>
       </c>
       <c r="H336" t="n">
         <v>83460</v>
@@ -10142,7 +10142,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>1.37430596351624</v>
+        <v>1.37430584430695</v>
       </c>
       <c r="H337" t="n">
         <v>27300</v>
@@ -10171,7 +10171,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G338" t="n">
-        <v>1.42945218086243</v>
+        <v>1.42945230007172</v>
       </c>
       <c r="H338" t="n">
         <v>17160</v>
@@ -10229,7 +10229,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G340" t="n">
-        <v>1.41493988037109</v>
+        <v>1.41494011878967</v>
       </c>
       <c r="H340" t="n">
         <v>10140</v>
@@ -10287,7 +10287,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>1.42945218086243</v>
+        <v>1.42945230007172</v>
       </c>
       <c r="H342" t="n">
         <v>24960</v>
@@ -10316,7 +10316,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G343" t="n">
-        <v>1.44178748130798</v>
+        <v>1.44178760051727</v>
       </c>
       <c r="H343" t="n">
         <v>8580</v>
@@ -10345,7 +10345,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>1.40768396854401</v>
+        <v>1.40768384933472</v>
       </c>
       <c r="H344" t="n">
         <v>6240</v>
@@ -10374,7 +10374,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G345" t="n">
-        <v>1.41493988037109</v>
+        <v>1.41494011878967</v>
       </c>
       <c r="H345" t="n">
         <v>14040</v>
@@ -10432,7 +10432,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G347" t="n">
-        <v>1.47298884391785</v>
+        <v>1.47298872470856</v>
       </c>
       <c r="H347" t="n">
         <v>5460</v>
@@ -10461,7 +10461,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G348" t="n">
-        <v>1.55861079692841</v>
+        <v>1.5586109161377</v>
       </c>
       <c r="H348" t="n">
         <v>28080</v>
@@ -10548,7 +10548,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G351" t="n">
-        <v>1.41566562652588</v>
+        <v>1.41566550731659</v>
       </c>
       <c r="H351" t="n">
         <v>35100</v>
@@ -10635,7 +10635,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>1.43235456943512</v>
+        <v>1.43235468864441</v>
       </c>
       <c r="H354" t="n">
         <v>6240</v>
@@ -10664,7 +10664,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G355" t="n">
-        <v>1.47008645534515</v>
+        <v>1.47008633613586</v>
       </c>
       <c r="H355" t="n">
         <v>2340</v>
@@ -10693,7 +10693,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G356" t="n">
-        <v>1.43453133106232</v>
+        <v>1.43453145027161</v>
       </c>
       <c r="H356" t="n">
         <v>20280</v>
@@ -10751,7 +10751,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>1.49330592155457</v>
+        <v>1.49330604076385</v>
       </c>
       <c r="H358" t="n">
         <v>11700</v>
@@ -10867,7 +10867,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H362" t="n">
         <v>10140</v>
@@ -11012,7 +11012,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G367" t="n">
-        <v>1.54554986953735</v>
+        <v>1.54554998874664</v>
       </c>
       <c r="H367" t="n">
         <v>16380</v>
@@ -11070,7 +11070,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.5847327709198</v>
+        <v>1.58473289012909</v>
       </c>
       <c r="H369" t="n">
         <v>21840</v>
@@ -11099,7 +11099,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H370" t="n">
         <v>38220</v>
@@ -11157,7 +11157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H372" t="n">
         <v>10920</v>
@@ -11273,7 +11273,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G376" t="n">
-        <v>1.59344029426575</v>
+        <v>1.59344017505646</v>
       </c>
       <c r="H376" t="n">
         <v>2340</v>
@@ -11360,7 +11360,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.77919614315033</v>
+        <v>1.77919626235962</v>
       </c>
       <c r="H379" t="n">
         <v>138840</v>
@@ -11505,7 +11505,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G384" t="n">
-        <v>2.10281848907471</v>
+        <v>2.10281872749329</v>
       </c>
       <c r="H384" t="n">
         <v>68640</v>
@@ -11534,7 +11534,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G385" t="n">
-        <v>2.16522121429443</v>
+        <v>2.16522097587585</v>
       </c>
       <c r="H385" t="n">
         <v>147420</v>
@@ -11563,7 +11563,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>2.0999162197113</v>
+        <v>2.09991598129272</v>
       </c>
       <c r="H386" t="n">
         <v>116220</v>
@@ -11592,7 +11592,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>2.0331597328186</v>
+        <v>2.03315997123718</v>
       </c>
       <c r="H387" t="n">
         <v>159120</v>
@@ -11621,7 +11621,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G388" t="n">
-        <v>1.98817217350006</v>
+        <v>1.98817205429077</v>
       </c>
       <c r="H388" t="n">
         <v>55380</v>
@@ -11650,7 +11650,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G389" t="n">
-        <v>2.00558662414551</v>
+        <v>2.00558686256409</v>
       </c>
       <c r="H389" t="n">
         <v>10920</v>
@@ -11708,7 +11708,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G391" t="n">
-        <v>1.93447697162628</v>
+        <v>1.93447685241699</v>
       </c>
       <c r="H391" t="n">
         <v>17940</v>
@@ -11766,7 +11766,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318425655365</v>
+        <v>1.94318413734436</v>
       </c>
       <c r="H393" t="n">
         <v>3900</v>
@@ -11795,7 +11795,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G394" t="n">
-        <v>1.90109872817993</v>
+        <v>1.90109884738922</v>
       </c>
       <c r="H394" t="n">
         <v>17160</v>
@@ -11824,7 +11824,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G395" t="n">
-        <v>1.86917209625244</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H395" t="n">
         <v>8580</v>
@@ -11853,7 +11853,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G396" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128167152405</v>
       </c>
       <c r="H396" t="n">
         <v>21060</v>
@@ -11940,7 +11940,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98817217350006</v>
+        <v>1.98817205429077</v>
       </c>
       <c r="H399" t="n">
         <v>11700</v>
@@ -11998,7 +11998,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G401" t="n">
-        <v>1.89239168167114</v>
+        <v>1.89239156246185</v>
       </c>
       <c r="H401" t="n">
         <v>15600</v>
@@ -12027,7 +12027,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.86191582679749</v>
+        <v>1.86191594600677</v>
       </c>
       <c r="H402" t="n">
         <v>91260</v>
@@ -12056,7 +12056,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G403" t="n">
-        <v>1.78645253181458</v>
+        <v>1.786452293396</v>
       </c>
       <c r="H403" t="n">
         <v>37440</v>
@@ -12085,7 +12085,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563543319702</v>
+        <v>1.82563555240631</v>
       </c>
       <c r="H404" t="n">
         <v>66300</v>
@@ -12114,7 +12114,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H405" t="n">
         <v>109200</v>
@@ -12143,7 +12143,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H406" t="n">
         <v>160680</v>
@@ -12172,7 +12172,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G407" t="n">
-        <v>1.75742793083191</v>
+        <v>1.7574280500412</v>
       </c>
       <c r="H407" t="n">
         <v>31980</v>
@@ -12230,7 +12230,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G409" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H409" t="n">
         <v>10140</v>
@@ -12288,7 +12288,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>1.78935503959656</v>
+        <v>1.78935492038727</v>
       </c>
       <c r="H411" t="n">
         <v>780</v>
@@ -12317,7 +12317,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G412" t="n">
-        <v>1.78935503959656</v>
+        <v>1.78935492038727</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H417" t="n">
         <v>48360</v>
@@ -12491,7 +12491,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G418" t="n">
-        <v>1.65874493122101</v>
+        <v>1.6587450504303</v>
       </c>
       <c r="H418" t="n">
         <v>25740</v>
@@ -12665,7 +12665,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G424" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837952136993</v>
       </c>
       <c r="H424" t="n">
         <v>19500</v>
@@ -12781,7 +12781,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G428" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H428" t="n">
         <v>27300</v>
@@ -12810,7 +12810,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G429" t="n">
-        <v>1.94898927211761</v>
+        <v>1.94898915290833</v>
       </c>
       <c r="H429" t="n">
         <v>84240</v>
@@ -12868,7 +12868,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H431" t="n">
         <v>25740</v>
@@ -12897,7 +12897,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H432" t="n">
         <v>12480</v>
@@ -12955,7 +12955,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H434" t="n">
         <v>18720</v>
@@ -12984,7 +12984,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>1.85175740718842</v>
+        <v>1.85175728797913</v>
       </c>
       <c r="H435" t="n">
         <v>10140</v>
@@ -13013,7 +13013,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>1.8575621843338</v>
+        <v>1.85756230354309</v>
       </c>
       <c r="H436" t="n">
         <v>3900</v>
@@ -13042,7 +13042,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G437" t="n">
-        <v>1.81112337112427</v>
+        <v>1.81112325191498</v>
       </c>
       <c r="H437" t="n">
         <v>24960</v>
@@ -13071,7 +13071,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G438" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H438" t="n">
         <v>8580</v>
@@ -13100,7 +13100,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>1.85030627250671</v>
+        <v>1.85030603408813</v>
       </c>
       <c r="H439" t="n">
         <v>46020</v>
@@ -13129,7 +13129,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>1.83724510669708</v>
+        <v>1.83724522590637</v>
       </c>
       <c r="H440" t="n">
         <v>16380</v>
@@ -13158,7 +13158,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G441" t="n">
-        <v>1.84595239162445</v>
+        <v>1.84595227241516</v>
       </c>
       <c r="H441" t="n">
         <v>780</v>
@@ -13216,7 +13216,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G443" t="n">
-        <v>1.87352573871613</v>
+        <v>1.87352561950684</v>
       </c>
       <c r="H443" t="n">
         <v>24180</v>
@@ -13303,7 +13303,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G446" t="n">
-        <v>2.01139163970947</v>
+        <v>2.01139187812805</v>
       </c>
       <c r="H446" t="n">
         <v>130260</v>
@@ -13332,7 +13332,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G447" t="n">
-        <v>1.97801375389099</v>
+        <v>1.9780136346817</v>
       </c>
       <c r="H447" t="n">
         <v>216060</v>
@@ -13361,7 +13361,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93302583694458</v>
+        <v>1.93302571773529</v>
       </c>
       <c r="H448" t="n">
         <v>14040</v>
@@ -13390,7 +13390,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G449" t="n">
-        <v>1.86917209625244</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H449" t="n">
         <v>28860</v>
@@ -13419,7 +13419,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>1.89964771270752</v>
+        <v>1.89964759349823</v>
       </c>
       <c r="H450" t="n">
         <v>81120</v>
@@ -13448,7 +13448,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G451" t="n">
-        <v>1.86917209625244</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H451" t="n">
         <v>76440</v>
@@ -13477,7 +13477,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>1.85030627250671</v>
+        <v>1.85030603408813</v>
       </c>
       <c r="H452" t="n">
         <v>22620</v>
@@ -13535,7 +13535,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207436561584</v>
+        <v>1.87207424640656</v>
       </c>
       <c r="H454" t="n">
         <v>31200</v>
@@ -13564,7 +13564,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>1.8575621843338</v>
+        <v>1.85756230354309</v>
       </c>
       <c r="H455" t="n">
         <v>18720</v>
@@ -13622,7 +13622,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H457" t="n">
         <v>205920</v>
@@ -13680,7 +13680,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G459" t="n">
-        <v>1.88513553142548</v>
+        <v>1.8851352930069</v>
       </c>
       <c r="H459" t="n">
         <v>58500</v>
@@ -13709,7 +13709,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>1.90109872817993</v>
+        <v>1.90109884738922</v>
       </c>
       <c r="H460" t="n">
         <v>16380</v>
@@ -13738,7 +13738,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G461" t="n">
-        <v>1.87787938117981</v>
+        <v>1.87787926197052</v>
       </c>
       <c r="H461" t="n">
         <v>12480</v>
@@ -13767,7 +13767,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>1.92141592502594</v>
+        <v>1.92141604423523</v>
       </c>
       <c r="H462" t="n">
         <v>85800</v>
@@ -13796,7 +13796,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G463" t="n">
-        <v>1.94463539123535</v>
+        <v>1.94463551044464</v>
       </c>
       <c r="H463" t="n">
         <v>32760</v>
@@ -13825,7 +13825,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G464" t="n">
-        <v>1.94463539123535</v>
+        <v>1.94463551044464</v>
       </c>
       <c r="H464" t="n">
         <v>11700</v>
@@ -13854,7 +13854,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G465" t="n">
-        <v>1.94463539123535</v>
+        <v>1.94463551044464</v>
       </c>
       <c r="H465" t="n">
         <v>14820</v>
@@ -13883,7 +13883,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G466" t="n">
-        <v>1.94463539123535</v>
+        <v>1.94463551044464</v>
       </c>
       <c r="H466" t="n">
         <v>137280</v>
@@ -13912,7 +13912,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>1.90835499763489</v>
+        <v>1.90835511684418</v>
       </c>
       <c r="H467" t="n">
         <v>35100</v>
@@ -13941,7 +13941,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>1.90109872817993</v>
+        <v>1.90109884738922</v>
       </c>
       <c r="H468" t="n">
         <v>78000</v>
@@ -13970,7 +13970,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>1.92286729812622</v>
+        <v>1.92286717891693</v>
       </c>
       <c r="H469" t="n">
         <v>34320</v>
@@ -13999,7 +13999,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G470" t="n">
-        <v>1.90254998207092</v>
+        <v>1.90255010128021</v>
       </c>
       <c r="H470" t="n">
         <v>18720</v>
@@ -14028,7 +14028,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G471" t="n">
-        <v>1.9040013551712</v>
+        <v>1.90400123596191</v>
       </c>
       <c r="H471" t="n">
         <v>3900</v>
@@ -14057,7 +14057,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>1.89094030857086</v>
+        <v>1.89094018936157</v>
       </c>
       <c r="H472" t="n">
         <v>6240</v>
@@ -14086,7 +14086,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G473" t="n">
-        <v>1.90254998207092</v>
+        <v>1.90255010128021</v>
       </c>
       <c r="H473" t="n">
         <v>15600</v>
@@ -14144,7 +14144,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G475" t="n">
-        <v>1.90980613231659</v>
+        <v>1.90980637073517</v>
       </c>
       <c r="H475" t="n">
         <v>13260</v>
@@ -14202,7 +14202,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G477" t="n">
-        <v>1.82273292541504</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H477" t="n">
         <v>10920</v>
@@ -14231,7 +14231,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G478" t="n">
-        <v>1.82273292541504</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H478" t="n">
         <v>13260</v>
@@ -14260,7 +14260,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>1.82273292541504</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H479" t="n">
         <v>6240</v>
@@ -14318,7 +14318,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>1.72114741802216</v>
+        <v>1.72114753723145</v>
       </c>
       <c r="H481" t="n">
         <v>14820</v>
@@ -14347,7 +14347,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G482" t="n">
-        <v>1.80822086334229</v>
+        <v>1.808220744133</v>
       </c>
       <c r="H482" t="n">
         <v>25740</v>
@@ -14405,7 +14405,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G484" t="n">
-        <v>1.80096471309662</v>
+        <v>1.80096483230591</v>
       </c>
       <c r="H484" t="n">
         <v>2340</v>
@@ -14492,7 +14492,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G487" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837952136993</v>
       </c>
       <c r="H487" t="n">
         <v>2340</v>
@@ -14608,7 +14608,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G491" t="n">
-        <v>1.83869624137878</v>
+        <v>1.83869636058807</v>
       </c>
       <c r="H491" t="n">
         <v>9360</v>
@@ -14637,7 +14637,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G492" t="n">
-        <v>1.85175740718842</v>
+        <v>1.85175728797913</v>
       </c>
       <c r="H492" t="n">
         <v>14040</v>
@@ -14666,7 +14666,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G493" t="n">
-        <v>1.84159874916077</v>
+        <v>1.84159886837006</v>
       </c>
       <c r="H493" t="n">
         <v>49920</v>
@@ -14724,7 +14724,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H495" t="n">
         <v>34320</v>
@@ -14753,7 +14753,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>1.828537940979</v>
+        <v>1.82853770256042</v>
       </c>
       <c r="H496" t="n">
         <v>50700</v>
@@ -14898,7 +14898,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G501" t="n">
-        <v>1.8836841583252</v>
+        <v>1.88368427753448</v>
       </c>
       <c r="H501" t="n">
         <v>10140</v>
@@ -14927,7 +14927,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G502" t="n">
-        <v>1.87062323093414</v>
+        <v>1.87062346935272</v>
       </c>
       <c r="H502" t="n">
         <v>10140</v>
@@ -14956,7 +14956,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128167152405</v>
       </c>
       <c r="H503" t="n">
         <v>7020</v>
@@ -15130,7 +15130,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G509" t="n">
-        <v>1.80096471309662</v>
+        <v>1.80096483230591</v>
       </c>
       <c r="H509" t="n">
         <v>5460</v>
@@ -15304,7 +15304,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>1.828537940979</v>
+        <v>1.82853770256042</v>
       </c>
       <c r="H515" t="n">
         <v>9360</v>
@@ -15362,7 +15362,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>1.85030627250671</v>
+        <v>1.85030603408813</v>
       </c>
       <c r="H517" t="n">
         <v>16380</v>
@@ -15449,7 +15449,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G520" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H520" t="n">
         <v>17160</v>
@@ -15507,7 +15507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H522" t="n">
         <v>3120</v>
@@ -15536,7 +15536,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G523" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H523" t="n">
         <v>2340</v>
@@ -15565,7 +15565,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H524" t="n">
         <v>7020</v>
@@ -15594,7 +15594,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G525" t="n">
-        <v>1.8865864276886</v>
+        <v>1.88658654689789</v>
       </c>
       <c r="H525" t="n">
         <v>31980</v>
@@ -15623,7 +15623,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G526" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128167152405</v>
       </c>
       <c r="H526" t="n">
         <v>11700</v>
@@ -15652,7 +15652,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>1.8575621843338</v>
+        <v>1.85756230354309</v>
       </c>
       <c r="H527" t="n">
         <v>8580</v>
@@ -15681,7 +15681,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>1.92286729812622</v>
+        <v>1.92286717891693</v>
       </c>
       <c r="H528" t="n">
         <v>124020</v>
@@ -15710,7 +15710,7 @@
         <v>2.75</v>
       </c>
       <c r="G529" t="n">
-        <v>1.99542820453644</v>
+        <v>1.99542808532715</v>
       </c>
       <c r="H529" t="n">
         <v>39780</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H530" t="n">
         <v>56940</v>
@@ -15768,7 +15768,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H531" t="n">
         <v>25740</v>
@@ -15826,7 +15826,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G533" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128167152405</v>
       </c>
       <c r="H533" t="n">
         <v>7800</v>
@@ -15855,7 +15855,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H534" t="n">
         <v>3900</v>
@@ -15884,7 +15884,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128167152405</v>
       </c>
       <c r="H535" t="n">
         <v>10920</v>
@@ -15913,7 +15913,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H536" t="n">
         <v>30420</v>
@@ -15942,7 +15942,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G537" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H537" t="n">
         <v>12480</v>
@@ -15971,7 +15971,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G538" t="n">
-        <v>1.79225730895996</v>
+        <v>1.79225742816925</v>
       </c>
       <c r="H538" t="n">
         <v>3120</v>
@@ -16029,7 +16029,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G540" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H540" t="n">
         <v>44460</v>
@@ -16087,7 +16087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H542" t="n">
         <v>19500</v>
@@ -16145,7 +16145,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H544" t="n">
         <v>1560</v>
@@ -16174,7 +16174,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G545" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H545" t="n">
         <v>61620</v>
@@ -16203,7 +16203,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G546" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H546" t="n">
         <v>10140</v>
@@ -16290,7 +16290,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G549" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H549" t="n">
         <v>23400</v>
@@ -16377,7 +16377,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G552" t="n">
-        <v>1.76323294639587</v>
+        <v>1.76323282718658</v>
       </c>
       <c r="H552" t="n">
         <v>780</v>
@@ -16435,7 +16435,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G554" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H554" t="n">
         <v>1560</v>
@@ -16464,7 +16464,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H555" t="n">
         <v>14820</v>
@@ -16522,7 +16522,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H557" t="n">
         <v>7800</v>
@@ -16551,7 +16551,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G558" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H558" t="n">
         <v>4680</v>
@@ -16580,7 +16580,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G559" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H559" t="n">
         <v>11700</v>
@@ -16609,7 +16609,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H560" t="n">
         <v>4680</v>
@@ -16638,7 +16638,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G561" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H561" t="n">
         <v>1560</v>
@@ -16667,7 +16667,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G562" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H562" t="n">
         <v>3120</v>
@@ -16696,7 +16696,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H563" t="n">
         <v>4680</v>
@@ -16725,7 +16725,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G564" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H564" t="n">
         <v>59280</v>
@@ -16841,7 +16841,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G568" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H568" t="n">
         <v>16380</v>
@@ -16899,7 +16899,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H570" t="n">
         <v>5460</v>
@@ -16928,7 +16928,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G571" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H571" t="n">
         <v>2340</v>
@@ -16986,7 +16986,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G573" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H573" t="n">
         <v>34320</v>
@@ -17015,7 +17015,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G574" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H574" t="n">
         <v>3900</v>
@@ -17044,7 +17044,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G575" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H575" t="n">
         <v>780</v>
@@ -17073,7 +17073,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H576" t="n">
         <v>22620</v>
@@ -17131,7 +17131,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H578" t="n">
         <v>1560</v>
@@ -17160,7 +17160,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G579" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H579" t="n">
         <v>7800</v>
@@ -17189,7 +17189,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G580" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H580" t="n">
         <v>1560</v>
@@ -17218,7 +17218,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H581" t="n">
         <v>3900</v>
@@ -17247,7 +17247,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H582" t="n">
         <v>17940</v>
@@ -17276,7 +17276,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H583" t="n">
         <v>8580</v>
@@ -17305,7 +17305,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H586" t="n">
         <v>7020</v>
@@ -17392,7 +17392,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H587" t="n">
         <v>7020</v>
@@ -17421,7 +17421,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H588" t="n">
         <v>6240</v>
@@ -17479,7 +17479,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H590" t="n">
         <v>1560</v>
@@ -17508,7 +17508,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G591" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H591" t="n">
         <v>3900</v>
@@ -17566,7 +17566,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G593" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H593" t="n">
         <v>780</v>
@@ -17595,7 +17595,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H594" t="n">
         <v>4680</v>
@@ -17740,7 +17740,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H599" t="n">
         <v>188760</v>
@@ -17827,7 +17827,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H602" t="n">
         <v>60060</v>
@@ -17856,7 +17856,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>1.76323294639587</v>
+        <v>1.76323282718658</v>
       </c>
       <c r="H603" t="n">
         <v>39000</v>
@@ -17885,7 +17885,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H604" t="n">
         <v>16380</v>
@@ -17914,7 +17914,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G605" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H605" t="n">
         <v>20280</v>
@@ -17943,7 +17943,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H606" t="n">
         <v>15600</v>
@@ -17972,7 +17972,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H607" t="n">
         <v>15600</v>
@@ -18001,7 +18001,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H608" t="n">
         <v>7020</v>
@@ -18030,7 +18030,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G609" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H609" t="n">
         <v>24180</v>
@@ -18059,7 +18059,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H610" t="n">
         <v>12480</v>
@@ -18117,7 +18117,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>1.57457423210144</v>
+        <v>1.57457435131073</v>
       </c>
       <c r="H612" t="n">
         <v>10140</v>
@@ -18146,7 +18146,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>1.57457423210144</v>
+        <v>1.57457435131073</v>
       </c>
       <c r="H613" t="n">
         <v>43680</v>
@@ -18175,7 +18175,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G614" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H614" t="n">
         <v>23400</v>
@@ -18233,7 +18233,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>1.48750102519989</v>
+        <v>1.4875009059906</v>
       </c>
       <c r="H616" t="n">
         <v>27300</v>
@@ -18262,7 +18262,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>1.54554986953735</v>
+        <v>1.54554998874664</v>
       </c>
       <c r="H617" t="n">
         <v>14040</v>
@@ -18291,7 +18291,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G618" t="n">
-        <v>1.54554986953735</v>
+        <v>1.54554998874664</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>1.52378141880035</v>
+        <v>1.52378153800964</v>
       </c>
       <c r="H622" t="n">
         <v>10140</v>
@@ -18436,7 +18436,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G623" t="n">
-        <v>1.55280601978302</v>
+        <v>1.55280590057373</v>
       </c>
       <c r="H623" t="n">
         <v>780</v>
@@ -18465,7 +18465,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G624" t="n">
-        <v>1.55280601978302</v>
+        <v>1.55280590057373</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18610,7 +18610,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G629" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H629" t="n">
         <v>8580</v>
@@ -18639,7 +18639,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G630" t="n">
-        <v>1.52378141880035</v>
+        <v>1.52378153800964</v>
       </c>
       <c r="H630" t="n">
         <v>780</v>
@@ -18668,7 +18668,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G631" t="n">
-        <v>1.52378141880035</v>
+        <v>1.52378153800964</v>
       </c>
       <c r="H631" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>1.52378141880035</v>
+        <v>1.52378153800964</v>
       </c>
       <c r="H637" t="n">
         <v>5460</v>
@@ -19016,7 +19016,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H643" t="n">
         <v>102180</v>
@@ -19074,7 +19074,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.74872076511383</v>
+        <v>1.74872088432312</v>
       </c>
       <c r="H645" t="n">
         <v>30420</v>
@@ -19132,7 +19132,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H647" t="n">
         <v>7800</v>
@@ -19161,7 +19161,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H648" t="n">
         <v>26520</v>
@@ -19277,7 +19277,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H652" t="n">
         <v>9360</v>
@@ -19306,7 +19306,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G653" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H653" t="n">
         <v>1560</v>
@@ -19335,7 +19335,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H654" t="n">
         <v>4680</v>
@@ -19451,7 +19451,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G658" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H658" t="n">
         <v>2340</v>
@@ -19480,7 +19480,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H659" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G660" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G662" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H662" t="n">
         <v>3900</v>
@@ -19596,7 +19596,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H664" t="n">
         <v>10140</v>
@@ -19654,7 +19654,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G668" t="n">
-        <v>1.54554986953735</v>
+        <v>1.54554998874664</v>
       </c>
       <c r="H668" t="n">
         <v>8580</v>
@@ -19915,7 +19915,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H674" t="n">
         <v>1560</v>
@@ -20002,7 +20002,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G677" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H677" t="n">
         <v>780</v>
@@ -20031,7 +20031,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>1.67615950107574</v>
+        <v>1.67615962028503</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G679" t="n">
-        <v>1.61085474491119</v>
+        <v>1.61085486412048</v>
       </c>
       <c r="H679" t="n">
         <v>5460</v>
@@ -20089,7 +20089,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G680" t="n">
-        <v>1.61085474491119</v>
+        <v>1.61085486412048</v>
       </c>
       <c r="H680" t="n">
         <v>780</v>
@@ -20118,7 +20118,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H681" t="n">
         <v>3900</v>
@@ -20147,7 +20147,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G682" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H682" t="n">
         <v>5460</v>
@@ -20176,7 +20176,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H683" t="n">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G684" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H684" t="n">
         <v>780</v>
@@ -20234,7 +20234,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H685" t="n">
         <v>0</v>
@@ -20292,7 +20292,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G687" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H687" t="n">
         <v>780</v>
@@ -20437,7 +20437,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H692" t="n">
         <v>1560</v>
@@ -20495,7 +20495,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G694" t="n">
-        <v>1.62536704540253</v>
+        <v>1.62536692619324</v>
       </c>
       <c r="H694" t="n">
         <v>10140</v>
@@ -20524,7 +20524,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>1.79225730895996</v>
+        <v>1.79225742816925</v>
       </c>
       <c r="H695" t="n">
         <v>46020</v>
@@ -20553,7 +20553,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G696" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H696" t="n">
         <v>55380</v>
@@ -20582,7 +20582,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H697" t="n">
         <v>6240</v>
@@ -20611,7 +20611,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H698" t="n">
         <v>4680</v>
@@ -20814,7 +20814,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H705" t="n">
         <v>22620</v>
@@ -20843,7 +20843,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G706" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792795181274</v>
       </c>
       <c r="H706" t="n">
         <v>18720</v>
@@ -20901,7 +20901,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G708" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H708" t="n">
         <v>5460</v>
@@ -20959,7 +20959,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G710" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H710" t="n">
         <v>69420</v>
@@ -21017,7 +21017,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G712" t="n">
-        <v>1.74872076511383</v>
+        <v>1.74872088432312</v>
       </c>
       <c r="H712" t="n">
         <v>28860</v>
@@ -21104,7 +21104,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79225730895996</v>
+        <v>1.79225742816925</v>
       </c>
       <c r="H715" t="n">
         <v>20280</v>
@@ -21133,7 +21133,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G716" t="n">
-        <v>1.79225730895996</v>
+        <v>1.79225742816925</v>
       </c>
       <c r="H716" t="n">
         <v>18720</v>
@@ -21162,7 +21162,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225730895996</v>
+        <v>1.79225742816925</v>
       </c>
       <c r="H717" t="n">
         <v>9360</v>
@@ -21220,7 +21220,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G719" t="n">
-        <v>1.76323294639587</v>
+        <v>1.76323282718658</v>
       </c>
       <c r="H719" t="n">
         <v>9360</v>
@@ -21249,7 +21249,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G720" t="n">
-        <v>1.79225730895996</v>
+        <v>1.79225742816925</v>
       </c>
       <c r="H720" t="n">
         <v>18720</v>
@@ -21278,7 +21278,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G721" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H721" t="n">
         <v>14040</v>
@@ -21307,7 +21307,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G722" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G723" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H724" t="n">
         <v>1560</v>
@@ -21394,7 +21394,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H725" t="n">
         <v>1560</v>
@@ -21423,7 +21423,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G726" t="n">
-        <v>1.79225730895996</v>
+        <v>1.79225742816925</v>
       </c>
       <c r="H726" t="n">
         <v>2340</v>
@@ -21481,7 +21481,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H728" t="n">
         <v>780</v>
@@ -21539,7 +21539,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H730" t="n">
         <v>780</v>
@@ -21684,7 +21684,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G735" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H735" t="n">
         <v>7800</v>
@@ -21713,7 +21713,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G736" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H736" t="n">
         <v>24960</v>
@@ -21771,7 +21771,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>1.76323294639587</v>
+        <v>1.76323282718658</v>
       </c>
       <c r="H738" t="n">
         <v>4680</v>
@@ -21800,7 +21800,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G739" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H739" t="n">
         <v>780</v>
@@ -21829,7 +21829,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G740" t="n">
-        <v>1.77774512767792</v>
+        <v>1.77774524688721</v>
       </c>
       <c r="H740" t="n">
         <v>29640</v>
@@ -21887,7 +21887,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H742" t="n">
         <v>780</v>
@@ -21916,7 +21916,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G743" t="n">
-        <v>1.79225730895996</v>
+        <v>1.79225742816925</v>
       </c>
       <c r="H743" t="n">
         <v>3120</v>
@@ -21945,7 +21945,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>1.828537940979</v>
+        <v>1.82853770256042</v>
       </c>
       <c r="H744" t="n">
         <v>2340</v>
@@ -21974,7 +21974,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H745" t="n">
         <v>780</v>
@@ -22003,7 +22003,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H746" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H752" t="n">
         <v>1560</v>
@@ -22206,7 +22206,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G753" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G754" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H754" t="n">
         <v>28080</v>
@@ -22264,7 +22264,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G755" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H755" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G756" t="n">
-        <v>1.74872076511383</v>
+        <v>1.74872088432312</v>
       </c>
       <c r="H756" t="n">
         <v>3120</v>
@@ -22322,7 +22322,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>1.74872076511383</v>
+        <v>1.74872088432312</v>
       </c>
       <c r="H757" t="n">
         <v>2340</v>
@@ -22351,7 +22351,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G758" t="n">
-        <v>1.74872076511383</v>
+        <v>1.74872088432312</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22380,7 +22380,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>1.72695255279541</v>
+        <v>1.72695243358612</v>
       </c>
       <c r="H759" t="n">
         <v>3120</v>
@@ -22496,7 +22496,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H763" t="n">
         <v>3900</v>
@@ -22525,7 +22525,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H764" t="n">
         <v>4680</v>
@@ -22554,7 +22554,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G765" t="n">
-        <v>1.6834157705307</v>
+        <v>1.68341565132141</v>
       </c>
       <c r="H765" t="n">
         <v>4680</v>
@@ -22612,7 +22612,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G767" t="n">
-        <v>1.7124400138855</v>
+        <v>1.71244013309479</v>
       </c>
       <c r="H767" t="n">
         <v>780</v>
@@ -22641,7 +22641,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G768" t="n">
-        <v>1.79225730895996</v>
+        <v>1.79225742816925</v>
       </c>
       <c r="H768" t="n">
         <v>1560</v>
@@ -22757,7 +22757,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>1.828537940979</v>
+        <v>1.82853770256042</v>
       </c>
       <c r="H772" t="n">
         <v>3120</v>
@@ -22786,7 +22786,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H773" t="n">
         <v>3120</v>
@@ -22815,7 +22815,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -22844,7 +22844,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G775" t="n">
-        <v>1.828537940979</v>
+        <v>1.82853770256042</v>
       </c>
       <c r="H775" t="n">
         <v>3120</v>
@@ -22873,7 +22873,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>1.8575621843338</v>
+        <v>1.85756230354309</v>
       </c>
       <c r="H776" t="n">
         <v>5460</v>
@@ -22902,7 +22902,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H777" t="n">
         <v>3900</v>
@@ -22931,7 +22931,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G778" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128167152405</v>
       </c>
       <c r="H778" t="n">
         <v>2340</v>
@@ -22960,7 +22960,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>1.82128179073334</v>
+        <v>1.82128167152405</v>
       </c>
       <c r="H779" t="n">
         <v>780</v>
@@ -22989,7 +22989,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G780" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H780" t="n">
         <v>94380</v>
@@ -23047,7 +23047,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>1.90109872817993</v>
+        <v>1.90109884738922</v>
       </c>
       <c r="H782" t="n">
         <v>19500</v>
@@ -23076,7 +23076,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90835499763489</v>
+        <v>1.90835511684418</v>
       </c>
       <c r="H783" t="n">
         <v>11700</v>
@@ -23105,7 +23105,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H784" t="n">
         <v>8580</v>
@@ -23163,7 +23163,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>1.96640372276306</v>
+        <v>1.96640396118164</v>
       </c>
       <c r="H786" t="n">
         <v>26520</v>
@@ -23221,7 +23221,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G788" t="n">
-        <v>2.01719665527344</v>
+        <v>2.01719641685486</v>
       </c>
       <c r="H788" t="n">
         <v>21060</v>
@@ -23250,7 +23250,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G789" t="n">
-        <v>2.06073307991028</v>
+        <v>2.0607328414917</v>
       </c>
       <c r="H789" t="n">
         <v>39780</v>
@@ -23279,7 +23279,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G790" t="n">
-        <v>2.01719665527344</v>
+        <v>2.01719641685486</v>
       </c>
       <c r="H790" t="n">
         <v>35880</v>
@@ -23366,7 +23366,7 @@
         <v>2.75</v>
       </c>
       <c r="G793" t="n">
-        <v>1.99542820453644</v>
+        <v>1.99542808532715</v>
       </c>
       <c r="H793" t="n">
         <v>9360</v>
@@ -23395,7 +23395,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.97365987300873</v>
+        <v>1.97365999221802</v>
       </c>
       <c r="H794" t="n">
         <v>5460</v>
@@ -23453,7 +23453,7 @@
         <v>2.75</v>
       </c>
       <c r="G796" t="n">
-        <v>1.99542820453644</v>
+        <v>1.99542808532715</v>
       </c>
       <c r="H796" t="n">
         <v>8580</v>
@@ -23511,7 +23511,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G798" t="n">
-        <v>1.97365987300873</v>
+        <v>1.97365999221802</v>
       </c>
       <c r="H798" t="n">
         <v>10920</v>
@@ -23569,7 +23569,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G800" t="n">
-        <v>2.01719665527344</v>
+        <v>2.01719641685486</v>
       </c>
       <c r="H800" t="n">
         <v>1560</v>
@@ -23685,7 +23685,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G804" t="n">
-        <v>2.11152577400208</v>
+        <v>2.11152601242065</v>
       </c>
       <c r="H804" t="n">
         <v>19500</v>
@@ -23714,7 +23714,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G805" t="n">
-        <v>2.13329410552979</v>
+        <v>2.13329434394836</v>
       </c>
       <c r="H805" t="n">
         <v>59280</v>
@@ -23743,7 +23743,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>2.13329410552979</v>
+        <v>2.13329434394836</v>
       </c>
       <c r="H806" t="n">
         <v>7800</v>
@@ -23772,7 +23772,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G807" t="n">
-        <v>2.11152577400208</v>
+        <v>2.11152601242065</v>
       </c>
       <c r="H807" t="n">
         <v>32760</v>
@@ -23801,7 +23801,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H808" t="n">
         <v>16380</v>
@@ -23888,7 +23888,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G811" t="n">
-        <v>2.09701347351074</v>
+        <v>2.09701371192932</v>
       </c>
       <c r="H811" t="n">
         <v>22620</v>
@@ -23917,7 +23917,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G812" t="n">
-        <v>2.1550624370575</v>
+        <v>2.15506267547607</v>
       </c>
       <c r="H812" t="n">
         <v>28860</v>
@@ -23946,7 +23946,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G813" t="n">
-        <v>2.18408703804016</v>
+        <v>2.18408679962158</v>
       </c>
       <c r="H813" t="n">
         <v>27300</v>
@@ -23975,7 +23975,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G814" t="n">
-        <v>2.16957473754883</v>
+        <v>2.16957449913025</v>
       </c>
       <c r="H814" t="n">
         <v>12480</v>
@@ -24004,7 +24004,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G815" t="n">
-        <v>2.16957473754883</v>
+        <v>2.16957449913025</v>
       </c>
       <c r="H815" t="n">
         <v>3900</v>
@@ -24265,7 +24265,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G824" t="n">
-        <v>2.29292869567871</v>
+        <v>2.29292845726013</v>
       </c>
       <c r="H824" t="n">
         <v>28860</v>
@@ -24294,7 +24294,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G825" t="n">
-        <v>2.28567218780518</v>
+        <v>2.28567242622375</v>
       </c>
       <c r="H825" t="n">
         <v>38220</v>
@@ -24323,7 +24323,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G826" t="n">
-        <v>2.29292869567871</v>
+        <v>2.29292845726013</v>
       </c>
       <c r="H826" t="n">
         <v>15600</v>
@@ -24352,7 +24352,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H827" t="n">
         <v>48360</v>
@@ -24410,7 +24410,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G829" t="n">
-        <v>2.30744051933289</v>
+        <v>2.30744075775146</v>
       </c>
       <c r="H829" t="n">
         <v>10140</v>
@@ -24468,7 +24468,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H831" t="n">
         <v>21060</v>
@@ -24526,7 +24526,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G833" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H833" t="n">
         <v>7800</v>
@@ -24555,7 +24555,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G834" t="n">
-        <v>2.34372091293335</v>
+        <v>2.34372115135193</v>
       </c>
       <c r="H834" t="n">
         <v>21060</v>
@@ -24584,7 +24584,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G835" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H835" t="n">
         <v>160680</v>
@@ -24729,7 +24729,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>2.38725757598877</v>
+        <v>2.38725781440735</v>
       </c>
       <c r="H840" t="n">
         <v>12897</v>
@@ -24845,7 +24845,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G844" t="n">
-        <v>2.34372091293335</v>
+        <v>2.34372115135193</v>
       </c>
       <c r="H844" t="n">
         <v>15924</v>
@@ -24903,7 +24903,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G846" t="n">
-        <v>2.30744051933289</v>
+        <v>2.30744075775146</v>
       </c>
       <c r="H846" t="n">
         <v>15073</v>
@@ -24990,7 +24990,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H849" t="n">
         <v>10904</v>
@@ -25019,7 +25019,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H850" t="n">
         <v>8210</v>
@@ -25077,7 +25077,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.29292869567871</v>
+        <v>2.29292845726013</v>
       </c>
       <c r="H852" t="n">
         <v>5016</v>
@@ -25106,7 +25106,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>2.32195281982422</v>
+        <v>2.3219530582428</v>
       </c>
       <c r="H853" t="n">
         <v>50</v>
@@ -25309,7 +25309,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H860" t="n">
         <v>76082</v>
@@ -25338,7 +25338,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.4017698764801</v>
+        <v>2.40176963806152</v>
       </c>
       <c r="H861" t="n">
         <v>16837</v>
@@ -25512,7 +25512,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G867" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H867" t="n">
         <v>10186</v>
@@ -25570,7 +25570,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G869" t="n">
-        <v>2.35097742080688</v>
+        <v>2.35097718238831</v>
       </c>
       <c r="H869" t="n">
         <v>9650</v>
@@ -25715,7 +25715,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>2.38725757598877</v>
+        <v>2.38725781440735</v>
       </c>
       <c r="H874" t="n">
         <v>4200</v>
@@ -25773,7 +25773,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.38725757598877</v>
+        <v>2.38725781440735</v>
       </c>
       <c r="H876" t="n">
         <v>4500</v>
@@ -25976,7 +25976,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G883" t="n">
-        <v>2.75731897354126</v>
+        <v>2.75731873512268</v>
       </c>
       <c r="H883" t="n">
         <v>172820</v>
@@ -26005,7 +26005,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>2.86616039276123</v>
+        <v>2.86616063117981</v>
       </c>
       <c r="H884" t="n">
         <v>57963</v>
@@ -26063,7 +26063,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G886" t="n">
-        <v>2.62670922279358</v>
+        <v>2.626708984375</v>
       </c>
       <c r="H886" t="n">
         <v>81513</v>
@@ -26150,7 +26150,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G889" t="n">
-        <v>2.78634309768677</v>
+        <v>2.78634333610535</v>
       </c>
       <c r="H889" t="n">
         <v>24677</v>
@@ -26179,7 +26179,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G890" t="n">
-        <v>2.85164833068848</v>
+        <v>2.85164856910706</v>
       </c>
       <c r="H890" t="n">
         <v>25193</v>
@@ -26295,7 +26295,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H894" t="n">
         <v>94893</v>
@@ -26353,7 +26353,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G896" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H896" t="n">
         <v>72677</v>
@@ -26440,7 +26440,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G899" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H899" t="n">
         <v>24854</v>
@@ -26527,7 +26527,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G902" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H902" t="n">
         <v>22470</v>
@@ -26701,7 +26701,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.69201397895813</v>
+        <v>2.69201421737671</v>
       </c>
       <c r="H908" t="n">
         <v>34513</v>
@@ -26730,7 +26730,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G909" t="n">
-        <v>2.75731897354126</v>
+        <v>2.75731873512268</v>
       </c>
       <c r="H909" t="n">
         <v>19473</v>
@@ -26817,7 +26817,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G912" t="n">
-        <v>2.78634309768677</v>
+        <v>2.78634333610535</v>
       </c>
       <c r="H912" t="n">
         <v>13525</v>
@@ -26846,7 +26846,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G913" t="n">
-        <v>2.85164833068848</v>
+        <v>2.85164856910706</v>
       </c>
       <c r="H913" t="n">
         <v>11840</v>
@@ -26875,7 +26875,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>2.69201397895813</v>
+        <v>2.69201421737671</v>
       </c>
       <c r="H914" t="n">
         <v>12512</v>
@@ -26904,7 +26904,7 @@
         <v>3.75</v>
       </c>
       <c r="G915" t="n">
-        <v>2.7210385799408</v>
+        <v>2.72103834152222</v>
       </c>
       <c r="H915" t="n">
         <v>13535</v>
@@ -26933,7 +26933,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G916" t="n">
-        <v>2.6775016784668</v>
+        <v>2.67750191688538</v>
       </c>
       <c r="H916" t="n">
         <v>25856</v>
@@ -27078,7 +27078,7 @@
         <v>3.75</v>
       </c>
       <c r="G921" t="n">
-        <v>2.7210385799408</v>
+        <v>2.72103834152222</v>
       </c>
       <c r="H921" t="n">
         <v>6560</v>
@@ -27107,7 +27107,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>2.75731897354126</v>
+        <v>2.75731873512268</v>
       </c>
       <c r="H922" t="n">
         <v>3293</v>
@@ -27339,7 +27339,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G930" t="n">
-        <v>2.94597768783569</v>
+        <v>2.94597744941711</v>
       </c>
       <c r="H930" t="n">
         <v>43272</v>
@@ -27397,7 +27397,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H932" t="n">
         <v>33419</v>
@@ -27484,7 +27484,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G935" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H935" t="n">
         <v>4741</v>
@@ -27571,7 +27571,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H938" t="n">
         <v>933</v>
@@ -27600,7 +27600,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G939" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H939" t="n">
         <v>11330</v>
@@ -27658,7 +27658,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G941" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H941" t="n">
         <v>30216</v>
@@ -27774,7 +27774,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G945" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H945" t="n">
         <v>76005</v>
@@ -27803,7 +27803,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H946" t="n">
         <v>19605</v>
@@ -27861,7 +27861,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>2.82987976074219</v>
+        <v>2.82988023757935</v>
       </c>
       <c r="H948" t="n">
         <v>14110</v>
@@ -27890,7 +27890,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G949" t="n">
-        <v>2.92420935630798</v>
+        <v>2.92420959472656</v>
       </c>
       <c r="H949" t="n">
         <v>11372</v>
@@ -27919,7 +27919,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G950" t="n">
-        <v>2.92420935630798</v>
+        <v>2.92420959472656</v>
       </c>
       <c r="H950" t="n">
         <v>90795</v>
@@ -27948,7 +27948,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G951" t="n">
-        <v>2.97500205039978</v>
+        <v>2.9750018119812</v>
       </c>
       <c r="H951" t="n">
         <v>11343</v>
@@ -28006,7 +28006,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H953" t="n">
         <v>9849</v>
@@ -28180,7 +28180,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G959" t="n">
-        <v>2.94597768783569</v>
+        <v>2.94597744941711</v>
       </c>
       <c r="H959" t="n">
         <v>1795</v>
@@ -28209,7 +28209,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>2.97500205039978</v>
+        <v>2.9750018119812</v>
       </c>
       <c r="H960" t="n">
         <v>1063</v>
@@ -28238,7 +28238,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04756283760071</v>
+        <v>3.04756307601929</v>
       </c>
       <c r="H961" t="n">
         <v>80606</v>
@@ -28267,7 +28267,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G962" t="n">
-        <v>3.04756283760071</v>
+        <v>3.04756307601929</v>
       </c>
       <c r="H962" t="n">
         <v>13068</v>
@@ -28441,7 +28441,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.09109973907471</v>
+        <v>3.09109997749329</v>
       </c>
       <c r="H968" t="n">
         <v>35917</v>
@@ -28528,7 +28528,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H971" t="n">
         <v>186625</v>
@@ -28586,7 +28586,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G973" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H973" t="n">
         <v>97364</v>
@@ -28673,7 +28673,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H976" t="n">
         <v>15487</v>
@@ -28731,7 +28731,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G978" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H978" t="n">
         <v>30478</v>
@@ -28789,7 +28789,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G980" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H980" t="n">
         <v>24764</v>
@@ -28876,7 +28876,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G983" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H983" t="n">
         <v>21629</v>
@@ -28905,7 +28905,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G984" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H984" t="n">
         <v>38692</v>
@@ -28963,7 +28963,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H986" t="n">
         <v>7440</v>
@@ -29050,7 +29050,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H989" t="n">
         <v>14239</v>
@@ -29108,7 +29108,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H991" t="n">
         <v>1571</v>
@@ -29166,7 +29166,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G993" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H993" t="n">
         <v>20606</v>
@@ -29224,7 +29224,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H995" t="n">
         <v>16856</v>
@@ -29282,7 +29282,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G997" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H997" t="n">
         <v>6558</v>
@@ -29311,7 +29311,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G998" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H998" t="n">
         <v>18950</v>
@@ -29340,7 +29340,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G999" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H999" t="n">
         <v>37168</v>
@@ -29369,7 +29369,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1000" t="n">
         <v>54268</v>
@@ -29398,7 +29398,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1001" t="n">
         <v>10476</v>
@@ -29427,7 +29427,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506344795227</v>
+        <v>3.34506320953369</v>
       </c>
       <c r="H1002" t="n">
         <v>39069</v>
@@ -29456,7 +29456,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506344795227</v>
+        <v>3.34506320953369</v>
       </c>
       <c r="H1003" t="n">
         <v>16302</v>
@@ -29543,7 +29543,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1006" t="n">
         <v>10001</v>
@@ -29572,7 +29572,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.27250242233276</v>
+        <v>3.27250266075134</v>
       </c>
       <c r="H1007" t="n">
         <v>9721</v>
@@ -29630,7 +29630,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1009" t="n">
         <v>15854</v>
@@ -29659,7 +29659,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1010" t="n">
         <v>47398</v>
@@ -29688,7 +29688,7 @@
         <v>4.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1011" t="n">
         <v>33300</v>
@@ -29717,7 +29717,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1012" t="n">
         <v>11599</v>
@@ -29804,7 +29804,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1015" t="n">
         <v>6208</v>
@@ -29862,7 +29862,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1017" t="n">
         <v>7311</v>
@@ -29920,7 +29920,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1019" t="n">
         <v>8234</v>
@@ -29949,7 +29949,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1020" t="n">
         <v>6405</v>
@@ -29978,7 +29978,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1021" t="n">
         <v>6794</v>
@@ -30007,7 +30007,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1022" t="n">
         <v>5304</v>
@@ -30036,7 +30036,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1023" t="n">
         <v>110997</v>
@@ -30065,7 +30065,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1024" t="n">
         <v>30338</v>
@@ -30094,7 +30094,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1025" t="n">
         <v>7029</v>
@@ -30123,7 +30123,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1026" t="n">
         <v>9496</v>
@@ -30239,7 +30239,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1030" t="n">
         <v>4817</v>
@@ -30384,7 +30384,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.3160388469696</v>
+        <v>3.31603908538818</v>
       </c>
       <c r="H1035" t="n">
         <v>1434</v>
@@ -30500,7 +30500,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1039" t="n">
         <v>5793</v>
@@ -30587,7 +30587,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.3160388469696</v>
+        <v>3.31603908538818</v>
       </c>
       <c r="H1042" t="n">
         <v>3589</v>
@@ -30616,7 +30616,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1043" t="n">
         <v>7290</v>
@@ -30645,7 +30645,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1044" t="n">
         <v>14888</v>
@@ -30674,7 +30674,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1045" t="n">
         <v>64967</v>
@@ -30703,7 +30703,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1046" t="n">
         <v>20955</v>
@@ -30732,7 +30732,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1047" t="n">
         <v>7582</v>
@@ -30790,7 +30790,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.49744153022766</v>
+        <v>3.49744176864624</v>
       </c>
       <c r="H1049" t="n">
         <v>115874</v>
@@ -30877,7 +30877,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.46116065979004</v>
+        <v>3.46116089820862</v>
       </c>
       <c r="H1052" t="n">
         <v>14242</v>
@@ -30935,7 +30935,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1054" t="n">
         <v>13296</v>
@@ -30964,7 +30964,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1055" t="n">
         <v>10130</v>
@@ -31022,7 +31022,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1057" t="n">
         <v>42170</v>
@@ -31080,7 +31080,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1059" t="n">
         <v>7168</v>
@@ -31109,7 +31109,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1060" t="n">
         <v>5775</v>
@@ -31138,7 +31138,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1061" t="n">
         <v>16035</v>
@@ -31167,7 +31167,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1062" t="n">
         <v>7972</v>
@@ -31341,7 +31341,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1068" t="n">
         <v>4927</v>
@@ -31428,7 +31428,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.75731897354126</v>
+        <v>2.75731873512268</v>
       </c>
       <c r="H1071" t="n">
         <v>29481</v>
@@ -31457,7 +31457,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1072" t="n">
         <v>5534</v>
@@ -31486,7 +31486,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.81536793708801</v>
+        <v>2.81536769866943</v>
       </c>
       <c r="H1073" t="n">
         <v>20606</v>
@@ -31660,7 +31660,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1079" t="n">
         <v>9861</v>
@@ -31689,7 +31689,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1080" t="n">
         <v>3234</v>
@@ -31718,7 +31718,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1081" t="n">
         <v>5600</v>
@@ -31747,7 +31747,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.04756283760071</v>
+        <v>3.04756307601929</v>
       </c>
       <c r="H1082" t="n">
         <v>10011</v>
@@ -31979,7 +31979,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1090" t="n">
         <v>1665</v>
@@ -32008,7 +32008,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1091" t="n">
         <v>2260</v>
@@ -32066,7 +32066,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1093" t="n">
         <v>700</v>
@@ -32095,7 +32095,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1094" t="n">
         <v>2341</v>
@@ -32269,7 +32269,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1100" t="n">
         <v>3580</v>
@@ -32298,7 +32298,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1101" t="n">
         <v>0</v>
@@ -32327,7 +32327,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1102" t="n">
         <v>1000</v>
@@ -32501,7 +32501,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1108" t="n">
         <v>8900</v>
@@ -32530,7 +32530,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.3160388469696</v>
+        <v>3.31603908538818</v>
       </c>
       <c r="H1109" t="n">
         <v>3795</v>
@@ -32559,7 +32559,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.3160388469696</v>
+        <v>3.31603908538818</v>
       </c>
       <c r="H1110" t="n">
         <v>8580</v>
@@ -32646,7 +32646,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1113" t="n">
         <v>6422</v>
@@ -32675,7 +32675,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1114" t="n">
         <v>18796</v>
@@ -32733,7 +32733,7 @@
         <v>4.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1116" t="n">
         <v>5851</v>
@@ -32762,7 +32762,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.38134360313416</v>
+        <v>3.38134384155273</v>
       </c>
       <c r="H1117" t="n">
         <v>6259</v>
@@ -32791,7 +32791,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1118" t="n">
         <v>4473</v>
@@ -32849,7 +32849,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1120" t="n">
         <v>1900</v>
@@ -32936,7 +32936,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1123" t="n">
         <v>7177</v>
@@ -32965,7 +32965,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.55549025535583</v>
+        <v>3.55549049377441</v>
       </c>
       <c r="H1124" t="n">
         <v>72339</v>
@@ -33023,7 +33023,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.65707588195801</v>
+        <v>3.65707540512085</v>
       </c>
       <c r="H1126" t="n">
         <v>19826</v>
@@ -33081,7 +33081,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1128" t="n">
         <v>56766</v>
@@ -33110,7 +33110,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1129" t="n">
         <v>46422</v>
@@ -33139,7 +33139,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1130" t="n">
         <v>32706</v>
@@ -33197,7 +33197,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1132" t="n">
         <v>48820</v>
@@ -33226,7 +33226,7 @@
         <v>5.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.99085640907288</v>
+        <v>3.9908561706543</v>
       </c>
       <c r="H1133" t="n">
         <v>9842</v>
@@ -33255,7 +33255,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1134" t="n">
         <v>5306</v>
@@ -33284,7 +33284,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1135" t="n">
         <v>25296</v>
@@ -33342,7 +33342,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1137" t="n">
         <v>5042</v>
@@ -33371,7 +33371,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.7151243686676</v>
+        <v>3.71512460708618</v>
       </c>
       <c r="H1138" t="n">
         <v>22247</v>
@@ -33458,7 +33458,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1141" t="n">
         <v>4495</v>
@@ -33545,7 +33545,7 @@
         <v>5.5</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.99085640907288</v>
+        <v>3.9908561706543</v>
       </c>
       <c r="H1144" t="n">
         <v>14778</v>
@@ -33574,7 +33574,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1145" t="n">
         <v>22850</v>
@@ -33603,7 +33603,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1146" t="n">
         <v>15890</v>
@@ -33690,7 +33690,7 @@
         <v>5.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.99085640907288</v>
+        <v>3.9908561706543</v>
       </c>
       <c r="H1149" t="n">
         <v>13231</v>
@@ -33748,7 +33748,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1151" t="n">
         <v>26095</v>
@@ -33777,7 +33777,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1152" t="n">
         <v>10478</v>
@@ -33806,7 +33806,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1153" t="n">
         <v>21813</v>
@@ -33835,7 +33835,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1154" t="n">
         <v>1906</v>
@@ -33864,7 +33864,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1155" t="n">
         <v>10260</v>
@@ -33922,7 +33922,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414849281311</v>
       </c>
       <c r="H1157" t="n">
         <v>9285</v>
@@ -34009,7 +34009,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1160" t="n">
         <v>4001</v>
@@ -34038,7 +34038,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1161" t="n">
         <v>2059</v>
@@ -34096,7 +34096,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1163" t="n">
         <v>13967</v>
@@ -34125,7 +34125,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1164" t="n">
         <v>4764</v>
@@ -34183,7 +34183,7 @@
         <v>5.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.99085640907288</v>
+        <v>3.9908561706543</v>
       </c>
       <c r="H1166" t="n">
         <v>10671</v>
@@ -34212,7 +34212,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1167" t="n">
         <v>13772</v>
@@ -34328,7 +34328,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1171" t="n">
         <v>4137</v>
@@ -34357,7 +34357,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1172" t="n">
         <v>2024</v>
@@ -34386,7 +34386,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.94731974601746</v>
+        <v>3.94731998443604</v>
       </c>
       <c r="H1173" t="n">
         <v>10698</v>
@@ -34589,7 +34589,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1180" t="n">
         <v>7056</v>
@@ -34821,7 +34821,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1188" t="n">
         <v>10086</v>
@@ -34850,7 +34850,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1189" t="n">
         <v>10107</v>
@@ -34879,7 +34879,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1190" t="n">
         <v>7775</v>
@@ -34908,7 +34908,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1191" t="n">
         <v>4710</v>
@@ -34966,7 +34966,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1193" t="n">
         <v>2426</v>
@@ -34995,7 +34995,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1194" t="n">
         <v>142</v>
@@ -35082,7 +35082,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1197" t="n">
         <v>30860</v>
@@ -35111,7 +35111,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1198" t="n">
         <v>50079</v>
@@ -35140,7 +35140,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1199" t="n">
         <v>12657</v>
@@ -35169,7 +35169,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1200" t="n">
         <v>27790</v>
@@ -35227,7 +35227,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1202" t="n">
         <v>6086</v>
@@ -35256,7 +35256,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.49744153022766</v>
+        <v>3.49744176864624</v>
       </c>
       <c r="H1203" t="n">
         <v>20815</v>
@@ -35285,7 +35285,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1204" t="n">
         <v>68407</v>
@@ -35401,7 +35401,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823398590088</v>
       </c>
       <c r="H1208" t="n">
         <v>22103</v>
@@ -35517,7 +35517,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414849281311</v>
       </c>
       <c r="H1212" t="n">
         <v>14075</v>
@@ -35604,7 +35604,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1215" t="n">
         <v>10438</v>
@@ -35720,7 +35720,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.5917706489563</v>
+        <v>3.59177041053772</v>
       </c>
       <c r="H1219" t="n">
         <v>16841</v>
@@ -35778,7 +35778,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.56274628639221</v>
+        <v>3.56274652481079</v>
       </c>
       <c r="H1221" t="n">
         <v>6421</v>
@@ -35836,7 +35836,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1223" t="n">
         <v>30985</v>
@@ -35894,7 +35894,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1225" t="n">
         <v>6466</v>
@@ -35923,7 +35923,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.27250242233276</v>
+        <v>3.27250266075134</v>
       </c>
       <c r="H1226" t="n">
         <v>14233</v>
@@ -35952,7 +35952,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1227" t="n">
         <v>30722</v>
@@ -36039,7 +36039,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.04030728340149</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1230" t="n">
         <v>5716</v>
@@ -36097,7 +36097,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1232" t="n">
         <v>5283</v>
@@ -36126,7 +36126,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1233" t="n">
         <v>16931</v>
@@ -36155,7 +36155,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1234" t="n">
         <v>6553</v>
@@ -36242,7 +36242,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1237" t="n">
         <v>14176</v>
@@ -36329,7 +36329,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1240" t="n">
         <v>7122</v>
@@ -36880,7 +36880,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.45390510559082</v>
+        <v>3.45390486717224</v>
       </c>
       <c r="H1259" t="n">
         <v>43313</v>
@@ -36967,7 +36967,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1262" t="n">
         <v>34766</v>
@@ -36996,7 +36996,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1263" t="n">
         <v>50036</v>
@@ -37054,7 +37054,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1265" t="n">
         <v>5142</v>
@@ -37083,7 +37083,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1266" t="n">
         <v>4695</v>
@@ -37112,7 +37112,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1267" t="n">
         <v>3452</v>
@@ -37199,7 +37199,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1270" t="n">
         <v>4921</v>
@@ -37344,7 +37344,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1275" t="n">
         <v>10861</v>
@@ -37373,7 +37373,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1276" t="n">
         <v>27245</v>
@@ -37402,7 +37402,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1277" t="n">
         <v>21823</v>
@@ -37431,7 +37431,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1278" t="n">
         <v>9835</v>
@@ -37605,7 +37605,7 @@
         <v>4.75</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1284" t="n">
         <v>11081</v>
@@ -37634,7 +37634,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1285" t="n">
         <v>25356</v>
@@ -37721,7 +37721,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1288" t="n">
         <v>12450</v>
@@ -37750,7 +37750,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1289" t="n">
         <v>7312</v>
@@ -37779,7 +37779,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1290" t="n">
         <v>1409</v>
@@ -37953,7 +37953,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.424880027771</v>
+        <v>3.42488026618958</v>
       </c>
       <c r="H1296" t="n">
         <v>4205</v>
@@ -37982,7 +37982,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1297" t="n">
         <v>1957</v>
@@ -38011,7 +38011,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1298" t="n">
         <v>6670</v>
@@ -38069,7 +38069,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1300" t="n">
         <v>5359</v>
@@ -38098,7 +38098,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1301" t="n">
         <v>10152</v>
@@ -38156,7 +38156,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1303" t="n">
         <v>4673</v>
@@ -38185,7 +38185,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1304" t="n">
         <v>962</v>
@@ -38214,7 +38214,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1305" t="n">
         <v>4061</v>
@@ -38272,7 +38272,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1307" t="n">
         <v>7092</v>
@@ -38388,7 +38388,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1311" t="n">
         <v>6454</v>
@@ -38446,7 +38446,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1313" t="n">
         <v>3117</v>
@@ -38475,7 +38475,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1314" t="n">
         <v>3011</v>
@@ -38678,7 +38678,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1321" t="n">
         <v>8489</v>
@@ -38736,7 +38736,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1323" t="n">
         <v>4444</v>
@@ -38823,7 +38823,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1326" t="n">
         <v>10486</v>
@@ -38852,7 +38852,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1327" t="n">
         <v>6300</v>
@@ -38910,7 +38910,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1329" t="n">
         <v>16178</v>
@@ -39171,7 +39171,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.10561203956604</v>
+        <v>3.10561180114746</v>
       </c>
       <c r="H1338" t="n">
         <v>5392</v>
@@ -39229,7 +39229,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1340" t="n">
         <v>17409</v>
@@ -39490,7 +39490,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1349" t="n">
         <v>8614</v>
@@ -39519,7 +39519,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1350" t="n">
         <v>4086</v>
@@ -39548,7 +39548,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1351" t="n">
         <v>3069</v>
@@ -39577,7 +39577,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1352" t="n">
         <v>7141</v>
@@ -39809,7 +39809,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.04756283760071</v>
+        <v>3.04756307601929</v>
       </c>
       <c r="H1360" t="n">
         <v>7116</v>
@@ -39896,7 +39896,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1363" t="n">
         <v>3600</v>
@@ -39925,7 +39925,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1364" t="n">
         <v>1163</v>
@@ -40012,7 +40012,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.01128244400024</v>
+        <v>3.01128268241882</v>
       </c>
       <c r="H1367" t="n">
         <v>10781</v>
@@ -40041,7 +40041,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.04030728340149</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1368" t="n">
         <v>5348</v>
@@ -40070,7 +40070,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.04030728340149</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1369" t="n">
         <v>0</v>
@@ -40099,7 +40099,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1370" t="n">
         <v>18996</v>
@@ -40215,7 +40215,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1374" t="n">
         <v>10811</v>
@@ -40244,7 +40244,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1375" t="n">
         <v>4165</v>
@@ -40302,7 +40302,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1377" t="n">
         <v>2348</v>
@@ -40360,7 +40360,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1379" t="n">
         <v>54641</v>
@@ -40418,7 +40418,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1381" t="n">
         <v>3677</v>
@@ -40476,7 +40476,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1383" t="n">
         <v>14259</v>
@@ -40534,7 +40534,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1385" t="n">
         <v>11019</v>
@@ -40563,7 +40563,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1386" t="n">
         <v>3395</v>
@@ -40679,7 +40679,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1390" t="n">
         <v>16793</v>
@@ -40766,7 +40766,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1393" t="n">
         <v>5386</v>
@@ -40824,7 +40824,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1395" t="n">
         <v>1849</v>
@@ -40853,7 +40853,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1396" t="n">
         <v>6794</v>
@@ -40882,7 +40882,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1397" t="n">
         <v>4300</v>
@@ -40911,7 +40911,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1398" t="n">
         <v>620</v>
@@ -40969,7 +40969,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1400" t="n">
         <v>4767</v>
@@ -41027,7 +41027,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1402" t="n">
         <v>1524</v>
@@ -41056,7 +41056,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1403" t="n">
         <v>8875</v>
@@ -41288,7 +41288,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1411" t="n">
         <v>1122</v>
@@ -41317,7 +41317,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1412" t="n">
         <v>2509</v>
@@ -41346,7 +41346,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1413" t="n">
         <v>5049</v>
@@ -41404,7 +41404,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1415" t="n">
         <v>2778</v>
@@ -41433,7 +41433,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1416" t="n">
         <v>1050</v>
@@ -41549,7 +41549,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1420" t="n">
         <v>78</v>
@@ -41810,7 +41810,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1429" t="n">
         <v>825</v>
@@ -41897,7 +41897,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1432" t="n">
         <v>7465</v>
@@ -41955,7 +41955,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1434" t="n">
         <v>1100</v>
@@ -41984,7 +41984,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1435" t="n">
         <v>750</v>
@@ -42013,7 +42013,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1436" t="n">
         <v>1300</v>
@@ -42071,7 +42071,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1438" t="n">
         <v>3809</v>
@@ -42100,7 +42100,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1439" t="n">
         <v>5734</v>
@@ -42129,7 +42129,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1440" t="n">
         <v>2550</v>
@@ -42158,7 +42158,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1441" t="n">
         <v>4620</v>
@@ -42216,7 +42216,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.3595757484436</v>
+        <v>3.35957551002502</v>
       </c>
       <c r="H1443" t="n">
         <v>29451</v>
@@ -42245,7 +42245,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.27250242233276</v>
+        <v>3.27250266075134</v>
       </c>
       <c r="H1444" t="n">
         <v>5300</v>
@@ -42274,7 +42274,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.27250242233276</v>
+        <v>3.27250266075134</v>
       </c>
       <c r="H1445" t="n">
         <v>13047</v>
@@ -42303,7 +42303,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1446" t="n">
         <v>16300</v>
@@ -42506,7 +42506,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1453" t="n">
         <v>45648</v>
@@ -42535,7 +42535,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1454" t="n">
         <v>3635</v>
@@ -42564,7 +42564,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1455" t="n">
         <v>5451</v>
@@ -42593,7 +42593,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1456" t="n">
         <v>13978</v>
@@ -42680,7 +42680,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1459" t="n">
         <v>1518</v>
@@ -42709,7 +42709,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1460" t="n">
         <v>3482</v>
@@ -42738,7 +42738,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1461" t="n">
         <v>8936</v>
@@ -42796,7 +42796,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1463" t="n">
         <v>1065</v>
@@ -42825,7 +42825,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.22170948982239</v>
+        <v>3.22170972824097</v>
       </c>
       <c r="H1464" t="n">
         <v>2007</v>
@@ -42970,7 +42970,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1469" t="n">
         <v>39138</v>
@@ -43057,7 +43057,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.27250242233276</v>
+        <v>3.27250266075134</v>
       </c>
       <c r="H1472" t="n">
         <v>10406</v>
@@ -43173,7 +43173,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.27250242233276</v>
+        <v>3.27250266075134</v>
       </c>
       <c r="H1476" t="n">
         <v>6866</v>
@@ -43347,7 +43347,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1482" t="n">
         <v>50</v>
@@ -43376,7 +43376,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1483" t="n">
         <v>11720</v>
@@ -43405,7 +43405,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1484" t="n">
         <v>224</v>
@@ -43492,7 +43492,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1487" t="n">
         <v>19033</v>
@@ -43521,7 +43521,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1488" t="n">
         <v>15813</v>
@@ -43550,7 +43550,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.35231900215149</v>
+        <v>3.35231924057007</v>
       </c>
       <c r="H1489" t="n">
         <v>8856</v>
@@ -43579,7 +43579,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1490" t="n">
         <v>6932</v>
@@ -43608,7 +43608,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1491" t="n">
         <v>8001</v>
@@ -43666,7 +43666,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1493" t="n">
         <v>60540</v>
@@ -43724,7 +43724,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.62079477310181</v>
+        <v>3.62079501152039</v>
       </c>
       <c r="H1495" t="n">
         <v>45483</v>
@@ -43753,7 +43753,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1496" t="n">
         <v>18770</v>
@@ -43782,7 +43782,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1497" t="n">
         <v>8020</v>
@@ -43811,7 +43811,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1498" t="n">
         <v>13327</v>
@@ -43840,7 +43840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1499" t="n">
         <v>6935</v>
@@ -43869,7 +43869,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1500" t="n">
         <v>6069</v>
@@ -43898,7 +43898,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1501" t="n">
         <v>485</v>
@@ -43927,7 +43927,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1502" t="n">
         <v>5142</v>
@@ -43956,7 +43956,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.55549025535583</v>
+        <v>3.55549049377441</v>
       </c>
       <c r="H1503" t="n">
         <v>11660</v>
@@ -43985,7 +43985,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414849281311</v>
       </c>
       <c r="H1504" t="n">
         <v>13228</v>
@@ -44072,7 +44072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1507" t="n">
         <v>4706</v>
@@ -44101,7 +44101,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1508" t="n">
         <v>7146</v>
@@ -44159,7 +44159,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1510" t="n">
         <v>5436</v>
@@ -44217,7 +44217,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1512" t="n">
         <v>4106</v>
@@ -44275,7 +44275,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.53372168540955</v>
+        <v>3.53372192382812</v>
       </c>
       <c r="H1514" t="n">
         <v>2693</v>
@@ -44333,7 +44333,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1516" t="n">
         <v>1000</v>
@@ -44449,7 +44449,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1520" t="n">
         <v>1907</v>
@@ -44478,7 +44478,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1521" t="n">
         <v>1900</v>
@@ -44507,7 +44507,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1522" t="n">
         <v>0</v>
@@ -44536,7 +44536,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1523" t="n">
         <v>1405</v>
@@ -44565,7 +44565,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.55549025535583</v>
+        <v>3.55549049377441</v>
       </c>
       <c r="H1524" t="n">
         <v>3725</v>
@@ -44594,7 +44594,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1525" t="n">
         <v>4339</v>
@@ -44623,7 +44623,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1526" t="n">
         <v>0</v>
@@ -44652,7 +44652,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1527" t="n">
         <v>5409</v>
@@ -44681,7 +44681,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1528" t="n">
         <v>5601</v>
@@ -44710,7 +44710,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1529" t="n">
         <v>7906</v>
@@ -44797,7 +44797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1532" t="n">
         <v>5293</v>
@@ -44826,7 +44826,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1533" t="n">
         <v>4376</v>
@@ -44913,7 +44913,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1536" t="n">
         <v>50</v>
@@ -44971,7 +44971,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1538" t="n">
         <v>5573</v>
@@ -45000,7 +45000,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1539" t="n">
         <v>12112</v>
@@ -45058,7 +45058,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1541" t="n">
         <v>1000</v>
@@ -45087,7 +45087,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.58451461791992</v>
+        <v>3.5845148563385</v>
       </c>
       <c r="H1542" t="n">
         <v>1515</v>
@@ -45145,7 +45145,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1544" t="n">
         <v>3200</v>
@@ -45261,7 +45261,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1548" t="n">
         <v>3525</v>
@@ -45290,7 +45290,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.7151243686676</v>
+        <v>3.71512460708618</v>
       </c>
       <c r="H1549" t="n">
         <v>4878</v>
@@ -45319,7 +45319,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1550" t="n">
         <v>3930</v>
@@ -45348,7 +45348,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1551" t="n">
         <v>3888</v>
@@ -45406,7 +45406,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1553" t="n">
         <v>2243</v>
@@ -45435,7 +45435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1554" t="n">
         <v>3630</v>
@@ -45493,7 +45493,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.65707588195801</v>
+        <v>3.65707540512085</v>
       </c>
       <c r="H1556" t="n">
         <v>255</v>
@@ -45638,7 +45638,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1561" t="n">
         <v>1450</v>
@@ -45667,7 +45667,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.62079477310181</v>
+        <v>3.62079501152039</v>
       </c>
       <c r="H1562" t="n">
         <v>1718</v>
@@ -45696,7 +45696,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.5917706489563</v>
+        <v>3.59177041053772</v>
       </c>
       <c r="H1563" t="n">
         <v>400</v>
@@ -45812,7 +45812,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.5917706489563</v>
+        <v>3.59177041053772</v>
       </c>
       <c r="H1567" t="n">
         <v>9490</v>
@@ -45841,7 +45841,7 @@
         <v>4.75</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1568" t="n">
         <v>7375</v>
@@ -45870,7 +45870,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585590362549</v>
       </c>
       <c r="H1569" t="n">
         <v>5281</v>
@@ -45899,7 +45899,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1570" t="n">
         <v>2484</v>
@@ -45957,7 +45957,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1572" t="n">
-        <v>3.09109973907471</v>
+        <v>3.09109997749329</v>
       </c>
       <c r="H1572" t="n">
         <v>10541</v>
@@ -45986,7 +45986,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1573" t="n">
         <v>2602</v>
@@ -46015,7 +46015,7 @@
         <v>4.75</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.44664859771729</v>
+        <v>3.44664883613586</v>
       </c>
       <c r="H1574" t="n">
         <v>5518</v>
@@ -46102,7 +46102,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.45390510559082</v>
+        <v>3.45390486717224</v>
       </c>
       <c r="H1577" t="n">
         <v>210</v>
@@ -46160,7 +46160,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.65707588195801</v>
+        <v>3.65707540512085</v>
       </c>
       <c r="H1579" t="n">
         <v>25968</v>
@@ -46189,7 +46189,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1580" t="n">
         <v>4781</v>
@@ -46218,7 +46218,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.7151243686676</v>
+        <v>3.71512460708618</v>
       </c>
       <c r="H1581" t="n">
         <v>3800</v>
@@ -46363,7 +46363,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414849281311</v>
       </c>
       <c r="H1586" t="n">
         <v>8413</v>
@@ -46421,7 +46421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1588" t="n">
         <v>169</v>
@@ -46450,7 +46450,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414849281311</v>
       </c>
       <c r="H1589" t="n">
         <v>3324</v>
@@ -46566,7 +46566,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.65707588195801</v>
+        <v>3.65707540512085</v>
       </c>
       <c r="H1593" t="n">
         <v>19445</v>
@@ -46595,7 +46595,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1594" t="n">
         <v>4764</v>
@@ -46624,7 +46624,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.7151243686676</v>
+        <v>3.71512460708618</v>
       </c>
       <c r="H1595" t="n">
         <v>1760</v>
@@ -46682,7 +46682,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1597" t="n">
         <v>3080</v>
@@ -46740,7 +46740,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.70061254501343</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1599" t="n">
         <v>2133</v>
@@ -46798,7 +46798,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1601" t="n">
         <v>30682</v>
@@ -46856,7 +46856,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1603" t="n">
         <v>3077</v>
@@ -46885,7 +46885,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414849281311</v>
       </c>
       <c r="H1604" t="n">
         <v>786</v>
@@ -46914,7 +46914,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1605" t="n">
         <v>100</v>
@@ -46943,7 +46943,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H1606" t="n">
         <v>9900</v>
@@ -47088,7 +47088,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.5917706489563</v>
+        <v>3.59177041053772</v>
       </c>
       <c r="H1611" t="n">
         <v>3751</v>
@@ -47117,7 +47117,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.62079477310181</v>
+        <v>3.62079501152039</v>
       </c>
       <c r="H1612" t="n">
         <v>1394</v>
@@ -47146,7 +47146,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.46116065979004</v>
+        <v>3.46116089820862</v>
       </c>
       <c r="H1613" t="n">
         <v>14628</v>
@@ -47175,7 +47175,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.43213677406311</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1614" t="n">
         <v>7016</v>
@@ -47233,7 +47233,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.52646589279175</v>
+        <v>3.52646565437317</v>
       </c>
       <c r="H1616" t="n">
         <v>1810</v>
@@ -47262,7 +47262,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823398590088</v>
       </c>
       <c r="H1617" t="n">
         <v>20</v>
@@ -47523,7 +47523,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.58451461791992</v>
+        <v>3.5845148563385</v>
       </c>
       <c r="H1626" t="n">
         <v>830</v>
@@ -47552,7 +47552,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.58451461791992</v>
+        <v>3.5845148563385</v>
       </c>
       <c r="H1627" t="n">
         <v>0</v>
@@ -47581,7 +47581,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823398590088</v>
       </c>
       <c r="H1628" t="n">
         <v>1040</v>
@@ -47610,7 +47610,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.52646589279175</v>
+        <v>3.52646565437317</v>
       </c>
       <c r="H1629" t="n">
         <v>5510</v>
@@ -47639,7 +47639,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1630" t="n">
         <v>17514</v>
@@ -47668,7 +47668,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1631" t="n">
         <v>7208</v>
@@ -47784,7 +47784,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.38134360313416</v>
+        <v>3.38134384155273</v>
       </c>
       <c r="H1635" t="n">
         <v>170</v>
@@ -47842,7 +47842,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.27250242233276</v>
+        <v>3.27250266075134</v>
       </c>
       <c r="H1637" t="n">
         <v>4239</v>
@@ -47871,7 +47871,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1638" t="n">
         <v>2288</v>
@@ -47987,7 +47987,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.25798988342285</v>
+        <v>3.25798964500427</v>
       </c>
       <c r="H1642" t="n">
         <v>783</v>
@@ -48045,7 +48045,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1644" t="n">
         <v>1681</v>
@@ -48103,7 +48103,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1646" t="n">
         <v>3452</v>
@@ -48132,7 +48132,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1647" t="n">
         <v>817</v>
@@ -48335,7 +48335,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1654" t="n">
         <v>300</v>
@@ -48364,7 +48364,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1655" t="n">
         <v>5550</v>
@@ -48393,7 +48393,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.30152702331543</v>
+        <v>3.30152654647827</v>
       </c>
       <c r="H1656" t="n">
         <v>2320</v>
@@ -48422,7 +48422,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.45390510559082</v>
+        <v>3.45390486717224</v>
       </c>
       <c r="H1657" t="n">
         <v>23337</v>
@@ -48741,7 +48741,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1668" t="n">
-        <v>3.5917706489563</v>
+        <v>3.59177041053772</v>
       </c>
       <c r="H1668" t="n">
         <v>15918</v>
@@ -48944,7 +48944,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.5917706489563</v>
+        <v>3.59177041053772</v>
       </c>
       <c r="H1675" t="n">
         <v>1250</v>
@@ -49002,7 +49002,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.64256358146667</v>
+        <v>3.6425633430481</v>
       </c>
       <c r="H1677" t="n">
         <v>4660</v>
@@ -49031,7 +49031,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.65707588195801</v>
+        <v>3.65707540512085</v>
       </c>
       <c r="H1678" t="n">
         <v>5800</v>
@@ -49060,7 +49060,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.56274628639221</v>
+        <v>3.56274652481079</v>
       </c>
       <c r="H1679" t="n">
         <v>432</v>
@@ -49147,7 +49147,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823398590088</v>
       </c>
       <c r="H1682" t="n">
         <v>1533</v>
@@ -49176,7 +49176,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1683" t="n">
-        <v>3.5917706489563</v>
+        <v>3.59177041053772</v>
       </c>
       <c r="H1683" t="n">
         <v>1137</v>
@@ -49205,7 +49205,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1684" t="n">
         <v>600</v>
@@ -49234,7 +49234,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.5917706489563</v>
+        <v>3.59177041053772</v>
       </c>
       <c r="H1685" t="n">
         <v>2350</v>
@@ -49292,7 +49292,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1687" t="n">
         <v>994</v>
@@ -49350,7 +49350,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.57000231742859</v>
+        <v>3.57000255584717</v>
       </c>
       <c r="H1689" t="n">
         <v>2005</v>
@@ -49379,7 +49379,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.57000231742859</v>
+        <v>3.57000255584717</v>
       </c>
       <c r="H1690" t="n">
         <v>100</v>
@@ -49408,7 +49408,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.55549025535583</v>
+        <v>3.55549049377441</v>
       </c>
       <c r="H1691" t="n">
         <v>34603</v>
@@ -49437,7 +49437,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.55549025535583</v>
+        <v>3.55549049377441</v>
       </c>
       <c r="H1692" t="n">
         <v>150</v>
@@ -49466,7 +49466,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.55549025535583</v>
+        <v>3.55549049377441</v>
       </c>
       <c r="H1693" t="n">
         <v>0</v>
@@ -49495,7 +49495,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.55549025535583</v>
+        <v>3.55549049377441</v>
       </c>
       <c r="H1694" t="n">
         <v>7420</v>
@@ -49930,7 +49930,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1709" t="n">
         <v>274</v>
@@ -50017,7 +50017,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.3668315410614</v>
+        <v>3.36683130264282</v>
       </c>
       <c r="H1712" t="n">
         <v>1216</v>
@@ -50104,7 +50104,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.27250242233276</v>
+        <v>3.27250266075134</v>
       </c>
       <c r="H1715" t="n">
         <v>200</v>
@@ -50191,7 +50191,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1718" t="n">
         <v>120</v>
@@ -50220,7 +50220,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1719" t="n">
         <v>0</v>
@@ -50423,7 +50423,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1726" t="n">
-        <v>3.25073409080505</v>
+        <v>3.25073385238647</v>
       </c>
       <c r="H1726" t="n">
         <v>741</v>
@@ -50452,7 +50452,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1727" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1727" t="n">
         <v>5846</v>
@@ -50539,7 +50539,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1730" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1730" t="n">
         <v>4450</v>
@@ -50858,7 +50858,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1741" t="n">
         <v>2248</v>
@@ -50887,7 +50887,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.10561203956604</v>
+        <v>3.10561180114746</v>
       </c>
       <c r="H1742" t="n">
         <v>1600</v>
@@ -51003,7 +51003,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1746" t="n">
         <v>12</v>
@@ -51032,7 +51032,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1747" t="n">
         <v>0</v>
@@ -51090,7 +51090,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1749" t="n">
         <v>287</v>
@@ -51148,7 +51148,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.81536793708801</v>
+        <v>2.81536769866943</v>
       </c>
       <c r="H1751" t="n">
         <v>9700</v>
@@ -51206,7 +51206,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1753" t="n">
         <v>5741</v>
@@ -51264,7 +51264,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.82987976074219</v>
+        <v>2.82988023757935</v>
       </c>
       <c r="H1755" t="n">
         <v>3343</v>
@@ -51467,7 +51467,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.77908730506897</v>
+        <v>2.77908706665039</v>
       </c>
       <c r="H1762" t="n">
         <v>3130</v>
@@ -51554,7 +51554,7 @@
         <v>3.75</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.7210385799408</v>
+        <v>2.72103834152222</v>
       </c>
       <c r="H1765" t="n">
         <v>1347</v>
@@ -51670,7 +51670,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.04030728340149</v>
+        <v>3.04030704498291</v>
       </c>
       <c r="H1769" t="n">
         <v>640</v>
@@ -51844,7 +51844,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1775" t="n">
-        <v>3.04756283760071</v>
+        <v>3.04756307601929</v>
       </c>
       <c r="H1775" t="n">
         <v>2109</v>
@@ -51902,7 +51902,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.04756283760071</v>
+        <v>3.04756307601929</v>
       </c>
       <c r="H1777" t="n">
         <v>1250</v>
@@ -51989,7 +51989,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.10561203956604</v>
+        <v>3.10561180114746</v>
       </c>
       <c r="H1780" t="n">
         <v>250</v>
@@ -52047,7 +52047,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1782" t="n">
         <v>1781</v>
@@ -52134,7 +52134,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.10561203956604</v>
+        <v>3.10561180114746</v>
       </c>
       <c r="H1785" t="n">
         <v>3649</v>
@@ -52192,7 +52192,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.10561203956604</v>
+        <v>3.10561180114746</v>
       </c>
       <c r="H1787" t="n">
         <v>391</v>
@@ -52337,7 +52337,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.04756283760071</v>
+        <v>3.04756307601929</v>
       </c>
       <c r="H1792" t="n">
         <v>1250</v>
@@ -52366,7 +52366,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.99677014350891</v>
+        <v>2.99677038192749</v>
       </c>
       <c r="H1793" t="n">
         <v>801</v>
@@ -52395,7 +52395,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.04756283760071</v>
+        <v>3.04756307601929</v>
       </c>
       <c r="H1794" t="n">
         <v>4601</v>
@@ -52453,7 +52453,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1796" t="n">
         <v>6947</v>
@@ -52598,7 +52598,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1801" t="n">
         <v>3471</v>
@@ -52627,7 +52627,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.14914846420288</v>
+        <v>3.14914870262146</v>
       </c>
       <c r="H1802" t="n">
         <v>0</v>
@@ -52656,7 +52656,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1803" t="n">
         <v>3480</v>
@@ -52685,7 +52685,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1804" t="n">
         <v>600</v>
@@ -52714,7 +52714,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1805" t="n">
         <v>2591</v>
@@ -52772,7 +52772,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H1807" t="n">
         <v>335044</v>
@@ -52801,7 +52801,7 @@
         <v>5.5</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.99085640907288</v>
+        <v>3.9908561706543</v>
       </c>
       <c r="H1808" t="n">
         <v>262088</v>
@@ -52830,7 +52830,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H1809" t="n">
         <v>175714</v>
@@ -52917,7 +52917,7 @@
         <v>5.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>3.99085640907288</v>
+        <v>3.9908561706543</v>
       </c>
       <c r="H1812" t="n">
         <v>34810</v>
@@ -53004,7 +53004,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1815" t="n">
         <v>60991</v>
@@ -53033,7 +53033,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1816" t="n">
         <v>112390</v>
@@ -53091,7 +53091,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1818" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1818" t="n">
         <v>134056</v>
@@ -53120,7 +53120,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1819" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H1819" t="n">
         <v>74184</v>
@@ -53178,7 +53178,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.97634434700012</v>
+        <v>3.97634410858154</v>
       </c>
       <c r="H1821" t="n">
         <v>18995</v>
@@ -53207,7 +53207,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1822" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1822" t="n">
         <v>12683</v>
@@ -53265,7 +53265,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1824" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1824" t="n">
         <v>24046</v>
@@ -53323,7 +53323,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1826" t="n">
         <v>14213</v>
@@ -53352,7 +53352,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.25207662582397</v>
+        <v>4.25207614898682</v>
       </c>
       <c r="H1827" t="n">
         <v>11550</v>
@@ -53497,7 +53497,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H1832" t="n">
         <v>41917</v>
@@ -53526,7 +53526,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.2375636100769</v>
+        <v>4.23756408691406</v>
       </c>
       <c r="H1833" t="n">
         <v>51308</v>
@@ -53555,7 +53555,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.2375636100769</v>
+        <v>4.23756408691406</v>
       </c>
       <c r="H1834" t="n">
         <v>45922</v>
@@ -53613,7 +53613,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.19402694702148</v>
+        <v>4.19402742385864</v>
       </c>
       <c r="H1836" t="n">
         <v>12941</v>
@@ -53671,7 +53671,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1838" t="n">
         <v>12403</v>
@@ -53700,7 +53700,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1839" t="n">
         <v>11869</v>
@@ -53758,7 +53758,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1841" t="n">
         <v>745</v>
@@ -53816,7 +53816,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1843" t="n">
         <v>36831</v>
@@ -53845,7 +53845,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H1844" t="n">
         <v>7782</v>
@@ -53961,7 +53961,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.31012487411499</v>
+        <v>4.31012535095215</v>
       </c>
       <c r="H1848" t="n">
         <v>15922</v>
@@ -53990,7 +53990,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.31012487411499</v>
+        <v>4.31012535095215</v>
       </c>
       <c r="H1849" t="n">
         <v>15739</v>
@@ -54106,7 +54106,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1853" t="n">
-        <v>4.57134437561035</v>
+        <v>4.57134485244751</v>
       </c>
       <c r="H1853" t="n">
         <v>46979</v>
@@ -54193,7 +54193,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1856" t="n">
-        <v>4.36817407608032</v>
+        <v>4.36817359924316</v>
       </c>
       <c r="H1856" t="n">
         <v>18268</v>
@@ -54367,7 +54367,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H1862" t="n">
         <v>7193</v>
@@ -54396,7 +54396,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1863" t="n">
         <v>33360</v>
@@ -54454,7 +54454,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1865" t="n">
         <v>13474</v>
@@ -54512,7 +54512,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1867" t="n">
         <v>2075</v>
@@ -54657,7 +54657,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1872" t="n">
         <v>20141</v>
@@ -54686,7 +54686,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1873" t="n">
         <v>10475</v>
@@ -54715,7 +54715,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1874" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1874" t="n">
         <v>18932</v>
@@ -54744,7 +54744,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1875" t="n">
         <v>13180</v>
@@ -54773,7 +54773,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1876" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1876" t="n">
         <v>17270</v>
@@ -54889,7 +54889,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1880" t="n">
         <v>33774</v>
@@ -54918,7 +54918,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1881" t="n">
         <v>12398</v>
@@ -54976,7 +54976,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1883" t="n">
         <v>9022</v>
@@ -55063,7 +55063,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H1886" t="n">
         <v>7240</v>
@@ -55121,7 +55121,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1888" t="n">
         <v>60636</v>
@@ -55179,7 +55179,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1890" t="n">
-        <v>4.03439331054688</v>
+        <v>4.03439283370972</v>
       </c>
       <c r="H1890" t="n">
         <v>22609</v>
@@ -55208,7 +55208,7 @@
         <v>5.5</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.99085640907288</v>
+        <v>3.9908561706543</v>
       </c>
       <c r="H1891" t="n">
         <v>22700</v>
@@ -55266,7 +55266,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1893" t="n">
-        <v>4.16500234603882</v>
+        <v>4.16500282287598</v>
       </c>
       <c r="H1893" t="n">
         <v>45449</v>
@@ -55353,7 +55353,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1896" t="n">
-        <v>4.3246374130249</v>
+        <v>4.32463693618774</v>
       </c>
       <c r="H1896" t="n">
         <v>4810</v>
@@ -55411,7 +55411,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.455246925354</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H1898" t="n">
         <v>11695</v>
@@ -55469,7 +55469,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1900" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1900" t="n">
         <v>15662</v>
@@ -55498,7 +55498,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1901" t="n">
         <v>26842</v>
@@ -55556,7 +55556,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1903" t="n">
         <v>21319</v>
@@ -55585,7 +55585,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1904" t="n">
         <v>8188</v>
@@ -55643,7 +55643,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1906" t="n">
         <v>38626</v>
@@ -55730,7 +55730,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1909" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1909" t="n">
         <v>3775</v>
@@ -55759,7 +55759,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1910" t="n">
         <v>20341</v>
@@ -55817,7 +55817,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1912" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1912" t="n">
         <v>32655</v>
@@ -55846,7 +55846,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.57134437561035</v>
+        <v>4.57134485244751</v>
       </c>
       <c r="H1913" t="n">
         <v>8500</v>
@@ -55875,7 +55875,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>4.58585739135742</v>
+        <v>4.58585691452026</v>
       </c>
       <c r="H1914" t="n">
         <v>11300</v>
@@ -55933,7 +55933,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.31012487411499</v>
+        <v>4.31012535095215</v>
       </c>
       <c r="H1916" t="n">
         <v>26741</v>
@@ -55991,7 +55991,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1918" t="n">
-        <v>4.36817407608032</v>
+        <v>4.36817359924316</v>
       </c>
       <c r="H1918" t="n">
         <v>11920</v>
@@ -56049,7 +56049,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1920" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1920" t="n">
         <v>99275</v>
@@ -56078,7 +56078,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1921" t="n">
         <v>45350</v>
@@ -56107,7 +56107,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1922" t="n">
         <v>46575</v>
@@ -56194,7 +56194,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1925" t="n">
         <v>43840</v>
@@ -56223,7 +56223,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1926" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1926" t="n">
         <v>32624</v>
@@ -56252,7 +56252,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.58585739135742</v>
+        <v>4.58585691452026</v>
       </c>
       <c r="H1927" t="n">
         <v>15606</v>
@@ -56281,7 +56281,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1928" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1928" t="n">
         <v>36250</v>
@@ -56310,7 +56310,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1929" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1929" t="n">
         <v>8594</v>
@@ -56339,7 +56339,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1930" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1930" t="n">
         <v>9421</v>
@@ -56368,7 +56368,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1931" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1931" t="n">
         <v>77323</v>
@@ -56397,7 +56397,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1932" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1932" t="n">
         <v>32327</v>
@@ -56426,7 +56426,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1933" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1933" t="n">
         <v>13860</v>
@@ -56455,7 +56455,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1934" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1934" t="n">
         <v>14123</v>
@@ -56484,7 +56484,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1935" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H1935" t="n">
         <v>4650</v>
@@ -56629,7 +56629,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1940" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1940" t="n">
         <v>12318</v>
@@ -56658,7 +56658,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1941" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1941" t="n">
         <v>34148</v>
@@ -56687,7 +56687,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1942" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1942" t="n">
         <v>2500</v>
@@ -56716,7 +56716,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1943" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1943" t="n">
         <v>13135</v>
@@ -56745,7 +56745,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1944" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1944" t="n">
         <v>83501</v>
@@ -56774,7 +56774,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1945" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1945" t="n">
         <v>19357</v>
@@ -56803,7 +56803,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1946" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H1946" t="n">
         <v>80165</v>
@@ -57093,7 +57093,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1956" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1956" t="n">
         <v>10749</v>
@@ -57151,7 +57151,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1958" t="n">
         <v>15475</v>
@@ -57180,7 +57180,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1959" t="n">
-        <v>4.80353975296021</v>
+        <v>4.80353927612305</v>
       </c>
       <c r="H1959" t="n">
         <v>1004</v>
@@ -57209,7 +57209,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1960" t="n">
-        <v>4.83256435394287</v>
+        <v>4.83256387710571</v>
       </c>
       <c r="H1960" t="n">
         <v>3682</v>
@@ -57238,7 +57238,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1961" t="n">
-        <v>4.80353975296021</v>
+        <v>4.80353927612305</v>
       </c>
       <c r="H1961" t="n">
         <v>19601</v>
@@ -57325,7 +57325,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1964" t="n">
-        <v>4.83256435394287</v>
+        <v>4.83256387710571</v>
       </c>
       <c r="H1964" t="n">
         <v>17330</v>
@@ -57499,7 +57499,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1970" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1970" t="n">
         <v>95721</v>
@@ -57528,7 +57528,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1971" t="n">
         <v>18833</v>
@@ -57557,7 +57557,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1972" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H1972" t="n">
         <v>23900</v>
@@ -57586,7 +57586,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1973" t="n">
-        <v>4.6874418258667</v>
+        <v>4.68744230270386</v>
       </c>
       <c r="H1973" t="n">
         <v>14880</v>
@@ -57702,7 +57702,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1977" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H1977" t="n">
         <v>91508</v>
@@ -57789,7 +57789,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1980" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1980" t="n">
         <v>6300</v>
@@ -57963,7 +57963,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1986" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1986" t="n">
         <v>10900</v>
@@ -58079,7 +58079,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1990" t="n">
-        <v>4.80353975296021</v>
+        <v>4.80353927612305</v>
       </c>
       <c r="H1990" t="n">
         <v>5520</v>
@@ -58137,7 +58137,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1992" t="n">
         <v>13140</v>
@@ -58195,7 +58195,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H1994" t="n">
         <v>6925</v>
@@ -58456,7 +58456,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2003" t="n">
         <v>46780</v>
@@ -58485,7 +58485,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2004" t="n">
         <v>30486</v>
@@ -58514,7 +58514,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2005" t="n">
         <v>48454</v>
@@ -58804,7 +58804,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2015" t="n">
         <v>50010</v>
@@ -58833,7 +58833,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.70195484161377</v>
+        <v>4.70195436477661</v>
       </c>
       <c r="H2016" t="n">
         <v>74404</v>
@@ -58862,7 +58862,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.64390563964844</v>
+        <v>4.6439061164856</v>
       </c>
       <c r="H2017" t="n">
         <v>32700</v>
@@ -58891,7 +58891,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H2018" t="n">
         <v>92013</v>
@@ -58978,7 +58978,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.36817407608032</v>
+        <v>4.36817359924316</v>
       </c>
       <c r="H2021" t="n">
         <v>49804</v>
@@ -59007,7 +59007,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.31012487411499</v>
+        <v>4.31012535095215</v>
       </c>
       <c r="H2022" t="n">
         <v>52338</v>
@@ -59036,7 +59036,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H2023" t="n">
         <v>15139</v>
@@ -59094,7 +59094,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.19402694702148</v>
+        <v>4.19402742385864</v>
       </c>
       <c r="H2025" t="n">
         <v>29656</v>
@@ -59123,7 +59123,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.19402694702148</v>
+        <v>4.19402742385864</v>
       </c>
       <c r="H2026" t="n">
         <v>18031</v>
@@ -59152,7 +59152,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.22305154800415</v>
+        <v>4.22305202484131</v>
       </c>
       <c r="H2027" t="n">
         <v>12317</v>
@@ -59181,7 +59181,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.22305154800415</v>
+        <v>4.22305202484131</v>
       </c>
       <c r="H2028" t="n">
         <v>3331</v>
@@ -59239,7 +59239,7 @@
         <v>5.5</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.99085640907288</v>
+        <v>3.9908561706543</v>
       </c>
       <c r="H2030" t="n">
         <v>85194</v>
@@ -59297,7 +59297,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.97634434700012</v>
+        <v>3.97634410858154</v>
       </c>
       <c r="H2032" t="n">
         <v>7326</v>
@@ -59326,7 +59326,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H2033" t="n">
         <v>53963</v>
@@ -59355,7 +59355,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2034" t="n">
         <v>62502</v>
@@ -59384,7 +59384,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2035" t="n">
         <v>25964</v>
@@ -59442,7 +59442,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2037" t="n">
         <v>19540</v>
@@ -59558,7 +59558,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H2041" t="n">
         <v>5845</v>
@@ -59587,7 +59587,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.8892707824707</v>
+        <v>3.88927102088928</v>
       </c>
       <c r="H2042" t="n">
         <v>15623</v>
@@ -59645,7 +59645,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2044" t="n">
         <v>13762</v>
@@ -59674,7 +59674,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2045" t="n">
         <v>12427</v>
@@ -59703,7 +59703,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H2046" t="n">
         <v>11724</v>
@@ -59761,7 +59761,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2048" t="n">
         <v>18302</v>
@@ -59819,7 +59819,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2050" t="n">
         <v>13500</v>
@@ -59906,7 +59906,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2053" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2053" t="n">
         <v>2480</v>
@@ -59935,7 +59935,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2054" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2054" t="n">
         <v>6321</v>
@@ -59964,7 +59964,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2055" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2055" t="n">
         <v>1020</v>
@@ -59993,7 +59993,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2056" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2056" t="n">
         <v>0</v>
@@ -60022,7 +60022,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2057" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2057" t="n">
         <v>1050</v>
@@ -60109,7 +60109,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2060" t="n">
-        <v>3.80219745635986</v>
+        <v>3.80219769477844</v>
       </c>
       <c r="H2060" t="n">
         <v>8933</v>
@@ -60138,7 +60138,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2061" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2061" t="n">
         <v>122</v>
@@ -60312,7 +60312,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2067" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H2067" t="n">
         <v>1</v>
@@ -60341,7 +60341,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2068" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H2068" t="n">
         <v>738</v>
@@ -60399,7 +60399,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2070" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2070" t="n">
         <v>7354</v>
@@ -60428,7 +60428,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2071" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2071" t="n">
         <v>380</v>
@@ -60457,7 +60457,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2072" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2072" t="n">
         <v>562</v>
@@ -60486,7 +60486,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2073" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2073" t="n">
         <v>1000</v>
@@ -60515,7 +60515,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2074" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2074" t="n">
         <v>3250</v>
@@ -60573,7 +60573,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2076" t="n">
-        <v>3.74414873123169</v>
+        <v>3.74414849281311</v>
       </c>
       <c r="H2076" t="n">
         <v>21034</v>
@@ -60631,7 +60631,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2078" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H2078" t="n">
         <v>19403</v>
@@ -60689,7 +60689,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2080" t="n">
-        <v>3.7731728553772</v>
+        <v>3.77317309379578</v>
       </c>
       <c r="H2080" t="n">
         <v>3325</v>
@@ -60718,7 +60718,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2081" t="n">
         <v>5369</v>
@@ -60805,7 +60805,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.04890489578247</v>
+        <v>4.04890537261963</v>
       </c>
       <c r="H2084" t="n">
         <v>22246</v>
@@ -60863,7 +60863,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H2086" t="n">
         <v>3284</v>
@@ -61066,7 +61066,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2093" t="n">
-        <v>4.19402694702148</v>
+        <v>4.19402742385864</v>
       </c>
       <c r="H2093" t="n">
         <v>102597</v>
@@ -61182,7 +61182,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2097" t="n">
-        <v>4.455246925354</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H2097" t="n">
         <v>25254</v>
@@ -61211,7 +61211,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2098" t="n">
-        <v>4.455246925354</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H2098" t="n">
         <v>16270</v>
@@ -61385,7 +61385,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.58585739135742</v>
+        <v>4.58585691452026</v>
       </c>
       <c r="H2104" t="n">
         <v>8575</v>
@@ -61414,7 +61414,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H2105" t="n">
         <v>6270</v>
@@ -61472,7 +61472,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2107" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H2107" t="n">
         <v>22131</v>
@@ -61501,7 +61501,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2108" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H2108" t="n">
         <v>5235</v>
@@ -61530,7 +61530,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H2109" t="n">
         <v>9985</v>
@@ -61559,7 +61559,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2110" t="n">
-        <v>4.77451515197754</v>
+        <v>4.7745156288147</v>
       </c>
       <c r="H2110" t="n">
         <v>17810</v>
@@ -61675,7 +61675,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2114" t="n">
-        <v>5.02122259140015</v>
+        <v>5.0212230682373</v>
       </c>
       <c r="H2114" t="n">
         <v>66210</v>
@@ -61704,7 +61704,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2115" t="n">
-        <v>5.23890542984009</v>
+        <v>5.23890590667725</v>
       </c>
       <c r="H2115" t="n">
         <v>77346</v>
@@ -61762,7 +61762,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2117" t="n">
-        <v>5.32597923278809</v>
+        <v>5.32597970962524</v>
       </c>
       <c r="H2117" t="n">
         <v>52433</v>
@@ -61849,7 +61849,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2120" t="n">
-        <v>5.32597923278809</v>
+        <v>5.32597970962524</v>
       </c>
       <c r="H2120" t="n">
         <v>58295</v>
@@ -61907,7 +61907,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2122" t="n">
-        <v>5.71780872344971</v>
+        <v>5.71780920028687</v>
       </c>
       <c r="H2122" t="n">
         <v>237009</v>
@@ -61936,7 +61936,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2123" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2123" t="n">
         <v>156082</v>
@@ -61994,7 +61994,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2125" t="n">
-        <v>5.74200296401978</v>
+        <v>5.74200248718262</v>
       </c>
       <c r="H2125" t="n">
         <v>31598</v>
@@ -62168,7 +62168,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2131" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2131" t="n">
         <v>5020</v>
@@ -62516,7 +62516,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2143" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2143" t="n">
         <v>4615</v>
@@ -62545,7 +62545,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2144" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2144" t="n">
         <v>3322</v>
@@ -62603,7 +62603,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2146" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2146" t="n">
         <v>4610</v>
@@ -62661,7 +62661,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2148" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2148" t="n">
         <v>6369</v>
@@ -62835,7 +62835,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2154" t="n">
-        <v>5.50006437301636</v>
+        <v>5.50006484985352</v>
       </c>
       <c r="H2154" t="n">
         <v>72558</v>
@@ -62951,7 +62951,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2158" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2158" t="n">
         <v>4098</v>
@@ -63154,7 +63154,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2165" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2165" t="n">
         <v>15059</v>
@@ -63241,7 +63241,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2168" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2168" t="n">
         <v>11763</v>
@@ -63270,7 +63270,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2169" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2169" t="n">
         <v>1246</v>
@@ -63328,7 +63328,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2171" t="n">
-        <v>5.67748546600342</v>
+        <v>5.67748594284058</v>
       </c>
       <c r="H2171" t="n">
         <v>13431</v>
@@ -63415,7 +63415,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2174" t="n">
-        <v>5.7903904914856</v>
+        <v>5.79039001464844</v>
       </c>
       <c r="H2174" t="n">
         <v>33583</v>
@@ -63444,7 +63444,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2175" t="n">
-        <v>5.7903904914856</v>
+        <v>5.79039001464844</v>
       </c>
       <c r="H2175" t="n">
         <v>2041</v>
@@ -64082,7 +64082,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2197" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2197" t="n">
         <v>46134</v>
@@ -64140,7 +64140,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2199" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2199" t="n">
         <v>43455</v>
@@ -64198,7 +64198,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2201" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2201" t="n">
         <v>36088</v>
@@ -64256,7 +64256,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2203" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2203" t="n">
         <v>37217</v>
@@ -64285,7 +64285,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2204" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2204" t="n">
         <v>39475</v>
@@ -64314,7 +64314,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2205" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2205" t="n">
         <v>38442</v>
@@ -79951,6 +79951,64 @@
         <v>7186</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>1.79499995708466</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>1.7849999666214</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>1.7849999666214</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>3480</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -543,7 +543,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17537927627563</v>
+        <v>2.17537951469421</v>
       </c>
       <c r="H6" t="n">
         <v>1800</v>
@@ -572,7 +572,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G7" t="n">
-        <v>2.17537927627563</v>
+        <v>2.17537951469421</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>2.99799990653992</v>
       </c>
       <c r="G8" t="n">
-        <v>2.17537927627563</v>
+        <v>2.17537951469421</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1042697429657</v>
+        <v>2.10426998138428</v>
       </c>
       <c r="H18" t="n">
         <v>3000</v>
@@ -949,7 +949,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2044038772583</v>
+        <v>2.20440411567688</v>
       </c>
       <c r="H20" t="n">
         <v>600</v>
@@ -1036,7 +1036,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14345240592957</v>
+        <v>2.14345288276672</v>
       </c>
       <c r="H23" t="n">
         <v>1800</v>
@@ -1065,7 +1065,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14345240592957</v>
+        <v>2.14345288276672</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14345240592957</v>
+        <v>2.14345288276672</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14345240592957</v>
+        <v>2.14345288276672</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14055037498474</v>
+        <v>2.14055013656616</v>
       </c>
       <c r="H29" t="n">
         <v>600</v>
@@ -1239,7 +1239,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16231846809387</v>
+        <v>2.16231870651245</v>
       </c>
       <c r="H30" t="n">
         <v>1200</v>
@@ -1268,7 +1268,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G31" t="n">
-        <v>2.13474535942078</v>
+        <v>2.1347451210022</v>
       </c>
       <c r="H31" t="n">
         <v>3000</v>
@@ -1297,7 +1297,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H32" t="n">
         <v>3000</v>
@@ -1326,7 +1326,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G37" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G38" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G44" t="n">
-        <v>2.2044038772583</v>
+        <v>2.20440411567688</v>
       </c>
       <c r="H44" t="n">
         <v>4800</v>
@@ -1703,7 +1703,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G46" t="n">
-        <v>2.24648928642273</v>
+        <v>2.24648952484131</v>
       </c>
       <c r="H46" t="n">
         <v>600</v>
@@ -1732,7 +1732,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G47" t="n">
-        <v>2.16086721420288</v>
+        <v>2.16086745262146</v>
       </c>
       <c r="H47" t="n">
         <v>1800</v>
@@ -1819,7 +1819,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>2.17247724533081</v>
+        <v>2.17247700691223</v>
       </c>
       <c r="H50" t="n">
         <v>600</v>
@@ -1848,7 +1848,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G51" t="n">
-        <v>2.22617220878601</v>
+        <v>2.22617244720459</v>
       </c>
       <c r="H51" t="n">
         <v>2400</v>
@@ -1877,7 +1877,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G52" t="n">
-        <v>2.22617220878601</v>
+        <v>2.22617244720459</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G53" t="n">
-        <v>2.25519680976868</v>
+        <v>2.2551965713501</v>
       </c>
       <c r="H53" t="n">
         <v>3000</v>
@@ -2283,7 +2283,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G66" t="n">
-        <v>2.24503827095032</v>
+        <v>2.24503803253174</v>
       </c>
       <c r="H66" t="n">
         <v>1200</v>
@@ -2312,7 +2312,7 @@
         <v>3.09400010108948</v>
       </c>
       <c r="G67" t="n">
-        <v>2.24503827095032</v>
+        <v>2.24503803253174</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G68" t="n">
-        <v>2.17973327636719</v>
+        <v>2.17973303794861</v>
       </c>
       <c r="H68" t="n">
         <v>5400</v>
@@ -2370,7 +2370,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G69" t="n">
-        <v>2.23052597045898</v>
+        <v>2.23052573204041</v>
       </c>
       <c r="H69" t="n">
         <v>7200</v>
@@ -2428,7 +2428,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H71" t="n">
         <v>1560</v>
@@ -2457,7 +2457,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G72" t="n">
-        <v>1.71824491024017</v>
+        <v>1.71824514865875</v>
       </c>
       <c r="H72" t="n">
         <v>780</v>
@@ -2515,7 +2515,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G74" t="n">
-        <v>1.76758658885956</v>
+        <v>1.76758670806885</v>
       </c>
       <c r="H74" t="n">
         <v>1560</v>
@@ -2544,7 +2544,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G75" t="n">
-        <v>1.76468408107758</v>
+        <v>1.76468420028687</v>
       </c>
       <c r="H75" t="n">
         <v>780</v>
@@ -2573,7 +2573,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G76" t="n">
-        <v>1.76468408107758</v>
+        <v>1.76468420028687</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H83" t="n">
         <v>780</v>
@@ -2863,7 +2863,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G86" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H86" t="n">
         <v>5460</v>
@@ -2950,7 +2950,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G89" t="n">
-        <v>1.73275721073151</v>
+        <v>1.7327573299408</v>
       </c>
       <c r="H89" t="n">
         <v>1560</v>
@@ -3298,7 +3298,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H101" t="n">
         <v>2340</v>
@@ -3385,7 +3385,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63117170333862</v>
+        <v>1.63117182254791</v>
       </c>
       <c r="H104" t="n">
         <v>1560</v>
@@ -3414,7 +3414,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G105" t="n">
-        <v>1.63117170333862</v>
+        <v>1.63117182254791</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>1.62826931476593</v>
+        <v>1.62826943397522</v>
       </c>
       <c r="H106" t="n">
         <v>3120</v>
@@ -3472,7 +3472,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62826931476593</v>
+        <v>1.62826943397522</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62826931476593</v>
+        <v>1.62826943397522</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G109" t="n">
-        <v>1.62826931476593</v>
+        <v>1.62826943397522</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>1.62826931476593</v>
+        <v>1.62826943397522</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G113" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H113" t="n">
         <v>780</v>
@@ -3907,7 +3907,7 @@
         <v>2.25</v>
       </c>
       <c r="G122" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H122" t="n">
         <v>5460</v>
@@ -3936,7 +3936,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H123" t="n">
         <v>780</v>
@@ -3965,7 +3965,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G124" t="n">
-        <v>1.67180597782135</v>
+        <v>1.67180585861206</v>
       </c>
       <c r="H124" t="n">
         <v>3900</v>
@@ -4023,7 +4023,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G126" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H126" t="n">
         <v>3120</v>
@@ -4052,7 +4052,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G127" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G128" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G129" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G131" t="n">
-        <v>1.54990339279175</v>
+        <v>1.54990351200104</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G132" t="n">
-        <v>1.54409861564636</v>
+        <v>1.54409873485565</v>
       </c>
       <c r="H132" t="n">
         <v>2340</v>
@@ -4226,7 +4226,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G133" t="n">
-        <v>1.54409861564636</v>
+        <v>1.54409873485565</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H140" t="n">
         <v>3900</v>
@@ -4458,7 +4458,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H141" t="n">
         <v>19500</v>
@@ -4487,7 +4487,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H142" t="n">
         <v>3900</v>
@@ -4516,7 +4516,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>1.40768384933472</v>
+        <v>1.40768396854401</v>
       </c>
       <c r="H144" t="n">
         <v>4680</v>
@@ -4574,7 +4574,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H145" t="n">
         <v>3900</v>
@@ -4603,7 +4603,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>1.34600710868835</v>
+        <v>1.34600698947906</v>
       </c>
       <c r="H146" t="n">
         <v>1560</v>
@@ -4690,7 +4690,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G149" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H149" t="n">
         <v>17160</v>
@@ -4719,7 +4719,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G150" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H150" t="n">
         <v>2340</v>
@@ -4748,7 +4748,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G152" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G155" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G156" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G157" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G158" t="n">
-        <v>1.39099490642548</v>
+        <v>1.39099478721619</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G160" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H160" t="n">
         <v>5460</v>
@@ -5038,7 +5038,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G161" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G165" t="n">
-        <v>1.27925086021423</v>
+        <v>1.27925097942352</v>
       </c>
       <c r="H165" t="n">
         <v>780</v>
@@ -5386,7 +5386,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G173" t="n">
-        <v>1.33947658538818</v>
+        <v>1.33947646617889</v>
       </c>
       <c r="H173" t="n">
         <v>780</v>
@@ -5415,7 +5415,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H174" t="n">
         <v>780</v>
@@ -5444,7 +5444,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G175" t="n">
-        <v>1.36269593238831</v>
+        <v>1.3626960515976</v>
       </c>
       <c r="H175" t="n">
         <v>780</v>
@@ -5473,7 +5473,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G176" t="n">
-        <v>1.36269593238831</v>
+        <v>1.3626960515976</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>1.35544002056122</v>
+        <v>1.35543990135193</v>
       </c>
       <c r="H177" t="n">
         <v>780</v>
@@ -5879,7 +5879,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.32061076164246</v>
+        <v>1.32061064243317</v>
       </c>
       <c r="H190" t="n">
         <v>2340</v>
@@ -5966,7 +5966,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G193" t="n">
-        <v>1.24224472045898</v>
+        <v>1.24224483966827</v>
       </c>
       <c r="H193" t="n">
         <v>1560</v>
@@ -5995,7 +5995,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G194" t="n">
-        <v>1.24224472045898</v>
+        <v>1.24224483966827</v>
       </c>
       <c r="H194" t="n">
         <v>780</v>
@@ -6227,7 +6227,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22628128528595</v>
+        <v>1.22628140449524</v>
       </c>
       <c r="H202" t="n">
         <v>1560</v>
@@ -6285,7 +6285,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>1.3133544921875</v>
+        <v>1.31335461139679</v>
       </c>
       <c r="H204" t="n">
         <v>1560</v>
@@ -6314,7 +6314,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>1.3133544921875</v>
+        <v>1.31335461139679</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>1.3133544921875</v>
+        <v>1.31335461139679</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G207" t="n">
-        <v>1.3133544921875</v>
+        <v>1.31335461139679</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>1.3133544921875</v>
+        <v>1.31335461139679</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>1.3133544921875</v>
+        <v>1.31335461139679</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G210" t="n">
-        <v>1.3133544921875</v>
+        <v>1.31335461139679</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G211" t="n">
-        <v>1.3133544921875</v>
+        <v>1.31335461139679</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G212" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H212" t="n">
         <v>780</v>
@@ -6546,7 +6546,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H213" t="n">
         <v>1560</v>
@@ -6575,7 +6575,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H218" t="n">
         <v>780</v>
@@ -6720,7 +6720,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G223" t="n">
-        <v>1.30247032642365</v>
+        <v>1.30247044563293</v>
       </c>
       <c r="H223" t="n">
         <v>3120</v>
@@ -6865,7 +6865,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G224" t="n">
-        <v>1.30247032642365</v>
+        <v>1.30247044563293</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H233" t="n">
         <v>6240</v>
@@ -7155,7 +7155,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G235" t="n">
-        <v>1.21902513504028</v>
+        <v>1.21902525424957</v>
       </c>
       <c r="H235" t="n">
         <v>2340</v>
@@ -7213,7 +7213,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G236" t="n">
-        <v>1.21902513504028</v>
+        <v>1.21902525424957</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G239" t="n">
-        <v>1.2110435962677</v>
+        <v>1.21104347705841</v>
       </c>
       <c r="H239" t="n">
         <v>3120</v>
@@ -7329,7 +7329,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G240" t="n">
-        <v>1.2110435962677</v>
+        <v>1.21104347705841</v>
       </c>
       <c r="H240" t="n">
         <v>1560</v>
@@ -7387,7 +7387,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>1.17403745651245</v>
+        <v>1.17403733730316</v>
       </c>
       <c r="H242" t="n">
         <v>1560</v>
@@ -7416,7 +7416,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>1.17403745651245</v>
+        <v>1.17403733730316</v>
       </c>
       <c r="H243" t="n">
         <v>16380</v>
@@ -7532,7 +7532,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18854951858521</v>
+        <v>1.18854963779449</v>
       </c>
       <c r="H247" t="n">
         <v>3900</v>
@@ -7561,7 +7561,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18854951858521</v>
+        <v>1.18854963779449</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G260" t="n">
-        <v>1.25240337848663</v>
+        <v>1.25240325927734</v>
       </c>
       <c r="H260" t="n">
         <v>3120</v>
@@ -8286,7 +8286,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G273" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H273" t="n">
         <v>3900</v>
@@ -8315,7 +8315,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G274" t="n">
-        <v>1.27707409858704</v>
+        <v>1.27707397937775</v>
       </c>
       <c r="H274" t="n">
         <v>8580</v>
@@ -8344,7 +8344,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H275" t="n">
         <v>72540</v>
@@ -8373,7 +8373,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G276" t="n">
-        <v>1.58328151702881</v>
+        <v>1.5832816362381</v>
       </c>
       <c r="H276" t="n">
         <v>86580</v>
@@ -8402,7 +8402,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G277" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H277" t="n">
         <v>13260</v>
@@ -8431,7 +8431,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G278" t="n">
-        <v>1.46718406677246</v>
+        <v>1.46718394756317</v>
       </c>
       <c r="H278" t="n">
         <v>15600</v>
@@ -8460,7 +8460,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>1.40768384933472</v>
+        <v>1.40768396854401</v>
       </c>
       <c r="H279" t="n">
         <v>7020</v>
@@ -8518,7 +8518,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G281" t="n">
-        <v>1.42727530002594</v>
+        <v>1.42727541923523</v>
       </c>
       <c r="H281" t="n">
         <v>7800</v>
@@ -8576,7 +8576,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32133615016937</v>
+        <v>1.32133626937866</v>
       </c>
       <c r="H283" t="n">
         <v>3900</v>
@@ -8779,7 +8779,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G290" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H290" t="n">
         <v>1560</v>
@@ -8808,7 +8808,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G291" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G292" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.21176898479462</v>
+        <v>1.21176910400391</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G294" t="n">
-        <v>1.2110435962677</v>
+        <v>1.21104347705841</v>
       </c>
       <c r="H294" t="n">
         <v>3900</v>
@@ -8924,7 +8924,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G295" t="n">
-        <v>1.2110435962677</v>
+        <v>1.21104347705841</v>
       </c>
       <c r="H295" t="n">
         <v>3120</v>
@@ -8953,7 +8953,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G296" t="n">
-        <v>1.2110435962677</v>
+        <v>1.21104347705841</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G301" t="n">
-        <v>1.21902513504028</v>
+        <v>1.21902525424957</v>
       </c>
       <c r="H301" t="n">
         <v>6240</v>
@@ -9185,7 +9185,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G304" t="n">
-        <v>1.24950075149536</v>
+        <v>1.24950087070465</v>
       </c>
       <c r="H304" t="n">
         <v>780</v>
@@ -9243,7 +9243,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G306" t="n">
-        <v>1.37865936756134</v>
+        <v>1.37865948677063</v>
       </c>
       <c r="H306" t="n">
         <v>7800</v>
@@ -9301,7 +9301,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G308" t="n">
-        <v>1.34890949726105</v>
+        <v>1.34890937805176</v>
       </c>
       <c r="H308" t="n">
         <v>1560</v>
@@ -9330,7 +9330,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G309" t="n">
-        <v>1.34890949726105</v>
+        <v>1.34890937805176</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G318" t="n">
-        <v>1.4845986366272</v>
+        <v>1.48459851741791</v>
       </c>
       <c r="H318" t="n">
         <v>7800</v>
@@ -9620,7 +9620,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H319" t="n">
         <v>30420</v>
@@ -9678,7 +9678,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H321" t="n">
         <v>83460</v>
@@ -9707,7 +9707,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G322" t="n">
-        <v>1.67035472393036</v>
+        <v>1.67035484313965</v>
       </c>
       <c r="H322" t="n">
         <v>65520</v>
@@ -9736,7 +9736,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H323" t="n">
         <v>76440</v>
@@ -9794,7 +9794,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H325" t="n">
         <v>14820</v>
@@ -9823,7 +9823,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H326" t="n">
         <v>30420</v>
@@ -9939,7 +9939,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G330" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H330" t="n">
         <v>10140</v>
@@ -9968,7 +9968,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>1.48024487495422</v>
+        <v>1.48024499416351</v>
       </c>
       <c r="H331" t="n">
         <v>3900</v>
@@ -9997,7 +9997,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G332" t="n">
-        <v>1.40478134155273</v>
+        <v>1.40478146076202</v>
       </c>
       <c r="H332" t="n">
         <v>53040</v>
@@ -10026,7 +10026,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>1.48024487495422</v>
+        <v>1.48024499416351</v>
       </c>
       <c r="H333" t="n">
         <v>10140</v>
@@ -10055,7 +10055,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>1.48024487495422</v>
+        <v>1.48024499416351</v>
       </c>
       <c r="H334" t="n">
         <v>3120</v>
@@ -10084,7 +10084,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G335" t="n">
-        <v>1.43815946578979</v>
+        <v>1.43815958499908</v>
       </c>
       <c r="H335" t="n">
         <v>56160</v>
@@ -10171,7 +10171,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G338" t="n">
-        <v>1.42945230007172</v>
+        <v>1.42945218086243</v>
       </c>
       <c r="H338" t="n">
         <v>17160</v>
@@ -10200,7 +10200,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G339" t="n">
-        <v>1.42872655391693</v>
+        <v>1.42872667312622</v>
       </c>
       <c r="H339" t="n">
         <v>1560</v>
@@ -10229,7 +10229,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G340" t="n">
-        <v>1.41494011878967</v>
+        <v>1.41493999958038</v>
       </c>
       <c r="H340" t="n">
         <v>10140</v>
@@ -10287,7 +10287,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>1.42945230007172</v>
+        <v>1.42945218086243</v>
       </c>
       <c r="H342" t="n">
         <v>24960</v>
@@ -10345,7 +10345,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>1.40768384933472</v>
+        <v>1.40768396854401</v>
       </c>
       <c r="H344" t="n">
         <v>6240</v>
@@ -10374,7 +10374,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G345" t="n">
-        <v>1.41494011878967</v>
+        <v>1.41493999958038</v>
       </c>
       <c r="H345" t="n">
         <v>14040</v>
@@ -10432,7 +10432,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G347" t="n">
-        <v>1.47298872470856</v>
+        <v>1.47298884391785</v>
       </c>
       <c r="H347" t="n">
         <v>5460</v>
@@ -10461,7 +10461,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5586109161377</v>
+        <v>1.55861079692841</v>
       </c>
       <c r="H348" t="n">
         <v>28080</v>
@@ -10548,7 +10548,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G351" t="n">
-        <v>1.41566550731659</v>
+        <v>1.41566562652588</v>
       </c>
       <c r="H351" t="n">
         <v>35100</v>
@@ -10664,7 +10664,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G355" t="n">
-        <v>1.47008633613586</v>
+        <v>1.47008645534515</v>
       </c>
       <c r="H355" t="n">
         <v>2340</v>
@@ -10751,7 +10751,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>1.49330604076385</v>
+        <v>1.49330592155457</v>
       </c>
       <c r="H358" t="n">
         <v>11700</v>
@@ -10809,7 +10809,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G360" t="n">
-        <v>1.47879374027252</v>
+        <v>1.47879385948181</v>
       </c>
       <c r="H360" t="n">
         <v>6240</v>
@@ -10867,7 +10867,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H362" t="n">
         <v>10140</v>
@@ -11012,7 +11012,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G367" t="n">
-        <v>1.54554998874664</v>
+        <v>1.54554986953735</v>
       </c>
       <c r="H367" t="n">
         <v>16380</v>
@@ -11070,7 +11070,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.58473289012909</v>
+        <v>1.5847327709198</v>
       </c>
       <c r="H369" t="n">
         <v>21840</v>
@@ -11099,7 +11099,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H370" t="n">
         <v>38220</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H371" t="n">
         <v>27300</v>
@@ -11157,7 +11157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H372" t="n">
         <v>10920</v>
@@ -11215,7 +11215,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H374" t="n">
         <v>6240</v>
@@ -11244,7 +11244,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H375" t="n">
         <v>2340</v>
@@ -11447,7 +11447,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G382" t="n">
-        <v>1.82708656787872</v>
+        <v>1.82708668708801</v>
       </c>
       <c r="H382" t="n">
         <v>68640</v>
@@ -11476,7 +11476,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>1.95914769172668</v>
+        <v>1.95914781093597</v>
       </c>
       <c r="H383" t="n">
         <v>76440</v>
@@ -11505,7 +11505,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G384" t="n">
-        <v>2.10281872749329</v>
+        <v>2.10281848907471</v>
       </c>
       <c r="H384" t="n">
         <v>68640</v>
@@ -11563,7 +11563,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>2.09991598129272</v>
+        <v>2.0999162197113</v>
       </c>
       <c r="H386" t="n">
         <v>116220</v>
@@ -11650,7 +11650,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G389" t="n">
-        <v>2.00558686256409</v>
+        <v>2.00558662414551</v>
       </c>
       <c r="H389" t="n">
         <v>10920</v>
@@ -11737,7 +11737,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G392" t="n">
-        <v>1.95044016838074</v>
+        <v>1.95044028759003</v>
       </c>
       <c r="H392" t="n">
         <v>20280</v>
@@ -11766,7 +11766,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318413734436</v>
+        <v>1.94318437576294</v>
       </c>
       <c r="H393" t="n">
         <v>3900</v>
@@ -11824,7 +11824,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G395" t="n">
-        <v>1.86917197704315</v>
+        <v>1.86917221546173</v>
       </c>
       <c r="H395" t="n">
         <v>8580</v>
@@ -11911,7 +11911,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G398" t="n">
-        <v>2.01574516296387</v>
+        <v>2.01574540138245</v>
       </c>
       <c r="H398" t="n">
         <v>72540</v>
@@ -12056,7 +12056,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G403" t="n">
-        <v>1.786452293396</v>
+        <v>1.78645241260529</v>
       </c>
       <c r="H403" t="n">
         <v>37440</v>
@@ -12085,7 +12085,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563555240631</v>
+        <v>1.82563519477844</v>
       </c>
       <c r="H404" t="n">
         <v>66300</v>
@@ -12114,7 +12114,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H405" t="n">
         <v>109200</v>
@@ -12143,7 +12143,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H406" t="n">
         <v>160680</v>
@@ -12172,7 +12172,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G407" t="n">
-        <v>1.7574280500412</v>
+        <v>1.75742793083191</v>
       </c>
       <c r="H407" t="n">
         <v>31980</v>
@@ -12230,7 +12230,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G409" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H409" t="n">
         <v>10140</v>
@@ -12462,7 +12462,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.69067192077637</v>
+        <v>1.69067180156708</v>
       </c>
       <c r="H417" t="n">
         <v>48360</v>
@@ -12491,7 +12491,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G418" t="n">
-        <v>1.6587450504303</v>
+        <v>1.65874493122101</v>
       </c>
       <c r="H418" t="n">
         <v>25740</v>
@@ -12607,7 +12607,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73856210708618</v>
+        <v>1.73856198787689</v>
       </c>
       <c r="H422" t="n">
         <v>40560</v>
@@ -12636,7 +12636,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>1.806769490242</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H423" t="n">
         <v>48360</v>
@@ -12665,7 +12665,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G424" t="n">
-        <v>1.81837952136993</v>
+        <v>1.81837928295135</v>
       </c>
       <c r="H424" t="n">
         <v>19500</v>
@@ -12723,7 +12723,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G426" t="n">
-        <v>1.806769490242</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H426" t="n">
         <v>27300</v>
@@ -12752,7 +12752,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>1.79951345920563</v>
+        <v>1.79951333999634</v>
       </c>
       <c r="H427" t="n">
         <v>1560</v>
@@ -12839,7 +12839,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.91561114788055</v>
+        <v>1.91561126708984</v>
       </c>
       <c r="H430" t="n">
         <v>19500</v>
@@ -12984,7 +12984,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>1.85175728797913</v>
+        <v>1.85175752639771</v>
       </c>
       <c r="H435" t="n">
         <v>10140</v>
@@ -13013,7 +13013,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>1.85756230354309</v>
+        <v>1.85756206512451</v>
       </c>
       <c r="H436" t="n">
         <v>3900</v>
@@ -13071,7 +13071,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G438" t="n">
-        <v>1.76468408107758</v>
+        <v>1.76468420028687</v>
       </c>
       <c r="H438" t="n">
         <v>8580</v>
@@ -13100,7 +13100,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>1.85030603408813</v>
+        <v>1.85030615329742</v>
       </c>
       <c r="H439" t="n">
         <v>46020</v>
@@ -13216,7 +13216,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G443" t="n">
-        <v>1.87352561950684</v>
+        <v>1.87352573871613</v>
       </c>
       <c r="H443" t="n">
         <v>24180</v>
@@ -13303,7 +13303,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G446" t="n">
-        <v>2.01139187812805</v>
+        <v>2.01139163970947</v>
       </c>
       <c r="H446" t="n">
         <v>130260</v>
@@ -13361,7 +13361,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93302571773529</v>
+        <v>1.93302595615387</v>
       </c>
       <c r="H448" t="n">
         <v>14040</v>
@@ -13390,7 +13390,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G449" t="n">
-        <v>1.86917197704315</v>
+        <v>1.86917221546173</v>
       </c>
       <c r="H449" t="n">
         <v>28860</v>
@@ -13448,7 +13448,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G451" t="n">
-        <v>1.86917197704315</v>
+        <v>1.86917221546173</v>
       </c>
       <c r="H451" t="n">
         <v>76440</v>
@@ -13477,7 +13477,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>1.85030603408813</v>
+        <v>1.85030615329742</v>
       </c>
       <c r="H452" t="n">
         <v>22620</v>
@@ -13506,7 +13506,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G453" t="n">
-        <v>1.84014761447906</v>
+        <v>1.84014773368835</v>
       </c>
       <c r="H453" t="n">
         <v>10140</v>
@@ -13535,7 +13535,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207424640656</v>
+        <v>1.87207460403442</v>
       </c>
       <c r="H454" t="n">
         <v>31200</v>
@@ -13564,7 +13564,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>1.85756230354309</v>
+        <v>1.85756206512451</v>
       </c>
       <c r="H455" t="n">
         <v>18720</v>
@@ -13622,7 +13622,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>1.93737924098969</v>
+        <v>1.93737947940826</v>
       </c>
       <c r="H457" t="n">
         <v>205920</v>
@@ -13651,7 +13651,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>1.91561114788055</v>
+        <v>1.91561126708984</v>
       </c>
       <c r="H458" t="n">
         <v>38220</v>
@@ -13680,7 +13680,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G459" t="n">
-        <v>1.8851352930069</v>
+        <v>1.88513541221619</v>
       </c>
       <c r="H459" t="n">
         <v>58500</v>
@@ -13738,7 +13738,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G461" t="n">
-        <v>1.87787926197052</v>
+        <v>1.87787938117981</v>
       </c>
       <c r="H461" t="n">
         <v>12480</v>
@@ -13767,7 +13767,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>1.92141604423523</v>
+        <v>1.92141580581665</v>
       </c>
       <c r="H462" t="n">
         <v>85800</v>
@@ -13912,7 +13912,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>1.90835511684418</v>
+        <v>1.90835499763489</v>
       </c>
       <c r="H467" t="n">
         <v>35100</v>
@@ -13970,7 +13970,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>1.92286717891693</v>
+        <v>1.92286729812622</v>
       </c>
       <c r="H469" t="n">
         <v>34320</v>
@@ -13999,7 +13999,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G470" t="n">
-        <v>1.90255010128021</v>
+        <v>1.90254998207092</v>
       </c>
       <c r="H470" t="n">
         <v>18720</v>
@@ -14057,7 +14057,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>1.89094018936157</v>
+        <v>1.89094042778015</v>
       </c>
       <c r="H472" t="n">
         <v>6240</v>
@@ -14086,7 +14086,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G473" t="n">
-        <v>1.90255010128021</v>
+        <v>1.90254998207092</v>
       </c>
       <c r="H473" t="n">
         <v>15600</v>
@@ -14115,7 +14115,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>1.88078165054321</v>
+        <v>1.8807817697525</v>
       </c>
       <c r="H474" t="n">
         <v>24180</v>
@@ -14144,7 +14144,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G475" t="n">
-        <v>1.90980637073517</v>
+        <v>1.9098060131073</v>
       </c>
       <c r="H475" t="n">
         <v>13260</v>
@@ -14173,7 +14173,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G476" t="n">
-        <v>1.87497711181641</v>
+        <v>1.87497699260712</v>
       </c>
       <c r="H476" t="n">
         <v>3120</v>
@@ -14202,7 +14202,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G477" t="n">
-        <v>1.82273316383362</v>
+        <v>1.82273304462433</v>
       </c>
       <c r="H477" t="n">
         <v>10920</v>
@@ -14231,7 +14231,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G478" t="n">
-        <v>1.82273316383362</v>
+        <v>1.82273304462433</v>
       </c>
       <c r="H478" t="n">
         <v>13260</v>
@@ -14260,7 +14260,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>1.82273316383362</v>
+        <v>1.82273304462433</v>
       </c>
       <c r="H479" t="n">
         <v>6240</v>
@@ -14318,7 +14318,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>1.72114753723145</v>
+        <v>1.72114741802216</v>
       </c>
       <c r="H481" t="n">
         <v>14820</v>
@@ -14347,7 +14347,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G482" t="n">
-        <v>1.808220744133</v>
+        <v>1.80822086334229</v>
       </c>
       <c r="H482" t="n">
         <v>25740</v>
@@ -14376,7 +14376,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H483" t="n">
         <v>7020</v>
@@ -14405,7 +14405,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G484" t="n">
-        <v>1.80096483230591</v>
+        <v>1.80096459388733</v>
       </c>
       <c r="H484" t="n">
         <v>2340</v>
@@ -14492,7 +14492,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G487" t="n">
-        <v>1.81837952136993</v>
+        <v>1.81837928295135</v>
       </c>
       <c r="H487" t="n">
         <v>2340</v>
@@ -14608,7 +14608,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G491" t="n">
-        <v>1.83869636058807</v>
+        <v>1.83869624137878</v>
       </c>
       <c r="H491" t="n">
         <v>9360</v>
@@ -14637,7 +14637,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G492" t="n">
-        <v>1.85175728797913</v>
+        <v>1.85175752639771</v>
       </c>
       <c r="H492" t="n">
         <v>14040</v>
@@ -14695,7 +14695,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G494" t="n">
-        <v>1.88078165054321</v>
+        <v>1.8807817697525</v>
       </c>
       <c r="H494" t="n">
         <v>35880</v>
@@ -14724,7 +14724,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H495" t="n">
         <v>34320</v>
@@ -14753,7 +14753,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>1.82853770256042</v>
+        <v>1.82853782176971</v>
       </c>
       <c r="H496" t="n">
         <v>50700</v>
@@ -14840,7 +14840,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H499" t="n">
         <v>10920</v>
@@ -14869,7 +14869,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G501" t="n">
-        <v>1.88368427753448</v>
+        <v>1.8836841583252</v>
       </c>
       <c r="H501" t="n">
         <v>10140</v>
@@ -14927,7 +14927,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G502" t="n">
-        <v>1.87062346935272</v>
+        <v>1.87062335014343</v>
       </c>
       <c r="H502" t="n">
         <v>10140</v>
@@ -15014,7 +15014,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H505" t="n">
         <v>780</v>
@@ -15043,7 +15043,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G509" t="n">
-        <v>1.80096483230591</v>
+        <v>1.80096459388733</v>
       </c>
       <c r="H509" t="n">
         <v>5460</v>
@@ -15159,7 +15159,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G510" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H510" t="n">
         <v>1560</v>
@@ -15188,7 +15188,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G511" t="n">
-        <v>1.82998919487</v>
+        <v>1.82998931407928</v>
       </c>
       <c r="H511" t="n">
         <v>3120</v>
@@ -15217,7 +15217,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G512" t="n">
-        <v>1.77629375457764</v>
+        <v>1.77629387378693</v>
       </c>
       <c r="H512" t="n">
         <v>3900</v>
@@ -15246,7 +15246,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>1.79951345920563</v>
+        <v>1.79951333999634</v>
       </c>
       <c r="H513" t="n">
         <v>6240</v>
@@ -15275,7 +15275,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H514" t="n">
         <v>4680</v>
@@ -15304,7 +15304,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>1.82853770256042</v>
+        <v>1.82853782176971</v>
       </c>
       <c r="H515" t="n">
         <v>9360</v>
@@ -15362,7 +15362,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>1.85030603408813</v>
+        <v>1.85030615329742</v>
       </c>
       <c r="H517" t="n">
         <v>16380</v>
@@ -15391,7 +15391,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G518" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H518" t="n">
         <v>10920</v>
@@ -15449,7 +15449,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G520" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H520" t="n">
         <v>17160</v>
@@ -15478,7 +15478,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>1.806769490242</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H521" t="n">
         <v>780</v>
@@ -15507,7 +15507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H522" t="n">
         <v>3120</v>
@@ -15536,7 +15536,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G523" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H523" t="n">
         <v>2340</v>
@@ -15565,7 +15565,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H524" t="n">
         <v>7020</v>
@@ -15652,7 +15652,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>1.85756230354309</v>
+        <v>1.85756206512451</v>
       </c>
       <c r="H527" t="n">
         <v>8580</v>
@@ -15681,7 +15681,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>1.92286717891693</v>
+        <v>1.92286729812622</v>
       </c>
       <c r="H528" t="n">
         <v>124020</v>
@@ -15710,7 +15710,7 @@
         <v>2.75</v>
       </c>
       <c r="G529" t="n">
-        <v>1.99542808532715</v>
+        <v>1.99542820453644</v>
       </c>
       <c r="H529" t="n">
         <v>39780</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.93737924098969</v>
+        <v>1.93737947940826</v>
       </c>
       <c r="H530" t="n">
         <v>56940</v>
@@ -15768,7 +15768,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>1.89384257793427</v>
+        <v>1.89384281635284</v>
       </c>
       <c r="H531" t="n">
         <v>25740</v>
@@ -15797,7 +15797,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H532" t="n">
         <v>46020</v>
@@ -15855,7 +15855,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H534" t="n">
         <v>3900</v>
@@ -15913,7 +15913,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H536" t="n">
         <v>30420</v>
@@ -15942,7 +15942,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G537" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H537" t="n">
         <v>12480</v>
@@ -16029,7 +16029,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G540" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H540" t="n">
         <v>44460</v>
@@ -16087,7 +16087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H542" t="n">
         <v>19500</v>
@@ -16145,7 +16145,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G544" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H544" t="n">
         <v>1560</v>
@@ -16203,7 +16203,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G546" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H546" t="n">
         <v>10140</v>
@@ -16232,7 +16232,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G547" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H547" t="n">
         <v>8580</v>
@@ -16290,7 +16290,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G549" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H549" t="n">
         <v>23400</v>
@@ -16377,7 +16377,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G552" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H552" t="n">
         <v>780</v>
@@ -16435,7 +16435,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G554" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H554" t="n">
         <v>1560</v>
@@ -16522,7 +16522,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.69067192077637</v>
+        <v>1.69067180156708</v>
       </c>
       <c r="H557" t="n">
         <v>7800</v>
@@ -16580,7 +16580,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G559" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H559" t="n">
         <v>11700</v>
@@ -16609,7 +16609,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>1.69067192077637</v>
+        <v>1.69067180156708</v>
       </c>
       <c r="H560" t="n">
         <v>4680</v>
@@ -16638,7 +16638,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G561" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H561" t="n">
         <v>1560</v>
@@ -16667,7 +16667,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G562" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H562" t="n">
         <v>3120</v>
@@ -16696,7 +16696,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>1.69067192077637</v>
+        <v>1.69067180156708</v>
       </c>
       <c r="H563" t="n">
         <v>4680</v>
@@ -16725,7 +16725,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G564" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H564" t="n">
         <v>59280</v>
@@ -16754,7 +16754,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H565" t="n">
         <v>4680</v>
@@ -16841,7 +16841,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G568" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H568" t="n">
         <v>16380</v>
@@ -16899,7 +16899,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H570" t="n">
         <v>5460</v>
@@ -16986,7 +16986,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G573" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H573" t="n">
         <v>34320</v>
@@ -17073,7 +17073,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H576" t="n">
         <v>22620</v>
@@ -17131,7 +17131,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H578" t="n">
         <v>1560</v>
@@ -17160,7 +17160,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G579" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H579" t="n">
         <v>7800</v>
@@ -17218,7 +17218,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H581" t="n">
         <v>3900</v>
@@ -17247,7 +17247,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H582" t="n">
         <v>17940</v>
@@ -17276,7 +17276,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H583" t="n">
         <v>8580</v>
@@ -17305,7 +17305,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H585" t="n">
         <v>105300</v>
@@ -17363,7 +17363,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>1.69067192077637</v>
+        <v>1.69067180156708</v>
       </c>
       <c r="H586" t="n">
         <v>7020</v>
@@ -17392,7 +17392,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>1.69067192077637</v>
+        <v>1.69067180156708</v>
       </c>
       <c r="H587" t="n">
         <v>7020</v>
@@ -17421,7 +17421,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H588" t="n">
         <v>6240</v>
@@ -17537,7 +17537,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H592" t="n">
         <v>4680</v>
@@ -17566,7 +17566,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G593" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H593" t="n">
         <v>780</v>
@@ -17595,7 +17595,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H594" t="n">
         <v>4680</v>
@@ -17653,7 +17653,7 @@
         <v>2.25</v>
       </c>
       <c r="G596" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H596" t="n">
         <v>4680</v>
@@ -17682,7 +17682,7 @@
         <v>2.25</v>
       </c>
       <c r="G597" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H597" t="n">
         <v>15600</v>
@@ -17711,7 +17711,7 @@
         <v>2.25</v>
       </c>
       <c r="G598" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>2.25</v>
       </c>
       <c r="G600" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H600" t="n">
         <v>131820</v>
@@ -17856,7 +17856,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G603" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H603" t="n">
         <v>39000</v>
@@ -17885,7 +17885,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.69067192077637</v>
+        <v>1.69067180156708</v>
       </c>
       <c r="H604" t="n">
         <v>16380</v>
@@ -17914,7 +17914,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G605" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H605" t="n">
         <v>20280</v>
@@ -17943,7 +17943,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H606" t="n">
         <v>15600</v>
@@ -17972,7 +17972,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H607" t="n">
         <v>15600</v>
@@ -18001,7 +18001,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H608" t="n">
         <v>7020</v>
@@ -18059,7 +18059,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H610" t="n">
         <v>12480</v>
@@ -18175,7 +18175,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G614" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H614" t="n">
         <v>23400</v>
@@ -18233,7 +18233,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G616" t="n">
-        <v>1.4875009059906</v>
+        <v>1.48750102519989</v>
       </c>
       <c r="H616" t="n">
         <v>27300</v>
@@ -18262,7 +18262,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>1.54554998874664</v>
+        <v>1.54554986953735</v>
       </c>
       <c r="H617" t="n">
         <v>14040</v>
@@ -18291,7 +18291,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G618" t="n">
-        <v>1.54554998874664</v>
+        <v>1.54554986953735</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H622" t="n">
         <v>10140</v>
@@ -18436,7 +18436,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G623" t="n">
-        <v>1.55280590057373</v>
+        <v>1.55280601978302</v>
       </c>
       <c r="H623" t="n">
         <v>780</v>
@@ -18465,7 +18465,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G624" t="n">
-        <v>1.55280590057373</v>
+        <v>1.55280601978302</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>1.48024487495422</v>
+        <v>1.48024499416351</v>
       </c>
       <c r="H628" t="n">
         <v>5460</v>
@@ -18610,7 +18610,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G629" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H629" t="n">
         <v>8580</v>
@@ -18639,7 +18639,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G630" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H630" t="n">
         <v>780</v>
@@ -18668,7 +18668,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G631" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H631" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>1.52378153800964</v>
+        <v>1.52378141880035</v>
       </c>
       <c r="H637" t="n">
         <v>5460</v>
@@ -18958,7 +18958,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H641" t="n">
         <v>25740</v>
@@ -19016,7 +19016,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H643" t="n">
         <v>102180</v>
@@ -19132,7 +19132,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H647" t="n">
         <v>7800</v>
@@ -19190,7 +19190,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H649" t="n">
         <v>5460</v>
@@ -19306,7 +19306,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G653" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H653" t="n">
         <v>1560</v>
@@ -19335,7 +19335,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H654" t="n">
         <v>4680</v>
@@ -19625,7 +19625,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H664" t="n">
         <v>10140</v>
@@ -19654,7 +19654,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19683,7 +19683,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H666" t="n">
         <v>780</v>
@@ -19712,7 +19712,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H667" t="n">
         <v>1560</v>
@@ -19741,7 +19741,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G668" t="n">
-        <v>1.54554998874664</v>
+        <v>1.54554986953735</v>
       </c>
       <c r="H668" t="n">
         <v>8580</v>
@@ -19770,7 +19770,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H669" t="n">
         <v>5460</v>
@@ -19799,7 +19799,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>2.25</v>
       </c>
       <c r="G671" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H671" t="n">
         <v>7800</v>
@@ -19857,7 +19857,7 @@
         <v>2.25</v>
       </c>
       <c r="G672" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>2.25</v>
       </c>
       <c r="G673" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H674" t="n">
         <v>1560</v>
@@ -19944,7 +19944,7 @@
         <v>2.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H675" t="n">
         <v>2340</v>
@@ -20060,7 +20060,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G679" t="n">
-        <v>1.61085486412048</v>
+        <v>1.61085474491119</v>
       </c>
       <c r="H679" t="n">
         <v>5460</v>
@@ -20089,7 +20089,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G680" t="n">
-        <v>1.61085486412048</v>
+        <v>1.61085474491119</v>
       </c>
       <c r="H680" t="n">
         <v>780</v>
@@ -20118,7 +20118,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H681" t="n">
         <v>3900</v>
@@ -20263,7 +20263,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H686" t="n">
         <v>5460</v>
@@ -20321,7 +20321,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H688" t="n">
         <v>2340</v>
@@ -20437,7 +20437,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H692" t="n">
         <v>1560</v>
@@ -20466,7 +20466,7 @@
         <v>2.25</v>
       </c>
       <c r="G693" t="n">
-        <v>1.6326230764389</v>
+        <v>1.63262295722961</v>
       </c>
       <c r="H693" t="n">
         <v>1560</v>
@@ -20553,7 +20553,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G696" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H696" t="n">
         <v>55380</v>
@@ -20582,7 +20582,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H697" t="n">
         <v>6240</v>
@@ -20611,7 +20611,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H698" t="n">
         <v>4680</v>
@@ -20669,7 +20669,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G700" t="n">
-        <v>1.806769490242</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H700" t="n">
         <v>49140</v>
@@ -20756,7 +20756,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H703" t="n">
         <v>14040</v>
@@ -20843,7 +20843,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G706" t="n">
-        <v>1.69792795181274</v>
+        <v>1.69792783260345</v>
       </c>
       <c r="H706" t="n">
         <v>18720</v>
@@ -20901,7 +20901,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G708" t="n">
-        <v>1.6616473197937</v>
+        <v>1.66164755821228</v>
       </c>
       <c r="H708" t="n">
         <v>5460</v>
@@ -20959,7 +20959,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H710" t="n">
         <v>69420</v>
@@ -21191,7 +21191,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G718" t="n">
-        <v>1.806769490242</v>
+        <v>1.80676960945129</v>
       </c>
       <c r="H718" t="n">
         <v>4680</v>
@@ -21220,7 +21220,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G719" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H719" t="n">
         <v>9360</v>
@@ -21278,7 +21278,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G721" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H721" t="n">
         <v>14040</v>
@@ -21307,7 +21307,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G722" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -21336,7 +21336,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G723" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H724" t="n">
         <v>1560</v>
@@ -21394,7 +21394,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H725" t="n">
         <v>1560</v>
@@ -21481,7 +21481,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H728" t="n">
         <v>780</v>
@@ -21539,7 +21539,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H730" t="n">
         <v>780</v>
@@ -21626,7 +21626,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.79951345920563</v>
+        <v>1.79951333999634</v>
       </c>
       <c r="H733" t="n">
         <v>13260</v>
@@ -21684,7 +21684,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G735" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H735" t="n">
         <v>7800</v>
@@ -21713,7 +21713,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G736" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H736" t="n">
         <v>24960</v>
@@ -21771,7 +21771,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>1.76323282718658</v>
+        <v>1.76323294639587</v>
       </c>
       <c r="H738" t="n">
         <v>4680</v>
@@ -21800,7 +21800,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G739" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H739" t="n">
         <v>780</v>
@@ -21829,7 +21829,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G740" t="n">
-        <v>1.77774524688721</v>
+        <v>1.77774512767792</v>
       </c>
       <c r="H740" t="n">
         <v>29640</v>
@@ -21887,7 +21887,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H742" t="n">
         <v>780</v>
@@ -21945,7 +21945,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>1.82853770256042</v>
+        <v>1.82853782176971</v>
       </c>
       <c r="H744" t="n">
         <v>2340</v>
@@ -21974,7 +21974,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H745" t="n">
         <v>780</v>
@@ -22003,7 +22003,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H746" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H752" t="n">
         <v>1560</v>
@@ -22206,7 +22206,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G753" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G754" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H754" t="n">
         <v>28080</v>
@@ -22264,7 +22264,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G755" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H755" t="n">
         <v>0</v>
@@ -22380,7 +22380,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G759" t="n">
-        <v>1.72695243358612</v>
+        <v>1.72695255279541</v>
       </c>
       <c r="H759" t="n">
         <v>3120</v>
@@ -22409,7 +22409,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H760" t="n">
         <v>7800</v>
@@ -22438,7 +22438,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H763" t="n">
         <v>3900</v>
@@ -22525,7 +22525,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>1.63987910747528</v>
+        <v>1.63987922668457</v>
       </c>
       <c r="H764" t="n">
         <v>4680</v>
@@ -22554,7 +22554,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G765" t="n">
-        <v>1.68341565132141</v>
+        <v>1.6834157705307</v>
       </c>
       <c r="H765" t="n">
         <v>4680</v>
@@ -22583,7 +22583,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G766" t="n">
-        <v>1.71969616413116</v>
+        <v>1.71969604492188</v>
       </c>
       <c r="H766" t="n">
         <v>780</v>
@@ -22699,7 +22699,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.83579397201538</v>
+        <v>1.83579385280609</v>
       </c>
       <c r="H770" t="n">
         <v>41340</v>
@@ -22757,7 +22757,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>1.82853770256042</v>
+        <v>1.82853782176971</v>
       </c>
       <c r="H772" t="n">
         <v>3120</v>
@@ -22786,7 +22786,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H773" t="n">
         <v>3120</v>
@@ -22815,7 +22815,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -22844,7 +22844,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G775" t="n">
-        <v>1.82853770256042</v>
+        <v>1.82853782176971</v>
       </c>
       <c r="H775" t="n">
         <v>3120</v>
@@ -22873,7 +22873,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>1.85756230354309</v>
+        <v>1.85756206512451</v>
       </c>
       <c r="H776" t="n">
         <v>5460</v>
@@ -22902,7 +22902,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84304988384247</v>
       </c>
       <c r="H777" t="n">
         <v>3900</v>
@@ -22989,7 +22989,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G780" t="n">
-        <v>1.89384257793427</v>
+        <v>1.89384281635284</v>
       </c>
       <c r="H780" t="n">
         <v>94380</v>
@@ -23018,7 +23018,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G781" t="n">
-        <v>1.91561114788055</v>
+        <v>1.91561126708984</v>
       </c>
       <c r="H781" t="n">
         <v>66300</v>
@@ -23076,7 +23076,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90835511684418</v>
+        <v>1.90835499763489</v>
       </c>
       <c r="H783" t="n">
         <v>11700</v>
@@ -23105,7 +23105,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>1.93737924098969</v>
+        <v>1.93737947940826</v>
       </c>
       <c r="H784" t="n">
         <v>8580</v>
@@ -23163,7 +23163,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>1.96640396118164</v>
+        <v>1.96640372276306</v>
       </c>
       <c r="H786" t="n">
         <v>26520</v>
@@ -23250,7 +23250,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G789" t="n">
-        <v>2.0607328414917</v>
+        <v>2.06073307991028</v>
       </c>
       <c r="H789" t="n">
         <v>39780</v>
@@ -23308,7 +23308,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>2.00994038581848</v>
+        <v>2.0099401473999</v>
       </c>
       <c r="H791" t="n">
         <v>10140</v>
@@ -23366,7 +23366,7 @@
         <v>2.75</v>
       </c>
       <c r="G793" t="n">
-        <v>1.99542808532715</v>
+        <v>1.99542820453644</v>
       </c>
       <c r="H793" t="n">
         <v>9360</v>
@@ -23453,7 +23453,7 @@
         <v>2.75</v>
       </c>
       <c r="G796" t="n">
-        <v>1.99542808532715</v>
+        <v>1.99542820453644</v>
       </c>
       <c r="H796" t="n">
         <v>8580</v>
@@ -23482,7 +23482,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>2.00994038581848</v>
+        <v>2.0099401473999</v>
       </c>
       <c r="H797" t="n">
         <v>7020</v>
@@ -23540,7 +23540,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>2.00994038581848</v>
+        <v>2.0099401473999</v>
       </c>
       <c r="H799" t="n">
         <v>3120</v>
@@ -23598,7 +23598,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.05347681045532</v>
+        <v>2.0534770488739</v>
       </c>
       <c r="H801" t="n">
         <v>23400</v>
@@ -23714,7 +23714,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G805" t="n">
-        <v>2.13329434394836</v>
+        <v>2.13329410552979</v>
       </c>
       <c r="H805" t="n">
         <v>59280</v>
@@ -23743,7 +23743,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>2.13329434394836</v>
+        <v>2.13329410552979</v>
       </c>
       <c r="H806" t="n">
         <v>7800</v>
@@ -23801,7 +23801,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>2.1042697429657</v>
+        <v>2.10426998138428</v>
       </c>
       <c r="H808" t="n">
         <v>16380</v>
@@ -23830,7 +23830,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>2.04622077941895</v>
+        <v>2.04622101783752</v>
       </c>
       <c r="H809" t="n">
         <v>69420</v>
@@ -23917,7 +23917,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G812" t="n">
-        <v>2.15506267547607</v>
+        <v>2.1550624370575</v>
       </c>
       <c r="H812" t="n">
         <v>28860</v>
@@ -23975,7 +23975,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G814" t="n">
-        <v>2.16957449913025</v>
+        <v>2.16957473754883</v>
       </c>
       <c r="H814" t="n">
         <v>12480</v>
@@ -24004,7 +24004,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G815" t="n">
-        <v>2.16957449913025</v>
+        <v>2.16957473754883</v>
       </c>
       <c r="H815" t="n">
         <v>3900</v>
@@ -24062,7 +24062,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>2.22036719322205</v>
+        <v>2.22036743164062</v>
       </c>
       <c r="H817" t="n">
         <v>12480</v>
@@ -24091,7 +24091,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>2.22036719322205</v>
+        <v>2.22036743164062</v>
       </c>
       <c r="H818" t="n">
         <v>20280</v>
@@ -24120,7 +24120,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H819" t="n">
         <v>217620</v>
@@ -24149,7 +24149,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>2.27116012573242</v>
+        <v>2.271160364151</v>
       </c>
       <c r="H820" t="n">
         <v>33540</v>
@@ -24236,7 +24236,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G823" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H823" t="n">
         <v>10140</v>
@@ -24352,7 +24352,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H827" t="n">
         <v>48360</v>
@@ -24410,7 +24410,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G829" t="n">
-        <v>2.30744075775146</v>
+        <v>2.30744051933289</v>
       </c>
       <c r="H829" t="n">
         <v>10140</v>
@@ -24468,7 +24468,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H831" t="n">
         <v>21060</v>
@@ -24729,7 +24729,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G840" t="n">
-        <v>2.38725781440735</v>
+        <v>2.38725757598877</v>
       </c>
       <c r="H840" t="n">
         <v>12897</v>
@@ -24903,7 +24903,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G846" t="n">
-        <v>2.30744075775146</v>
+        <v>2.30744051933289</v>
       </c>
       <c r="H846" t="n">
         <v>15073</v>
@@ -24990,7 +24990,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H849" t="n">
         <v>10904</v>
@@ -25019,7 +25019,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H850" t="n">
         <v>8210</v>
@@ -25106,7 +25106,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>2.3219530582428</v>
+        <v>2.32195281982422</v>
       </c>
       <c r="H853" t="n">
         <v>50</v>
@@ -25164,7 +25164,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G855" t="n">
-        <v>2.27116012573242</v>
+        <v>2.271160364151</v>
       </c>
       <c r="H855" t="n">
         <v>1450</v>
@@ -25193,7 +25193,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G856" t="n">
-        <v>2.24939155578613</v>
+        <v>2.24939179420471</v>
       </c>
       <c r="H856" t="n">
         <v>2255</v>
@@ -25338,7 +25338,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.40176963806152</v>
+        <v>2.4017698764801</v>
       </c>
       <c r="H861" t="n">
         <v>16837</v>
@@ -25628,7 +25628,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>2.36548948287964</v>
+        <v>2.36548924446106</v>
       </c>
       <c r="H871" t="n">
         <v>7362</v>
@@ -25715,7 +25715,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G874" t="n">
-        <v>2.38725781440735</v>
+        <v>2.38725757598877</v>
       </c>
       <c r="H874" t="n">
         <v>4200</v>
@@ -25744,7 +25744,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>2.43805027008057</v>
+        <v>2.43805050849915</v>
       </c>
       <c r="H875" t="n">
         <v>10391</v>
@@ -25773,7 +25773,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G876" t="n">
-        <v>2.38725781440735</v>
+        <v>2.38725757598877</v>
       </c>
       <c r="H876" t="n">
         <v>4500</v>
@@ -25889,7 +25889,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>2.53237986564636</v>
+        <v>2.53237962722778</v>
       </c>
       <c r="H880" t="n">
         <v>62911</v>
@@ -25976,7 +25976,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G883" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H883" t="n">
         <v>172820</v>
@@ -26005,7 +26005,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>2.86616063117981</v>
+        <v>2.86616039276123</v>
       </c>
       <c r="H884" t="n">
         <v>57963</v>
@@ -26063,7 +26063,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G886" t="n">
-        <v>2.626708984375</v>
+        <v>2.62670922279358</v>
       </c>
       <c r="H886" t="n">
         <v>81513</v>
@@ -26179,7 +26179,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G890" t="n">
-        <v>2.85164856910706</v>
+        <v>2.85164833068848</v>
       </c>
       <c r="H890" t="n">
         <v>25193</v>
@@ -26208,7 +26208,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>2.96048974990845</v>
+        <v>2.96048998832703</v>
       </c>
       <c r="H891" t="n">
         <v>107136</v>
@@ -26237,7 +26237,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>2.91695332527161</v>
+        <v>2.91695308685303</v>
       </c>
       <c r="H892" t="n">
         <v>43603</v>
@@ -26353,7 +26353,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G896" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H896" t="n">
         <v>72677</v>
@@ -26614,7 +26614,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G905" t="n">
-        <v>2.91695332527161</v>
+        <v>2.91695308685303</v>
       </c>
       <c r="H905" t="n">
         <v>10749</v>
@@ -26701,7 +26701,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.69201421737671</v>
+        <v>2.69201397895813</v>
       </c>
       <c r="H908" t="n">
         <v>34513</v>
@@ -26730,7 +26730,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G909" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H909" t="n">
         <v>19473</v>
@@ -26759,7 +26759,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G910" t="n">
-        <v>2.77183103561401</v>
+        <v>2.77183127403259</v>
       </c>
       <c r="H910" t="n">
         <v>6976</v>
@@ -26846,7 +26846,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G913" t="n">
-        <v>2.85164856910706</v>
+        <v>2.85164833068848</v>
       </c>
       <c r="H913" t="n">
         <v>11840</v>
@@ -26875,7 +26875,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>2.69201421737671</v>
+        <v>2.69201397895813</v>
       </c>
       <c r="H914" t="n">
         <v>12512</v>
@@ -27107,7 +27107,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H922" t="n">
         <v>3293</v>
@@ -27136,7 +27136,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>2.79359936714172</v>
+        <v>2.7935996055603</v>
       </c>
       <c r="H923" t="n">
         <v>1820</v>
@@ -27165,7 +27165,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G924" t="n">
-        <v>2.95323371887207</v>
+        <v>2.95323395729065</v>
       </c>
       <c r="H924" t="n">
         <v>19608</v>
@@ -27252,7 +27252,7 @@
         <v>4.25</v>
       </c>
       <c r="G927" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H927" t="n">
         <v>5320</v>
@@ -27281,7 +27281,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G928" t="n">
-        <v>3.02579498291016</v>
+        <v>3.02579474449158</v>
       </c>
       <c r="H928" t="n">
         <v>9639</v>
@@ -27339,7 +27339,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G930" t="n">
-        <v>2.94597744941711</v>
+        <v>2.94597768783569</v>
       </c>
       <c r="H930" t="n">
         <v>43272</v>
@@ -27484,7 +27484,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G935" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H935" t="n">
         <v>4741</v>
@@ -27513,7 +27513,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G936" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H936" t="n">
         <v>5875</v>
@@ -27571,7 +27571,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H938" t="n">
         <v>933</v>
@@ -27600,7 +27600,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G939" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H939" t="n">
         <v>11330</v>
@@ -27716,7 +27716,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G943" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H943" t="n">
         <v>53741</v>
@@ -27745,7 +27745,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H944" t="n">
         <v>64664</v>
@@ -27861,7 +27861,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>2.82988023757935</v>
+        <v>2.82987999916077</v>
       </c>
       <c r="H948" t="n">
         <v>14110</v>
@@ -27890,7 +27890,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G949" t="n">
-        <v>2.92420959472656</v>
+        <v>2.92420935630798</v>
       </c>
       <c r="H949" t="n">
         <v>11372</v>
@@ -27919,7 +27919,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G950" t="n">
-        <v>2.92420959472656</v>
+        <v>2.92420935630798</v>
       </c>
       <c r="H950" t="n">
         <v>90795</v>
@@ -27948,7 +27948,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G951" t="n">
-        <v>2.9750018119812</v>
+        <v>2.97500205039978</v>
       </c>
       <c r="H951" t="n">
         <v>11343</v>
@@ -28006,7 +28006,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H953" t="n">
         <v>9849</v>
@@ -28035,7 +28035,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>3.02579498291016</v>
+        <v>3.02579474449158</v>
       </c>
       <c r="H954" t="n">
         <v>10340</v>
@@ -28151,7 +28151,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>2.96048974990845</v>
+        <v>2.96048998832703</v>
       </c>
       <c r="H958" t="n">
         <v>3050</v>
@@ -28180,7 +28180,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G959" t="n">
-        <v>2.94597744941711</v>
+        <v>2.94597768783569</v>
       </c>
       <c r="H959" t="n">
         <v>1795</v>
@@ -28209,7 +28209,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>2.9750018119812</v>
+        <v>2.97500205039978</v>
       </c>
       <c r="H960" t="n">
         <v>1063</v>
@@ -28238,7 +28238,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G961" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H961" t="n">
         <v>80606</v>
@@ -28267,7 +28267,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G962" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H962" t="n">
         <v>13068</v>
@@ -28354,7 +28354,7 @@
         <v>4.25</v>
       </c>
       <c r="G965" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H965" t="n">
         <v>5360</v>
@@ -28412,7 +28412,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H967" t="n">
         <v>21145</v>
@@ -28441,7 +28441,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G968" t="n">
-        <v>3.09109997749329</v>
+        <v>3.09109973907471</v>
       </c>
       <c r="H968" t="n">
         <v>35917</v>
@@ -28528,7 +28528,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H971" t="n">
         <v>186625</v>
@@ -28557,7 +28557,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939208984375</v>
       </c>
       <c r="H972" t="n">
         <v>174496</v>
@@ -28673,7 +28673,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H976" t="n">
         <v>15487</v>
@@ -28789,7 +28789,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G980" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H980" t="n">
         <v>24764</v>
@@ -28876,7 +28876,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G983" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H983" t="n">
         <v>21629</v>
@@ -28905,7 +28905,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G984" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H984" t="n">
         <v>38692</v>
@@ -28934,7 +28934,7 @@
         <v>4.5</v>
       </c>
       <c r="G985" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H985" t="n">
         <v>33365</v>
@@ -28963,7 +28963,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H986" t="n">
         <v>7440</v>
@@ -28992,7 +28992,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G987" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H987" t="n">
         <v>10030</v>
@@ -29050,7 +29050,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H989" t="n">
         <v>14239</v>
@@ -29079,7 +29079,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G990" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H990" t="n">
         <v>1190</v>
@@ -29108,7 +29108,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H991" t="n">
         <v>1571</v>
@@ -29166,7 +29166,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G993" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H993" t="n">
         <v>20606</v>
@@ -29253,7 +29253,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G996" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H996" t="n">
         <v>13997</v>
@@ -29282,7 +29282,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G997" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H997" t="n">
         <v>6558</v>
@@ -29311,7 +29311,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G998" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H998" t="n">
         <v>18950</v>
@@ -29340,7 +29340,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G999" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H999" t="n">
         <v>37168</v>
@@ -29369,7 +29369,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1000" t="n">
         <v>54268</v>
@@ -29427,7 +29427,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506320953369</v>
+        <v>3.34506368637085</v>
       </c>
       <c r="H1002" t="n">
         <v>39069</v>
@@ -29456,7 +29456,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506320953369</v>
+        <v>3.34506368637085</v>
       </c>
       <c r="H1003" t="n">
         <v>16302</v>
@@ -29572,7 +29572,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1007" t="n">
         <v>9721</v>
@@ -29659,7 +29659,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1010" t="n">
         <v>47398</v>
@@ -29688,7 +29688,7 @@
         <v>4.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1011" t="n">
         <v>33300</v>
@@ -29717,7 +29717,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1012" t="n">
         <v>11599</v>
@@ -29804,7 +29804,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1015" t="n">
         <v>6208</v>
@@ -29833,7 +29833,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939208984375</v>
       </c>
       <c r="H1016" t="n">
         <v>5463</v>
@@ -29891,7 +29891,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1018" t="n">
         <v>5814</v>
@@ -30007,7 +30007,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1022" t="n">
         <v>5304</v>
@@ -30123,7 +30123,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1026" t="n">
         <v>9496</v>
@@ -30152,7 +30152,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1027" t="n">
         <v>3600</v>
@@ -30181,7 +30181,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1028" t="n">
         <v>12697</v>
@@ -30239,7 +30239,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.38859987258911</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1030" t="n">
         <v>4817</v>
@@ -30268,7 +30268,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1031" t="n">
         <v>6405</v>
@@ -30471,7 +30471,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1038" t="n">
         <v>17540</v>
@@ -30500,7 +30500,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1039" t="n">
         <v>5793</v>
@@ -30616,7 +30616,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1043" t="n">
         <v>7290</v>
@@ -30645,7 +30645,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.38859987258911</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1044" t="n">
         <v>14888</v>
@@ -30732,7 +30732,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1047" t="n">
         <v>7582</v>
@@ -30761,7 +30761,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.51920962333679</v>
+        <v>3.51920986175537</v>
       </c>
       <c r="H1048" t="n">
         <v>47843</v>
@@ -30935,7 +30935,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1054" t="n">
         <v>13296</v>
@@ -30964,7 +30964,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1055" t="n">
         <v>10130</v>
@@ -31022,7 +31022,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1057" t="n">
         <v>42170</v>
@@ -31080,7 +31080,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1059" t="n">
         <v>7168</v>
@@ -31109,7 +31109,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1060" t="n">
         <v>5775</v>
@@ -31138,7 +31138,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1061" t="n">
         <v>16035</v>
@@ -31167,7 +31167,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1062" t="n">
         <v>7972</v>
@@ -31283,7 +31283,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.75006294250488</v>
+        <v>2.7500627040863</v>
       </c>
       <c r="H1066" t="n">
         <v>9851</v>
@@ -31341,7 +31341,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.85890460014343</v>
+        <v>2.85890436172485</v>
       </c>
       <c r="H1068" t="n">
         <v>4927</v>
@@ -31428,7 +31428,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.75731873512268</v>
+        <v>2.75731897354126</v>
       </c>
       <c r="H1071" t="n">
         <v>29481</v>
@@ -31457,7 +31457,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.85890460014343</v>
+        <v>2.85890436172485</v>
       </c>
       <c r="H1072" t="n">
         <v>5534</v>
@@ -31486,7 +31486,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.81536769866943</v>
+        <v>2.81536793708801</v>
       </c>
       <c r="H1073" t="n">
         <v>20606</v>
@@ -31602,7 +31602,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.96048974990845</v>
+        <v>2.96048998832703</v>
       </c>
       <c r="H1077" t="n">
         <v>21146</v>
@@ -31660,7 +31660,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1079" t="n">
         <v>9861</v>
@@ -31689,7 +31689,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1080" t="n">
         <v>3234</v>
@@ -31718,7 +31718,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1081" t="n">
         <v>5600</v>
@@ -31747,7 +31747,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1082" t="n">
         <v>10011</v>
@@ -31776,7 +31776,7 @@
         <v>4.25</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1083" t="n">
         <v>1090</v>
@@ -31805,7 +31805,7 @@
         <v>4.25</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1084" t="n">
         <v>5636</v>
@@ -31863,7 +31863,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1086" t="n">
         <v>29157</v>
@@ -31979,7 +31979,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1090" t="n">
         <v>1665</v>
@@ -32008,7 +32008,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1091" t="n">
         <v>2260</v>
@@ -32066,7 +32066,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1093" t="n">
         <v>700</v>
@@ -32095,7 +32095,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1094" t="n">
         <v>2341</v>
@@ -32240,7 +32240,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1099" t="n">
         <v>3444</v>
@@ -32269,7 +32269,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1100" t="n">
         <v>3580</v>
@@ -32298,7 +32298,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1101" t="n">
         <v>0</v>
@@ -32327,7 +32327,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1102" t="n">
         <v>1000</v>
@@ -32356,7 +32356,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1103" t="n">
         <v>1500</v>
@@ -32414,7 +32414,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1105" t="n">
         <v>10871</v>
@@ -32501,7 +32501,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1108" t="n">
         <v>8900</v>
@@ -32646,7 +32646,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1113" t="n">
         <v>6422</v>
@@ -32733,7 +32733,7 @@
         <v>4.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1116" t="n">
         <v>5851</v>
@@ -32762,7 +32762,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.38134384155273</v>
+        <v>3.38134360313416</v>
       </c>
       <c r="H1117" t="n">
         <v>6259</v>
@@ -32791,7 +32791,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1118" t="n">
         <v>4473</v>
@@ -32820,7 +32820,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939208984375</v>
       </c>
       <c r="H1119" t="n">
         <v>5400</v>
@@ -32849,7 +32849,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.38859987258911</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1120" t="n">
         <v>1900</v>
@@ -32936,7 +32936,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1123" t="n">
         <v>7177</v>
@@ -32965,7 +32965,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1124" t="n">
         <v>72339</v>
@@ -33023,7 +33023,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707564353943</v>
       </c>
       <c r="H1126" t="n">
         <v>19826</v>
@@ -33052,7 +33052,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67158794403076</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1127" t="n">
         <v>34476</v>
@@ -33081,7 +33081,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1128" t="n">
         <v>56766</v>
@@ -33110,7 +33110,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1129" t="n">
         <v>46422</v>
@@ -33197,7 +33197,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.93280792236328</v>
+        <v>3.93280744552612</v>
       </c>
       <c r="H1132" t="n">
         <v>48820</v>
@@ -33226,7 +33226,7 @@
         <v>5.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1133" t="n">
         <v>9842</v>
@@ -33313,7 +33313,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1136" t="n">
         <v>25075</v>
@@ -33371,7 +33371,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71512460708618</v>
+        <v>3.71512413024902</v>
       </c>
       <c r="H1138" t="n">
         <v>22247</v>
@@ -33400,7 +33400,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.91829538345337</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1139" t="n">
         <v>19815</v>
@@ -33429,7 +33429,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H1140" t="n">
         <v>3336</v>
@@ -33487,7 +33487,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.91829538345337</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1142" t="n">
         <v>37130</v>
@@ -33516,7 +33516,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.91829538345337</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1143" t="n">
         <v>640</v>
@@ -33545,7 +33545,7 @@
         <v>5.5</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1144" t="n">
         <v>14778</v>
@@ -33574,7 +33574,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.93280792236328</v>
+        <v>3.93280744552612</v>
       </c>
       <c r="H1145" t="n">
         <v>22850</v>
@@ -33632,7 +33632,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.91829538345337</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1147" t="n">
         <v>3374</v>
@@ -33661,7 +33661,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.91829538345337</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1148" t="n">
         <v>8142</v>
@@ -33690,7 +33690,7 @@
         <v>5.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1149" t="n">
         <v>13231</v>
@@ -33719,7 +33719,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.91829538345337</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1150" t="n">
         <v>7492</v>
@@ -33777,7 +33777,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1152" t="n">
         <v>10478</v>
@@ -33806,7 +33806,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1153" t="n">
         <v>21813</v>
@@ -33835,7 +33835,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1154" t="n">
         <v>1906</v>
@@ -33893,7 +33893,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.67158794403076</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1156" t="n">
         <v>8378</v>
@@ -33922,7 +33922,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1157" t="n">
         <v>9285</v>
@@ -34009,7 +34009,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1160" t="n">
         <v>4001</v>
@@ -34038,7 +34038,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1161" t="n">
         <v>2059</v>
@@ -34067,7 +34067,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H1162" t="n">
         <v>100</v>
@@ -34125,7 +34125,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1164" t="n">
         <v>4764</v>
@@ -34154,7 +34154,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91829538345337</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H1165" t="n">
         <v>2040</v>
@@ -34183,7 +34183,7 @@
         <v>5.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1166" t="n">
         <v>10671</v>
@@ -34473,7 +34473,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1176" t="n">
         <v>13558</v>
@@ -34531,7 +34531,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1178" t="n">
         <v>6879</v>
@@ -34589,7 +34589,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1180" t="n">
         <v>7056</v>
@@ -34618,7 +34618,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1181" t="n">
         <v>18443</v>
@@ -34647,7 +34647,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.09244155883789</v>
+        <v>4.09244203567505</v>
       </c>
       <c r="H1182" t="n">
         <v>18197</v>
@@ -34676,7 +34676,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1183" t="n">
         <v>6092</v>
@@ -34705,7 +34705,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1184" t="n">
         <v>469</v>
@@ -34734,7 +34734,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.09244155883789</v>
+        <v>4.09244203567505</v>
       </c>
       <c r="H1185" t="n">
         <v>36410</v>
@@ -34763,7 +34763,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1186" t="n">
         <v>7610</v>
@@ -34792,7 +34792,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1187" t="n">
         <v>3406</v>
@@ -34850,7 +34850,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1189" t="n">
         <v>10107</v>
@@ -34879,7 +34879,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.1214656829834</v>
+        <v>4.12146615982056</v>
       </c>
       <c r="H1190" t="n">
         <v>7775</v>
@@ -34908,7 +34908,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.1214656829834</v>
+        <v>4.12146615982056</v>
       </c>
       <c r="H1191" t="n">
         <v>4710</v>
@@ -34937,7 +34937,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1192" t="n">
         <v>5638</v>
@@ -35024,7 +35024,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.09244155883789</v>
+        <v>4.09244203567505</v>
       </c>
       <c r="H1195" t="n">
         <v>3000</v>
@@ -35053,7 +35053,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.09244155883789</v>
+        <v>4.09244203567505</v>
       </c>
       <c r="H1196" t="n">
         <v>1995</v>
@@ -35111,7 +35111,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1198" t="n">
         <v>50079</v>
@@ -35198,7 +35198,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.67158794403076</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1201" t="n">
         <v>24329</v>
@@ -35227,7 +35227,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1202" t="n">
         <v>6086</v>
@@ -35285,7 +35285,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1204" t="n">
         <v>68407</v>
@@ -35372,7 +35372,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1207" t="n">
         <v>10763</v>
@@ -35401,7 +35401,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.54823398590088</v>
+        <v>3.5482337474823</v>
       </c>
       <c r="H1208" t="n">
         <v>22103</v>
@@ -35488,7 +35488,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1211" t="n">
-        <v>3.59902691841125</v>
+        <v>3.59902667999268</v>
       </c>
       <c r="H1211" t="n">
         <v>352</v>
@@ -35517,7 +35517,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1212" t="n">
         <v>14075</v>
@@ -35546,7 +35546,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1213" t="n">
         <v>21223</v>
@@ -35720,7 +35720,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1219" t="n">
         <v>16841</v>
@@ -35749,7 +35749,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1220" t="n">
         <v>4577</v>
@@ -35778,7 +35778,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1221" t="n">
-        <v>3.56274652481079</v>
+        <v>3.56274628639221</v>
       </c>
       <c r="H1221" t="n">
         <v>6421</v>
@@ -35894,7 +35894,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1225" t="n">
         <v>6466</v>
@@ -35923,7 +35923,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1226" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1226" t="n">
         <v>14233</v>
@@ -36097,7 +36097,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1232" t="n">
         <v>5283</v>
@@ -36126,7 +36126,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1233" t="n">
         <v>16931</v>
@@ -36155,7 +36155,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1234" t="n">
         <v>6553</v>
@@ -36213,7 +36213,7 @@
         <v>4.5</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1236" t="n">
         <v>2054</v>
@@ -36242,7 +36242,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1237" t="n">
         <v>14176</v>
@@ -36329,7 +36329,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1240" t="n">
         <v>7122</v>
@@ -36416,7 +36416,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.51920962333679</v>
+        <v>3.51920986175537</v>
       </c>
       <c r="H1243" t="n">
         <v>5838</v>
@@ -36445,7 +36445,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.51920962333679</v>
+        <v>3.51920986175537</v>
       </c>
       <c r="H1244" t="n">
         <v>3480</v>
@@ -36532,7 +36532,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1247" t="n">
         <v>11380</v>
@@ -36561,7 +36561,7 @@
         <v>4.5</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1248" t="n">
         <v>26609</v>
@@ -36677,7 +36677,7 @@
         <v>4.5</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1252" t="n">
         <v>1600</v>
@@ -36764,7 +36764,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1255" t="n">
         <v>4486</v>
@@ -36793,7 +36793,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1256" t="n">
         <v>1710</v>
@@ -36851,7 +36851,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1258" t="n">
         <v>64400</v>
@@ -36880,7 +36880,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.45390486717224</v>
+        <v>3.45390510559082</v>
       </c>
       <c r="H1259" t="n">
         <v>43313</v>
@@ -36909,7 +36909,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1260" t="n">
         <v>6745</v>
@@ -36967,7 +36967,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1262" t="n">
         <v>34766</v>
@@ -36996,7 +36996,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1263" t="n">
         <v>50036</v>
@@ -37054,7 +37054,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1265" t="n">
         <v>5142</v>
@@ -37112,7 +37112,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1267" t="n">
         <v>3452</v>
@@ -37141,7 +37141,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1268" t="n">
         <v>21156</v>
@@ -37199,7 +37199,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1270" t="n">
         <v>4921</v>
@@ -37257,7 +37257,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1272" t="n">
         <v>5925</v>
@@ -37344,7 +37344,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1275" t="n">
         <v>10861</v>
@@ -37460,7 +37460,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1279" t="n">
         <v>7535</v>
@@ -37605,7 +37605,7 @@
         <v>4.75</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1284" t="n">
         <v>11081</v>
@@ -37634,7 +37634,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1285" t="n">
         <v>25356</v>
@@ -37663,7 +37663,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1286" t="n">
         <v>5539</v>
@@ -37721,7 +37721,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1288" t="n">
         <v>12450</v>
@@ -37750,7 +37750,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1289" t="n">
         <v>7312</v>
@@ -37779,7 +37779,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1290" t="n">
         <v>1409</v>
@@ -37982,7 +37982,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1297" t="n">
         <v>1957</v>
@@ -38069,7 +38069,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.38859987258911</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1300" t="n">
         <v>5359</v>
@@ -38098,7 +38098,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1301" t="n">
         <v>10152</v>
@@ -38301,7 +38301,7 @@
         <v>4.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1308" t="n">
         <v>7301</v>
@@ -38388,7 +38388,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1311" t="n">
         <v>6454</v>
@@ -38446,7 +38446,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1313" t="n">
         <v>3117</v>
@@ -38475,7 +38475,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1314" t="n">
         <v>3011</v>
@@ -38649,7 +38649,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.12738013267517</v>
+        <v>3.12738037109375</v>
       </c>
       <c r="H1320" t="n">
         <v>1761</v>
@@ -38678,7 +38678,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1321" t="n">
         <v>8489</v>
@@ -38736,7 +38736,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1323" t="n">
         <v>4444</v>
@@ -38794,7 +38794,7 @@
         <v>4.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1325" t="n">
         <v>2200</v>
@@ -38852,7 +38852,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1327" t="n">
         <v>6300</v>
@@ -38910,7 +38910,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1329" t="n">
         <v>16178</v>
@@ -38997,7 +38997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1332" t="n">
         <v>27465</v>
@@ -39084,7 +39084,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.12738013267517</v>
+        <v>3.12738037109375</v>
       </c>
       <c r="H1335" t="n">
         <v>10710</v>
@@ -39113,7 +39113,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.12738013267517</v>
+        <v>3.12738037109375</v>
       </c>
       <c r="H1336" t="n">
         <v>11184</v>
@@ -39171,7 +39171,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1338" t="n">
         <v>5392</v>
@@ -39200,7 +39200,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.12738013267517</v>
+        <v>3.12738037109375</v>
       </c>
       <c r="H1339" t="n">
         <v>19456</v>
@@ -39229,7 +39229,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1340" t="n">
         <v>17409</v>
@@ -39258,7 +39258,7 @@
         <v>4.25</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1341" t="n">
         <v>11730</v>
@@ -39345,7 +39345,7 @@
         <v>4.25</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1344" t="n">
         <v>21349</v>
@@ -39635,7 +39635,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.96048974990845</v>
+        <v>2.96048998832703</v>
       </c>
       <c r="H1354" t="n">
         <v>25565</v>
@@ -39664,7 +39664,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.91695332527161</v>
+        <v>2.91695308685303</v>
       </c>
       <c r="H1355" t="n">
         <v>4255</v>
@@ -39809,7 +39809,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1360" t="n">
         <v>7116</v>
@@ -40215,7 +40215,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1374" t="n">
         <v>10811</v>
@@ -40244,7 +40244,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1375" t="n">
         <v>4165</v>
@@ -40302,7 +40302,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1377" t="n">
         <v>2348</v>
@@ -40360,7 +40360,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1379" t="n">
         <v>54641</v>
@@ -40418,7 +40418,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1381" t="n">
         <v>3677</v>
@@ -40534,7 +40534,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1385" t="n">
         <v>11019</v>
@@ -40563,7 +40563,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1386" t="n">
         <v>3395</v>
@@ -40621,7 +40621,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1388" t="n">
         <v>11935</v>
@@ -40650,7 +40650,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1389" t="n">
         <v>9357</v>
@@ -40766,7 +40766,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1393" t="n">
         <v>5386</v>
@@ -40795,7 +40795,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1394" t="n">
         <v>6035</v>
@@ -40824,7 +40824,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1395" t="n">
         <v>1849</v>
@@ -40853,7 +40853,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1396" t="n">
         <v>6794</v>
@@ -40882,7 +40882,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1397" t="n">
         <v>4300</v>
@@ -40911,7 +40911,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1398" t="n">
         <v>620</v>
@@ -40969,7 +40969,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1400" t="n">
         <v>4767</v>
@@ -40998,7 +40998,7 @@
         <v>4.5</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1401" t="n">
         <v>951</v>
@@ -41027,7 +41027,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1402" t="n">
         <v>1524</v>
@@ -41056,7 +41056,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1403" t="n">
         <v>8875</v>
@@ -41201,7 +41201,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1408" t="n">
         <v>6595</v>
@@ -41375,7 +41375,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1414" t="n">
         <v>2111</v>
@@ -41404,7 +41404,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1415" t="n">
         <v>2778</v>
@@ -41433,7 +41433,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1416" t="n">
         <v>1050</v>
@@ -41462,7 +41462,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1417" t="n">
         <v>120</v>
@@ -41491,7 +41491,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1418" t="n">
         <v>5000</v>
@@ -41549,7 +41549,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1420" t="n">
         <v>78</v>
@@ -41607,7 +41607,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1422" t="n">
         <v>744</v>
@@ -41636,7 +41636,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1423" t="n">
         <v>2812</v>
@@ -41665,7 +41665,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12738013267517</v>
+        <v>3.12738037109375</v>
       </c>
       <c r="H1424" t="n">
         <v>4050</v>
@@ -41810,7 +41810,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1429" t="n">
         <v>825</v>
@@ -41926,7 +41926,7 @@
         <v>4.5</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1433" t="n">
         <v>1489</v>
@@ -41955,7 +41955,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1434" t="n">
         <v>1100</v>
@@ -41984,7 +41984,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1435" t="n">
         <v>750</v>
@@ -42013,7 +42013,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1436" t="n">
         <v>1300</v>
@@ -42071,7 +42071,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1438" t="n">
         <v>3809</v>
@@ -42100,7 +42100,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1439" t="n">
         <v>5734</v>
@@ -42129,7 +42129,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1440" t="n">
         <v>2550</v>
@@ -42158,7 +42158,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1441" t="n">
         <v>4620</v>
@@ -42245,7 +42245,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1444" t="n">
         <v>5300</v>
@@ -42274,7 +42274,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1445" t="n">
         <v>13047</v>
@@ -42303,7 +42303,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1446" t="n">
         <v>16300</v>
@@ -42506,7 +42506,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1453" t="n">
         <v>45648</v>
@@ -42535,7 +42535,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1454" t="n">
         <v>3635</v>
@@ -42564,7 +42564,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1455" t="n">
         <v>5451</v>
@@ -42593,7 +42593,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1456" t="n">
         <v>13978</v>
@@ -42622,7 +42622,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1457" t="n">
         <v>17253</v>
@@ -42680,7 +42680,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1459" t="n">
         <v>1518</v>
@@ -42709,7 +42709,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1460" t="n">
         <v>3482</v>
@@ -42738,7 +42738,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1461" t="n">
         <v>8936</v>
@@ -42796,7 +42796,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1463" t="n">
         <v>1065</v>
@@ -42825,7 +42825,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.22170972824097</v>
+        <v>3.22170948982239</v>
       </c>
       <c r="H1464" t="n">
         <v>2007</v>
@@ -42854,7 +42854,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1465" t="n">
         <v>16590</v>
@@ -42883,7 +42883,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1466" t="n">
         <v>9378</v>
@@ -42970,7 +42970,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.27975821495056</v>
+        <v>3.27975845336914</v>
       </c>
       <c r="H1469" t="n">
         <v>39138</v>
@@ -43057,7 +43057,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1472" t="n">
         <v>10406</v>
@@ -43144,7 +43144,7 @@
         <v>4.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1475" t="n">
         <v>11700</v>
@@ -43173,7 +43173,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1476" t="n">
         <v>6866</v>
@@ -43347,7 +43347,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1482" t="n">
         <v>50</v>
@@ -43376,7 +43376,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1483" t="n">
         <v>11720</v>
@@ -43405,7 +43405,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1484" t="n">
         <v>224</v>
@@ -43492,7 +43492,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1487" t="n">
         <v>19033</v>
@@ -43521,7 +43521,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1488" t="n">
         <v>15813</v>
@@ -43579,7 +43579,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1490" t="n">
         <v>6932</v>
@@ -43608,7 +43608,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1491" t="n">
         <v>8001</v>
@@ -43666,7 +43666,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1493" t="n">
         <v>60540</v>
@@ -43695,7 +43695,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.43939232826233</v>
+        <v>3.43939208984375</v>
       </c>
       <c r="H1494" t="n">
         <v>44032</v>
@@ -43753,7 +43753,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1496" t="n">
         <v>18770</v>
@@ -43782,7 +43782,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1497" t="n">
         <v>8020</v>
@@ -43811,7 +43811,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1498" t="n">
         <v>13327</v>
@@ -43840,7 +43840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1499" t="n">
         <v>6935</v>
@@ -43898,7 +43898,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1501" t="n">
         <v>485</v>
@@ -43927,7 +43927,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1502" t="n">
         <v>5142</v>
@@ -43956,7 +43956,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1503" t="n">
         <v>11660</v>
@@ -43985,7 +43985,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1504" t="n">
         <v>13228</v>
@@ -44072,7 +44072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1507" t="n">
         <v>4706</v>
@@ -44101,7 +44101,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1508" t="n">
         <v>7146</v>
@@ -44159,7 +44159,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1510" t="n">
         <v>5436</v>
@@ -44217,7 +44217,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H1512" t="n">
         <v>4106</v>
@@ -44304,7 +44304,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1515" t="n">
         <v>2780</v>
@@ -44391,7 +44391,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1518" t="n">
         <v>2560</v>
@@ -44449,7 +44449,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1520" t="n">
         <v>1907</v>
@@ -44478,7 +44478,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1521" t="n">
         <v>1900</v>
@@ -44507,7 +44507,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1522" t="n">
         <v>0</v>
@@ -44565,7 +44565,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1524" t="n">
         <v>3725</v>
@@ -44652,7 +44652,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1527" t="n">
         <v>5409</v>
@@ -44710,7 +44710,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1529" t="n">
         <v>7906</v>
@@ -44739,7 +44739,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1530" t="n">
         <v>6286</v>
@@ -44768,7 +44768,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1531" t="n">
         <v>8224</v>
@@ -44797,7 +44797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1532" t="n">
         <v>5293</v>
@@ -44855,7 +44855,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1534" t="n">
         <v>5194</v>
@@ -44884,7 +44884,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1535" t="n">
         <v>0</v>
@@ -45000,7 +45000,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1539" t="n">
         <v>12112</v>
@@ -45116,7 +45116,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1543" t="n">
         <v>1010</v>
@@ -45145,7 +45145,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1544" t="n">
         <v>3200</v>
@@ -45174,7 +45174,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.67158794403076</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1545" t="n">
         <v>400</v>
@@ -45203,7 +45203,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.59902691841125</v>
+        <v>3.59902667999268</v>
       </c>
       <c r="H1546" t="n">
         <v>1320</v>
@@ -45290,7 +45290,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.71512460708618</v>
+        <v>3.71512413024902</v>
       </c>
       <c r="H1549" t="n">
         <v>4878</v>
@@ -45319,7 +45319,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1550" t="n">
         <v>3930</v>
@@ -45377,7 +45377,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.67158794403076</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1552" t="n">
         <v>900</v>
@@ -45406,7 +45406,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1553" t="n">
         <v>2243</v>
@@ -45464,7 +45464,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.67158794403076</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1555" t="n">
         <v>10</v>
@@ -45493,7 +45493,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707564353943</v>
       </c>
       <c r="H1556" t="n">
         <v>255</v>
@@ -45609,7 +45609,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.51920962333679</v>
+        <v>3.51920986175537</v>
       </c>
       <c r="H1560" t="n">
         <v>5958</v>
@@ -45638,7 +45638,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1561" t="n">
         <v>1450</v>
@@ -45696,7 +45696,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1563" t="n">
         <v>400</v>
@@ -45754,7 +45754,7 @@
         <v>4.5</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1565" t="n">
         <v>28829</v>
@@ -45812,7 +45812,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1567" t="n">
         <v>9490</v>
@@ -45841,7 +45841,7 @@
         <v>4.75</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1568" t="n">
         <v>7375</v>
@@ -45870,7 +45870,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.39585590362549</v>
+        <v>3.39585566520691</v>
       </c>
       <c r="H1569" t="n">
         <v>5281</v>
@@ -45899,7 +45899,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1570" t="n">
         <v>2484</v>
@@ -45928,7 +45928,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1571" t="n">
         <v>4522</v>
@@ -45957,7 +45957,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1572" t="n">
-        <v>3.09109997749329</v>
+        <v>3.09109973907471</v>
       </c>
       <c r="H1572" t="n">
         <v>10541</v>
@@ -45986,7 +45986,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1573" t="n">
         <v>2602</v>
@@ -46015,7 +46015,7 @@
         <v>4.75</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.44664883613586</v>
+        <v>3.44664859771729</v>
       </c>
       <c r="H1574" t="n">
         <v>5518</v>
@@ -46044,7 +46044,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1575" t="n">
         <v>3340</v>
@@ -46102,7 +46102,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.45390486717224</v>
+        <v>3.45390510559082</v>
       </c>
       <c r="H1577" t="n">
         <v>210</v>
@@ -46160,7 +46160,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707564353943</v>
       </c>
       <c r="H1579" t="n">
         <v>25968</v>
@@ -46189,7 +46189,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1580" t="n">
         <v>4781</v>
@@ -46218,7 +46218,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.71512460708618</v>
+        <v>3.71512413024902</v>
       </c>
       <c r="H1581" t="n">
         <v>3800</v>
@@ -46334,7 +46334,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.67158794403076</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1585" t="n">
         <v>7040</v>
@@ -46363,7 +46363,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1586" t="n">
         <v>8413</v>
@@ -46421,7 +46421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1588" t="n">
         <v>169</v>
@@ -46450,7 +46450,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1589" t="n">
         <v>3324</v>
@@ -46566,7 +46566,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707564353943</v>
       </c>
       <c r="H1593" t="n">
         <v>19445</v>
@@ -46595,7 +46595,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.68610000610352</v>
+        <v>3.68609976768494</v>
       </c>
       <c r="H1594" t="n">
         <v>4764</v>
@@ -46624,7 +46624,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.71512460708618</v>
+        <v>3.71512413024902</v>
       </c>
       <c r="H1595" t="n">
         <v>1760</v>
@@ -46711,7 +46711,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.67158794403076</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1598" t="n">
         <v>2389</v>
@@ -46740,7 +46740,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.70061206817627</v>
+        <v>3.70061230659485</v>
       </c>
       <c r="H1599" t="n">
         <v>2133</v>
@@ -46798,7 +46798,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H1601" t="n">
         <v>30682</v>
@@ -46827,7 +46827,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1602" t="n">
         <v>2064</v>
@@ -46885,7 +46885,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H1604" t="n">
         <v>786</v>
@@ -47001,7 +47001,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1608" t="n">
         <v>2503</v>
@@ -47030,7 +47030,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.67158794403076</v>
+        <v>3.67158770561218</v>
       </c>
       <c r="H1609" t="n">
         <v>1293</v>
@@ -47088,7 +47088,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1611" t="n">
         <v>3751</v>
@@ -47175,7 +47175,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1614" t="n">
         <v>7016</v>
@@ -47233,7 +47233,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.52646565437317</v>
+        <v>3.52646589279175</v>
       </c>
       <c r="H1616" t="n">
         <v>1810</v>
@@ -47262,7 +47262,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.54823398590088</v>
+        <v>3.5482337474823</v>
       </c>
       <c r="H1617" t="n">
         <v>20</v>
@@ -47378,7 +47378,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1621" t="n">
         <v>3604</v>
@@ -47436,7 +47436,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1623" t="n">
         <v>400</v>
@@ -47465,7 +47465,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.51920962333679</v>
+        <v>3.51920986175537</v>
       </c>
       <c r="H1624" t="n">
         <v>3315</v>
@@ -47581,7 +47581,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.54823398590088</v>
+        <v>3.5482337474823</v>
       </c>
       <c r="H1628" t="n">
         <v>1040</v>
@@ -47610,7 +47610,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.52646565437317</v>
+        <v>3.52646589279175</v>
       </c>
       <c r="H1629" t="n">
         <v>5510</v>
@@ -47639,7 +47639,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1630" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1630" t="n">
         <v>17514</v>
@@ -47668,7 +47668,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38859987258911</v>
+        <v>3.38860011100769</v>
       </c>
       <c r="H1631" t="n">
         <v>7208</v>
@@ -47784,7 +47784,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.38134384155273</v>
+        <v>3.38134360313416</v>
       </c>
       <c r="H1635" t="n">
         <v>170</v>
@@ -47842,7 +47842,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1637" t="n">
         <v>4239</v>
@@ -47871,7 +47871,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1638" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1638" t="n">
         <v>2288</v>
@@ -47900,7 +47900,7 @@
         <v>4.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1639" t="n">
         <v>2094</v>
@@ -47987,7 +47987,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1642" t="n">
-        <v>3.25798964500427</v>
+        <v>3.25798988342285</v>
       </c>
       <c r="H1642" t="n">
         <v>783</v>
@@ -48045,7 +48045,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1644" t="n">
         <v>1681</v>
@@ -48132,7 +48132,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1647" t="n">
         <v>817</v>
@@ -48190,7 +48190,7 @@
         <v>4.25</v>
       </c>
       <c r="G1649" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1649" t="n">
         <v>2289</v>
@@ -48219,7 +48219,7 @@
         <v>4.25</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1650" t="n">
         <v>1800</v>
@@ -48277,7 +48277,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H1652" t="n">
         <v>400</v>
@@ -48335,7 +48335,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1654" t="n">
         <v>300</v>
@@ -48364,7 +48364,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.3232946395874</v>
+        <v>3.32329511642456</v>
       </c>
       <c r="H1655" t="n">
         <v>5550</v>
@@ -48393,7 +48393,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1656" t="n">
-        <v>3.30152654647827</v>
+        <v>3.30152678489685</v>
       </c>
       <c r="H1656" t="n">
         <v>2320</v>
@@ -48422,7 +48422,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1657" t="n">
-        <v>3.45390486717224</v>
+        <v>3.45390510559082</v>
       </c>
       <c r="H1657" t="n">
         <v>23337</v>
@@ -48538,7 +48538,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.61353898048401</v>
+        <v>3.61353921890259</v>
       </c>
       <c r="H1661" t="n">
         <v>2400</v>
@@ -48741,7 +48741,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1668" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1668" t="n">
         <v>15918</v>
@@ -48944,7 +48944,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1675" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1675" t="n">
         <v>1250</v>
@@ -49031,7 +49031,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.65707540512085</v>
+        <v>3.65707564353943</v>
       </c>
       <c r="H1678" t="n">
         <v>5800</v>
@@ -49060,7 +49060,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1679" t="n">
-        <v>3.56274652481079</v>
+        <v>3.56274628639221</v>
       </c>
       <c r="H1679" t="n">
         <v>432</v>
@@ -49147,7 +49147,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.54823398590088</v>
+        <v>3.5482337474823</v>
       </c>
       <c r="H1682" t="n">
         <v>1533</v>
@@ -49176,7 +49176,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1683" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1683" t="n">
         <v>1137</v>
@@ -49205,7 +49205,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1684" t="n">
         <v>600</v>
@@ -49234,7 +49234,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1685" t="n">
-        <v>3.59177041053772</v>
+        <v>3.5917706489563</v>
       </c>
       <c r="H1685" t="n">
         <v>2350</v>
@@ -49263,7 +49263,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.59902691841125</v>
+        <v>3.59902667999268</v>
       </c>
       <c r="H1686" t="n">
         <v>300</v>
@@ -49292,7 +49292,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.57725858688354</v>
+        <v>3.57725834846497</v>
       </c>
       <c r="H1687" t="n">
         <v>994</v>
@@ -49321,7 +49321,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.59902691841125</v>
+        <v>3.59902667999268</v>
       </c>
       <c r="H1688" t="n">
         <v>100</v>
@@ -49350,7 +49350,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.57000255584717</v>
+        <v>3.57000231742859</v>
       </c>
       <c r="H1689" t="n">
         <v>2005</v>
@@ -49379,7 +49379,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.57000255584717</v>
+        <v>3.57000231742859</v>
       </c>
       <c r="H1690" t="n">
         <v>100</v>
@@ -49408,7 +49408,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1691" t="n">
         <v>34603</v>
@@ -49437,7 +49437,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1692" t="n">
         <v>150</v>
@@ -49466,7 +49466,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1693" t="n">
         <v>0</v>
@@ -49495,7 +49495,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.55549049377441</v>
+        <v>3.55549025535583</v>
       </c>
       <c r="H1694" t="n">
         <v>7420</v>
@@ -49524,7 +49524,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1695" t="n">
         <v>17559</v>
@@ -49582,7 +49582,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1697" t="n">
-        <v>3.51920962333679</v>
+        <v>3.51920986175537</v>
       </c>
       <c r="H1697" t="n">
         <v>887</v>
@@ -49611,7 +49611,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1698" t="n">
-        <v>3.51920962333679</v>
+        <v>3.51920986175537</v>
       </c>
       <c r="H1698" t="n">
         <v>450</v>
@@ -49640,7 +49640,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1699" t="n">
-        <v>3.51920962333679</v>
+        <v>3.51920986175537</v>
       </c>
       <c r="H1699" t="n">
         <v>800</v>
@@ -49669,7 +49669,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.51920962333679</v>
+        <v>3.51920986175537</v>
       </c>
       <c r="H1700" t="n">
         <v>50</v>
@@ -49698,7 +49698,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1701" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1701" t="n">
         <v>50</v>
@@ -49727,7 +49727,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1702" t="n">
         <v>666</v>
@@ -49756,7 +49756,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.37408781051636</v>
+        <v>3.37408757209778</v>
       </c>
       <c r="H1703" t="n">
         <v>14671</v>
@@ -49930,7 +49930,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1709" t="n">
         <v>274</v>
@@ -49959,7 +49959,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1710" t="n">
         <v>97360</v>
@@ -50017,7 +50017,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1712" t="n">
-        <v>3.36683130264282</v>
+        <v>3.3668315410614</v>
       </c>
       <c r="H1712" t="n">
         <v>1216</v>
@@ -50104,7 +50104,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1715" t="n">
-        <v>3.27250266075134</v>
+        <v>3.27250242233276</v>
       </c>
       <c r="H1715" t="n">
         <v>200</v>
@@ -50133,7 +50133,7 @@
         <v>4.5</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1716" t="n">
         <v>1525</v>
@@ -50162,7 +50162,7 @@
         <v>4.5</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.26524615287781</v>
+        <v>3.26524591445923</v>
       </c>
       <c r="H1717" t="n">
         <v>0</v>
@@ -50191,7 +50191,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1718" t="n">
         <v>120</v>
@@ -50220,7 +50220,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1719" t="n">
         <v>0</v>
@@ -50249,7 +50249,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1720" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1720" t="n">
         <v>3273</v>
@@ -50278,7 +50278,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.12738013267517</v>
+        <v>3.12738037109375</v>
       </c>
       <c r="H1721" t="n">
         <v>1702</v>
@@ -50365,7 +50365,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H1724" t="n">
         <v>821</v>
@@ -50394,7 +50394,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1725" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1725" t="n">
         <v>778</v>
@@ -50481,7 +50481,7 @@
         <v>4.25</v>
       </c>
       <c r="G1728" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1728" t="n">
         <v>6938</v>
@@ -50626,7 +50626,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1733" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1733" t="n">
         <v>2901</v>
@@ -50655,7 +50655,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1734" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1734" t="n">
         <v>0</v>
@@ -50684,7 +50684,7 @@
         <v>4.25</v>
       </c>
       <c r="G1735" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1735" t="n">
         <v>249</v>
@@ -50800,7 +50800,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.12738013267517</v>
+        <v>3.12738037109375</v>
       </c>
       <c r="H1739" t="n">
         <v>1064</v>
@@ -50858,7 +50858,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1741" t="n">
         <v>2248</v>
@@ -50887,7 +50887,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1742" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1742" t="n">
         <v>1600</v>
@@ -50916,7 +50916,7 @@
         <v>4.25</v>
       </c>
       <c r="G1743" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1743" t="n">
         <v>809</v>
@@ -50974,7 +50974,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H1745" t="n">
         <v>8879</v>
@@ -51003,7 +51003,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1746" t="n">
         <v>12</v>
@@ -51032,7 +51032,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1747" t="n">
         <v>0</v>
@@ -51090,7 +51090,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1749" t="n">
         <v>287</v>
@@ -51148,7 +51148,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.81536769866943</v>
+        <v>2.81536793708801</v>
       </c>
       <c r="H1751" t="n">
         <v>9700</v>
@@ -51206,7 +51206,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.85890460014343</v>
+        <v>2.85890436172485</v>
       </c>
       <c r="H1753" t="n">
         <v>5741</v>
@@ -51264,7 +51264,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.82988023757935</v>
+        <v>2.82987999916077</v>
       </c>
       <c r="H1755" t="n">
         <v>3343</v>
@@ -51467,7 +51467,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.77908706665039</v>
+        <v>2.77908730506897</v>
       </c>
       <c r="H1762" t="n">
         <v>3130</v>
@@ -51612,7 +51612,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.02579498291016</v>
+        <v>3.02579474449158</v>
       </c>
       <c r="H1767" t="n">
         <v>4229</v>
@@ -51728,7 +51728,7 @@
         <v>4.25</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1771" t="n">
         <v>279</v>
@@ -51844,7 +51844,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1775" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1775" t="n">
         <v>2109</v>
@@ -51902,7 +51902,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1777" t="n">
         <v>1250</v>
@@ -51989,7 +51989,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1780" t="n">
         <v>250</v>
@@ -52047,7 +52047,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1782" t="n">
         <v>1781</v>
@@ -52105,7 +52105,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.12738013267517</v>
+        <v>3.12738037109375</v>
       </c>
       <c r="H1784" t="n">
         <v>2505</v>
@@ -52134,7 +52134,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1785" t="n">
         <v>3649</v>
@@ -52163,7 +52163,7 @@
         <v>4.25</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1786" t="n">
         <v>910</v>
@@ -52192,7 +52192,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.10561180114746</v>
+        <v>3.10561203956604</v>
       </c>
       <c r="H1787" t="n">
         <v>391</v>
@@ -52221,7 +52221,7 @@
         <v>4.25</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.08384370803833</v>
+        <v>3.08384346961975</v>
       </c>
       <c r="H1788" t="n">
         <v>2956</v>
@@ -52337,7 +52337,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1792" t="n">
         <v>1250</v>
@@ -52395,7 +52395,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.04756307601929</v>
+        <v>3.04756283760071</v>
       </c>
       <c r="H1794" t="n">
         <v>4601</v>
@@ -52424,7 +52424,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1795" t="n">
         <v>6895</v>
@@ -52453,7 +52453,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1796" t="n">
         <v>6947</v>
@@ -52511,7 +52511,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.18542885780334</v>
+        <v>3.18542909622192</v>
       </c>
       <c r="H1798" t="n">
         <v>2419</v>
@@ -52656,7 +52656,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1803" t="n">
         <v>3480</v>
@@ -52685,7 +52685,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1804" t="n">
         <v>600</v>
@@ -52714,7 +52714,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1805" t="n">
         <v>2591</v>
@@ -52743,7 +52743,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.09835577011108</v>
+        <v>3.0983555316925</v>
       </c>
       <c r="H1806" t="n">
         <v>3543</v>
@@ -52801,7 +52801,7 @@
         <v>5.5</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1808" t="n">
         <v>262088</v>
@@ -52859,7 +52859,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1810" t="n">
         <v>185319</v>
@@ -52917,7 +52917,7 @@
         <v>5.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1812" t="n">
         <v>34810</v>
@@ -52946,7 +52946,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.09244155883789</v>
+        <v>4.09244203567505</v>
       </c>
       <c r="H1813" t="n">
         <v>154634</v>
@@ -53004,7 +53004,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1815" t="n">
         <v>60991</v>
@@ -53062,7 +53062,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1817" t="n">
         <v>38559</v>
@@ -53091,7 +53091,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1818" t="n">
-        <v>3.93280792236328</v>
+        <v>3.93280744552612</v>
       </c>
       <c r="H1818" t="n">
         <v>134056</v>
@@ -53120,7 +53120,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1819" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H1819" t="n">
         <v>74184</v>
@@ -53207,7 +53207,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1822" t="n">
-        <v>3.93280792236328</v>
+        <v>3.93280744552612</v>
       </c>
       <c r="H1822" t="n">
         <v>12683</v>
@@ -53265,7 +53265,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1824" t="n">
-        <v>3.93280792236328</v>
+        <v>3.93280744552612</v>
       </c>
       <c r="H1824" t="n">
         <v>24046</v>
@@ -53497,7 +53497,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.26658868789673</v>
+        <v>4.26658821105957</v>
       </c>
       <c r="H1832" t="n">
         <v>41917</v>
@@ -53584,7 +53584,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1835" t="n">
         <v>12200</v>
@@ -53671,7 +53671,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.1214656829834</v>
+        <v>4.12146615982056</v>
       </c>
       <c r="H1838" t="n">
         <v>12403</v>
@@ -53700,7 +53700,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.2085394859314</v>
+        <v>4.20853996276855</v>
       </c>
       <c r="H1839" t="n">
         <v>11869</v>
@@ -53758,7 +53758,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.2085394859314</v>
+        <v>4.20853996276855</v>
       </c>
       <c r="H1841" t="n">
         <v>745</v>
@@ -53816,7 +53816,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.2085394859314</v>
+        <v>4.20853996276855</v>
       </c>
       <c r="H1843" t="n">
         <v>36831</v>
@@ -53845,7 +53845,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.26658868789673</v>
+        <v>4.26658821105957</v>
       </c>
       <c r="H1844" t="n">
         <v>7782</v>
@@ -53903,7 +53903,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.39719820022583</v>
+        <v>4.39719772338867</v>
       </c>
       <c r="H1846" t="n">
         <v>41545</v>
@@ -53961,7 +53961,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H1848" t="n">
         <v>15922</v>
@@ -53990,7 +53990,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H1849" t="n">
         <v>15739</v>
@@ -54164,7 +54164,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.39719820022583</v>
+        <v>4.39719772338867</v>
       </c>
       <c r="H1855" t="n">
         <v>14520</v>
@@ -54222,7 +54222,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>4.44073438644409</v>
+        <v>4.44073486328125</v>
       </c>
       <c r="H1857" t="n">
         <v>22756</v>
@@ -54338,7 +54338,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1861" t="n">
-        <v>4.28110074996948</v>
+        <v>4.28110027313232</v>
       </c>
       <c r="H1861" t="n">
         <v>43805</v>
@@ -54367,7 +54367,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.26658868789673</v>
+        <v>4.26658821105957</v>
       </c>
       <c r="H1862" t="n">
         <v>7193</v>
@@ -54396,7 +54396,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.2085394859314</v>
+        <v>4.20853996276855</v>
       </c>
       <c r="H1863" t="n">
         <v>33360</v>
@@ -54570,7 +54570,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>4.09244155883789</v>
+        <v>4.09244203567505</v>
       </c>
       <c r="H1869" t="n">
         <v>7070</v>
@@ -54657,7 +54657,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1872" t="n">
         <v>20141</v>
@@ -54686,7 +54686,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1873" t="n">
         <v>10475</v>
@@ -54744,7 +54744,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1875" t="n">
         <v>13180</v>
@@ -54802,7 +54802,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1877" t="n">
         <v>12120</v>
@@ -54831,7 +54831,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1878" t="n">
         <v>12000</v>
@@ -54860,7 +54860,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1879" t="n">
         <v>43513</v>
@@ -54918,7 +54918,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1881" t="n">
         <v>12398</v>
@@ -54947,7 +54947,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1882" t="n">
         <v>5633</v>
@@ -54976,7 +54976,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.1214656829834</v>
+        <v>4.12146615982056</v>
       </c>
       <c r="H1883" t="n">
         <v>9022</v>
@@ -55005,7 +55005,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1884" t="n">
         <v>4100</v>
@@ -55034,7 +55034,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H1885" t="n">
         <v>5</v>
@@ -55063,7 +55063,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H1886" t="n">
         <v>7240</v>
@@ -55150,7 +55150,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.01988077163696</v>
+        <v>4.0198802947998</v>
       </c>
       <c r="H1889" t="n">
         <v>16712</v>
@@ -55208,7 +55208,7 @@
         <v>5.5</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1891" t="n">
         <v>22700</v>
@@ -55295,7 +55295,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1894" t="n">
-        <v>4.28110074996948</v>
+        <v>4.28110027313232</v>
       </c>
       <c r="H1894" t="n">
         <v>66745</v>
@@ -55353,7 +55353,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1896" t="n">
-        <v>4.32463693618774</v>
+        <v>4.3246374130249</v>
       </c>
       <c r="H1896" t="n">
         <v>4810</v>
@@ -55382,7 +55382,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1897" t="n">
-        <v>4.44073438644409</v>
+        <v>4.44073486328125</v>
       </c>
       <c r="H1897" t="n">
         <v>33014</v>
@@ -55411,7 +55411,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.45524644851685</v>
+        <v>4.45524740219116</v>
       </c>
       <c r="H1898" t="n">
         <v>11695</v>
@@ -55469,7 +55469,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1900" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1900" t="n">
         <v>15662</v>
@@ -55498,7 +55498,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1901" t="n">
         <v>26842</v>
@@ -55556,7 +55556,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1903" t="n">
         <v>21319</v>
@@ -55643,7 +55643,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1906" t="n">
         <v>38626</v>
@@ -55730,7 +55730,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1909" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1909" t="n">
         <v>3775</v>
@@ -55759,7 +55759,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1910" t="n">
         <v>20341</v>
@@ -55817,7 +55817,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1912" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1912" t="n">
         <v>32655</v>
@@ -55904,7 +55904,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.54232025146484</v>
+        <v>4.542320728302</v>
       </c>
       <c r="H1915" t="n">
         <v>6100</v>
@@ -55933,7 +55933,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H1916" t="n">
         <v>26741</v>
@@ -55962,7 +55962,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.39719820022583</v>
+        <v>4.39719772338867</v>
       </c>
       <c r="H1917" t="n">
         <v>18820</v>
@@ -56049,7 +56049,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1920" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1920" t="n">
         <v>99275</v>
@@ -56078,7 +56078,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1921" t="n">
         <v>45350</v>
@@ -56107,7 +56107,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1922" t="n">
         <v>46575</v>
@@ -56194,7 +56194,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1925" t="n">
         <v>43840</v>
@@ -56223,7 +56223,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1926" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1926" t="n">
         <v>32624</v>
@@ -56281,7 +56281,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1928" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1928" t="n">
         <v>36250</v>
@@ -56310,7 +56310,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1929" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1929" t="n">
         <v>8594</v>
@@ -56339,7 +56339,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1930" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1930" t="n">
         <v>9421</v>
@@ -56368,7 +56368,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1931" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H1931" t="n">
         <v>77323</v>
@@ -56397,7 +56397,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1932" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1932" t="n">
         <v>32327</v>
@@ -56426,7 +56426,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1933" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1933" t="n">
         <v>13860</v>
@@ -56455,7 +56455,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1934" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1934" t="n">
         <v>14123</v>
@@ -56484,7 +56484,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1935" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H1935" t="n">
         <v>4650</v>
@@ -56629,7 +56629,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1940" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H1940" t="n">
         <v>12318</v>
@@ -56832,7 +56832,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1947" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1947" t="n">
         <v>11712</v>
@@ -56948,7 +56948,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1951" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1951" t="n">
         <v>112195</v>
@@ -56977,7 +56977,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1952" t="n">
         <v>58673</v>
@@ -57093,7 +57093,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1956" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1956" t="n">
         <v>10749</v>
@@ -57151,7 +57151,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1958" t="n">
         <v>15475</v>
@@ -57180,7 +57180,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1959" t="n">
-        <v>4.80353927612305</v>
+        <v>4.80353975296021</v>
       </c>
       <c r="H1959" t="n">
         <v>1004</v>
@@ -57209,7 +57209,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1960" t="n">
-        <v>4.83256387710571</v>
+        <v>4.83256435394287</v>
       </c>
       <c r="H1960" t="n">
         <v>3682</v>
@@ -57238,7 +57238,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1961" t="n">
-        <v>4.80353927612305</v>
+        <v>4.80353975296021</v>
       </c>
       <c r="H1961" t="n">
         <v>19601</v>
@@ -57325,7 +57325,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1964" t="n">
-        <v>4.83256387710571</v>
+        <v>4.83256435394287</v>
       </c>
       <c r="H1964" t="n">
         <v>17330</v>
@@ -57789,7 +57789,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1980" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1980" t="n">
         <v>6300</v>
@@ -57963,7 +57963,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1986" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1986" t="n">
         <v>10900</v>
@@ -58079,7 +58079,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1990" t="n">
-        <v>4.80353927612305</v>
+        <v>4.80353975296021</v>
       </c>
       <c r="H1990" t="n">
         <v>5520</v>
@@ -58137,7 +58137,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1992" t="n">
         <v>13140</v>
@@ -58166,7 +58166,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1993" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H1993" t="n">
         <v>22249</v>
@@ -58195,7 +58195,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H1994" t="n">
         <v>6925</v>
@@ -58543,7 +58543,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H2006" t="n">
         <v>63727</v>
@@ -58717,7 +58717,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.73097896575928</v>
+        <v>4.73097848892212</v>
       </c>
       <c r="H2012" t="n">
         <v>25464</v>
@@ -58862,7 +58862,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.6439061164856</v>
+        <v>4.64390563964844</v>
       </c>
       <c r="H2017" t="n">
         <v>32700</v>
@@ -58891,7 +58891,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.60036945343018</v>
+        <v>4.60036897659302</v>
       </c>
       <c r="H2018" t="n">
         <v>92013</v>
@@ -58949,7 +58949,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.54232025146484</v>
+        <v>4.542320728302</v>
       </c>
       <c r="H2020" t="n">
         <v>29342</v>
@@ -59007,7 +59007,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.31012535095215</v>
+        <v>4.31012487411499</v>
       </c>
       <c r="H2022" t="n">
         <v>52338</v>
@@ -59036,7 +59036,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.26658868789673</v>
+        <v>4.26658821105957</v>
       </c>
       <c r="H2023" t="n">
         <v>15139</v>
@@ -59239,7 +59239,7 @@
         <v>5.5</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.9908561706543</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H2030" t="n">
         <v>85194</v>
@@ -59355,7 +59355,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.87475848197937</v>
+        <v>3.87475895881653</v>
       </c>
       <c r="H2034" t="n">
         <v>62502</v>
@@ -59384,7 +59384,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2035" t="n">
         <v>25964</v>
@@ -59413,7 +59413,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2036" t="n">
         <v>14916</v>
@@ -59442,7 +59442,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.87475848197937</v>
+        <v>3.87475895881653</v>
       </c>
       <c r="H2037" t="n">
         <v>19540</v>
@@ -59471,7 +59471,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2038" t="n">
         <v>15489</v>
@@ -59500,7 +59500,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2039" t="n">
         <v>9796</v>
@@ -59529,7 +59529,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2040" t="n">
         <v>11666</v>
@@ -59558,7 +59558,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H2041" t="n">
         <v>5845</v>
@@ -59645,7 +59645,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2044" t="n">
         <v>13762</v>
@@ -59674,7 +59674,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.87475848197937</v>
+        <v>3.87475895881653</v>
       </c>
       <c r="H2045" t="n">
         <v>12427</v>
@@ -59703,7 +59703,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H2046" t="n">
         <v>11724</v>
@@ -59732,7 +59732,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.91829538345337</v>
+        <v>3.91829562187195</v>
       </c>
       <c r="H2047" t="n">
         <v>8651</v>
@@ -59761,7 +59761,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.87475848197937</v>
+        <v>3.87475895881653</v>
       </c>
       <c r="H2048" t="n">
         <v>18302</v>
@@ -59790,7 +59790,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2049" t="n">
         <v>16940</v>
@@ -59819,7 +59819,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2050" t="n">
         <v>13500</v>
@@ -59848,7 +59848,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2051" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2051" t="n">
         <v>1800</v>
@@ -59877,7 +59877,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2052" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H2052" t="n">
         <v>5484</v>
@@ -59906,7 +59906,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2053" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2053" t="n">
         <v>2480</v>
@@ -59935,7 +59935,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2054" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2054" t="n">
         <v>6321</v>
@@ -59964,7 +59964,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2055" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2055" t="n">
         <v>1020</v>
@@ -59993,7 +59993,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2056" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2056" t="n">
         <v>0</v>
@@ -60022,7 +60022,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2057" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2057" t="n">
         <v>1050</v>
@@ -60051,7 +60051,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2058" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2058" t="n">
         <v>1525</v>
@@ -60080,7 +60080,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2059" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2059" t="n">
         <v>800</v>
@@ -60138,7 +60138,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2061" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2061" t="n">
         <v>122</v>
@@ -60196,7 +60196,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2063" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2063" t="n">
         <v>12069</v>
@@ -60225,7 +60225,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2064" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2064" t="n">
         <v>1038</v>
@@ -60254,7 +60254,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2065" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2065" t="n">
         <v>1000</v>
@@ -60283,7 +60283,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2066" t="n">
-        <v>3.83122229576111</v>
+        <v>3.83122253417969</v>
       </c>
       <c r="H2066" t="n">
         <v>5374</v>
@@ -60312,7 +60312,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2067" t="n">
-        <v>3.81671023368835</v>
+        <v>3.81670999526978</v>
       </c>
       <c r="H2067" t="n">
         <v>1</v>
@@ -60399,7 +60399,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2070" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2070" t="n">
         <v>7354</v>
@@ -60428,7 +60428,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2071" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2071" t="n">
         <v>380</v>
@@ -60457,7 +60457,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2072" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2072" t="n">
         <v>562</v>
@@ -60486,7 +60486,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2073" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2073" t="n">
         <v>1000</v>
@@ -60515,7 +60515,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2074" t="n">
-        <v>3.78768515586853</v>
+        <v>3.78768563270569</v>
       </c>
       <c r="H2074" t="n">
         <v>3250</v>
@@ -60573,7 +60573,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2076" t="n">
-        <v>3.74414849281311</v>
+        <v>3.74414920806885</v>
       </c>
       <c r="H2076" t="n">
         <v>21034</v>
@@ -60718,7 +60718,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.84573435783386</v>
+        <v>3.84573459625244</v>
       </c>
       <c r="H2081" t="n">
         <v>5369</v>
@@ -60747,7 +60747,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H2082" t="n">
         <v>26100</v>
@@ -60776,7 +60776,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.10695362091064</v>
+        <v>4.1069540977478</v>
       </c>
       <c r="H2083" t="n">
         <v>11554</v>
@@ -60805,7 +60805,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.04890537261963</v>
+        <v>4.04890489578247</v>
       </c>
       <c r="H2084" t="n">
         <v>22246</v>
@@ -60863,7 +60863,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.1214656829834</v>
+        <v>4.12146615982056</v>
       </c>
       <c r="H2086" t="n">
         <v>3284</v>
@@ -60892,7 +60892,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.09244155883789</v>
+        <v>4.09244203567505</v>
       </c>
       <c r="H2087" t="n">
         <v>4634</v>
@@ -60921,7 +60921,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.09244155883789</v>
+        <v>4.09244203567505</v>
       </c>
       <c r="H2088" t="n">
         <v>13454</v>
@@ -60979,7 +60979,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H2090" t="n">
         <v>8585</v>
@@ -61008,7 +61008,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2091" t="n">
-        <v>4.06341743469238</v>
+        <v>4.06341695785522</v>
       </c>
       <c r="H2091" t="n">
         <v>8150</v>
@@ -61037,7 +61037,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2092" t="n">
-        <v>4.10695362091064</v>
+        <v>4.1069540977478</v>
       </c>
       <c r="H2092" t="n">
         <v>8611</v>
@@ -61124,7 +61124,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G2095" t="n">
-        <v>4.39719820022583</v>
+        <v>4.39719772338867</v>
       </c>
       <c r="H2095" t="n">
         <v>39523</v>
@@ -61182,7 +61182,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2097" t="n">
-        <v>4.45524644851685</v>
+        <v>4.45524740219116</v>
       </c>
       <c r="H2097" t="n">
         <v>25254</v>
@@ -61211,7 +61211,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2098" t="n">
-        <v>4.45524644851685</v>
+        <v>4.45524740219116</v>
       </c>
       <c r="H2098" t="n">
         <v>16270</v>
@@ -61414,7 +61414,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.61488151550293</v>
+        <v>4.61488103866577</v>
       </c>
       <c r="H2105" t="n">
         <v>6270</v>
@@ -61472,7 +61472,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2107" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2107" t="n">
         <v>22131</v>
@@ -61501,7 +61501,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2108" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2108" t="n">
         <v>5235</v>
@@ -61530,7 +61530,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2109" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2109" t="n">
         <v>9985</v>
@@ -61559,7 +61559,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2110" t="n">
-        <v>4.7745156288147</v>
+        <v>4.77451515197754</v>
       </c>
       <c r="H2110" t="n">
         <v>17810</v>
@@ -61791,7 +61791,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2118" t="n">
-        <v>5.36951637268066</v>
+        <v>5.36951589584351</v>
       </c>
       <c r="H2118" t="n">
         <v>35482</v>
@@ -61878,7 +61878,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2121" t="n">
-        <v>5.36951637268066</v>
+        <v>5.36951589584351</v>
       </c>
       <c r="H2121" t="n">
         <v>66450</v>
@@ -61907,7 +61907,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2122" t="n">
-        <v>5.71780920028687</v>
+        <v>5.71780872344971</v>
       </c>
       <c r="H2122" t="n">
         <v>237009</v>
@@ -61936,7 +61936,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2123" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2123" t="n">
         <v>156082</v>
@@ -61994,7 +61994,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2125" t="n">
-        <v>5.74200248718262</v>
+        <v>5.74200296401978</v>
       </c>
       <c r="H2125" t="n">
         <v>31598</v>
@@ -62168,7 +62168,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2131" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2131" t="n">
         <v>5020</v>
@@ -62516,7 +62516,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2143" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2143" t="n">
         <v>4615</v>
@@ -62545,7 +62545,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2144" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2144" t="n">
         <v>3322</v>
@@ -62603,7 +62603,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2146" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2146" t="n">
         <v>4610</v>
@@ -62661,7 +62661,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2148" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2148" t="n">
         <v>6369</v>
@@ -62835,7 +62835,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2154" t="n">
-        <v>5.50006484985352</v>
+        <v>5.50006437301636</v>
       </c>
       <c r="H2154" t="n">
         <v>72558</v>
@@ -62951,7 +62951,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2158" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2158" t="n">
         <v>4098</v>
@@ -63154,7 +63154,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2165" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2165" t="n">
         <v>15059</v>
@@ -63241,7 +63241,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2168" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2168" t="n">
         <v>11763</v>
@@ -63270,7 +63270,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2169" t="n">
-        <v>5.62909841537476</v>
+        <v>5.6290979385376</v>
       </c>
       <c r="H2169" t="n">
         <v>1246</v>
@@ -63328,7 +63328,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2171" t="n">
-        <v>5.67748594284058</v>
+        <v>5.67748546600342</v>
       </c>
       <c r="H2171" t="n">
         <v>13431</v>
@@ -63415,7 +63415,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2174" t="n">
-        <v>5.79039001464844</v>
+        <v>5.7903904914856</v>
       </c>
       <c r="H2174" t="n">
         <v>33583</v>
@@ -63444,7 +63444,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2175" t="n">
-        <v>5.79039001464844</v>
+        <v>5.7903904914856</v>
       </c>
       <c r="H2175" t="n">
         <v>2041</v>
@@ -64082,7 +64082,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2197" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2197" t="n">
         <v>46134</v>
@@ -64140,7 +64140,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2199" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2199" t="n">
         <v>43455</v>
@@ -64198,7 +64198,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2201" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2201" t="n">
         <v>36088</v>
@@ -64256,7 +64256,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2203" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2203" t="n">
         <v>37217</v>
@@ -64285,7 +64285,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2204" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2204" t="n">
         <v>39475</v>
@@ -64314,7 +64314,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2205" t="n">
-        <v>5.87103700637817</v>
+        <v>5.87103652954102</v>
       </c>
       <c r="H2205" t="n">
         <v>38442</v>
@@ -79997,7 +79997,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="E2746" t="n">
-        <v>1.77999997138977</v>
+        <v>1.75999999046326</v>
       </c>
       <c r="F2746" t="n">
         <v>1.75999999046326</v>
@@ -80009,6 +80009,35 @@
         <v>4500</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>1.79499995708466</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>2060</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -659,7 +659,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G10" t="n">
-        <v>2.13909888267517</v>
+        <v>2.13909912109375</v>
       </c>
       <c r="H10" t="n">
         <v>1200</v>
@@ -891,7 +891,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H18" t="n">
         <v>3000</v>
@@ -949,7 +949,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G20" t="n">
-        <v>2.20440411567688</v>
+        <v>2.2044038772583</v>
       </c>
       <c r="H20" t="n">
         <v>600</v>
@@ -978,7 +978,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G21" t="n">
-        <v>2.15215992927551</v>
+        <v>2.15216016769409</v>
       </c>
       <c r="H21" t="n">
         <v>2400</v>
@@ -1007,7 +1007,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G22" t="n">
-        <v>2.15215992927551</v>
+        <v>2.15216016769409</v>
       </c>
       <c r="H22" t="n">
         <v>600</v>
@@ -1036,7 +1036,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H23" t="n">
         <v>1800</v>
@@ -1065,7 +1065,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14345288276672</v>
+        <v>2.14345264434814</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G28" t="n">
-        <v>2.09120869636536</v>
+        <v>2.09120845794678</v>
       </c>
       <c r="H28" t="n">
         <v>1800</v>
@@ -1210,7 +1210,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14055013656616</v>
+        <v>2.14055037498474</v>
       </c>
       <c r="H29" t="n">
         <v>600</v>
@@ -1268,7 +1268,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G31" t="n">
-        <v>2.1347451210022</v>
+        <v>2.13474535942078</v>
       </c>
       <c r="H31" t="n">
         <v>3000</v>
@@ -1297,7 +1297,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H32" t="n">
         <v>3000</v>
@@ -1326,7 +1326,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G37" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G38" t="n">
-        <v>2.14200139045715</v>
+        <v>2.14200162887573</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G44" t="n">
-        <v>2.20440411567688</v>
+        <v>2.2044038772583</v>
       </c>
       <c r="H44" t="n">
         <v>4800</v>
@@ -1703,7 +1703,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G46" t="n">
-        <v>2.24648952484131</v>
+        <v>2.24648928642273</v>
       </c>
       <c r="H46" t="n">
         <v>600</v>
@@ -1732,7 +1732,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G47" t="n">
-        <v>2.16086745262146</v>
+        <v>2.16086721420288</v>
       </c>
       <c r="H47" t="n">
         <v>1800</v>
@@ -1819,7 +1819,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>2.17247700691223</v>
+        <v>2.17247724533081</v>
       </c>
       <c r="H50" t="n">
         <v>600</v>
@@ -1848,7 +1848,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G51" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H51" t="n">
         <v>2400</v>
@@ -1877,7 +1877,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G52" t="n">
-        <v>2.22617244720459</v>
+        <v>2.22617220878601</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G53" t="n">
-        <v>2.2551965713501</v>
+        <v>2.25519680976868</v>
       </c>
       <c r="H53" t="n">
         <v>3000</v>
@@ -2051,7 +2051,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23487949371338</v>
+        <v>2.2348792552948</v>
       </c>
       <c r="H58" t="n">
         <v>600</v>
@@ -2080,7 +2080,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>2.23487949371338</v>
+        <v>2.2348792552948</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G68" t="n">
-        <v>2.17973303794861</v>
+        <v>2.17973327636719</v>
       </c>
       <c r="H68" t="n">
         <v>5400</v>
@@ -2399,7 +2399,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G70" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H70" t="n">
         <v>27300</v>
@@ -2486,7 +2486,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G73" t="n">
-        <v>1.76903784275055</v>
+        <v>1.76903772354126</v>
       </c>
       <c r="H73" t="n">
         <v>780</v>
@@ -2515,7 +2515,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G74" t="n">
-        <v>1.76758670806885</v>
+        <v>1.76758658885956</v>
       </c>
       <c r="H74" t="n">
         <v>1560</v>
@@ -2544,7 +2544,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G75" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H75" t="n">
         <v>780</v>
@@ -2573,7 +2573,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G76" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G77" t="n">
-        <v>1.72259867191315</v>
+        <v>1.72259879112244</v>
       </c>
       <c r="H77" t="n">
         <v>780</v>
@@ -2631,7 +2631,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G78" t="n">
-        <v>1.72259867191315</v>
+        <v>1.72259879112244</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H82" t="n">
         <v>1560</v>
@@ -2776,7 +2776,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H83" t="n">
         <v>780</v>
@@ -2950,7 +2950,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G89" t="n">
-        <v>1.7327573299408</v>
+        <v>1.73275721073151</v>
       </c>
       <c r="H89" t="n">
         <v>1560</v>
@@ -3298,7 +3298,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H101" t="n">
         <v>2340</v>
@@ -3327,7 +3327,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G102" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H102" t="n">
         <v>13260</v>
@@ -3356,7 +3356,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G103" t="n">
-        <v>1.64568400382996</v>
+        <v>1.64568388462067</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G104" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H104" t="n">
         <v>1560</v>
@@ -3414,7 +3414,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G105" t="n">
-        <v>1.63117182254791</v>
+        <v>1.63117170333862</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G106" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H106" t="n">
         <v>3120</v>
@@ -3472,7 +3472,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G107" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G108" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G109" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G110" t="n">
-        <v>1.62826943397522</v>
+        <v>1.62826931476593</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G113" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H113" t="n">
         <v>780</v>
@@ -3907,7 +3907,7 @@
         <v>2.25</v>
       </c>
       <c r="G122" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H122" t="n">
         <v>5460</v>
@@ -3936,7 +3936,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H123" t="n">
         <v>780</v>
@@ -3965,7 +3965,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G124" t="n">
-        <v>1.67180585861206</v>
+        <v>1.67180609703064</v>
       </c>
       <c r="H124" t="n">
         <v>3900</v>
@@ -4023,7 +4023,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G126" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H126" t="n">
         <v>3120</v>
@@ -4052,7 +4052,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G127" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G128" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G129" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G130" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G131" t="n">
-        <v>1.54990351200104</v>
+        <v>1.54990339279175</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G132" t="n">
-        <v>1.54409873485565</v>
+        <v>1.54409861564636</v>
       </c>
       <c r="H132" t="n">
         <v>2340</v>
@@ -4226,7 +4226,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G133" t="n">
-        <v>1.54409873485565</v>
+        <v>1.54409861564636</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G134" t="n">
-        <v>1.48314726352692</v>
+        <v>1.48314738273621</v>
       </c>
       <c r="H134" t="n">
         <v>780</v>
@@ -4545,7 +4545,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>1.40768396854401</v>
+        <v>1.40768384933472</v>
       </c>
       <c r="H144" t="n">
         <v>4680</v>
@@ -4603,7 +4603,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G146" t="n">
-        <v>1.34600698947906</v>
+        <v>1.34600710868835</v>
       </c>
       <c r="H146" t="n">
         <v>1560</v>
@@ -4632,7 +4632,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G147" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317154884338</v>
       </c>
       <c r="H147" t="n">
         <v>4680</v>
@@ -4661,7 +4661,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G148" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317154884338</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G149" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H149" t="n">
         <v>17160</v>
@@ -4719,7 +4719,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G150" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H150" t="n">
         <v>2340</v>
@@ -4748,7 +4748,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G151" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G152" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G153" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G154" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G155" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G156" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G157" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G158" t="n">
-        <v>1.39099478721619</v>
+        <v>1.39099490642548</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G159" t="n">
-        <v>1.39317166805267</v>
+        <v>1.39317154884338</v>
       </c>
       <c r="H159" t="n">
         <v>13260</v>
@@ -5125,7 +5125,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>1.25095212459564</v>
+        <v>1.25095200538635</v>
       </c>
       <c r="H164" t="n">
         <v>780</v>
@@ -5154,7 +5154,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G165" t="n">
-        <v>1.27925097942352</v>
+        <v>1.27925086021423</v>
       </c>
       <c r="H165" t="n">
         <v>780</v>
@@ -5415,7 +5415,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H174" t="n">
         <v>780</v>
@@ -5502,7 +5502,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>1.35543990135193</v>
+        <v>1.35544002056122</v>
       </c>
       <c r="H177" t="n">
         <v>780</v>
@@ -5879,7 +5879,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.32061064243317</v>
+        <v>1.32061076164246</v>
       </c>
       <c r="H190" t="n">
         <v>2340</v>
@@ -5966,7 +5966,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G193" t="n">
-        <v>1.24224483966827</v>
+        <v>1.24224472045898</v>
       </c>
       <c r="H193" t="n">
         <v>1560</v>
@@ -5995,7 +5995,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G194" t="n">
-        <v>1.24224483966827</v>
+        <v>1.24224472045898</v>
       </c>
       <c r="H194" t="n">
         <v>780</v>
@@ -6024,7 +6024,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G195" t="n">
-        <v>1.26473867893219</v>
+        <v>1.2647385597229</v>
       </c>
       <c r="H195" t="n">
         <v>780</v>
@@ -6053,7 +6053,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G196" t="n">
-        <v>1.26473867893219</v>
+        <v>1.2647385597229</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G197" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H197" t="n">
         <v>1560</v>
@@ -6111,7 +6111,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G199" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G200" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22628140449524</v>
+        <v>1.22628128528595</v>
       </c>
       <c r="H202" t="n">
         <v>1560</v>
@@ -6285,7 +6285,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H204" t="n">
         <v>1560</v>
@@ -6314,7 +6314,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G205" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G207" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G209" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G210" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G211" t="n">
-        <v>1.31335461139679</v>
+        <v>1.3133544921875</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G212" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H212" t="n">
         <v>780</v>
@@ -6546,7 +6546,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H213" t="n">
         <v>1560</v>
@@ -6575,7 +6575,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H218" t="n">
         <v>780</v>
@@ -6720,7 +6720,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G223" t="n">
-        <v>1.30247044563293</v>
+        <v>1.30247032642365</v>
       </c>
       <c r="H223" t="n">
         <v>3120</v>
@@ -6865,7 +6865,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G224" t="n">
-        <v>1.30247044563293</v>
+        <v>1.30247032642365</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H233" t="n">
         <v>6240</v>
@@ -7155,7 +7155,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G235" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H235" t="n">
         <v>2340</v>
@@ -7213,7 +7213,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G236" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G239" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H239" t="n">
         <v>3120</v>
@@ -7329,7 +7329,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G240" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H240" t="n">
         <v>1560</v>
@@ -7532,7 +7532,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G247" t="n">
-        <v>1.18854963779449</v>
+        <v>1.18854951858521</v>
       </c>
       <c r="H247" t="n">
         <v>3900</v>
@@ -7561,7 +7561,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G248" t="n">
-        <v>1.18854963779449</v>
+        <v>1.18854951858521</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G273" t="n">
-        <v>1.30609846115112</v>
+        <v>1.30609834194183</v>
       </c>
       <c r="H273" t="n">
         <v>3900</v>
@@ -8315,7 +8315,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G274" t="n">
-        <v>1.27707397937775</v>
+        <v>1.27707409858704</v>
       </c>
       <c r="H274" t="n">
         <v>8580</v>
@@ -8344,7 +8344,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H275" t="n">
         <v>72540</v>
@@ -8373,7 +8373,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G276" t="n">
-        <v>1.5832816362381</v>
+        <v>1.58328151702881</v>
       </c>
       <c r="H276" t="n">
         <v>86580</v>
@@ -8402,7 +8402,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G277" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H277" t="n">
         <v>13260</v>
@@ -8460,7 +8460,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>1.40768396854401</v>
+        <v>1.40768384933472</v>
       </c>
       <c r="H279" t="n">
         <v>7020</v>
@@ -8576,7 +8576,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32133626937866</v>
+        <v>1.32133615016937</v>
       </c>
       <c r="H283" t="n">
         <v>3900</v>
@@ -8634,7 +8634,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G285" t="n">
-        <v>1.23353743553162</v>
+        <v>1.23353755474091</v>
       </c>
       <c r="H285" t="n">
         <v>5460</v>
@@ -8663,7 +8663,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H286" t="n">
         <v>3900</v>
@@ -8692,7 +8692,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G288" t="n">
-        <v>1.24804973602295</v>
+        <v>1.24804961681366</v>
       </c>
       <c r="H288" t="n">
         <v>780</v>
@@ -8895,7 +8895,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G294" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H294" t="n">
         <v>3900</v>
@@ -8924,7 +8924,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G295" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H295" t="n">
         <v>3120</v>
@@ -8953,7 +8953,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G296" t="n">
-        <v>1.21104347705841</v>
+        <v>1.2110435962677</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G301" t="n">
-        <v>1.21902525424957</v>
+        <v>1.21902513504028</v>
       </c>
       <c r="H301" t="n">
         <v>6240</v>
@@ -9127,7 +9127,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>1.23353743553162</v>
+        <v>1.23353755474091</v>
       </c>
       <c r="H302" t="n">
         <v>2340</v>
@@ -9185,7 +9185,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G304" t="n">
-        <v>1.24950087070465</v>
+        <v>1.24950075149536</v>
       </c>
       <c r="H304" t="n">
         <v>780</v>
@@ -9301,7 +9301,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G308" t="n">
-        <v>1.34890937805176</v>
+        <v>1.34890949726105</v>
       </c>
       <c r="H308" t="n">
         <v>1560</v>
@@ -9330,7 +9330,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G309" t="n">
-        <v>1.34890937805176</v>
+        <v>1.34890949726105</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G315" t="n">
-        <v>1.42074477672577</v>
+        <v>1.42074489593506</v>
       </c>
       <c r="H315" t="n">
         <v>8580</v>
@@ -9533,7 +9533,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G316" t="n">
-        <v>1.42074477672577</v>
+        <v>1.42074489593506</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>1.42219614982605</v>
+        <v>1.42219626903534</v>
       </c>
       <c r="H317" t="n">
         <v>3120</v>
@@ -9649,7 +9649,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G320" t="n">
-        <v>1.70083045959473</v>
+        <v>1.70083057880402</v>
       </c>
       <c r="H320" t="n">
         <v>370500</v>
@@ -9678,7 +9678,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H321" t="n">
         <v>83460</v>
@@ -9707,7 +9707,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G322" t="n">
-        <v>1.67035484313965</v>
+        <v>1.67035472393036</v>
       </c>
       <c r="H322" t="n">
         <v>65520</v>
@@ -9736,7 +9736,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H323" t="n">
         <v>76440</v>
@@ -9794,7 +9794,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H325" t="n">
         <v>14820</v>
@@ -9823,7 +9823,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H326" t="n">
         <v>30420</v>
@@ -9968,7 +9968,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024475574493</v>
       </c>
       <c r="H331" t="n">
         <v>3900</v>
@@ -9997,7 +9997,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G332" t="n">
-        <v>1.40478146076202</v>
+        <v>1.40478134155273</v>
       </c>
       <c r="H332" t="n">
         <v>53040</v>
@@ -10026,7 +10026,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024475574493</v>
       </c>
       <c r="H333" t="n">
         <v>10140</v>
@@ -10055,7 +10055,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024475574493</v>
       </c>
       <c r="H334" t="n">
         <v>3120</v>
@@ -10084,7 +10084,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G335" t="n">
-        <v>1.43815958499908</v>
+        <v>1.43815946578979</v>
       </c>
       <c r="H335" t="n">
         <v>56160</v>
@@ -10171,7 +10171,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G338" t="n">
-        <v>1.42945218086243</v>
+        <v>1.42945230007172</v>
       </c>
       <c r="H338" t="n">
         <v>17160</v>
@@ -10200,7 +10200,7 @@
         <v>1.96899998188019</v>
       </c>
       <c r="G339" t="n">
-        <v>1.42872667312622</v>
+        <v>1.42872655391693</v>
       </c>
       <c r="H339" t="n">
         <v>1560</v>
@@ -10287,7 +10287,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G342" t="n">
-        <v>1.42945218086243</v>
+        <v>1.42945230007172</v>
       </c>
       <c r="H342" t="n">
         <v>24960</v>
@@ -10345,7 +10345,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>1.40768396854401</v>
+        <v>1.40768384933472</v>
       </c>
       <c r="H344" t="n">
         <v>6240</v>
@@ -10432,7 +10432,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G347" t="n">
-        <v>1.47298884391785</v>
+        <v>1.47298872470856</v>
       </c>
       <c r="H347" t="n">
         <v>5460</v>
@@ -10490,7 +10490,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G349" t="n">
-        <v>1.52087903022766</v>
+        <v>1.52087914943695</v>
       </c>
       <c r="H349" t="n">
         <v>202800</v>
@@ -10519,7 +10519,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G350" t="n">
-        <v>1.43380582332611</v>
+        <v>1.4338059425354</v>
       </c>
       <c r="H350" t="n">
         <v>107640</v>
@@ -10664,7 +10664,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G355" t="n">
-        <v>1.47008645534515</v>
+        <v>1.47008633613586</v>
       </c>
       <c r="H355" t="n">
         <v>2340</v>
@@ -10751,7 +10751,7 @@
         <v>2.05800008773804</v>
       </c>
       <c r="G358" t="n">
-        <v>1.49330592155457</v>
+        <v>1.49330604076385</v>
       </c>
       <c r="H358" t="n">
         <v>11700</v>
@@ -10809,7 +10809,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G360" t="n">
-        <v>1.47879385948181</v>
+        <v>1.47879374027252</v>
       </c>
       <c r="H360" t="n">
         <v>6240</v>
@@ -10867,7 +10867,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H362" t="n">
         <v>10140</v>
@@ -11070,7 +11070,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.5847327709198</v>
+        <v>1.58473289012909</v>
       </c>
       <c r="H369" t="n">
         <v>21840</v>
@@ -11099,7 +11099,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H370" t="n">
         <v>38220</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H371" t="n">
         <v>27300</v>
@@ -11157,7 +11157,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G372" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H372" t="n">
         <v>10920</v>
@@ -11186,7 +11186,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H373" t="n">
         <v>780</v>
@@ -11215,7 +11215,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H374" t="n">
         <v>6240</v>
@@ -11244,7 +11244,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H375" t="n">
         <v>2340</v>
@@ -11331,7 +11331,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G378" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H378" t="n">
         <v>73320</v>
@@ -11360,7 +11360,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.77919626235962</v>
+        <v>1.77919614315033</v>
       </c>
       <c r="H379" t="n">
         <v>138840</v>
@@ -11389,7 +11389,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H380" t="n">
         <v>17160</v>
@@ -11447,7 +11447,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G382" t="n">
-        <v>1.82708668708801</v>
+        <v>1.82708656787872</v>
       </c>
       <c r="H382" t="n">
         <v>68640</v>
@@ -11476,7 +11476,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>1.95914781093597</v>
+        <v>1.95914769172668</v>
       </c>
       <c r="H383" t="n">
         <v>76440</v>
@@ -11563,7 +11563,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>2.0999162197113</v>
+        <v>2.09991598129272</v>
       </c>
       <c r="H386" t="n">
         <v>116220</v>
@@ -11621,7 +11621,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G388" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817229270935</v>
       </c>
       <c r="H388" t="n">
         <v>55380</v>
@@ -11650,7 +11650,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G389" t="n">
-        <v>2.00558662414551</v>
+        <v>2.00558686256409</v>
       </c>
       <c r="H389" t="n">
         <v>10920</v>
@@ -11737,7 +11737,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G392" t="n">
-        <v>1.95044028759003</v>
+        <v>1.95044016838074</v>
       </c>
       <c r="H392" t="n">
         <v>20280</v>
@@ -11766,7 +11766,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318437576294</v>
+        <v>1.94318413734436</v>
       </c>
       <c r="H393" t="n">
         <v>3900</v>
@@ -11824,7 +11824,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G395" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H395" t="n">
         <v>8580</v>
@@ -11853,7 +11853,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G396" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H396" t="n">
         <v>21060</v>
@@ -11940,7 +11940,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98817205429077</v>
+        <v>1.98817229270935</v>
       </c>
       <c r="H399" t="n">
         <v>11700</v>
@@ -12056,7 +12056,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G403" t="n">
-        <v>1.78645241260529</v>
+        <v>1.786452293396</v>
       </c>
       <c r="H403" t="n">
         <v>37440</v>
@@ -12085,7 +12085,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563519477844</v>
+        <v>1.82563555240631</v>
       </c>
       <c r="H404" t="n">
         <v>66300</v>
@@ -12114,7 +12114,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H405" t="n">
         <v>109200</v>
@@ -12201,7 +12201,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H408" t="n">
         <v>21060</v>
@@ -12462,7 +12462,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G417" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H417" t="n">
         <v>48360</v>
@@ -12607,7 +12607,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G422" t="n">
-        <v>1.73856198787689</v>
+        <v>1.73856210708618</v>
       </c>
       <c r="H422" t="n">
         <v>40560</v>
@@ -12636,7 +12636,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H423" t="n">
         <v>48360</v>
@@ -12665,7 +12665,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G424" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837952136993</v>
       </c>
       <c r="H424" t="n">
         <v>19500</v>
@@ -12694,7 +12694,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G425" t="n">
-        <v>1.79515981674194</v>
+        <v>1.79515969753265</v>
       </c>
       <c r="H425" t="n">
         <v>18720</v>
@@ -12723,7 +12723,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G426" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H426" t="n">
         <v>27300</v>
@@ -12839,7 +12839,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G430" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561114788055</v>
       </c>
       <c r="H430" t="n">
         <v>19500</v>
@@ -13013,7 +13013,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H436" t="n">
         <v>3900</v>
@@ -13071,7 +13071,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G438" t="n">
-        <v>1.76468420028687</v>
+        <v>1.76468408107758</v>
       </c>
       <c r="H438" t="n">
         <v>8580</v>
@@ -13100,7 +13100,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>1.85030615329742</v>
+        <v>1.85030603408813</v>
       </c>
       <c r="H439" t="n">
         <v>46020</v>
@@ -13158,7 +13158,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G441" t="n">
-        <v>1.84595227241516</v>
+        <v>1.84595251083374</v>
       </c>
       <c r="H441" t="n">
         <v>780</v>
@@ -13216,7 +13216,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G443" t="n">
-        <v>1.87352573871613</v>
+        <v>1.87352561950684</v>
       </c>
       <c r="H443" t="n">
         <v>24180</v>
@@ -13361,7 +13361,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G448" t="n">
-        <v>1.93302595615387</v>
+        <v>1.93302571773529</v>
       </c>
       <c r="H448" t="n">
         <v>14040</v>
@@ -13390,7 +13390,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G449" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H449" t="n">
         <v>28860</v>
@@ -13448,7 +13448,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G451" t="n">
-        <v>1.86917221546173</v>
+        <v>1.86917197704315</v>
       </c>
       <c r="H451" t="n">
         <v>76440</v>
@@ -13477,7 +13477,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>1.85030615329742</v>
+        <v>1.85030603408813</v>
       </c>
       <c r="H452" t="n">
         <v>22620</v>
@@ -13506,7 +13506,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G453" t="n">
-        <v>1.84014773368835</v>
+        <v>1.84014761447906</v>
       </c>
       <c r="H453" t="n">
         <v>10140</v>
@@ -13535,7 +13535,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207460403442</v>
+        <v>1.87207448482513</v>
       </c>
       <c r="H454" t="n">
         <v>31200</v>
@@ -13564,7 +13564,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H455" t="n">
         <v>18720</v>
@@ -13622,7 +13622,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H457" t="n">
         <v>205920</v>
@@ -13651,7 +13651,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561114788055</v>
       </c>
       <c r="H458" t="n">
         <v>38220</v>
@@ -13680,7 +13680,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G459" t="n">
-        <v>1.88513541221619</v>
+        <v>1.88513553142548</v>
       </c>
       <c r="H459" t="n">
         <v>58500</v>
@@ -13738,7 +13738,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G461" t="n">
-        <v>1.87787938117981</v>
+        <v>1.8778795003891</v>
       </c>
       <c r="H461" t="n">
         <v>12480</v>
@@ -13767,7 +13767,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>1.92141580581665</v>
+        <v>1.92141604423523</v>
       </c>
       <c r="H462" t="n">
         <v>85800</v>
@@ -13912,7 +13912,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>1.90835499763489</v>
+        <v>1.90835511684418</v>
       </c>
       <c r="H467" t="n">
         <v>35100</v>
@@ -13970,7 +13970,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>1.92286729812622</v>
+        <v>1.92286717891693</v>
       </c>
       <c r="H469" t="n">
         <v>34320</v>
@@ -13999,7 +13999,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G470" t="n">
-        <v>1.90254998207092</v>
+        <v>1.90255010128021</v>
       </c>
       <c r="H470" t="n">
         <v>18720</v>
@@ -14086,7 +14086,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G473" t="n">
-        <v>1.90254998207092</v>
+        <v>1.90255010128021</v>
       </c>
       <c r="H473" t="n">
         <v>15600</v>
@@ -14115,7 +14115,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>1.8807817697525</v>
+        <v>1.88078165054321</v>
       </c>
       <c r="H474" t="n">
         <v>24180</v>
@@ -14144,7 +14144,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G475" t="n">
-        <v>1.9098060131073</v>
+        <v>1.90980613231659</v>
       </c>
       <c r="H475" t="n">
         <v>13260</v>
@@ -14173,7 +14173,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G476" t="n">
-        <v>1.87497699260712</v>
+        <v>1.87497711181641</v>
       </c>
       <c r="H476" t="n">
         <v>3120</v>
@@ -14202,7 +14202,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G477" t="n">
-        <v>1.82273304462433</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H477" t="n">
         <v>10920</v>
@@ -14231,7 +14231,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G478" t="n">
-        <v>1.82273304462433</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H478" t="n">
         <v>13260</v>
@@ -14260,7 +14260,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>1.82273304462433</v>
+        <v>1.82273316383362</v>
       </c>
       <c r="H479" t="n">
         <v>6240</v>
@@ -14289,7 +14289,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H480" t="n">
         <v>28080</v>
@@ -14318,7 +14318,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>1.72114741802216</v>
+        <v>1.72114753723145</v>
       </c>
       <c r="H481" t="n">
         <v>14820</v>
@@ -14347,7 +14347,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G482" t="n">
-        <v>1.80822086334229</v>
+        <v>1.808220744133</v>
       </c>
       <c r="H482" t="n">
         <v>25740</v>
@@ -14376,7 +14376,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G483" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H483" t="n">
         <v>7020</v>
@@ -14492,7 +14492,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G487" t="n">
-        <v>1.81837928295135</v>
+        <v>1.81837952136993</v>
       </c>
       <c r="H487" t="n">
         <v>2340</v>
@@ -14608,7 +14608,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G491" t="n">
-        <v>1.83869624137878</v>
+        <v>1.83869636058807</v>
       </c>
       <c r="H491" t="n">
         <v>9360</v>
@@ -14666,7 +14666,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G493" t="n">
-        <v>1.84159886837006</v>
+        <v>1.84159898757935</v>
       </c>
       <c r="H493" t="n">
         <v>49920</v>
@@ -14695,7 +14695,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G494" t="n">
-        <v>1.8807817697525</v>
+        <v>1.88078165054321</v>
       </c>
       <c r="H494" t="n">
         <v>35880</v>
@@ -14724,7 +14724,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H495" t="n">
         <v>34320</v>
@@ -14753,7 +14753,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H496" t="n">
         <v>50700</v>
@@ -14840,7 +14840,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G499" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H499" t="n">
         <v>10920</v>
@@ -14869,7 +14869,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G502" t="n">
-        <v>1.87062335014343</v>
+        <v>1.87062323093414</v>
       </c>
       <c r="H502" t="n">
         <v>10140</v>
@@ -14956,7 +14956,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H503" t="n">
         <v>7020</v>
@@ -15014,7 +15014,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G505" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H505" t="n">
         <v>780</v>
@@ -15043,7 +15043,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G506" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G507" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G510" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H510" t="n">
         <v>1560</v>
@@ -15188,7 +15188,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G511" t="n">
-        <v>1.82998931407928</v>
+        <v>1.82998919487</v>
       </c>
       <c r="H511" t="n">
         <v>3120</v>
@@ -15217,7 +15217,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G512" t="n">
-        <v>1.77629387378693</v>
+        <v>1.77629375457764</v>
       </c>
       <c r="H512" t="n">
         <v>3900</v>
@@ -15275,7 +15275,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G514" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H514" t="n">
         <v>4680</v>
@@ -15304,7 +15304,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H515" t="n">
         <v>9360</v>
@@ -15362,7 +15362,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>1.85030615329742</v>
+        <v>1.85030603408813</v>
       </c>
       <c r="H517" t="n">
         <v>16380</v>
@@ -15391,7 +15391,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G518" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H518" t="n">
         <v>10920</v>
@@ -15478,7 +15478,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G521" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H521" t="n">
         <v>780</v>
@@ -15507,7 +15507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H522" t="n">
         <v>3120</v>
@@ -15565,7 +15565,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H524" t="n">
         <v>7020</v>
@@ -15623,7 +15623,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G526" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H526" t="n">
         <v>11700</v>
@@ -15652,7 +15652,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G527" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H527" t="n">
         <v>8580</v>
@@ -15681,7 +15681,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>1.92286729812622</v>
+        <v>1.92286717891693</v>
       </c>
       <c r="H528" t="n">
         <v>124020</v>
@@ -15710,7 +15710,7 @@
         <v>2.75</v>
       </c>
       <c r="G529" t="n">
-        <v>1.99542820453644</v>
+        <v>1.99542832374573</v>
       </c>
       <c r="H529" t="n">
         <v>39780</v>
@@ -15739,7 +15739,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G530" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H530" t="n">
         <v>56940</v>
@@ -15768,7 +15768,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H531" t="n">
         <v>25740</v>
@@ -15797,7 +15797,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G532" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H532" t="n">
         <v>46020</v>
@@ -15826,7 +15826,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G533" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H533" t="n">
         <v>7800</v>
@@ -15855,7 +15855,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H534" t="n">
         <v>3900</v>
@@ -15884,7 +15884,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H535" t="n">
         <v>10920</v>
@@ -15913,7 +15913,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H536" t="n">
         <v>30420</v>
@@ -15971,7 +15971,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G538" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H538" t="n">
         <v>3120</v>
@@ -16087,7 +16087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H542" t="n">
         <v>19500</v>
@@ -16232,7 +16232,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G547" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H547" t="n">
         <v>8580</v>
@@ -16290,7 +16290,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G549" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H549" t="n">
         <v>23400</v>
@@ -16319,7 +16319,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H550" t="n">
         <v>10140</v>
@@ -16348,7 +16348,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H553" t="n">
         <v>8580</v>
@@ -16522,7 +16522,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H557" t="n">
         <v>7800</v>
@@ -16609,7 +16609,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H560" t="n">
         <v>4680</v>
@@ -16667,7 +16667,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G562" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H562" t="n">
         <v>3120</v>
@@ -16696,7 +16696,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G563" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H563" t="n">
         <v>4680</v>
@@ -16725,7 +16725,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G564" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H564" t="n">
         <v>59280</v>
@@ -16754,7 +16754,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H565" t="n">
         <v>4680</v>
@@ -16957,7 +16957,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G572" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H572" t="n">
         <v>12480</v>
@@ -16986,7 +16986,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G573" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H573" t="n">
         <v>34320</v>
@@ -17073,7 +17073,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H576" t="n">
         <v>22620</v>
@@ -17131,7 +17131,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H578" t="n">
         <v>1560</v>
@@ -17160,7 +17160,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G579" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H579" t="n">
         <v>7800</v>
@@ -17218,7 +17218,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G581" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H581" t="n">
         <v>3900</v>
@@ -17247,7 +17247,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H582" t="n">
         <v>17940</v>
@@ -17276,7 +17276,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H583" t="n">
         <v>8580</v>
@@ -17305,7 +17305,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H585" t="n">
         <v>105300</v>
@@ -17363,7 +17363,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H586" t="n">
         <v>7020</v>
@@ -17392,7 +17392,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H587" t="n">
         <v>7020</v>
@@ -17421,7 +17421,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G588" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H588" t="n">
         <v>6240</v>
@@ -17537,7 +17537,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H592" t="n">
         <v>4680</v>
@@ -17595,7 +17595,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H594" t="n">
         <v>4680</v>
@@ -17653,7 +17653,7 @@
         <v>2.25</v>
       </c>
       <c r="G596" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H596" t="n">
         <v>4680</v>
@@ -17682,7 +17682,7 @@
         <v>2.25</v>
       </c>
       <c r="G597" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H597" t="n">
         <v>15600</v>
@@ -17711,7 +17711,7 @@
         <v>2.25</v>
       </c>
       <c r="G598" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>2.25</v>
       </c>
       <c r="G600" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H600" t="n">
         <v>131820</v>
@@ -17885,7 +17885,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.69067180156708</v>
+        <v>1.69067192077637</v>
       </c>
       <c r="H604" t="n">
         <v>16380</v>
@@ -17943,7 +17943,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G606" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H606" t="n">
         <v>15600</v>
@@ -17972,7 +17972,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H607" t="n">
         <v>15600</v>
@@ -18001,7 +18001,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H608" t="n">
         <v>7020</v>
@@ -18059,7 +18059,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G610" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H610" t="n">
         <v>12480</v>
@@ -18175,7 +18175,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G614" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H614" t="n">
         <v>23400</v>
@@ -18581,7 +18581,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>1.48024499416351</v>
+        <v>1.48024475574493</v>
       </c>
       <c r="H628" t="n">
         <v>5460</v>
@@ -18610,7 +18610,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G629" t="n">
-        <v>1.51652526855469</v>
+        <v>1.51652538776398</v>
       </c>
       <c r="H629" t="n">
         <v>8580</v>
@@ -18958,7 +18958,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H641" t="n">
         <v>25740</v>
@@ -19016,7 +19016,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G643" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H643" t="n">
         <v>102180</v>
@@ -19074,7 +19074,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G645" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H645" t="n">
         <v>30420</v>
@@ -19132,7 +19132,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H647" t="n">
         <v>7800</v>
@@ -19190,7 +19190,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H649" t="n">
         <v>5460</v>
@@ -19306,7 +19306,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G653" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H653" t="n">
         <v>1560</v>
@@ -19335,7 +19335,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H654" t="n">
         <v>4680</v>
@@ -19625,7 +19625,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H664" t="n">
         <v>10140</v>
@@ -19654,7 +19654,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>1.61811077594757</v>
+        <v>1.61811089515686</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19683,7 +19683,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H666" t="n">
         <v>780</v>
@@ -19712,7 +19712,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H667" t="n">
         <v>1560</v>
@@ -19770,7 +19770,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H669" t="n">
         <v>5460</v>
@@ -19799,7 +19799,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>2.25</v>
       </c>
       <c r="G671" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H671" t="n">
         <v>7800</v>
@@ -19857,7 +19857,7 @@
         <v>2.25</v>
       </c>
       <c r="G672" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>2.25</v>
       </c>
       <c r="G673" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.58908653259277</v>
+        <v>1.58908641338348</v>
       </c>
       <c r="H674" t="n">
         <v>1560</v>
@@ -19944,7 +19944,7 @@
         <v>2.25</v>
       </c>
       <c r="G675" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H675" t="n">
         <v>2340</v>
@@ -19973,7 +19973,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H676" t="n">
         <v>3120</v>
@@ -20118,7 +20118,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G681" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H681" t="n">
         <v>3900</v>
@@ -20263,7 +20263,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>1.59634256362915</v>
+        <v>1.59634268283844</v>
       </c>
       <c r="H686" t="n">
         <v>5460</v>
@@ -20321,7 +20321,7 @@
         <v>2.25</v>
       </c>
       <c r="G688" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H688" t="n">
         <v>2340</v>
@@ -20437,7 +20437,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H692" t="n">
         <v>1560</v>
@@ -20466,7 +20466,7 @@
         <v>2.25</v>
       </c>
       <c r="G693" t="n">
-        <v>1.63262295722961</v>
+        <v>1.6326230764389</v>
       </c>
       <c r="H693" t="n">
         <v>1560</v>
@@ -20524,7 +20524,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H695" t="n">
         <v>46020</v>
@@ -20669,7 +20669,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G700" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H700" t="n">
         <v>49140</v>
@@ -20756,7 +20756,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H703" t="n">
         <v>14040</v>
@@ -20843,7 +20843,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G706" t="n">
-        <v>1.69792783260345</v>
+        <v>1.69792807102203</v>
       </c>
       <c r="H706" t="n">
         <v>18720</v>
@@ -20872,7 +20872,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G707" t="n">
-        <v>1.64713525772095</v>
+        <v>1.64713513851166</v>
       </c>
       <c r="H707" t="n">
         <v>19500</v>
@@ -20901,7 +20901,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G708" t="n">
-        <v>1.66164755821228</v>
+        <v>1.6616473197937</v>
       </c>
       <c r="H708" t="n">
         <v>5460</v>
@@ -21017,7 +21017,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G712" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H712" t="n">
         <v>28860</v>
@@ -21046,7 +21046,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G713" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H713" t="n">
         <v>17160</v>
@@ -21075,7 +21075,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H714" t="n">
         <v>48360</v>
@@ -21104,7 +21104,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H715" t="n">
         <v>20280</v>
@@ -21133,7 +21133,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G716" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H716" t="n">
         <v>18720</v>
@@ -21162,7 +21162,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H717" t="n">
         <v>9360</v>
@@ -21191,7 +21191,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80676960945129</v>
+        <v>1.806769490242</v>
       </c>
       <c r="H718" t="n">
         <v>4680</v>
@@ -21249,7 +21249,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G720" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H720" t="n">
         <v>18720</v>
@@ -21365,7 +21365,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H724" t="n">
         <v>1560</v>
@@ -21394,7 +21394,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H725" t="n">
         <v>1560</v>
@@ -21423,7 +21423,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G726" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H726" t="n">
         <v>2340</v>
@@ -21452,7 +21452,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H727" t="n">
         <v>2340</v>
@@ -21481,7 +21481,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H728" t="n">
         <v>780</v>
@@ -21510,7 +21510,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G729" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H729" t="n">
         <v>2340</v>
@@ -21539,7 +21539,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H730" t="n">
         <v>780</v>
@@ -21568,7 +21568,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H731" t="n">
         <v>5460</v>
@@ -21858,7 +21858,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G741" t="n">
-        <v>1.77048909664154</v>
+        <v>1.77048897743225</v>
       </c>
       <c r="H741" t="n">
         <v>103740</v>
@@ -21887,7 +21887,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>1.78500115871429</v>
+        <v>1.78500127792358</v>
       </c>
       <c r="H742" t="n">
         <v>780</v>
@@ -21916,7 +21916,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G743" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H743" t="n">
         <v>3120</v>
@@ -21945,7 +21945,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H744" t="n">
         <v>2340</v>
@@ -21974,7 +21974,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H745" t="n">
         <v>780</v>
@@ -22003,7 +22003,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H746" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H750" t="n">
         <v>2340</v>
@@ -22148,7 +22148,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G751" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H751" t="n">
         <v>7800</v>
@@ -22293,7 +22293,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G756" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H756" t="n">
         <v>3120</v>
@@ -22322,7 +22322,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H757" t="n">
         <v>2340</v>
@@ -22351,7 +22351,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G758" t="n">
-        <v>1.74872088432312</v>
+        <v>1.74872076511383</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H760" t="n">
         <v>7800</v>
@@ -22438,7 +22438,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -22467,7 +22467,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>1.7559769153595</v>
+        <v>1.75597679615021</v>
       </c>
       <c r="H762" t="n">
         <v>780</v>
@@ -22525,7 +22525,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G764" t="n">
-        <v>1.63987922668457</v>
+        <v>1.63987910747528</v>
       </c>
       <c r="H764" t="n">
         <v>4680</v>
@@ -22583,7 +22583,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G766" t="n">
-        <v>1.71969604492188</v>
+        <v>1.71969628334045</v>
       </c>
       <c r="H766" t="n">
         <v>780</v>
@@ -22641,7 +22641,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G768" t="n">
-        <v>1.79225742816925</v>
+        <v>1.79225730895996</v>
       </c>
       <c r="H768" t="n">
         <v>1560</v>
@@ -22699,7 +22699,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.83579385280609</v>
+        <v>1.83579397201538</v>
       </c>
       <c r="H770" t="n">
         <v>41340</v>
@@ -22757,7 +22757,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H772" t="n">
         <v>3120</v>
@@ -22786,7 +22786,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H773" t="n">
         <v>3120</v>
@@ -22815,7 +22815,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -22844,7 +22844,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G775" t="n">
-        <v>1.82853782176971</v>
+        <v>1.828537940979</v>
       </c>
       <c r="H775" t="n">
         <v>3120</v>
@@ -22873,7 +22873,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>1.85756206512451</v>
+        <v>1.8575621843338</v>
       </c>
       <c r="H776" t="n">
         <v>5460</v>
@@ -22902,7 +22902,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84304988384247</v>
+        <v>1.84305000305176</v>
       </c>
       <c r="H777" t="n">
         <v>3900</v>
@@ -22931,7 +22931,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G778" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H778" t="n">
         <v>2340</v>
@@ -22960,7 +22960,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>1.82128167152405</v>
+        <v>1.82128190994263</v>
       </c>
       <c r="H779" t="n">
         <v>780</v>
@@ -22989,7 +22989,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G780" t="n">
-        <v>1.89384281635284</v>
+        <v>1.89384257793427</v>
       </c>
       <c r="H780" t="n">
         <v>94380</v>
@@ -23018,7 +23018,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G781" t="n">
-        <v>1.91561126708984</v>
+        <v>1.91561114788055</v>
       </c>
       <c r="H781" t="n">
         <v>66300</v>
@@ -23076,7 +23076,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90835499763489</v>
+        <v>1.90835511684418</v>
       </c>
       <c r="H783" t="n">
         <v>11700</v>
@@ -23105,7 +23105,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G784" t="n">
-        <v>1.93737947940826</v>
+        <v>1.93737924098969</v>
       </c>
       <c r="H784" t="n">
         <v>8580</v>
@@ -23163,7 +23163,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>1.96640372276306</v>
+        <v>1.96640396118164</v>
       </c>
       <c r="H786" t="n">
         <v>26520</v>
@@ -23250,7 +23250,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G789" t="n">
-        <v>2.06073307991028</v>
+        <v>2.0607328414917</v>
       </c>
       <c r="H789" t="n">
         <v>39780</v>
@@ -23308,7 +23308,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H791" t="n">
         <v>10140</v>
@@ -23366,7 +23366,7 @@
         <v>2.75</v>
       </c>
       <c r="G793" t="n">
-        <v>1.99542820453644</v>
+        <v>1.99542832374573</v>
       </c>
       <c r="H793" t="n">
         <v>9360</v>
@@ -23453,7 +23453,7 @@
         <v>2.75</v>
       </c>
       <c r="G796" t="n">
-        <v>1.99542820453644</v>
+        <v>1.99542832374573</v>
       </c>
       <c r="H796" t="n">
         <v>8580</v>
@@ -23482,7 +23482,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G797" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H797" t="n">
         <v>7020</v>
@@ -23540,7 +23540,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>2.0099401473999</v>
+        <v>2.00994038581848</v>
       </c>
       <c r="H799" t="n">
         <v>3120</v>
@@ -23598,7 +23598,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.0534770488739</v>
+        <v>2.05347681045532</v>
       </c>
       <c r="H801" t="n">
         <v>23400</v>
@@ -23627,7 +23627,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G802" t="n">
-        <v>2.06798911094666</v>
+        <v>2.06798887252808</v>
       </c>
       <c r="H802" t="n">
         <v>20280</v>
@@ -23656,7 +23656,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>2.06798911094666</v>
+        <v>2.06798887252808</v>
       </c>
       <c r="H803" t="n">
         <v>24180</v>
@@ -23714,7 +23714,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G805" t="n">
-        <v>2.13329410552979</v>
+        <v>2.13329434394836</v>
       </c>
       <c r="H805" t="n">
         <v>59280</v>
@@ -23743,7 +23743,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>2.13329410552979</v>
+        <v>2.13329434394836</v>
       </c>
       <c r="H806" t="n">
         <v>7800</v>
@@ -23801,7 +23801,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G808" t="n">
-        <v>2.10426998138428</v>
+        <v>2.1042697429657</v>
       </c>
       <c r="H808" t="n">
         <v>16380</v>
@@ -23830,7 +23830,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G809" t="n">
-        <v>2.04622101783752</v>
+        <v>2.04622077941895</v>
       </c>
       <c r="H809" t="n">
         <v>69420</v>
@@ -23859,7 +23859,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G810" t="n">
-        <v>2.06798911094666</v>
+        <v>2.06798887252808</v>
       </c>
       <c r="H810" t="n">
         <v>17160</v>
@@ -24062,7 +24062,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>2.22036743164062</v>
+        <v>2.22036719322205</v>
       </c>
       <c r="H817" t="n">
         <v>12480</v>
@@ -24091,7 +24091,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G818" t="n">
-        <v>2.22036743164062</v>
+        <v>2.22036719322205</v>
       </c>
       <c r="H818" t="n">
         <v>20280</v>
@@ -24149,7 +24149,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>2.271160364151</v>
+        <v>2.27116012573242</v>
       </c>
       <c r="H820" t="n">
         <v>33540</v>
@@ -24265,7 +24265,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G824" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H824" t="n">
         <v>28860</v>
@@ -24323,7 +24323,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G826" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H826" t="n">
         <v>15600</v>
@@ -24352,7 +24352,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H827" t="n">
         <v>48360</v>
@@ -24410,7 +24410,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G829" t="n">
-        <v>2.30744051933289</v>
+        <v>2.30744075775146</v>
       </c>
       <c r="H829" t="n">
         <v>10140</v>
@@ -24468,7 +24468,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H831" t="n">
         <v>21060</v>
@@ -24903,7 +24903,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G846" t="n">
-        <v>2.30744051933289</v>
+        <v>2.30744075775146</v>
       </c>
       <c r="H846" t="n">
         <v>15073</v>
@@ -24990,7 +24990,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H849" t="n">
         <v>10904</v>
@@ -25019,7 +25019,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.30018448829651</v>
+        <v>2.30018472671509</v>
       </c>
       <c r="H850" t="n">
         <v>8210</v>
@@ -25077,7 +25077,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G852" t="n">
-        <v>2.29292845726013</v>
+        <v>2.29292869567871</v>
       </c>
       <c r="H852" t="n">
         <v>5016</v>
@@ -25164,7 +25164,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G855" t="n">
-        <v>2.271160364151</v>
+        <v>2.27116012573242</v>
       </c>
       <c r="H855" t="n">
         <v>1450</v>
@@ -25744,7 +25744,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>2.43805050849915</v>
+        <v>2.43805027008057</v>
       </c>
       <c r="H875" t="n">
         <v>10391</v>
@@ -25802,7 +25802,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G877" t="n">
-        <v>2.46707487106323</v>
+        <v>2.46707510948181</v>
       </c>
       <c r="H877" t="n">
         <v>33973</v>
@@ -25831,7 +25831,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G878" t="n">
-        <v>2.4960994720459</v>
+        <v>2.49609923362732</v>
       </c>
       <c r="H878" t="n">
         <v>17250</v>
@@ -26005,7 +26005,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>2.86616039276123</v>
+        <v>2.86616063117981</v>
       </c>
       <c r="H884" t="n">
         <v>57963</v>
@@ -26063,7 +26063,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G886" t="n">
-        <v>2.62670922279358</v>
+        <v>2.626708984375</v>
       </c>
       <c r="H886" t="n">
         <v>81513</v>
@@ -26092,7 +26092,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>2.71378231048584</v>
+        <v>2.71378254890442</v>
       </c>
       <c r="H887" t="n">
         <v>234047</v>
@@ -26121,7 +26121,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G888" t="n">
-        <v>2.71378231048584</v>
+        <v>2.71378254890442</v>
       </c>
       <c r="H888" t="n">
         <v>28982</v>
@@ -26150,7 +26150,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G889" t="n">
-        <v>2.78634333610535</v>
+        <v>2.78634309768677</v>
       </c>
       <c r="H889" t="n">
         <v>24677</v>
@@ -26179,7 +26179,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G890" t="n">
-        <v>2.85164833068848</v>
+        <v>2.85164856910706</v>
       </c>
       <c r="H890" t="n">
         <v>25193</v>
@@ -26208,7 +26208,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048951148987</v>
       </c>
       <c r="H891" t="n">
         <v>107136</v>
@@ -26411,7 +26411,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G898" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H898" t="n">
         <v>48999</v>
@@ -26701,7 +26701,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>2.69201397895813</v>
+        <v>2.69201421737671</v>
       </c>
       <c r="H908" t="n">
         <v>34513</v>
@@ -26759,7 +26759,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G910" t="n">
-        <v>2.77183127403259</v>
+        <v>2.77183103561401</v>
       </c>
       <c r="H910" t="n">
         <v>6976</v>
@@ -26817,7 +26817,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G912" t="n">
-        <v>2.78634333610535</v>
+        <v>2.78634309768677</v>
       </c>
       <c r="H912" t="n">
         <v>13525</v>
@@ -26846,7 +26846,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G913" t="n">
-        <v>2.85164833068848</v>
+        <v>2.85164856910706</v>
       </c>
       <c r="H913" t="n">
         <v>11840</v>
@@ -26875,7 +26875,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>2.69201397895813</v>
+        <v>2.69201421737671</v>
       </c>
       <c r="H914" t="n">
         <v>12512</v>
@@ -26904,7 +26904,7 @@
         <v>3.75</v>
       </c>
       <c r="G915" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H915" t="n">
         <v>13535</v>
@@ -27020,7 +27020,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G919" t="n">
-        <v>2.69927000999451</v>
+        <v>2.69927024841309</v>
       </c>
       <c r="H919" t="n">
         <v>25674</v>
@@ -27078,7 +27078,7 @@
         <v>3.75</v>
       </c>
       <c r="G921" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H921" t="n">
         <v>6560</v>
@@ -27136,7 +27136,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>2.7935996055603</v>
+        <v>2.79359912872314</v>
       </c>
       <c r="H923" t="n">
         <v>1820</v>
@@ -27165,7 +27165,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G924" t="n">
-        <v>2.95323395729065</v>
+        <v>2.95323371887207</v>
       </c>
       <c r="H924" t="n">
         <v>19608</v>
@@ -27281,7 +27281,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G928" t="n">
-        <v>3.02579474449158</v>
+        <v>3.02579498291016</v>
       </c>
       <c r="H928" t="n">
         <v>9639</v>
@@ -27310,7 +27310,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H929" t="n">
         <v>11777</v>
@@ -27339,7 +27339,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G930" t="n">
-        <v>2.94597768783569</v>
+        <v>2.94597744941711</v>
       </c>
       <c r="H930" t="n">
         <v>43272</v>
@@ -27368,7 +27368,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G931" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H931" t="n">
         <v>15776</v>
@@ -27455,7 +27455,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G934" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H934" t="n">
         <v>14713</v>
@@ -27484,7 +27484,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G935" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H935" t="n">
         <v>4741</v>
@@ -27513,7 +27513,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G936" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H936" t="n">
         <v>5875</v>
@@ -27571,7 +27571,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H938" t="n">
         <v>933</v>
@@ -27600,7 +27600,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G939" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H939" t="n">
         <v>11330</v>
@@ -27745,7 +27745,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H944" t="n">
         <v>64664</v>
@@ -27977,7 +27977,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G952" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H952" t="n">
         <v>4634</v>
@@ -28006,7 +28006,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H953" t="n">
         <v>9849</v>
@@ -28035,7 +28035,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>3.02579474449158</v>
+        <v>3.02579498291016</v>
       </c>
       <c r="H954" t="n">
         <v>10340</v>
@@ -28093,7 +28093,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G956" t="n">
-        <v>2.9677460193634</v>
+        <v>2.96774578094482</v>
       </c>
       <c r="H956" t="n">
         <v>4718</v>
@@ -28151,7 +28151,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048951148987</v>
       </c>
       <c r="H958" t="n">
         <v>3050</v>
@@ -28180,7 +28180,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G959" t="n">
-        <v>2.94597768783569</v>
+        <v>2.94597744941711</v>
       </c>
       <c r="H959" t="n">
         <v>1795</v>
@@ -28383,7 +28383,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H966" t="n">
         <v>14910</v>
@@ -28412,7 +28412,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G967" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H967" t="n">
         <v>21145</v>
@@ -28528,7 +28528,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H971" t="n">
         <v>186625</v>
@@ -28557,7 +28557,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939256668091</v>
       </c>
       <c r="H972" t="n">
         <v>174496</v>
@@ -28644,7 +28644,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H975" t="n">
         <v>34502</v>
@@ -28673,7 +28673,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G976" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H976" t="n">
         <v>15487</v>
@@ -28702,7 +28702,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G977" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H977" t="n">
         <v>16396</v>
@@ -28876,7 +28876,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G983" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H983" t="n">
         <v>21629</v>
@@ -28934,7 +28934,7 @@
         <v>4.5</v>
       </c>
       <c r="G985" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H985" t="n">
         <v>33365</v>
@@ -28963,7 +28963,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H986" t="n">
         <v>7440</v>
@@ -28992,7 +28992,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G987" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H987" t="n">
         <v>10030</v>
@@ -29050,7 +29050,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H989" t="n">
         <v>14239</v>
@@ -29079,7 +29079,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G990" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H990" t="n">
         <v>1190</v>
@@ -29108,7 +29108,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H991" t="n">
         <v>1571</v>
@@ -29195,7 +29195,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G994" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H994" t="n">
         <v>9450</v>
@@ -29253,7 +29253,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G996" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H996" t="n">
         <v>13997</v>
@@ -29282,7 +29282,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G997" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H997" t="n">
         <v>6558</v>
@@ -29311,7 +29311,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G998" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H998" t="n">
         <v>18950</v>
@@ -29427,7 +29427,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506368637085</v>
+        <v>3.34506320953369</v>
       </c>
       <c r="H1002" t="n">
         <v>39069</v>
@@ -29456,7 +29456,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506368637085</v>
+        <v>3.34506320953369</v>
       </c>
       <c r="H1003" t="n">
         <v>16302</v>
@@ -29601,7 +29601,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1008" t="n">
         <v>10505</v>
@@ -29659,7 +29659,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1010" t="n">
         <v>47398</v>
@@ -29746,7 +29746,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1013" t="n">
         <v>14477</v>
@@ -29804,7 +29804,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1015" t="n">
         <v>6208</v>
@@ -29833,7 +29833,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939256668091</v>
       </c>
       <c r="H1016" t="n">
         <v>5463</v>
@@ -29891,7 +29891,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1018" t="n">
         <v>5814</v>
@@ -30007,7 +30007,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1022" t="n">
         <v>5304</v>
@@ -30123,7 +30123,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1026" t="n">
         <v>9496</v>
@@ -30152,7 +30152,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1027" t="n">
         <v>3600</v>
@@ -30181,7 +30181,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1028" t="n">
         <v>12697</v>
@@ -30239,7 +30239,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1030" t="n">
         <v>4817</v>
@@ -30268,7 +30268,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1031" t="n">
         <v>6405</v>
@@ -30413,7 +30413,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1036" t="n">
         <v>14790</v>
@@ -30616,7 +30616,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1043" t="n">
         <v>7290</v>
@@ -30645,7 +30645,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1044" t="n">
         <v>14888</v>
@@ -30732,7 +30732,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1047" t="n">
         <v>7582</v>
@@ -30761,7 +30761,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1048" t="n">
         <v>47843</v>
@@ -30790,7 +30790,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.49744176864624</v>
+        <v>3.49744153022766</v>
       </c>
       <c r="H1049" t="n">
         <v>115874</v>
@@ -30877,7 +30877,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.46116089820862</v>
+        <v>3.46116065979004</v>
       </c>
       <c r="H1052" t="n">
         <v>14242</v>
@@ -31080,7 +31080,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1059" t="n">
         <v>7168</v>
@@ -31109,7 +31109,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1060" t="n">
         <v>5775</v>
@@ -31138,7 +31138,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1061" t="n">
         <v>16035</v>
@@ -31167,7 +31167,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1062" t="n">
         <v>7972</v>
@@ -31196,7 +31196,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.9677460193634</v>
+        <v>2.96774578094482</v>
       </c>
       <c r="H1063" t="n">
         <v>109571</v>
@@ -31341,7 +31341,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1068" t="n">
         <v>4927</v>
@@ -31457,7 +31457,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1072" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1072" t="n">
         <v>5534</v>
@@ -31486,7 +31486,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.81536793708801</v>
+        <v>2.81536769866943</v>
       </c>
       <c r="H1073" t="n">
         <v>20606</v>
@@ -31602,7 +31602,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048951148987</v>
       </c>
       <c r="H1077" t="n">
         <v>21146</v>
@@ -31660,7 +31660,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1079" t="n">
         <v>9861</v>
@@ -31689,7 +31689,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1080" t="n">
         <v>3234</v>
@@ -31718,7 +31718,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1081" t="n">
         <v>5600</v>
@@ -31834,7 +31834,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1085" t="n">
         <v>1250</v>
@@ -31863,7 +31863,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1086" t="n">
         <v>29157</v>
@@ -31892,7 +31892,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1087" t="n">
         <v>8039</v>
@@ -31950,7 +31950,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1089" t="n">
         <v>6562</v>
@@ -32066,7 +32066,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1093" t="n">
         <v>700</v>
@@ -32095,7 +32095,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1094" t="n">
         <v>2341</v>
@@ -32124,7 +32124,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1095" t="n">
         <v>2562</v>
@@ -32153,7 +32153,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1096" t="n">
         <v>5877</v>
@@ -32182,7 +32182,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1097" t="n">
         <v>5476</v>
@@ -32211,7 +32211,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1098" t="n">
         <v>550</v>
@@ -32269,7 +32269,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1100" t="n">
         <v>3580</v>
@@ -32298,7 +32298,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1101" t="n">
         <v>0</v>
@@ -32327,7 +32327,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1102" t="n">
         <v>1000</v>
@@ -32443,7 +32443,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1106" t="n">
         <v>13345</v>
@@ -32588,7 +32588,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1111" t="n">
         <v>3778</v>
@@ -32762,7 +32762,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.38134360313416</v>
+        <v>3.38134384155273</v>
       </c>
       <c r="H1117" t="n">
         <v>6259</v>
@@ -32791,7 +32791,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1118" t="n">
         <v>4473</v>
@@ -32820,7 +32820,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939256668091</v>
       </c>
       <c r="H1119" t="n">
         <v>5400</v>
@@ -32849,7 +32849,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1120" t="n">
         <v>1900</v>
@@ -32936,7 +32936,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1123" t="n">
         <v>7177</v>
@@ -33023,7 +33023,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1126" t="n">
         <v>19826</v>
@@ -33052,7 +33052,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1127" t="n">
         <v>34476</v>
@@ -33081,7 +33081,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1128" t="n">
         <v>56766</v>
@@ -33110,7 +33110,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1129" t="n">
         <v>46422</v>
@@ -33197,7 +33197,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1132" t="n">
         <v>48820</v>
@@ -33226,7 +33226,7 @@
         <v>5.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1133" t="n">
         <v>9842</v>
@@ -33313,7 +33313,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1136" t="n">
         <v>25075</v>
@@ -33371,7 +33371,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1138" t="n">
         <v>22247</v>
@@ -33400,7 +33400,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1139" t="n">
         <v>19815</v>
@@ -33429,7 +33429,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H1140" t="n">
         <v>3336</v>
@@ -33487,7 +33487,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1142" t="n">
         <v>37130</v>
@@ -33516,7 +33516,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1143" t="n">
         <v>640</v>
@@ -33545,7 +33545,7 @@
         <v>5.5</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1144" t="n">
         <v>14778</v>
@@ -33574,7 +33574,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1145" t="n">
         <v>22850</v>
@@ -33632,7 +33632,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1147" t="n">
         <v>3374</v>
@@ -33661,7 +33661,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1148" t="n">
         <v>8142</v>
@@ -33690,7 +33690,7 @@
         <v>5.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1149" t="n">
         <v>13231</v>
@@ -33719,7 +33719,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1150" t="n">
         <v>7492</v>
@@ -33777,7 +33777,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1152" t="n">
         <v>10478</v>
@@ -33806,7 +33806,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1153" t="n">
         <v>21813</v>
@@ -33835,7 +33835,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1154" t="n">
         <v>1906</v>
@@ -33864,7 +33864,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1155" t="n">
         <v>10260</v>
@@ -33893,7 +33893,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1156" t="n">
         <v>8378</v>
@@ -33922,7 +33922,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1157" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1157" t="n">
         <v>9285</v>
@@ -34009,7 +34009,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1160" t="n">
         <v>4001</v>
@@ -34038,7 +34038,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1161" t="n">
         <v>2059</v>
@@ -34067,7 +34067,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H1162" t="n">
         <v>100</v>
@@ -34125,7 +34125,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1164" t="n">
         <v>4764</v>
@@ -34154,7 +34154,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H1165" t="n">
         <v>2040</v>
@@ -34183,7 +34183,7 @@
         <v>5.5</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1166" t="n">
         <v>10671</v>
@@ -34473,7 +34473,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1176" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1176" t="n">
         <v>13558</v>
@@ -34531,7 +34531,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1178" t="n">
         <v>6879</v>
@@ -34618,7 +34618,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1181" t="n">
         <v>18443</v>
@@ -34647,7 +34647,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1182" t="n">
         <v>18197</v>
@@ -34676,7 +34676,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1183" t="n">
         <v>6092</v>
@@ -34705,7 +34705,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1184" t="n">
         <v>469</v>
@@ -34734,7 +34734,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1185" t="n">
         <v>36410</v>
@@ -34763,7 +34763,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1186" t="n">
         <v>7610</v>
@@ -34792,7 +34792,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1187" t="n">
         <v>3406</v>
@@ -34879,7 +34879,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1190" t="n">
         <v>7775</v>
@@ -34908,7 +34908,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1191" t="n">
         <v>4710</v>
@@ -34937,7 +34937,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1192" t="n">
         <v>5638</v>
@@ -35024,7 +35024,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1195" t="n">
         <v>3000</v>
@@ -35053,7 +35053,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1196" t="n">
         <v>1995</v>
@@ -35111,7 +35111,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1198" t="n">
         <v>50079</v>
@@ -35169,7 +35169,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1200" t="n">
         <v>27790</v>
@@ -35198,7 +35198,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1201" t="n">
         <v>24329</v>
@@ -35227,7 +35227,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1202" t="n">
         <v>6086</v>
@@ -35256,7 +35256,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1203" t="n">
-        <v>3.49744176864624</v>
+        <v>3.49744153022766</v>
       </c>
       <c r="H1203" t="n">
         <v>20815</v>
@@ -35285,7 +35285,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1204" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1204" t="n">
         <v>68407</v>
@@ -35372,7 +35372,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1207" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1207" t="n">
         <v>10763</v>
@@ -35401,7 +35401,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1208" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1208" t="n">
         <v>22103</v>
@@ -35517,7 +35517,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1212" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1212" t="n">
         <v>14075</v>
@@ -35546,7 +35546,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1213" t="n">
         <v>21223</v>
@@ -35604,7 +35604,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1215" t="n">
         <v>10438</v>
@@ -35749,7 +35749,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1220" t="n">
         <v>4577</v>
@@ -35865,7 +35865,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1224" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1224" t="n">
         <v>26401</v>
@@ -35894,7 +35894,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1225" t="n">
         <v>6466</v>
@@ -35981,7 +35981,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1228" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1228" t="n">
         <v>9230</v>
@@ -36097,7 +36097,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1232" t="n">
         <v>5283</v>
@@ -36126,7 +36126,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1233" t="n">
         <v>16931</v>
@@ -36155,7 +36155,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1234" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1234" t="n">
         <v>6553</v>
@@ -36184,7 +36184,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1235" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1235" t="n">
         <v>8561</v>
@@ -36213,7 +36213,7 @@
         <v>4.5</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1236" t="n">
         <v>2054</v>
@@ -36329,7 +36329,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1240" t="n">
         <v>7122</v>
@@ -36387,7 +36387,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1242" t="n">
         <v>6033</v>
@@ -36416,7 +36416,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1243" t="n">
         <v>5838</v>
@@ -36445,7 +36445,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1244" t="n">
         <v>3480</v>
@@ -36532,7 +36532,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1247" t="n">
         <v>11380</v>
@@ -36561,7 +36561,7 @@
         <v>4.5</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1248" t="n">
         <v>26609</v>
@@ -36590,7 +36590,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1249" t="n">
         <v>42994</v>
@@ -36648,7 +36648,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1251" t="n">
         <v>5066</v>
@@ -36677,7 +36677,7 @@
         <v>4.5</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1252" t="n">
         <v>1600</v>
@@ -36764,7 +36764,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1255" t="n">
         <v>4486</v>
@@ -36793,7 +36793,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1256" t="n">
         <v>1710</v>
@@ -36851,7 +36851,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1258" t="n">
         <v>64400</v>
@@ -36909,7 +36909,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1260" t="n">
         <v>6745</v>
@@ -37025,7 +37025,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1264" t="n">
         <v>81171</v>
@@ -37112,7 +37112,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1267" t="n">
         <v>3452</v>
@@ -37199,7 +37199,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1270" t="n">
         <v>4921</v>
@@ -37344,7 +37344,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1275" t="n">
         <v>10861</v>
@@ -37460,7 +37460,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1279" t="n">
         <v>7535</v>
@@ -37663,7 +37663,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1286" t="n">
         <v>5539</v>
@@ -37692,7 +37692,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1287" t="n">
         <v>16906</v>
@@ -37721,7 +37721,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1288" t="n">
         <v>12450</v>
@@ -37779,7 +37779,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1290" t="n">
         <v>1409</v>
@@ -37808,7 +37808,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1291" t="n">
         <v>5199</v>
@@ -37982,7 +37982,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1297" t="n">
         <v>1957</v>
@@ -38069,7 +38069,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1300" t="n">
         <v>5359</v>
@@ -38098,7 +38098,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1301" t="n">
         <v>10152</v>
@@ -38243,7 +38243,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1306" t="n">
         <v>6992</v>
@@ -38301,7 +38301,7 @@
         <v>4.5</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1308" t="n">
         <v>7301</v>
@@ -38330,7 +38330,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1309" t="n">
         <v>5998</v>
@@ -38359,7 +38359,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1310" t="n">
         <v>6756</v>
@@ -38388,7 +38388,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1311" t="n">
         <v>6454</v>
@@ -38417,7 +38417,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.21445345878601</v>
+        <v>3.21445322036743</v>
       </c>
       <c r="H1312" t="n">
         <v>6901</v>
@@ -38475,7 +38475,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1314" t="n">
         <v>3011</v>
@@ -38562,7 +38562,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1317" t="n">
         <v>5781</v>
@@ -38649,7 +38649,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1320" t="n">
         <v>1761</v>
@@ -38707,7 +38707,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1322" t="n">
         <v>9474</v>
@@ -38736,7 +38736,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1323" t="n">
         <v>4444</v>
@@ -38765,7 +38765,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1324" t="n">
         <v>1910</v>
@@ -38794,7 +38794,7 @@
         <v>4.5</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1325" t="n">
         <v>2200</v>
@@ -38852,7 +38852,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1327" t="n">
         <v>6300</v>
@@ -38910,7 +38910,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1329" t="n">
         <v>16178</v>
@@ -38997,7 +38997,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1332" t="n">
         <v>27465</v>
@@ -39055,7 +39055,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1334" t="n">
         <v>11250</v>
@@ -39084,7 +39084,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1335" t="n">
         <v>10710</v>
@@ -39113,7 +39113,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1336" t="n">
         <v>11184</v>
@@ -39200,7 +39200,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1339" t="n">
         <v>19456</v>
@@ -39229,7 +39229,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1340" t="n">
         <v>17409</v>
@@ -39606,7 +39606,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1353" t="n">
-        <v>2.9677460193634</v>
+        <v>2.96774578094482</v>
       </c>
       <c r="H1353" t="n">
         <v>5928</v>
@@ -39635,7 +39635,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.96048998832703</v>
+        <v>2.96048951148987</v>
       </c>
       <c r="H1354" t="n">
         <v>25565</v>
@@ -39780,7 +39780,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1359" t="n">
         <v>118</v>
@@ -40128,7 +40128,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1371" t="n">
         <v>4451</v>
@@ -40215,7 +40215,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1374" t="n">
         <v>10811</v>
@@ -40273,7 +40273,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1376" t="n">
         <v>2672</v>
@@ -40302,7 +40302,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1377" t="n">
         <v>2348</v>
@@ -40360,7 +40360,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1379" t="n">
         <v>54641</v>
@@ -40389,7 +40389,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1380" t="n">
         <v>16504</v>
@@ -40534,7 +40534,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1385" t="n">
         <v>11019</v>
@@ -40563,7 +40563,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1386" t="n">
         <v>3395</v>
@@ -40592,7 +40592,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1387" t="n">
         <v>5638</v>
@@ -40621,7 +40621,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1388" t="n">
         <v>11935</v>
@@ -40650,7 +40650,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1389" t="n">
         <v>9357</v>
@@ -40766,7 +40766,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1393" t="n">
         <v>5386</v>
@@ -40795,7 +40795,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1394" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1394" t="n">
         <v>6035</v>
@@ -40824,7 +40824,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1395" t="n">
         <v>1849</v>
@@ -40882,7 +40882,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1397" t="n">
         <v>4300</v>
@@ -40911,7 +40911,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1398" t="n">
         <v>620</v>
@@ -40969,7 +40969,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1400" t="n">
         <v>4767</v>
@@ -40998,7 +40998,7 @@
         <v>4.5</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1401" t="n">
         <v>951</v>
@@ -41056,7 +41056,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1403" t="n">
         <v>8875</v>
@@ -41085,7 +41085,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1404" t="n">
         <v>12771</v>
@@ -41172,7 +41172,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1407" t="n">
         <v>4650</v>
@@ -41259,7 +41259,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1410" t="n">
         <v>4956</v>
@@ -41375,7 +41375,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1414" t="n">
         <v>2111</v>
@@ -41433,7 +41433,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1416" t="n">
         <v>1050</v>
@@ -41491,7 +41491,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1418" t="n">
         <v>5000</v>
@@ -41549,7 +41549,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1420" t="n">
         <v>78</v>
@@ -41665,7 +41665,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1424" t="n">
         <v>4050</v>
@@ -41781,7 +41781,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1428" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1428" t="n">
         <v>3401</v>
@@ -41926,7 +41926,7 @@
         <v>4.5</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1433" t="n">
         <v>1489</v>
@@ -42100,7 +42100,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1439" t="n">
         <v>5734</v>
@@ -42129,7 +42129,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1440" t="n">
         <v>2550</v>
@@ -42158,7 +42158,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1441" t="n">
         <v>4620</v>
@@ -42187,7 +42187,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1442" t="n">
         <v>1448</v>
@@ -42332,7 +42332,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.28701448440552</v>
+        <v>3.2870147228241</v>
       </c>
       <c r="H1447" t="n">
         <v>3401</v>
@@ -42419,7 +42419,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1450" t="n">
         <v>6564</v>
@@ -42477,7 +42477,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H1452" t="n">
         <v>13411</v>
@@ -42506,7 +42506,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1453" t="n">
         <v>45648</v>
@@ -42564,7 +42564,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1455" t="n">
         <v>5451</v>
@@ -42593,7 +42593,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1456" t="n">
         <v>13978</v>
@@ -42622,7 +42622,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1457" t="n">
         <v>17253</v>
@@ -42651,7 +42651,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1458" t="n">
         <v>3676</v>
@@ -42738,7 +42738,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1461" t="n">
         <v>8936</v>
@@ -42767,7 +42767,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1462" t="n">
         <v>3505</v>
@@ -42796,7 +42796,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1463" t="n">
         <v>1065</v>
@@ -42854,7 +42854,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1465" t="n">
         <v>16590</v>
@@ -42883,7 +42883,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1466" t="n">
         <v>9378</v>
@@ -42912,7 +42912,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1467" t="n">
         <v>6370</v>
@@ -42941,7 +42941,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1468" t="n">
         <v>3765</v>
@@ -42970,7 +42970,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.27975845336914</v>
+        <v>3.27975821495056</v>
       </c>
       <c r="H1469" t="n">
         <v>39138</v>
@@ -42999,7 +42999,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1470" t="n">
         <v>35930</v>
@@ -43115,7 +43115,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1474" t="n">
         <v>1250</v>
@@ -43144,7 +43144,7 @@
         <v>4.5</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1475" t="n">
         <v>11700</v>
@@ -43405,7 +43405,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1484" t="n">
         <v>224</v>
@@ -43434,7 +43434,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1485" t="n">
         <v>14577</v>
@@ -43463,7 +43463,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.29427051544189</v>
+        <v>3.29427027702332</v>
       </c>
       <c r="H1486" t="n">
         <v>1746</v>
@@ -43492,7 +43492,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1487" t="n">
         <v>19033</v>
@@ -43521,7 +43521,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1488" t="n">
         <v>15813</v>
@@ -43579,7 +43579,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1490" t="n">
         <v>6932</v>
@@ -43695,7 +43695,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.43939208984375</v>
+        <v>3.43939256668091</v>
       </c>
       <c r="H1494" t="n">
         <v>44032</v>
@@ -43753,7 +43753,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1496" t="n">
         <v>18770</v>
@@ -43782,7 +43782,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1497" t="n">
         <v>8020</v>
@@ -43811,7 +43811,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1498" t="n">
         <v>13327</v>
@@ -43840,7 +43840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1499" t="n">
         <v>6935</v>
@@ -43869,7 +43869,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1500" t="n">
         <v>6069</v>
@@ -43898,7 +43898,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1501" t="n">
         <v>485</v>
@@ -43927,7 +43927,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1502" t="n">
         <v>5142</v>
@@ -43985,7 +43985,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1504" t="n">
         <v>13228</v>
@@ -44072,7 +44072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1507" t="n">
         <v>4706</v>
@@ -44101,7 +44101,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1508" t="n">
         <v>7146</v>
@@ -44159,7 +44159,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1510" t="n">
         <v>5436</v>
@@ -44217,7 +44217,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H1512" t="n">
         <v>4106</v>
@@ -44304,7 +44304,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1515" t="n">
         <v>2780</v>
@@ -44333,7 +44333,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1516" t="n">
         <v>1000</v>
@@ -44391,7 +44391,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1518" t="n">
         <v>2560</v>
@@ -44420,7 +44420,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1519" t="n">
         <v>7090</v>
@@ -44449,7 +44449,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1520" t="n">
         <v>1907</v>
@@ -44478,7 +44478,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1521" t="n">
         <v>1900</v>
@@ -44507,7 +44507,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1522" t="n">
         <v>0</v>
@@ -44536,7 +44536,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1523" t="n">
         <v>1405</v>
@@ -44594,7 +44594,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1525" t="n">
         <v>4339</v>
@@ -44623,7 +44623,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1526" t="n">
         <v>0</v>
@@ -44652,7 +44652,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1527" t="n">
         <v>5409</v>
@@ -44710,7 +44710,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1529" t="n">
         <v>7906</v>
@@ -44739,7 +44739,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1530" t="n">
         <v>6286</v>
@@ -44768,7 +44768,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1531" t="n">
         <v>8224</v>
@@ -44797,7 +44797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1532" t="n">
         <v>5293</v>
@@ -44855,7 +44855,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1534" t="n">
         <v>5194</v>
@@ -44884,7 +44884,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1535" t="n">
         <v>0</v>
@@ -45000,7 +45000,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1539" t="n">
         <v>12112</v>
@@ -45058,7 +45058,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1541" t="n">
         <v>1000</v>
@@ -45087,7 +45087,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1542" t="n">
         <v>1515</v>
@@ -45116,7 +45116,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1543" t="n">
         <v>1010</v>
@@ -45145,7 +45145,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1544" t="n">
         <v>3200</v>
@@ -45174,7 +45174,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1545" t="n">
         <v>400</v>
@@ -45261,7 +45261,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1548" t="n">
         <v>3525</v>
@@ -45290,7 +45290,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1549" t="n">
         <v>4878</v>
@@ -45319,7 +45319,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1550" t="n">
         <v>3930</v>
@@ -45348,7 +45348,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1551" t="n">
         <v>3888</v>
@@ -45377,7 +45377,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1552" t="n">
         <v>900</v>
@@ -45406,7 +45406,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1553" t="n">
         <v>2243</v>
@@ -45435,7 +45435,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1554" t="n">
         <v>3630</v>
@@ -45464,7 +45464,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1555" t="n">
         <v>10</v>
@@ -45493,7 +45493,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1556" t="n">
         <v>255</v>
@@ -45522,7 +45522,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1557" t="n">
         <v>12141</v>
@@ -45609,7 +45609,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1560" t="n">
         <v>5958</v>
@@ -45638,7 +45638,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1561" t="n">
         <v>1450</v>
@@ -45725,7 +45725,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.50469732284546</v>
+        <v>3.50469756126404</v>
       </c>
       <c r="H1564" t="n">
         <v>4461</v>
@@ -45754,7 +45754,7 @@
         <v>4.5</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1565" t="n">
         <v>28829</v>
@@ -45783,7 +45783,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1566" t="n">
         <v>8114</v>
@@ -45870,7 +45870,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.39585566520691</v>
+        <v>3.39585614204407</v>
       </c>
       <c r="H1569" t="n">
         <v>5281</v>
@@ -45928,7 +45928,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1571" t="n">
         <v>4522</v>
@@ -45986,7 +45986,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1573" t="n">
         <v>2602</v>
@@ -46044,7 +46044,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1575" t="n">
         <v>3340</v>
@@ -46073,7 +46073,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1576" t="n">
         <v>3343</v>
@@ -46131,7 +46131,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1578" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1578" t="n">
         <v>5593</v>
@@ -46160,7 +46160,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1579" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1579" t="n">
         <v>25968</v>
@@ -46189,7 +46189,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1580" t="n">
         <v>4781</v>
@@ -46218,7 +46218,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1581" t="n">
         <v>3800</v>
@@ -46305,7 +46305,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1584" t="n">
         <v>3846</v>
@@ -46334,7 +46334,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1585" t="n">
         <v>7040</v>
@@ -46363,7 +46363,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1586" t="n">
         <v>8413</v>
@@ -46421,7 +46421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1588" t="n">
         <v>169</v>
@@ -46450,7 +46450,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1589" t="n">
         <v>3324</v>
@@ -46566,7 +46566,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1593" t="n">
         <v>19445</v>
@@ -46595,7 +46595,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.68609976768494</v>
+        <v>3.68610000610352</v>
       </c>
       <c r="H1594" t="n">
         <v>4764</v>
@@ -46624,7 +46624,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.71512413024902</v>
+        <v>3.7151243686676</v>
       </c>
       <c r="H1595" t="n">
         <v>1760</v>
@@ -46711,7 +46711,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1598" t="n">
         <v>2389</v>
@@ -46740,7 +46740,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.70061230659485</v>
+        <v>3.70061206817627</v>
       </c>
       <c r="H1599" t="n">
         <v>2133</v>
@@ -46798,7 +46798,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H1601" t="n">
         <v>30682</v>
@@ -46827,7 +46827,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H1602" t="n">
         <v>2064</v>
@@ -46885,7 +46885,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H1604" t="n">
         <v>786</v>
@@ -47001,7 +47001,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1608" t="n">
         <v>2503</v>
@@ -47030,7 +47030,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.67158770561218</v>
+        <v>3.67158794403076</v>
       </c>
       <c r="H1609" t="n">
         <v>1293</v>
@@ -47146,7 +47146,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.46116089820862</v>
+        <v>3.46116065979004</v>
       </c>
       <c r="H1613" t="n">
         <v>14628</v>
@@ -47175,7 +47175,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.43213653564453</v>
+        <v>3.43213629722595</v>
       </c>
       <c r="H1614" t="n">
         <v>7016</v>
@@ -47262,7 +47262,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1617" t="n">
         <v>20</v>
@@ -47291,7 +47291,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.54097819328308</v>
+        <v>3.5409779548645</v>
       </c>
       <c r="H1618" t="n">
         <v>4580</v>
@@ -47378,7 +47378,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1621" t="n">
         <v>3604</v>
@@ -47436,7 +47436,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1623" t="n">
         <v>400</v>
@@ -47465,7 +47465,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1624" t="n">
         <v>3315</v>
@@ -47494,7 +47494,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1625" t="n">
         <v>1136</v>
@@ -47523,7 +47523,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1626" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1626" t="n">
         <v>830</v>
@@ -47552,7 +47552,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.5845148563385</v>
+        <v>3.58451461791992</v>
       </c>
       <c r="H1627" t="n">
         <v>0</v>
@@ -47581,7 +47581,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1628" t="n">
         <v>1040</v>
@@ -47668,7 +47668,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>3.38860011100769</v>
+        <v>3.38859987258911</v>
       </c>
       <c r="H1631" t="n">
         <v>7208</v>
@@ -47784,7 +47784,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1635" t="n">
-        <v>3.38134360313416</v>
+        <v>3.38134384155273</v>
       </c>
       <c r="H1635" t="n">
         <v>170</v>
@@ -47900,7 +47900,7 @@
         <v>4.5</v>
       </c>
       <c r="G1639" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1639" t="n">
         <v>2094</v>
@@ -48045,7 +48045,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1644" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1644" t="n">
         <v>1681</v>
@@ -48132,7 +48132,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1647" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1647" t="n">
         <v>817</v>
@@ -48161,7 +48161,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H1648" t="n">
         <v>3850</v>
@@ -48277,7 +48277,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1652" t="n">
         <v>400</v>
@@ -48335,7 +48335,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1654" t="n">
-        <v>3.1999409198761</v>
+        <v>3.19994115829468</v>
       </c>
       <c r="H1654" t="n">
         <v>300</v>
@@ -48364,7 +48364,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1655" t="n">
-        <v>3.32329511642456</v>
+        <v>3.3232946395874</v>
       </c>
       <c r="H1655" t="n">
         <v>5550</v>
@@ -48451,7 +48451,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1658" t="n">
-        <v>3.49018526077271</v>
+        <v>3.49018549919128</v>
       </c>
       <c r="H1658" t="n">
         <v>18496</v>
@@ -48480,7 +48480,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1659" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1659" t="n">
         <v>230</v>
@@ -48509,7 +48509,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1660" t="n">
-        <v>3.51195383071899</v>
+        <v>3.51195359230042</v>
       </c>
       <c r="H1660" t="n">
         <v>600</v>
@@ -48538,7 +48538,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>3.61353921890259</v>
+        <v>3.61353898048401</v>
       </c>
       <c r="H1661" t="n">
         <v>2400</v>
@@ -48625,7 +48625,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1664" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1664" t="n">
         <v>2042</v>
@@ -48654,7 +48654,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1665" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1665" t="n">
         <v>900</v>
@@ -48683,7 +48683,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1666" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1666" t="n">
         <v>0</v>
@@ -48712,7 +48712,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1667" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1667" t="n">
         <v>0</v>
@@ -48973,7 +48973,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1676" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1676" t="n">
         <v>260</v>
@@ -49002,7 +49002,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1677" t="n">
-        <v>3.6425633430481</v>
+        <v>3.64256381988525</v>
       </c>
       <c r="H1677" t="n">
         <v>4660</v>
@@ -49031,7 +49031,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1678" t="n">
-        <v>3.65707564353943</v>
+        <v>3.65707588195801</v>
       </c>
       <c r="H1678" t="n">
         <v>5800</v>
@@ -49147,7 +49147,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1682" t="n">
-        <v>3.5482337474823</v>
+        <v>3.54823422431946</v>
       </c>
       <c r="H1682" t="n">
         <v>1533</v>
@@ -49205,7 +49205,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1684" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1684" t="n">
         <v>600</v>
@@ -49292,7 +49292,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="n">
-        <v>3.57725834846497</v>
+        <v>3.57725858688354</v>
       </c>
       <c r="H1687" t="n">
         <v>994</v>
@@ -49350,7 +49350,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.57000231742859</v>
+        <v>3.57000255584717</v>
       </c>
       <c r="H1689" t="n">
         <v>2005</v>
@@ -49379,7 +49379,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1690" t="n">
-        <v>3.57000231742859</v>
+        <v>3.57000255584717</v>
       </c>
       <c r="H1690" t="n">
         <v>100</v>
@@ -49524,7 +49524,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1695" t="n">
         <v>17559</v>
@@ -49553,7 +49553,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1696" t="n">
         <v>1050</v>
@@ -49582,7 +49582,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1697" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1697" t="n">
         <v>887</v>
@@ -49611,7 +49611,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1698" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1698" t="n">
         <v>450</v>
@@ -49640,7 +49640,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1699" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1699" t="n">
         <v>800</v>
@@ -49669,7 +49669,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.51920986175537</v>
+        <v>3.51920962333679</v>
       </c>
       <c r="H1700" t="n">
         <v>50</v>
@@ -49698,7 +49698,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1701" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1701" t="n">
         <v>50</v>
@@ -49727,7 +49727,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1702" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1702" t="n">
         <v>666</v>
@@ -49756,7 +49756,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1703" t="n">
-        <v>3.37408757209778</v>
+        <v>3.37408781051636</v>
       </c>
       <c r="H1703" t="n">
         <v>14671</v>
@@ -49785,7 +49785,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1704" t="n">
-        <v>3.47567319869995</v>
+        <v>3.47567296028137</v>
       </c>
       <c r="H1704" t="n">
         <v>18456</v>
@@ -49872,7 +49872,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1707" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1707" t="n">
         <v>3315</v>
@@ -49930,7 +49930,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1709" t="n">
-        <v>3.17817306518555</v>
+        <v>3.17817282676697</v>
       </c>
       <c r="H1709" t="n">
         <v>274</v>
@@ -49959,7 +49959,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1710" t="n">
         <v>97360</v>
@@ -50046,7 +50046,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1713" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1713" t="n">
         <v>4795</v>
@@ -50075,7 +50075,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1714" t="n">
-        <v>3.24347758293152</v>
+        <v>3.2434778213501</v>
       </c>
       <c r="H1714" t="n">
         <v>805</v>
@@ -50133,7 +50133,7 @@
         <v>4.5</v>
       </c>
       <c r="G1716" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1716" t="n">
         <v>1525</v>
@@ -50162,7 +50162,7 @@
         <v>4.5</v>
       </c>
       <c r="G1717" t="n">
-        <v>3.26524591445923</v>
+        <v>3.26524615287781</v>
       </c>
       <c r="H1717" t="n">
         <v>0</v>
@@ -50191,7 +50191,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1718" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1718" t="n">
         <v>120</v>
@@ -50220,7 +50220,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1719" t="n">
-        <v>3.23622155189514</v>
+        <v>3.23622179031372</v>
       </c>
       <c r="H1719" t="n">
         <v>0</v>
@@ -50278,7 +50278,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1721" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1721" t="n">
         <v>1702</v>
@@ -50307,7 +50307,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1722" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1722" t="n">
         <v>1741</v>
@@ -50336,7 +50336,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1723" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1723" t="n">
         <v>2060</v>
@@ -50365,7 +50365,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1724" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1724" t="n">
         <v>821</v>
@@ -50568,7 +50568,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1731" t="n">
-        <v>3.22896552085876</v>
+        <v>3.22896575927734</v>
       </c>
       <c r="H1731" t="n">
         <v>1300</v>
@@ -50713,7 +50713,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1736" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1736" t="n">
         <v>49</v>
@@ -50800,7 +50800,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1739" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1739" t="n">
         <v>1064</v>
@@ -50829,7 +50829,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1740" t="n">
-        <v>3.14189219474792</v>
+        <v>3.1418924331665</v>
       </c>
       <c r="H1740" t="n">
         <v>751</v>
@@ -50858,7 +50858,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1741" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1741" t="n">
         <v>2248</v>
@@ -50974,7 +50974,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1745" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1745" t="n">
         <v>8879</v>
@@ -51003,7 +51003,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1746" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1746" t="n">
         <v>12</v>
@@ -51032,7 +51032,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1747" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1747" t="n">
         <v>0</v>
@@ -51090,7 +51090,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.03305053710938</v>
+        <v>3.03305077552795</v>
       </c>
       <c r="H1749" t="n">
         <v>287</v>
@@ -51119,7 +51119,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.9677460193634</v>
+        <v>2.96774578094482</v>
       </c>
       <c r="H1750" t="n">
         <v>3120</v>
@@ -51148,7 +51148,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.81536793708801</v>
+        <v>2.81536769866943</v>
       </c>
       <c r="H1751" t="n">
         <v>9700</v>
@@ -51206,7 +51206,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.85890436172485</v>
+        <v>2.85890460014343</v>
       </c>
       <c r="H1753" t="n">
         <v>5741</v>
@@ -51467,7 +51467,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.77908730506897</v>
+        <v>2.77908706665039</v>
       </c>
       <c r="H1762" t="n">
         <v>3130</v>
@@ -51554,7 +51554,7 @@
         <v>3.75</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.72103834152222</v>
+        <v>2.7210385799408</v>
       </c>
       <c r="H1765" t="n">
         <v>1347</v>
@@ -51612,7 +51612,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.02579474449158</v>
+        <v>3.02579498291016</v>
       </c>
       <c r="H1767" t="n">
         <v>4229</v>
@@ -51873,7 +51873,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H1776" t="n">
         <v>4594</v>
@@ -52047,7 +52047,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1782" t="n">
         <v>1781</v>
@@ -52105,7 +52105,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.12738037109375</v>
+        <v>3.12738013267517</v>
       </c>
       <c r="H1784" t="n">
         <v>2505</v>
@@ -52424,7 +52424,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.1926851272583</v>
+        <v>3.19268536567688</v>
       </c>
       <c r="H1795" t="n">
         <v>6895</v>
@@ -52453,7 +52453,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1796" t="n">
         <v>6947</v>
@@ -52569,7 +52569,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.05481910705566</v>
+        <v>3.05481934547424</v>
       </c>
       <c r="H1800" t="n">
         <v>1535</v>
@@ -52656,7 +52656,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1803" t="n">
         <v>3480</v>
@@ -52685,7 +52685,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1804" t="n">
         <v>600</v>
@@ -52714,7 +52714,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.11286807060242</v>
+        <v>3.11286783218384</v>
       </c>
       <c r="H1805" t="n">
         <v>2591</v>
@@ -52743,7 +52743,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.0983555316925</v>
+        <v>3.09835577011108</v>
       </c>
       <c r="H1806" t="n">
         <v>3543</v>
@@ -52801,7 +52801,7 @@
         <v>5.5</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1808" t="n">
         <v>262088</v>
@@ -52859,7 +52859,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1810" t="n">
         <v>185319</v>
@@ -52917,7 +52917,7 @@
         <v>5.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1812" t="n">
         <v>34810</v>
@@ -52946,7 +52946,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1813" t="n">
         <v>154634</v>
@@ -52975,7 +52975,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.13597822189331</v>
+        <v>4.13597774505615</v>
       </c>
       <c r="H1814" t="n">
         <v>56145</v>
@@ -53062,7 +53062,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1817" t="n">
         <v>38559</v>
@@ -53091,7 +53091,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1818" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1818" t="n">
         <v>134056</v>
@@ -53120,7 +53120,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1819" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H1819" t="n">
         <v>74184</v>
@@ -53178,7 +53178,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.97634410858154</v>
+        <v>3.9763445854187</v>
       </c>
       <c r="H1821" t="n">
         <v>18995</v>
@@ -53207,7 +53207,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1822" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1822" t="n">
         <v>12683</v>
@@ -53265,7 +53265,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1824" t="n">
-        <v>3.93280744552612</v>
+        <v>3.93280792236328</v>
       </c>
       <c r="H1824" t="n">
         <v>24046</v>
@@ -53352,7 +53352,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.25207614898682</v>
+        <v>4.25207662582397</v>
       </c>
       <c r="H1827" t="n">
         <v>11550</v>
@@ -53497,7 +53497,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H1832" t="n">
         <v>41917</v>
@@ -53526,7 +53526,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.23756408691406</v>
+        <v>4.23756456375122</v>
       </c>
       <c r="H1833" t="n">
         <v>51308</v>
@@ -53555,7 +53555,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.23756408691406</v>
+        <v>4.23756456375122</v>
       </c>
       <c r="H1834" t="n">
         <v>45922</v>
@@ -53584,7 +53584,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1835" t="n">
         <v>12200</v>
@@ -53642,7 +53642,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.13597822189331</v>
+        <v>4.13597774505615</v>
       </c>
       <c r="H1837" t="n">
         <v>9877</v>
@@ -53671,7 +53671,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1838" t="n">
         <v>12403</v>
@@ -53700,7 +53700,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1839" t="n">
         <v>11869</v>
@@ -53758,7 +53758,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1841" t="n">
         <v>745</v>
@@ -53787,7 +53787,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.13597822189331</v>
+        <v>4.13597774505615</v>
       </c>
       <c r="H1842" t="n">
         <v>5600</v>
@@ -53816,7 +53816,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1843" t="n">
         <v>36831</v>
@@ -53845,7 +53845,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H1844" t="n">
         <v>7782</v>
@@ -53903,7 +53903,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1846" t="n">
         <v>41545</v>
@@ -54164,7 +54164,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1855" t="n">
         <v>14520</v>
@@ -54222,7 +54222,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>4.44073486328125</v>
+        <v>4.44073438644409</v>
       </c>
       <c r="H1857" t="n">
         <v>22756</v>
@@ -54338,7 +54338,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1861" t="n">
-        <v>4.28110027313232</v>
+        <v>4.28110074996948</v>
       </c>
       <c r="H1861" t="n">
         <v>43805</v>
@@ -54367,7 +54367,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H1862" t="n">
         <v>7193</v>
@@ -54396,7 +54396,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.20853996276855</v>
+        <v>4.2085394859314</v>
       </c>
       <c r="H1863" t="n">
         <v>33360</v>
@@ -54425,7 +54425,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1864" t="n">
-        <v>4.17951536178589</v>
+        <v>4.17951488494873</v>
       </c>
       <c r="H1864" t="n">
         <v>18040</v>
@@ -54570,7 +54570,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1869" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H1869" t="n">
         <v>7070</v>
@@ -54802,7 +54802,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1877" t="n">
         <v>12120</v>
@@ -54831,7 +54831,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1878" t="n">
         <v>12000</v>
@@ -54860,7 +54860,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1879" t="n">
         <v>43513</v>
@@ -54947,7 +54947,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1882" t="n">
         <v>5633</v>
@@ -54976,7 +54976,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H1883" t="n">
         <v>9022</v>
@@ -55005,7 +55005,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1884" t="n">
         <v>4100</v>
@@ -55034,7 +55034,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H1885" t="n">
         <v>5</v>
@@ -55150,7 +55150,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.0198802947998</v>
+        <v>4.01988077163696</v>
       </c>
       <c r="H1889" t="n">
         <v>16712</v>
@@ -55208,7 +55208,7 @@
         <v>5.5</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H1891" t="n">
         <v>22700</v>
@@ -55295,7 +55295,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1894" t="n">
-        <v>4.28110027313232</v>
+        <v>4.28110074996948</v>
       </c>
       <c r="H1894" t="n">
         <v>66745</v>
@@ -55382,7 +55382,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1897" t="n">
-        <v>4.44073486328125</v>
+        <v>4.44073438644409</v>
       </c>
       <c r="H1897" t="n">
         <v>33014</v>
@@ -55411,7 +55411,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.45524740219116</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H1898" t="n">
         <v>11695</v>
@@ -55556,7 +55556,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1903" t="n">
         <v>21319</v>
@@ -55759,7 +55759,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1910" t="n">
         <v>20341</v>
@@ -55817,7 +55817,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1912" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1912" t="n">
         <v>32655</v>
@@ -55875,7 +55875,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H1914" t="n">
         <v>11300</v>
@@ -55904,7 +55904,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.542320728302</v>
+        <v>4.54232025146484</v>
       </c>
       <c r="H1915" t="n">
         <v>6100</v>
@@ -55962,7 +55962,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H1917" t="n">
         <v>18820</v>
@@ -56049,7 +56049,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1920" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1920" t="n">
         <v>99275</v>
@@ -56107,7 +56107,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1922" t="n">
         <v>46575</v>
@@ -56194,7 +56194,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1925" t="n">
         <v>43840</v>
@@ -56223,7 +56223,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1926" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1926" t="n">
         <v>32624</v>
@@ -56252,7 +56252,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H1927" t="n">
         <v>15606</v>
@@ -56281,7 +56281,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1928" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1928" t="n">
         <v>36250</v>
@@ -56310,7 +56310,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1929" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1929" t="n">
         <v>8594</v>
@@ -56339,7 +56339,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1930" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1930" t="n">
         <v>9421</v>
@@ -56368,7 +56368,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1931" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H1931" t="n">
         <v>77323</v>
@@ -56629,7 +56629,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1940" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H1940" t="n">
         <v>12318</v>
@@ -58891,7 +58891,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.60036897659302</v>
+        <v>4.60036945343018</v>
       </c>
       <c r="H2018" t="n">
         <v>92013</v>
@@ -58949,7 +58949,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.542320728302</v>
+        <v>4.54232025146484</v>
       </c>
       <c r="H2020" t="n">
         <v>29342</v>
@@ -59036,7 +59036,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.26658821105957</v>
+        <v>4.26658868789673</v>
       </c>
       <c r="H2023" t="n">
         <v>15139</v>
@@ -59239,7 +59239,7 @@
         <v>5.5</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.99085640907288</v>
+        <v>3.99085664749146</v>
       </c>
       <c r="H2030" t="n">
         <v>85194</v>
@@ -59297,7 +59297,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.97634410858154</v>
+        <v>3.9763445854187</v>
       </c>
       <c r="H2032" t="n">
         <v>7326</v>
@@ -59355,7 +59355,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2034" t="n">
         <v>62502</v>
@@ -59384,7 +59384,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2035" t="n">
         <v>25964</v>
@@ -59413,7 +59413,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2036" t="n">
         <v>14916</v>
@@ -59442,7 +59442,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2037" t="n">
         <v>19540</v>
@@ -59471,7 +59471,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2038" t="n">
         <v>15489</v>
@@ -59500,7 +59500,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2039" t="n">
         <v>9796</v>
@@ -59529,7 +59529,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2040" t="n">
         <v>11666</v>
@@ -59558,7 +59558,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H2041" t="n">
         <v>5845</v>
@@ -59645,7 +59645,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2044" t="n">
         <v>13762</v>
@@ -59674,7 +59674,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2045" t="n">
         <v>12427</v>
@@ -59703,7 +59703,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H2046" t="n">
         <v>11724</v>
@@ -59732,7 +59732,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.91829562187195</v>
+        <v>3.91829538345337</v>
       </c>
       <c r="H2047" t="n">
         <v>8651</v>
@@ -59761,7 +59761,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.87475895881653</v>
+        <v>3.87475848197937</v>
       </c>
       <c r="H2048" t="n">
         <v>18302</v>
@@ -59790,7 +59790,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2049" t="n">
         <v>16940</v>
@@ -59819,7 +59819,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2050" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2050" t="n">
         <v>13500</v>
@@ -59848,7 +59848,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2051" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2051" t="n">
         <v>1800</v>
@@ -59877,7 +59877,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2052" t="n">
-        <v>3.8602466583252</v>
+        <v>3.86024641990662</v>
       </c>
       <c r="H2052" t="n">
         <v>5484</v>
@@ -59906,7 +59906,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2053" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2053" t="n">
         <v>2480</v>
@@ -59935,7 +59935,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2054" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2054" t="n">
         <v>6321</v>
@@ -59964,7 +59964,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2055" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2055" t="n">
         <v>1020</v>
@@ -59993,7 +59993,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2056" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2056" t="n">
         <v>0</v>
@@ -60022,7 +60022,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2057" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2057" t="n">
         <v>1050</v>
@@ -60051,7 +60051,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2058" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2058" t="n">
         <v>1525</v>
@@ -60080,7 +60080,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2059" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2059" t="n">
         <v>800</v>
@@ -60138,7 +60138,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2061" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2061" t="n">
         <v>122</v>
@@ -60196,7 +60196,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2063" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2063" t="n">
         <v>12069</v>
@@ -60225,7 +60225,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2064" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2064" t="n">
         <v>1038</v>
@@ -60254,7 +60254,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2065" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2065" t="n">
         <v>1000</v>
@@ -60283,7 +60283,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2066" t="n">
-        <v>3.83122253417969</v>
+        <v>3.83122229576111</v>
       </c>
       <c r="H2066" t="n">
         <v>5374</v>
@@ -60312,7 +60312,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2067" t="n">
-        <v>3.81670999526978</v>
+        <v>3.81671023368835</v>
       </c>
       <c r="H2067" t="n">
         <v>1</v>
@@ -60399,7 +60399,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2070" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2070" t="n">
         <v>7354</v>
@@ -60428,7 +60428,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2071" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2071" t="n">
         <v>380</v>
@@ -60457,7 +60457,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2072" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2072" t="n">
         <v>562</v>
@@ -60486,7 +60486,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2073" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2073" t="n">
         <v>1000</v>
@@ -60515,7 +60515,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2074" t="n">
-        <v>3.78768563270569</v>
+        <v>3.78768515586853</v>
       </c>
       <c r="H2074" t="n">
         <v>3250</v>
@@ -60573,7 +60573,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2076" t="n">
-        <v>3.74414920806885</v>
+        <v>3.74414896965027</v>
       </c>
       <c r="H2076" t="n">
         <v>21034</v>
@@ -60718,7 +60718,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2081" t="n">
-        <v>3.84573459625244</v>
+        <v>3.84573435783386</v>
       </c>
       <c r="H2081" t="n">
         <v>5369</v>
@@ -60747,7 +60747,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2082" t="n">
         <v>26100</v>
@@ -60776,7 +60776,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.1069540977478</v>
+        <v>4.10695362091064</v>
       </c>
       <c r="H2083" t="n">
         <v>11554</v>
@@ -60834,7 +60834,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.13597822189331</v>
+        <v>4.13597774505615</v>
       </c>
       <c r="H2085" t="n">
         <v>12713</v>
@@ -60863,7 +60863,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.12146615982056</v>
+        <v>4.1214656829834</v>
       </c>
       <c r="H2086" t="n">
         <v>3284</v>
@@ -60892,7 +60892,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H2087" t="n">
         <v>4634</v>
@@ -60921,7 +60921,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2088" t="n">
-        <v>4.09244203567505</v>
+        <v>4.09244155883789</v>
       </c>
       <c r="H2088" t="n">
         <v>13454</v>
@@ -60979,7 +60979,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2090" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2090" t="n">
         <v>8585</v>
@@ -61008,7 +61008,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2091" t="n">
-        <v>4.06341695785522</v>
+        <v>4.06341743469238</v>
       </c>
       <c r="H2091" t="n">
         <v>8150</v>
@@ -61037,7 +61037,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2092" t="n">
-        <v>4.1069540977478</v>
+        <v>4.10695362091064</v>
       </c>
       <c r="H2092" t="n">
         <v>8611</v>
@@ -61124,7 +61124,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G2095" t="n">
-        <v>4.39719772338867</v>
+        <v>4.39719820022583</v>
       </c>
       <c r="H2095" t="n">
         <v>39523</v>
@@ -61182,7 +61182,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2097" t="n">
-        <v>4.45524740219116</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H2097" t="n">
         <v>25254</v>
@@ -61211,7 +61211,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2098" t="n">
-        <v>4.45524740219116</v>
+        <v>4.45524644851685</v>
       </c>
       <c r="H2098" t="n">
         <v>16270</v>
@@ -61385,7 +61385,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.58585691452026</v>
+        <v>4.58585739135742</v>
       </c>
       <c r="H2104" t="n">
         <v>8575</v>
@@ -61414,7 +61414,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2105" t="n">
-        <v>4.61488103866577</v>
+        <v>4.61488151550293</v>
       </c>
       <c r="H2105" t="n">
         <v>6270</v>
@@ -61704,7 +61704,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2115" t="n">
-        <v>5.23890590667725</v>
+        <v>5.23890542984009</v>
       </c>
       <c r="H2115" t="n">
         <v>77346</v>
@@ -61762,7 +61762,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2117" t="n">
-        <v>5.32597970962524</v>
+        <v>5.32597923278809</v>
       </c>
       <c r="H2117" t="n">
         <v>52433</v>
@@ -61849,7 +61849,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2120" t="n">
-        <v>5.32597970962524</v>
+        <v>5.32597923278809</v>
       </c>
       <c r="H2120" t="n">
         <v>58295</v>
@@ -61907,7 +61907,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G2122" t="n">
-        <v>5.71780872344971</v>
+        <v>5.71780920028687</v>
       </c>
       <c r="H2122" t="n">
         <v>237009</v>
@@ -61936,7 +61936,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2123" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2123" t="n">
         <v>156082</v>
@@ -61994,7 +61994,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2125" t="n">
-        <v>5.74200296401978</v>
+        <v>5.74200248718262</v>
       </c>
       <c r="H2125" t="n">
         <v>31598</v>
@@ -62168,7 +62168,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2131" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2131" t="n">
         <v>5020</v>
@@ -62516,7 +62516,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2143" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2143" t="n">
         <v>4615</v>
@@ -62545,7 +62545,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2144" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2144" t="n">
         <v>3322</v>
@@ -62603,7 +62603,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2146" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2146" t="n">
         <v>4610</v>
@@ -62661,7 +62661,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2148" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2148" t="n">
         <v>6369</v>
@@ -62835,7 +62835,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2154" t="n">
-        <v>5.50006437301636</v>
+        <v>5.50006484985352</v>
       </c>
       <c r="H2154" t="n">
         <v>72558</v>
@@ -62951,7 +62951,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2158" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2158" t="n">
         <v>4098</v>
@@ -63154,7 +63154,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2165" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2165" t="n">
         <v>15059</v>
@@ -63241,7 +63241,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2168" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2168" t="n">
         <v>11763</v>
@@ -63270,7 +63270,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2169" t="n">
-        <v>5.6290979385376</v>
+        <v>5.62909841537476</v>
       </c>
       <c r="H2169" t="n">
         <v>1246</v>
@@ -63328,7 +63328,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2171" t="n">
-        <v>5.67748546600342</v>
+        <v>5.67748594284058</v>
       </c>
       <c r="H2171" t="n">
         <v>13431</v>
@@ -63415,7 +63415,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2174" t="n">
-        <v>5.7903904914856</v>
+        <v>5.79039001464844</v>
       </c>
       <c r="H2174" t="n">
         <v>33583</v>
@@ -63444,7 +63444,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2175" t="n">
-        <v>5.7903904914856</v>
+        <v>5.79039001464844</v>
       </c>
       <c r="H2175" t="n">
         <v>2041</v>
@@ -64082,7 +64082,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2197" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2197" t="n">
         <v>46134</v>
@@ -64140,7 +64140,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2199" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2199" t="n">
         <v>43455</v>
@@ -64198,7 +64198,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2201" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2201" t="n">
         <v>36088</v>
@@ -64256,7 +64256,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2203" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2203" t="n">
         <v>37217</v>
@@ -64285,7 +64285,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2204" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2204" t="n">
         <v>39475</v>
@@ -64314,7 +64314,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2205" t="n">
-        <v>5.87103652954102</v>
+        <v>5.87103700637817</v>
       </c>
       <c r="H2205" t="n">
         <v>38442</v>

--- a/data/GROW.MI.xlsx
+++ b/data/GROW.MI.xlsx
@@ -688,7 +688,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G11" t="n">
-        <v>2.13184285163879</v>
+        <v>2.13184309005737</v>
       </c>
       <c r="H11" t="n">
         <v>1800</v>
@@ -717,7 +717,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G12" t="n">
-        <v>2.13184285163879</v>
+        <v>2.13184309005737</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2044038772583</v>
+        <v>2.20440411567688</v>
       </c>
       <c r="H20" t="n">
         <v>600</v>
@@ -978,7 +978,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G21" t="n">
-        <v>2.15216016769409</v>
+        <v>2.15215992927551</v>
       </c>
       <c r="H21" t="n">
         <v>2400</v>
@@ -1007,7 +1007,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G22" t="n">
-        <v>2.15216016769409</v>
+        <v>2.15215992927551</v>
       </c>
       <c r="H22" t="n">
         <v>600</v>
@@ -1152,7 +1152,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08540391921997</v>
+        <v>2.08540368080139</v>
       </c>
       <c r="H27" t="n">
         <v>9600</v>
@@ -1297,7 +1297,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H32" t="n">
         <v>3000</v>
@@ -1326,7 +1326,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G37" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G38" t="n">
-        <v>2.14200162887573</v>
+        <v>2.14200139045715</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G44" t="n">
-        <v>2.2044038772583</v>
+        <v>2.20440411567688</v>
       </c>
       <c r="H44" t="n">
         <v>4800</v>
@@ -1703,7 +1703,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G46" t="n">
-        <v>2.24648928642273</v>
+        <v>2.24648904800415</v>
       </c>
       <c r="H46" t="n">
         <v>600</v>
@@ -1819,7 +1819,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G50" t="n">
-        <v>2.17247724533081</v>
+        <v>2.17247700691223</v>
       </c>
       <c r="H50" t="n">
         <v>600</v>
@@ -2051,7 +2051,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>2.2348792552948</v>
+        <v>2.23487949371338</v>
       </c>
       <c r="H58" t="n">
         <v>600</v>
@@ -2080,7 +2080,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>2.2348792552948</v>
+        <v>2.23487949371338</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G68" t="n">
-        <v>2.17973327636719</v>
+        <v>2.17973303794861</v>
       </c>
       <c r="H68" t="n">
         <v>5400</v>
@@ -2399,7 +2399,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G70" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H70" t="n">
         <v>27300</v>
@@ -2776,7 +2776,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H83" t="n">
         <v>780</v>
@@ -2834,7 +2834,7 @@
         <v>2.5</v>
       </c>
       <c r="G85" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H85" t="n">
         <v>3900</v>
@@ -2950,7 +2950,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G89" t="n">
-        <v>1.73275721073151</v>
+        <v>1.7327573299408</v>
       </c>
       <c r="H89" t="n">
         <v>1560</v>
@@ -3095,7 +3095,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G94" t="n">
-        <v>1.69937920570374</v>
+        <v>1.69937932491302</v>
       </c>
       <c r="H94" t="n">
         <v>2340</v>
@@ -3124,7 +3124,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H95" t="n">
         <v>3120</v>
@@ -3153,7 +3153,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G96" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G98" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H101" t="n">
         <v>2340</v>
@@ -3646,7 +3646,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G113" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H113" t="n">
         <v>780</v>
@@ -3936,7 +3936,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H123" t="n">
         <v>780</v>
@@ -3965,7 +3965,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G124" t="n">
-        <v>1.67180609703064</v>
+        <v>1.67180597782135</v>
       </c>
       <c r="H124" t="n">
         <v>3900</v>
@@ -4255,7 +4255,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G134" t="n">
-        <v>1.48314738273621</v>
+        <v>1.48314726352692</v>
       </c>
       <c r="H134" t="n">
         <v>780</v>
@@ -4545,7 +4545,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G144" t="n">
-        <v>1.40768384933472</v>
+        <v>1.40768396854401</v>
       </c>
       <c r="H144" t="n">
         <v>4680</v>
@@ -4632,7 +4632,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G147" t="n">
-        <v>1.39317154884338</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H147" t="n">
         <v>4680</v>
@@ -4661,7 +4661,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G148" t="n">
-        <v>1.39317154884338</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G159" t="n">
-        <v>1.39317154884338</v>
+        <v>1.39317166805267</v>
       </c>
       <c r="H159" t="n">
         <v>13260</v>
@@ -5357,7 +5357,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G172" t="n">
-        <v>1.33875095844269</v>
+        <v>1.3387508392334</v>
       </c>
       <c r="H172" t="n">
         <v>1560</v>
@@ -5415,7 +5415,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H174" t="n">
         <v>780</v>
@@ -5531,7 +5531,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G178" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H178" t="n">
         <v>780</v>
@@ -5560,7 +5560,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G179" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G180" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G181" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G182" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G183" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G184" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G185" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G186" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G187" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G188" t="n">
-        <v>1.33584845066071</v>
+        <v>1.33584833145142</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G190" t="n">
-        <v>1.32061076164246</v>
+        <v>1.32061064243317</v>
       </c>
       <c r="H190" t="n">
         <v>2340</v>
@@ -5966,7 +5966,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G193" t="n">
-        <v>1.24224472045898</v>
+        <v>1.24224483966827</v>
       </c>
       <c r="H193" t="n">
         <v>1560</v>
@@ -5995,7 +5995,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G194" t="n">
-        <v>1.24224472045898</v>
+        <v>1.24224483966827</v>
       </c>
       <c r="H194" t="n">
         <v>780</v>
@@ -6024,7 +6024,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G195" t="n">
-        <v>1.2647385597229</v>
+        <v>1.26473867893219</v>
       </c>
       <c r="H195" t="n">
         <v>780</v>
@@ -6053,7 +6053,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G196" t="n">
-        <v>1.2647385597229</v>
+        <v>1.26473867893219</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G197" t="n">
-        <v>1.24804961681366</v>
+        <v>1.24804973602295</v>
       </c>
       <c r="H197" t="n">
         <v>1560</v>
@@ -6111,7 +6111,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>1.24804961681366</v>
+        <v>1.24804973602295</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G199" t="n">
-        <v>1.24804961681366</v>
+        <v>1.24804973602295</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G200" t="n">
-        <v>1.24804961681366</v>
+        <v>1.24804973602295</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>1.24804961681366</v>
+        <v>1.24804973602295</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G202" t="n">
-        <v>1.22628128528595</v>
+        <v>1.22628140449524</v>
       </c>
       <c r="H202" t="n">
         <v>1560</v>
@@ -6256,7 +6256,7 @@
         <v>1.75</v>
       </c>
       <c r="G203" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H203" t="n">
         <v>5460</v>
@@ -6517,7 +6517,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G212" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H212" t="n">
         <v>780</v>
@@ -6546,7 +6546,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H213" t="n">
         <v>1560</v>
@@ -6575,7 +6575,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G216" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G218" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H218" t="n">
         <v>780</v>
@@ -6720,7 +6720,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G230" t="n">
-        <v>1.25530576705933</v>
+        <v>1.25530564785004</v>
       </c>
       <c r="H230" t="n">
         <v>7020</v>
@@ -7068,7 +7068,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G231" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H231" t="n">
         <v>3120</v>
@@ -7097,7 +7097,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G232" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G233" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H233" t="n">
         <v>6240</v>
@@ -7155,7 +7155,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G234" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H242" t="n">
         <v>1560</v>
@@ -7416,7 +7416,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G243" t="n">
-        <v>1.17403733730316</v>
+        <v>1.17403745651245</v>
       </c>
       <c r="H243" t="n">
         <v>16380</v>
@@ -7590,7 +7590,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G249" t="n">
-        <v>1.20451295375824</v>
+        <v>1.20451307296753</v>
       </c>
       <c r="H249" t="n">
         <v>2340</v>
@@ -7619,7 +7619,7 @@
         <v>1.75</v>
       </c>
       <c r="G250" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H250" t="n">
         <v>6240</v>
@@ -7648,7 +7648,7 @@
         <v>1.75</v>
       </c>
       <c r="G251" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>1.75</v>
       </c>
       <c r="G252" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>1.75</v>
       </c>
       <c r="G253" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H253" t="n">
         <v>780</v>
@@ -7735,7 +7735,7 @@
         <v>1.75</v>
       </c>
       <c r="G254" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>1.75</v>
       </c>
       <c r="G255" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H255" t="n">
         <v>780</v>
@@ -7793,7 +7793,7 @@
         <v>1.75</v>
       </c>
       <c r="G256" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>1.75</v>
       </c>
       <c r="G257" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>1.75</v>
       </c>
       <c r="G258" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H258" t="n">
         <v>31980</v>
@@ -7880,7 +7880,7 @@
         <v>1.75</v>
       </c>
       <c r="G259" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>1.75</v>
       </c>
       <c r="G262" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H262" t="n">
         <v>3900</v>
@@ -7996,7 +7996,7 @@
         <v>1.75</v>
       </c>
       <c r="G263" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H263" t="n">
         <v>780</v>
@@ -8025,7 +8025,7 @@
         <v>1.75</v>
       </c>
       <c r="G264" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>1.75</v>
       </c>
       <c r="G265" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>1.75</v>
       </c>
       <c r="G266" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>1.75</v>
       </c>
       <c r="G267" t="n">
-        <v>1.26981794834137</v>
+        <v>1.26981806755066</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G273" t="n">
-        <v>1.30609834194183</v>
+        <v>1.30609846115112</v>
       </c>
       <c r="H273" t="n">
         <v>3900</v>
@@ -8344,7 +8344,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H275" t="n">
         <v>72540</v>
@@ -8402,7 +8402,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G277" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H277" t="n">
         <v>13260</v>
@@ -8460,7 +8460,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G279" t="n">
-        <v>1.40768384933472</v>
+        <v>1.40768396854401</v>
       </c>
       <c r="H279" t="n">
         <v>7020</v>
@@ -8576,7 +8576,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G283" t="n">
-        <v>1.32133615016937</v>
+        <v>1.32133626937866</v>
       </c>
       <c r="H283" t="n">
         <v>3900</v>
@@ -8605,7 +8605,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G284" t="n">
-        <v>1.25748252868652</v>
+        <v>1.25748264789581</v>
       </c>
       <c r="H284" t="n">
         <v>14820</v>
@@ -8634,7 +8634,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G285" t="n">
-        <v>1.23353755474091</v>
+        <v>1.23353743553162</v>
       </c>
       <c r="H285" t="n">
         <v>5460</v>
@@ -8663,7 +8663,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G286" t="n">
-        <v>1.24804961681366</v>
+        <v>1.24804973602295</v>
       </c>
       <c r="H286" t="n">
         <v>3900</v>
@@ -8692,7 +8692,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G287" t="n">
-        <v>1.24804961681366</v>
+        <v>1.24804973602295</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G288" t="n">
-        <v>1.24804961681366</v>
+        <v>1.24804973602295</v>
       </c>
       <c r="H288" t="n">
         <v>780</v>
@@ -8750,7 +8750,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G289" t="n">
-        <v>1.20741546154022</v>
+        <v>1.20741558074951</v>
       </c>
       <c r="H289" t="n">
         <v>24180</v>
@@ -8982,7 +8982,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.17186057567596</v>
+        <v>1.17186045646667</v>
       </c>
       <c r="H297" t="n">
         <v>3120</v>
@@ -9127,7 +9127,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>1.23353755474091</v>
+        <v>1.23353743553162</v>
       </c>
       <c r="H302" t="n">
         <v>2340</v>
@@ -9156,7 +9156,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G303" t="n">
-        <v>1.24877524375916</v>
+        <v>1.24877512454987</v>
       </c>
       <c r="H303" t="n">
         <v>6240</v>
@@ -9185,7 +9185,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G304" t="n">
-        <v>1.24950075149536</v>
+        <v>1.24950087070465</v>
       </c>
       <c r="H304" t="n">
         <v>780</v>
@@ -9446,7 +9446,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G313" t="n">
-        <v>1.48895227909088</v>
+        <v>1.48895215988159</v>
       </c>
       <c r="H313" t="n">
         <v>6240</v>
@@ -9562,7 +9562,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>1.42219626903534</v>
+        <v>1.42219614982605</v>
       </c>
       <c r="H317" t="n">
         <v>3120</v>
@@ -9678,7 +9678,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H321" t="n">
         <v>83460</v>
@@ -9707,7 +9707,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G322" t="n">
-        <v>1.67035472393036</v>
+        <v>1.67035484313965</v>
       </c>
       <c r="H322" t="n">
         <v>65520</v>
@@ -9736,7 +9736,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H323" t="n">
         <v>76440</v>
@@ -9794,7 +9794,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H325" t="n">
         <v>14820</v>
@@ -9823,7 +9823,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G326" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H326" t="n">
         <v>30420</v>
@@ -9910,7 +9910,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G329" t="n">
-        <v>1.51072061061859</v>
+        <v>1.5107204914093</v>
       </c>
       <c r="H329" t="n">
         <v>9360</v>
@@ -9968,7 +9968,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G331" t="n">
-        <v>1.48024475574493</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H331" t="n">
         <v>3900</v>
@@ -9997,7 +9997,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G332" t="n">
-        <v>1.40478134155273</v>
+        <v>1.40478146076202</v>
       </c>
       <c r="H332" t="n">
         <v>53040</v>
@@ -10026,7 +10026,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>1.48024475574493</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H333" t="n">
         <v>10140</v>
@@ -10055,7 +10055,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>1.48024475574493</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H334" t="n">
         <v>3120</v>
@@ -10084,7 +10084,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G335" t="n">
-        <v>1.43815946578979</v>
+        <v>1.43815958499908</v>
       </c>
       <c r="H335" t="n">
         <v>56160</v>
@@ -10113,7 +10113,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G336" t="n">
-        <v>1.40260457992554</v>
+        <v>1.40260446071625</v>
       </c>
       <c r="H336" t="n">
         <v>83460</v>
@@ -10142,7 +10142,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G337" t="n">
-        <v>1.37430584430695</v>
+        <v>1.37430596351624</v>
       </c>
       <c r="H337" t="n">
         <v>27300</v>
@@ -10229,7 +10229,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G340" t="n">
-        <v>1.41493999958038</v>
+        <v>1.41493988037109</v>
       </c>
       <c r="H340" t="n">
         <v>10140</v>
@@ -10258,7 +10258,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G341" t="n">
-        <v>1.40405583381653</v>
+        <v>1.40405571460724</v>
       </c>
       <c r="H341" t="n">
         <v>7020</v>
@@ -10345,7 +10345,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>1.40768384933472</v>
+        <v>1.40768396854401</v>
       </c>
       <c r="H344" t="n">
         <v>6240</v>
@@ -10374,7 +10374,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G345" t="n">
-        <v>1.41493999958038</v>
+        <v>1.41493988037109</v>
       </c>
       <c r="H345" t="n">
         <v>14040</v>
@@ -10432,7 +10432,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G347" t="n">
-        <v>1.47298872470856</v>
+        <v>1.47298884391785</v>
       </c>
       <c r="H347" t="n">
         <v>5460</v>
@@ -10490,7 +10490,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G349" t="n">
-        <v>1.52087914943695</v>
+        <v>1.52087903022766</v>
       </c>
       <c r="H349" t="n">
         <v>202800</v>
@@ -10519,7 +10519,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G350" t="n">
-        <v>1.4338059425354</v>
+        <v>1.43380582332611</v>
       </c>
       <c r="H350" t="n">
         <v>107640</v>
@@ -10664,7 +10664,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G355" t="n">
-        <v>1.47008633613586</v>
+        <v>1.47008645534515</v>
       </c>
       <c r="H355" t="n">
         <v>2340</v>
@@ -10867,7 +10867,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G362" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H362" t="n">
         <v>10140</v>
@@ -10925,7 +10925,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.49475705623627</v>
+        <v>1.49475717544556</v>
       </c>
       <c r="H364" t="n">
         <v>11700</v>
@@ -11070,7 +11070,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.58473289012909</v>
+        <v>1.5847327709198</v>
       </c>
       <c r="H369" t="n">
         <v>21840</v>
@@ -11099,7 +11099,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G370" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H370" t="n">
         <v>38220</v>
@@ -11128,7 +11128,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H371" t="n">
         <v>27300</v>
@@ -11215,7 +11215,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H374" t="n">
         <v>6240</v>
@@ -11244,7 +11244,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H375" t="n">
         <v>2340</v>
@@ -11302,7 +11302,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H377" t="n">
         <v>166140</v>
@@ -11621,7 +11621,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G388" t="n">
-        <v>1.98817229270935</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H388" t="n">
         <v>55380</v>
@@ -11650,7 +11650,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G389" t="n">
-        <v>2.00558686256409</v>
+        <v>2.00558662414551</v>
       </c>
       <c r="H389" t="n">
         <v>10920</v>
@@ -11766,7 +11766,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G393" t="n">
-        <v>1.94318413734436</v>
+        <v>1.94318401813507</v>
       </c>
       <c r="H393" t="n">
         <v>3900</v>
@@ -11795,7 +11795,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G394" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H394" t="n">
         <v>17160</v>
@@ -11853,7 +11853,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G396" t="n">
-        <v>1.82128190994263</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H396" t="n">
         <v>21060</v>
@@ -11882,7 +11882,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G397" t="n">
-        <v>2.07234287261963</v>
+        <v>2.07234263420105</v>
       </c>
       <c r="H397" t="n">
         <v>136500</v>
@@ -11940,7 +11940,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98817229270935</v>
+        <v>1.98817217350006</v>
       </c>
       <c r="H399" t="n">
         <v>11700</v>
@@ -11998,7 +11998,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G401" t="n">
-        <v>1.89239156246185</v>
+        <v>1.89239168167114</v>
       </c>
       <c r="H401" t="n">
         <v>15600</v>
@@ -12027,7 +12027,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G402" t="n">
-        <v>1.86191594600677</v>
+        <v>1.86191606521606</v>
       </c>
       <c r="H402" t="n">
         <v>91260</v>
@@ -12085,7 +12085,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G404" t="n">
-        <v>1.82563555240631</v>
+        <v>1.82563543319702</v>
       </c>
       <c r="H404" t="n">
         <v>66300</v>
@@ -12114,7 +12114,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H405" t="n">
         <v>109200</v>
@@ -12201,7 +12201,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G408" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H408" t="n">
         <v>21060</v>
@@ -12288,7 +12288,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H411" t="n">
         <v>780</v>
@@ -12317,7 +12317,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G412" t="n">
-        <v>1.78935492038727</v>
+        <v>1.78935480117798</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G419" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H419" t="n">
         <v>31980</v>
@@ -12694,7 +12694,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G425" t="n">
-        <v>1.79515969753265</v>
+        <v>1.79515981674194</v>
       </c>
       <c r="H425" t="n">
         <v>18720</v>
@@ -12752,7 +12752,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>1.79951333999634</v>
+        <v>1.79951345920563</v>
       </c>
       <c r="H427" t="n">
         <v>1560</v>
@@ -12781,7 +12781,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H428" t="n">
         <v>27300</v>
@@ -12810,7 +12810,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G429" t="n">
-        <v>1.94898915290833</v>
+        <v>1.94898903369904</v>
       </c>
       <c r="H429" t="n">
         <v>84240</v>
@@ -12868,7 +12868,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G431" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H431" t="n">
         <v>25740</v>
@@ -12897,7 +12897,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H432" t="n">
         <v>12480</v>
@@ -12955,7 +12955,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H434" t="n">
         <v>18720</v>
@@ -12984,7 +12984,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G435" t="n">
-        <v>1.85175752639771</v>
+        <v>1.85175740718842</v>
       </c>
       <c r="H435" t="n">
         <v>10140</v>
@@ -13042,7 +13042,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G437" t="n">
-        <v>1.81112325191498</v>
+        <v>1.81112313270569</v>
       </c>
       <c r="H437" t="n">
         <v>24960</v>
@@ -13100,7 +13100,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>1.85030603408813</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H439" t="n">
         <v>46020</v>
@@ -13129,7 +13129,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>1.83724522590637</v>
+        <v>1.83724534511566</v>
       </c>
       <c r="H440" t="n">
         <v>16380</v>
@@ -13158,7 +13158,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G441" t="n">
-        <v>1.84595251083374</v>
+        <v>1.84595239162445</v>
       </c>
       <c r="H441" t="n">
         <v>780</v>
@@ -13216,7 +13216,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G443" t="n">
-        <v>1.87352561950684</v>
+        <v>1.87352573871613</v>
       </c>
       <c r="H443" t="n">
         <v>24180</v>
@@ -13332,7 +13332,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G447" t="n">
-        <v>1.9780136346817</v>
+        <v>1.97801375389099</v>
       </c>
       <c r="H447" t="n">
         <v>216060</v>
@@ -13477,7 +13477,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>1.85030603408813</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H452" t="n">
         <v>22620</v>
@@ -13535,7 +13535,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>1.87207448482513</v>
+        <v>1.87207436561584</v>
       </c>
       <c r="H454" t="n">
         <v>31200</v>
@@ -13709,7 +13709,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G460" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H460" t="n">
         <v>16380</v>
@@ -13738,7 +13738,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G461" t="n">
-        <v>1.8778795003891</v>
+        <v>1.87787938117981</v>
       </c>
       <c r="H461" t="n">
         <v>12480</v>
@@ -13767,7 +13767,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>1.92141604423523</v>
+        <v>1.92141592502594</v>
       </c>
       <c r="H462" t="n">
         <v>85800</v>
@@ -13796,7 +13796,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G463" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H463" t="n">
         <v>32760</v>
@@ -13825,7 +13825,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G464" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H464" t="n">
         <v>11700</v>
@@ -13854,7 +13854,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G465" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H465" t="n">
         <v>14820</v>
@@ -13883,7 +13883,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G466" t="n">
-        <v>1.94463551044464</v>
+        <v>1.94463539123535</v>
       </c>
       <c r="H466" t="n">
         <v>137280</v>
@@ -13912,7 +13912,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G467" t="n">
-        <v>1.90835511684418</v>
+        <v>1.90835499763489</v>
       </c>
       <c r="H467" t="n">
         <v>35100</v>
@@ -13941,7 +13941,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H468" t="n">
         <v>78000</v>
@@ -13970,7 +13970,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>1.92286717891693</v>
+        <v>1.92286729812622</v>
       </c>
       <c r="H469" t="n">
         <v>34320</v>
@@ -13999,7 +13999,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G470" t="n">
-        <v>1.90255010128021</v>
+        <v>1.90254998207092</v>
       </c>
       <c r="H470" t="n">
         <v>18720</v>
@@ -14028,7 +14028,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G471" t="n">
-        <v>1.90400123596191</v>
+        <v>1.9040013551712</v>
       </c>
       <c r="H471" t="n">
         <v>3900</v>
@@ -14057,7 +14057,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>1.89094042778015</v>
+        <v>1.89094030857086</v>
       </c>
       <c r="H472" t="n">
         <v>6240</v>
@@ -14086,7 +14086,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G473" t="n">
-        <v>1.90255010128021</v>
+        <v>1.90254998207092</v>
       </c>
       <c r="H473" t="n">
         <v>15600</v>
@@ -14115,7 +14115,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G474" t="n">
-        <v>1.88078165054321</v>
+        <v>1.88078188896179</v>
       </c>
       <c r="H474" t="n">
         <v>24180</v>
@@ -14173,7 +14173,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G476" t="n">
-        <v>1.87497711181641</v>
+        <v>1.87497687339783</v>
       </c>
       <c r="H476" t="n">
         <v>3120</v>
@@ -14289,7 +14289,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G480" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H480" t="n">
         <v>28080</v>
@@ -14347,7 +14347,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G482" t="n">
-        <v>1.808220744133</v>
+        <v>1.80822062492371</v>
       </c>
       <c r="H482" t="n">
         <v>25740</v>
@@ -14405,7 +14405,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G484" t="n">
-        <v>1.80096459388733</v>
+        <v>1.80096471309662</v>
       </c>
       <c r="H484" t="n">
         <v>2340</v>
@@ -14434,7 +14434,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H485" t="n">
         <v>8580</v>
@@ -14521,7 +14521,7 @@
         <v>2.5</v>
       </c>
       <c r="G488" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H488" t="n">
         <v>1560</v>
@@ -14550,7 +14550,7 @@
         <v>2.5</v>
       </c>
       <c r="G489" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H489" t="n">
         <v>2340</v>
@@ -14579,7 +14579,7 @@
         <v>2.5</v>
       </c>
       <c r="G490" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H490" t="n">
         <v>1560</v>
@@ -14608,7 +14608,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G491" t="n">
-        <v>1.83869636058807</v>
+        <v>1.83869624137878</v>
       </c>
       <c r="H491" t="n">
         <v>9360</v>
@@ -14637,7 +14637,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G492" t="n">
-        <v>1.85175752639771</v>
+        <v>1.85175740718842</v>
       </c>
       <c r="H492" t="n">
         <v>14040</v>
@@ -14695,7 +14695,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G494" t="n">
-        <v>1.88078165054321</v>
+        <v>1.88078188896179</v>
       </c>
       <c r="H494" t="n">
         <v>35880</v>
@@ -14724,7 +14724,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G495" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H495" t="n">
         <v>34320</v>
@@ -14782,7 +14782,7 @@
         <v>2.5</v>
       </c>
       <c r="G497" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H497" t="n">
         <v>6240</v>
@@ -14956,7 +14956,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G503" t="n">
-        <v>1.82128190994263</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H503" t="n">
         <v>7020</v>
@@ -15101,7 +15101,7 @@
         <v>2.5</v>
       </c>
       <c r="G508" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H508" t="n">
         <v>1560</v>
@@ -15130,7 +15130,7 @@
         <v>2.48200011253357</v>
       </c>
       <c r="G509" t="n">
-        <v>1.80096459388733</v>
+        <v>1.80096471309662</v>
       </c>
       <c r="H509" t="n">
         <v>5460</v>
@@ -15246,7 +15246,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G513" t="n">
-        <v>1.79951333999634</v>
+        <v>1.79951345920563</v>
       </c>
       <c r="H513" t="n">
         <v>6240</v>
@@ -15362,7 +15362,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>1.85030603408813</v>
+        <v>1.85030627250671</v>
       </c>
       <c r="H517" t="n">
         <v>16380</v>
@@ -15420,7 +15420,7 @@
         <v>2.5</v>
       </c>
       <c r="G519" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H519" t="n">
         <v>3120</v>
@@ -15507,7 +15507,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G522" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H522" t="n">
         <v>3120</v>
@@ -15565,7 +15565,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H524" t="n">
         <v>7020</v>
@@ -15594,7 +15594,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G525" t="n">
-        <v>1.88658654689789</v>
+        <v>1.88658666610718</v>
       </c>
       <c r="H525" t="n">
         <v>31980</v>
@@ -15623,7 +15623,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G526" t="n">
-        <v>1.82128190994263</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H526" t="n">
         <v>11700</v>
@@ -15681,7 +15681,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>1.92286717891693</v>
+        <v>1.92286729812622</v>
       </c>
       <c r="H528" t="n">
         <v>124020</v>
@@ -15710,7 +15710,7 @@
         <v>2.75</v>
       </c>
       <c r="G529" t="n">
-        <v>1.99542832374573</v>
+        <v>1.99542820453644</v>
       </c>
       <c r="H529" t="n">
         <v>39780</v>
@@ -15826,7 +15826,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G533" t="n">
-        <v>1.82128190994263</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H533" t="n">
         <v>7800</v>
@@ -15855,7 +15855,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H534" t="n">
         <v>3900</v>
@@ -15884,7 +15884,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.82128190994263</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H535" t="n">
         <v>10920</v>
@@ -15913,7 +15913,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H536" t="n">
         <v>30420</v>
@@ -16232,7 +16232,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G547" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H547" t="n">
         <v>8580</v>
@@ -16319,7 +16319,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H550" t="n">
         <v>10140</v>
@@ -16348,7 +16348,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G551" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G553" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H553" t="n">
         <v>8580</v>
@@ -16464,7 +16464,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H555" t="n">
         <v>14820</v>
@@ -16493,7 +16493,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G556" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H556" t="n">
         <v>8580</v>
@@ -16754,7 +16754,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G565" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H565" t="n">
         <v>4680</v>
@@ -16870,7 +16870,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H569" t="n">
         <v>9360</v>
@@ -16957,7 +16957,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G572" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H572" t="n">
         <v>12480</v>
@@ -17102,7 +17102,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H577" t="n">
         <v>5460</v>
@@ -17334,7 +17334,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G585" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H585" t="n">
         <v>105300</v>
@@ -17450,7 +17450,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G589" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H589" t="n">
         <v>7800</v>
@@ -17479,7 +17479,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H590" t="n">
         <v>1560</v>
@@ -17537,7 +17537,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G592" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H592" t="n">
         <v>4680</v>
@@ -17798,7 +17798,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G601" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H601" t="n">
         <v>98280</v>
@@ -17827,7 +17827,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H602" t="n">
         <v>60060</v>
@@ -17972,7 +17972,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H607" t="n">
         <v>15600</v>
@@ -18117,7 +18117,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>1.57457435131073</v>
+        <v>1.57457423210144</v>
       </c>
       <c r="H612" t="n">
         <v>10140</v>
@@ -18146,7 +18146,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>1.57457435131073</v>
+        <v>1.57457423210144</v>
       </c>
       <c r="H613" t="n">
         <v>43680</v>
@@ -18175,7 +18175,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G614" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H614" t="n">
         <v>23400</v>
@@ -18581,7 +18581,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>1.48024475574493</v>
+        <v>1.48024487495422</v>
       </c>
       <c r="H628" t="n">
         <v>5460</v>
@@ -18610,7 +18610,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G629" t="n">
-        <v>1.51652538776398</v>
+        <v>1.51652526855469</v>
       </c>
       <c r="H629" t="n">
         <v>8580</v>
@@ -18958,7 +18958,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G641" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H641" t="n">
         <v>25740</v>
@@ -19161,7 +19161,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H648" t="n">
         <v>26520</v>
@@ -19190,7 +19190,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H649" t="n">
         <v>5460</v>
@@ -19277,7 +19277,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H652" t="n">
         <v>9360</v>
@@ -19364,7 +19364,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G655" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H655" t="n">
         <v>2340</v>
@@ -19451,7 +19451,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G658" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H658" t="n">
         <v>2340</v>
@@ -19480,7 +19480,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H659" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G660" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -19538,7 +19538,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G661" t="n">
-        <v>1.66890358924866</v>
+        <v>1.66890370845795</v>
       </c>
       <c r="H661" t="n">
         <v>16380</v>
@@ -19625,7 +19625,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H664" t="n">
         <v>10140</v>
@@ -19654,7 +19654,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>1.61811089515686</v>
+        <v>1.61811077594757</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19683,7 +19683,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H666" t="n">
         <v>780</v>
@@ -19712,7 +19712,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H667" t="n">
         <v>1560</v>
@@ -19770,7 +19770,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H669" t="n">
         <v>5460</v>
@@ -19799,7 +19799,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G670" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.58908641338348</v>
+        <v>1.58908653259277</v>
       </c>
       <c r="H674" t="n">
         <v>1560</v>
@@ -20002,7 +20002,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G677" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H677" t="n">
         <v>780</v>
@@ -20031,7 +20031,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>1.67615962028503</v>
+        <v>1.67615973949432</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20263,7 +20263,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>1.59634268283844</v>
+        <v>1.59634256362915</v>
       </c>
       <c r="H686" t="n">
         <v>5460</v>
@@ -20756,7 +20756,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H703" t="n">
         <v>14040</v>
@@ -21075,7 +21075,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H714" t="n">
         <v>48360</v>
@@ -21365,7 +21365,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H724" t="n">
         <v>1560</v>
@@ -21394,7 +21394,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H725" t="n">
         <v>1560</v>
@@ -21452,7 +21452,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H727" t="n">
         <v>2340</v>
@@ -21481,7 +21481,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G728" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H728" t="n">
         <v>780</v>
@@ -21539,7 +21539,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H730" t="n">
         <v>780</v>
@@ -21568,7 +21568,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H731" t="n">
         <v>5460</v>
@@ -21626,7 +21626,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G733" t="n">
-        <v>1.79951333999634</v>
+        <v>1.79951345920563</v>
       </c>
       <c r="H733" t="n">
         <v>13260</v>
@@ -21655,7 +21655,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H734" t="n">
         <v>29640</v>
@@ -21742,7 +21742,7 @@
         <v>2.5</v>
       </c>
       <c r="G737" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H737" t="n">
         <v>10140</v>
@@ -21887,7 +21887,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>1.78500127792358</v>
+        <v>1.78500115871429</v>
       </c>
       <c r="H742" t="n">
         <v>780</v>
@@ -21974,7 +21974,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H745" t="n">
         <v>780</v>
@@ -22003,7 +22003,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H746" t="n">
         <v>0</v>
@@ -22032,7 +22032,7 @@
         <v>2.5</v>
       </c>
       <c r="G747" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H747" t="n">
         <v>9360</v>
@@ -22061,7 +22061,7 @@
         <v>2.5</v>
       </c>
       <c r="G748" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22090,7 +22090,7 @@
         <v>2.5</v>
       </c>
       <c r="G749" t="n">
-        <v>1.81402564048767</v>
+        <v>1.81402540206909</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G750" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H750" t="n">
         <v>2340</v>
@@ -22148,7 +22148,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G751" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H751" t="n">
         <v>7800</v>
@@ -22409,7 +22409,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H760" t="n">
         <v>7800</v>
@@ -22438,7 +22438,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -22467,7 +22467,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G762" t="n">
-        <v>1.75597679615021</v>
+        <v>1.7559769153595</v>
       </c>
       <c r="H762" t="n">
         <v>780</v>
@@ -22583,7 +22583,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G766" t="n">
-        <v>1.71969628334045</v>
+        <v>1.71969616413116</v>
       </c>
       <c r="H766" t="n">
         <v>780</v>
@@ -22786,7 +22786,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H773" t="n">
         <v>3120</v>
@@ -22815,7 +22815,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -22902,7 +22902,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>1.84305000305176</v>
+        <v>1.84305012226105</v>
       </c>
       <c r="H777" t="n">
         <v>3900</v>
@@ -22931,7 +22931,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G778" t="n">
-        <v>1.82128190994263</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H778" t="n">
         <v>2340</v>
@@ -22960,7 +22960,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>1.82128190994263</v>
+        <v>1.82128179073334</v>
       </c>
       <c r="H779" t="n">
         <v>780</v>
@@ -23047,7 +23047,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>1.90109884738922</v>
+        <v>1.90109872817993</v>
       </c>
       <c r="H782" t="n">
         <v>19500</v>
@@ -23076,7 +23076,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G783" t="n">
-        <v>1.90835511684418</v>
+        <v>1.90835499763489</v>
       </c>
       <c r="H783" t="n">
         <v>11700</v>
@@ -23366,7 +23366,7 @@
         <v>2.75</v>
       </c>
       <c r="G793" t="n">
-        <v>1.99542832374573</v>
+        <v>1.99542820453644</v>
       </c>
       <c r="H793" t="n">
         <v>9360</v>
@@ -23395,7 +23395,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G794" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365987300873</v>
       </c>
       <c r="H794" t="n">
         <v>5460</v>
@@ -23453,7 +23453,7 @@
         <v>2.75</v>
       </c>
       <c r="G796" t="n">
-        <v>1.99542832374573</v>
+        <v>1.99542820453644</v>
       </c>
       <c r="H796" t="n">
         <v>8580</v>
@@ -23511,7 +23511,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G798" t="n">
-        <v>1.97365999221802</v>
+        <v>1.97365987300873</v>
       </c>
       <c r="H798" t="n">
         <v>10920</v>
@@ -23598,7 +23598,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>2.05347681045532</v>
+        <v>2.0534770488739</v>
       </c>
       <c r="H801" t="n">
         <v>23400</v>
@@ -23627,7 +23627,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G802" t="n">
-        <v>2.06798887252808</v>
+        <v>2.06798911094666</v>
       </c>
       <c r="H802" t="n">
         <v>20280</v>
@@ -23656,7 +23656,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>2.06798887252808</v>
+        <v>2.06798911094666</v>
       </c>
       <c r="H803" t="n">
         <v>24180</v>
@@ -23714,7 +23714,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G805" t="n">
-        <v>2.13329434394836</v>
+        <v>2.13329410552979</v>
       </c>
       <c r="H805" t="n">
         <v>59280</v>
@@ -23743,7 +23743,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G806" t="n">
-        <v>2.13329434394836</v>
+        <v>2.13329410552979</v>
       </c>
       <c r="H806" t="n">
         <v>7800</v>
@@ -23859,7 +23859,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G810" t="n">
-        <v>2.06798887252808</v>
+        <v>2.06798911094666</v>
       </c>
       <c r="H810" t="n">
         <v>17160</v>
@@ -23888,7 +23888,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G811" t="n">
-        <v>2.09701371192932</v>
+        <v>2.09701347351074</v>
       </c>
       <c r="H811" t="n">
         <v>22620</v>
@@ -24352,7 +24352,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H827" t="n">
         <v>48360</v>
@@ -24410,7 +24410,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G829" t="n">
-        <v>2.30744075775146</v>
+        <v>2.30744051933289</v>
       </c>
       <c r="H829" t="n">
         <v>10140</v>
@@ -24439,7 +24439,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G830" t="n">
-        <v>2.25664782524109</v>
+        <v>2.25664806365967</v>
       </c>
       <c r="H830" t="n">
         <v>94380</v>
@@ -24468,7 +24468,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H831" t="n">
         <v>21060</v>
@@ -24555,7 +24555,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G834" t="n">
-        <v>2.34372115135193</v>
+        <v>2.34372091293335</v>
       </c>
       <c r="H834" t="n">
         <v>21060</v>
@@ -24845,7 +24845,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G844" t="n">
-        <v>2.34372115135193</v>
+        <v>2.34372091293335</v>
       </c>
       <c r="H844" t="n">
         <v>15924</v>
@@ -24903,7 +24903,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G846" t="n">
-        <v>2.30744075775146</v>
+        <v>2.30744051933289</v>
       </c>
       <c r="H846" t="n">
         <v>15073</v>
@@ -24990,7 +24990,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H849" t="n">
         <v>10904</v>
@@ -25019,7 +25019,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.30018472671509</v>
+        <v>2.30018448829651</v>
       </c>
       <c r="H850" t="n">
         <v>8210</v>
@@ -25135,7 +25135,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G854" t="n">
-        <v>2.25664782524109</v>
+        <v>2.25664806365967</v>
       </c>
       <c r="H854" t="n">
         <v>2735</v>
@@ -25628,7 +25628,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>2.36548924446106</v>
+        <v>2.36548948287964</v>
       </c>
       <c r="H871" t="n">
         <v>7362</v>
@@ -25802,7 +25802,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G877" t="n">
-        <v>2.46707510948181</v>
+        <v>2.46707487106323</v>
       </c>
       <c r="H877" t="n">
         <v>33973</v>
@@ -25831,7 +25831,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G878" t="n">
-        <v>2.49609923362732</v>
+        <v>2.4960994720459</v>
       </c>
       <c r="H878" t="n">
         <v>17250</v>
@@ -25889,7 +25889,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G880" t="n">
-        <v>2.53237962722778</v>
+        <v>2.53237986564636</v>
       </c>
       <c r="H880" t="n">
         <v>62911</v>
@@ -26005,7 +26005,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G884" t="n">
-        <v>2.86616063117981</v>
+        <v>2.86616039276123</v>
       </c>
       <c r="H884" t="n">
         <v>57963</v>
@@ -26092,7 +26092,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>2.71378254890442</v>
+        <v>2.71378231048584</v>
       </c>
       <c r="H887" t="n">
         <v>234047</v>
@@ -26121,7 +26121,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G888" t="n">
-        <v>2.71378254890442</v>
+        <v>2.71378231048584</v>
       </c>
       <c r="H888" t="n">
         <v>28982</v>
@@ -26150,7 +26150,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G889" t="n">
-        <v>2.78634309768677</v>
+        <v>2.78634333610535</v>
       </c>
       <c r="H889" t="n">
         <v>24677</v>
@@ -26179,7 +26179,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G890" t="n">
-        <v>2.85164856910706</v>
+        <v>2.85164833068848</v>
       </c>
       <c r="H890" t="n">
         <v>25193</v>
@@ -26208,7 +26208,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>2.96048951148987</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H891" t="n">
         <v>107136</v>
@@ -26295,7 +26295,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H894" t="n">
         <v>94893</v>
@@ -26440,7 +26440,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G899" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H899" t="n">
         <v>24854</v>
@@ -26788,7 +26788,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G911" t="n">
-        <v>2.74280667304993</v>
+        <v>2.74280691146851</v>
       </c>
       <c r="H911" t="n">
         <v>10183</v>
@@ -26817,7 +26817,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G912" t="n">
-        <v>2.78634309768677</v>
+        <v>2.78634333610535</v>
       </c>
       <c r="H912" t="n">
         <v>13525</v>
@@ -26846,7 +26846,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G913" t="n">
-        <v>2.85164856910706</v>
+        <v>2.85164833068848</v>
       </c>
       <c r="H913" t="n">
         <v>11840</v>
@@ -26933,7 +26933,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G916" t="n">
-        <v>2.67750191688538</v>
+        <v>2.6775016784668</v>
       </c>
       <c r="H916" t="n">
         <v>25856</v>
@@ -27049,7 +27049,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G920" t="n">
-        <v>2.670245885849</v>
+        <v>2.67024564743042</v>
       </c>
       <c r="H920" t="n">
         <v>37430</v>
@@ -27136,7 +27136,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>2.79359912872314</v>
+        <v>2.79359936714172</v>
       </c>
       <c r="H923" t="n">
         <v>1820</v>
@@ -27310,7 +27310,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H929" t="n">
         <v>11777</v>
@@ -27339,7 +27339,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G930" t="n">
-        <v>2.94597744941711</v>
+        <v>2.94597768783569</v>
       </c>
       <c r="H930" t="n">
         <v>43272</v>
@@ -27368,7 +27368,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G931" t="n">
-        <v>3.05481934547424</v>
+        <v>3.05481910705566</v>
       </c>
       <c r="H931" t="n">
         <v>15776</v>
@@ -27397,7 +27397,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G932" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H932" t="n">
         <v>33419</v>
@@ -27484,7 +27484,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G935" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H935" t="n">
         <v>4741</v>
@@ -27571,7 +27571,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H938" t="n">
         <v>933</v>
@@ -27600,7 +27600,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G939" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H939" t="n">
         <v>11330</v>
@@ -27716,7 +27716,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G943" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H943" t="n">
         <v>53741</v>
@@ -27745,7 +27745,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H944" t="n">
         <v>64664</v>
@@ -27861,7 +27861,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>2.82987999916077</v>
+        <v>2.82987976074219</v>
       </c>
       <c r="H948" t="n">
         <v>14110</v>
@@ -27977,7 +27977,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G952" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H952" t="n">
         <v>4634</v>
@@ -28006,7 +28006,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H953" t="n">
         <v>9849</v>
@@ -28093,7 +28093,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G956" t="n">
-        <v>2.96774578094482</v>
+        <v>2.9677460193634</v>
       </c>
       <c r="H956" t="n">
         <v>4718</v>
@@ -28151,7 +28151,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G958" t="n">
-        <v>2.96048951148987</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H958" t="n">
         <v>3050</v>
@@ -28180,7 +28180,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G959" t="n">
-        <v>2.94597744941711</v>
+        <v>2.94597768783569</v>
       </c>
       <c r="H959" t="n">
         <v>1795</v>
@@ -28383,7 +28383,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>3.05481934547424</v>
+        <v>3.05481910705566</v>
       </c>
       <c r="H966" t="n">
         <v>14910</v>
@@ -28557,7 +28557,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>3.43939256668091</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H972" t="n">
         <v>174496</v>
@@ -28731,7 +28731,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G978" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H978" t="n">
         <v>30478</v>
@@ -28876,7 +28876,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G983" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H983" t="n">
         <v>21629</v>
@@ -28905,7 +28905,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G984" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H984" t="n">
         <v>38692</v>
@@ -28963,7 +28963,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G986" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H986" t="n">
         <v>7440</v>
@@ -28992,7 +28992,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G987" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H987" t="n">
         <v>10030</v>
@@ -29050,7 +29050,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G989" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H989" t="n">
         <v>14239</v>
@@ -29079,7 +29079,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G990" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H990" t="n">
         <v>1190</v>
@@ -29108,7 +29108,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G991" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H991" t="n">
         <v>1571</v>
@@ -29224,7 +29224,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>3.14914870262146</v>
+        <v>3.14914846420288</v>
       </c>
       <c r="H995" t="n">
         <v>16856</v>
@@ -29253,7 +29253,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G996" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H996" t="n">
         <v>13997</v>
@@ -29282,7 +29282,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G997" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H997" t="n">
         <v>6558</v>
@@ -29311,7 +29311,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G998" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H998" t="n">
         <v>18950</v>
@@ -29340,7 +29340,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G999" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H999" t="n">
         <v>37168</v>
@@ -29427,7 +29427,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.34506320953369</v>
+        <v>3.34506344795227</v>
       </c>
       <c r="H1002" t="n">
         <v>39069</v>
@@ -29456,7 +29456,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.34506320953369</v>
+        <v>3.34506344795227</v>
       </c>
       <c r="H1003" t="n">
         <v>16302</v>
@@ -29485,7 +29485,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1004" t="n">
         <v>12630</v>
@@ -29514,7 +29514,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1005" t="n">
         <v>11452</v>
@@ -29659,7 +29659,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1010" t="n">
         <v>47398</v>
@@ -29804,7 +29804,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1015" t="n">
         <v>6208</v>
@@ -29833,7 +29833,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.43939256668091</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1016" t="n">
         <v>5463</v>
@@ -29920,7 +29920,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.35231924057007</v>
+        <v>3.35231947898865</v>
       </c>
       <c r="H1019" t="n">
         <v>8234</v>
@@ -30297,7 +30297,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.40311217308044</v>
+        <v>3.40311193466187</v>
       </c>
       <c r="H1032" t="n">
         <v>6573</v>
@@ -30326,7 +30326,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1033" t="n">
         <v>20527</v>
@@ -30384,7 +30384,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1035" t="n">
         <v>1434</v>
@@ -30471,7 +30471,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1038" t="n">
         <v>17540</v>
@@ -30587,7 +30587,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1042" t="n">
         <v>3589</v>
@@ -30732,7 +30732,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1047" t="n">
         <v>7582</v>
@@ -30906,7 +30906,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.13463640213013</v>
+        <v>3.13463664054871</v>
       </c>
       <c r="H1053" t="n">
         <v>70439</v>
@@ -30964,7 +30964,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1055" t="n">
         <v>10130</v>
@@ -31109,7 +31109,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.23622179031372</v>
+        <v>3.23622155189514</v>
       </c>
       <c r="H1060" t="n">
         <v>5775</v>
@@ -31138,7 +31138,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.19994115829468</v>
+        <v>3.1999409198761</v>
       </c>
       <c r="H1061" t="n">
         <v>16035</v>
@@ -31167,7 +31167,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.11286783218384</v>
+        <v>3.11286807060242</v>
       </c>
       <c r="H1062" t="n">
         <v>7972</v>
@@ -31196,7 +31196,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.96774578094482</v>
+        <v>2.9677460193634</v>
       </c>
       <c r="H1063" t="n">
         <v>109571</v>
@@ -31486,7 +31486,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.81536769866943</v>
+        <v>2.81536793708801</v>
       </c>
       <c r="H1073" t="n">
         <v>20606</v>
@@ -31602,7 +31602,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.96048951148987</v>
+        <v>2.96048974990845</v>
       </c>
       <c r="H1077" t="n">
         <v>21146</v>
@@ -31660,7 +31660,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1079" t="n">
         <v>9861</v>
@@ -31689,7 +31689,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1080" t="n">
         <v>3234</v>
@@ -31718,7 +31718,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.03305077552795</v>
+        <v>3.03305053710938</v>
       </c>
       <c r="H1081" t="n">
         <v>5600</v>
@@ -31863,7 +31863,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.19268536567688</v>
+        <v>3.1926851272583</v>
       </c>
       <c r="H1086" t="n">
         <v>29157</v>
@@ -32066,7 +32066,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1093" t="n">
         <v>700</v>
@@ -32095,7 +32095,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1094" t="n">
         <v>2341</v>
@@ -32240,7 +32240,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1099" t="n">
         <v>3444</v>
@@ -32269,7 +32269,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1100" t="n">
         <v>3580</v>
@@ -32298,7 +32298,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1101" t="n">
         <v>0</v>
@@ -32327,7 +32327,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.17817282676697</v>
+        <v>3.17817306518555</v>
       </c>
       <c r="H1102" t="n">
         <v>1000</v>
@@ -32356,7 +32356,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1103" t="n">
         <v>1500</v>
@@ -32414,7 +32414,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.18542909622192</v>
+        <v>3.18542885780334</v>
       </c>
       <c r="H1105" t="n">
         <v>10871</v>
@@ -32472,7 +32472,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.33780717849731</v>
+        <v>3.33780741691589</v>
       </c>
       <c r="H1107" t="n">
         <v>21593</v>
@@ -32501,7 +32501,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.30152678489685</v>
+        <v>3.30152702331543</v>
       </c>
       <c r="H1108" t="n">
         <v>8900</v>
@@ -32530,7 +32530,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1109" t="n">
         <v>3795</v>
@@ -32559,7 +32559,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.31603908538818</v>
+        <v>3.3160388469696</v>
       </c>
       <c r="H1110" t="n">
         <v>8580</v>
@@ -32820,7 +32820,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.43939256668091</v>
+        <v>3.43939232826233</v>
       </c>
       <c r="H1119" t="n">
         <v>5400</v>
@@ -32936,7 +32936,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.43213629722595</v>
+        <v>3.43213653564453</v>
       </c>
       <c r="H1123" t="n">
         <v>7177</v>
@@ -32994,7 +32994,7 @@
         <v>5</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.62805128097534</v>
+        <v>3.62805080413818</v>
       </c>
       <c r="H1125" t="n">
         <v>42472</v>
@@ -33139,7 +33139,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1130" t="n">
         <v>32706</v>
@@ -33226,7 +33226,7 @@
         <v>5.5</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.99085664749146</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1133" t="n">
         <v>9842</v>
@@ -33255,7 +33255,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1134" t="n">
         <v>5306</v>
@@ -33284,7 +33284,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1135" t="n">
         <v>25296</v>
@@ -33313,7 +33313,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.86024641990662</v>
+        <v>3.8602466583252</v>
       </c>
       <c r="H1136" t="n">
         <v>25075</v>
@@ -33342,7 +33342,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.88927102088928</v>
+        <v>3.8892707824707</v>
       </c>
       <c r="H1137" t="n">
         <v>5042</v>
@@ -33458,7 +33458,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.80219769477844</v>
+        <v>3.80219745635986</v>
       </c>
       <c r="H1141" t="n">
         <v>4495</v>
@@ -33545,7 +33545,7 @@
         <v>5.5</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.99085664749146</v>
+        <v>3.99085640907288</v>
       </c>
       <c r="H1144" t="n">
         <v>14778</v>
@@ -33603,7 +33603,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94731998443604</v>
+        <v>3.94731974601746</v>
       </c>
       <c r="H1146" t="n">
         <v>15890</v>
@@ -33690,7 +33690,7 @@
         <v>5.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.99085664749146